--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1475</v>
+        <v>1550</v>
       </c>
       <c r="F2" t="n">
-        <v>97.72</v>
+        <v>113.41</v>
       </c>
       <c r="G2" t="n">
-        <v>27.43</v>
+        <v>31.84</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.66</v>
+        <v>5.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1370</v>
+        <v>1475</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,7 +636,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.35</v>
+        <v>39.75</v>
       </c>
       <c r="F3" t="n">
         <v>11.12</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.13</v>
+        <v>1.02</v>
       </c>
       <c r="M3" t="n">
-        <v>39.3</v>
+        <v>39.35</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>140.5</v>
+        <v>141.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.3</v>
+        <v>16.53</v>
       </c>
       <c r="G4" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.35</v>
+        <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>141</v>
+        <v>140.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,7 +794,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6060</v>
+        <v>6090</v>
       </c>
       <c r="F5" t="n">
         <v>161.34</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-6.77</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>6500</v>
+        <v>6060</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>24.04</v>
+        <v>24.14</v>
       </c>
       <c r="G6" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.42</v>
+        <v>-1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>34.55</v>
+        <v>35.42</v>
       </c>
       <c r="G7" t="n">
-        <v>4.91</v>
+        <v>5.03</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.42</v>
+        <v>3.36</v>
       </c>
       <c r="M7" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>185.5</v>
       </c>
       <c r="F8" t="n">
-        <v>26.03</v>
+        <v>25.95</v>
       </c>
       <c r="G8" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.88</v>
+        <v>7.85</v>
       </c>
       <c r="M8" t="n">
-        <v>170.5</v>
+        <v>172</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>27.16</v>
+        <v>27.54</v>
       </c>
       <c r="G9" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.93</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F10" t="n">
         <v>18.99</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.86</v>
+        <v>3.16</v>
       </c>
       <c r="M10" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1355</v>
+        <v>1335</v>
       </c>
       <c r="F11" t="n">
-        <v>29.77</v>
+        <v>30.21</v>
       </c>
       <c r="G11" t="n">
-        <v>5.35</v>
+        <v>5.43</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.37</v>
+        <v>-1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F12" t="n">
-        <v>22.76</v>
+        <v>24.83</v>
       </c>
       <c r="G12" t="n">
-        <v>4.17</v>
+        <v>4.55</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.82</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>211.5</v>
+        <v>222</v>
       </c>
       <c r="F13" t="n">
-        <v>29.63</v>
+        <v>30.96</v>
       </c>
       <c r="G13" t="n">
-        <v>5.19</v>
+        <v>5.42</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1468,7 +1468,7 @@
         <v>4.96</v>
       </c>
       <c r="M13" t="n">
-        <v>201.5</v>
+        <v>211.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>142</v>
+        <v>141.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.43</v>
+        <v>28.63</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.7</v>
+        <v>-0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F15" t="n">
-        <v>20.33</v>
+        <v>20.37</v>
       </c>
       <c r="G15" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="M15" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4420</v>
+        <v>4845</v>
       </c>
       <c r="F16" t="n">
-        <v>132.97</v>
+        <v>146.21</v>
       </c>
       <c r="G16" t="n">
-        <v>40.61</v>
+        <v>44.66</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1709,8 +1709,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4420</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
@@ -1766,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="F17" t="n">
-        <v>63.37</v>
+        <v>73.37</v>
       </c>
       <c r="G17" t="n">
-        <v>18.56</v>
+        <v>21.49</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1785,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-4.76</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>1680</v>
+        <v>1600</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1843,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7110</v>
+        <v>7360</v>
       </c>
       <c r="F18" t="n">
-        <v>61.61</v>
+        <v>60.51</v>
       </c>
       <c r="G18" t="n">
-        <v>21.13</v>
+        <v>20.75</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1862,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>3.52</v>
       </c>
       <c r="M18" t="n">
-        <v>6990</v>
+        <v>7110</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1920,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="F19" t="n">
-        <v>69.33</v>
+        <v>69.03</v>
       </c>
       <c r="G19" t="n">
-        <v>12.71</v>
+        <v>12.66</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1939,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.98</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>703</v>
+        <v>738</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1997,7 +2001,7 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>89.8</v>
+        <v>95.7</v>
       </c>
       <c r="F20" t="n">
         <v>65.06999999999999</v>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.34</v>
+        <v>6.57</v>
       </c>
       <c r="M20" t="n">
-        <v>86.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2074,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>8015</v>
+        <v>8085</v>
       </c>
       <c r="F21" t="n">
-        <v>167.83</v>
+        <v>193.65</v>
       </c>
       <c r="G21" t="n">
-        <v>45.43</v>
+        <v>52.42</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2093,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.14</v>
+        <v>0.87</v>
       </c>
       <c r="M21" t="n">
-        <v>8190</v>
+        <v>8015</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2155,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2080</v>
+        <v>2160</v>
       </c>
       <c r="F22" t="n">
-        <v>64.18000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>31.08</v>
+        <v>35.28</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2174,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.21</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>2035</v>
+        <v>2080</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2236,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>412.5</v>
+        <v>453.5</v>
       </c>
       <c r="F23" t="n">
-        <v>43.47</v>
+        <v>46.47</v>
       </c>
       <c r="G23" t="n">
-        <v>6.44</v>
+        <v>6.89</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2255,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>9.710000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="M23" t="n">
-        <v>376</v>
+        <v>412.5</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2313,7 +2317,7 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1555</v>
+        <v>1680</v>
       </c>
       <c r="F24" t="n">
         <v>112.36</v>
@@ -2332,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1.58</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>1580</v>
+        <v>1555</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2377,12 +2381,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2391,20 +2395,20 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E25" t="n">
-        <v>36.15</v>
+        <v>170.5</v>
       </c>
       <c r="F25" t="n">
-        <v>130</v>
+        <v>39.28</v>
       </c>
       <c r="G25" t="n">
-        <v>3.03</v>
+        <v>2.12</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>158.2</v>
+        <v>12.4</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -2413,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.99</v>
+        <v>1.49</v>
       </c>
       <c r="M25" t="n">
-        <v>35.1</v>
+        <v>168</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2425,23 +2429,23 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ROE4低</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>5.2</v>
+        <v>22.1</v>
       </c>
       <c r="S25" t="n">
-        <v>97.8</v>
+        <v>14.6</v>
       </c>
       <c r="T25" t="n">
-        <v>130</v>
+        <v>34.2</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
@@ -2458,12 +2462,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2472,19 +2476,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E26" t="n">
-        <v>2035</v>
+        <v>38.5</v>
       </c>
       <c r="F26" t="n">
-        <v>267.41</v>
+        <v>124.63</v>
       </c>
       <c r="G26" t="n">
-        <v>44.41</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>158.2</v>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2492,10 +2498,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M26" t="n">
-        <v>2035</v>
+        <v>36.15</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2504,28 +2510,28 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>ROE4低</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>16.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.13</v>
+        <v>0.77</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="S26" t="n">
-        <v>118.8</v>
+        <v>97.8</v>
       </c>
       <c r="T26" t="n">
-        <v>310.9</v>
+        <v>130</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2537,12 +2543,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2551,21 +2557,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>627</v>
+        <v>2020</v>
       </c>
       <c r="F27" t="n">
-        <v>58.68</v>
+        <v>267.41</v>
       </c>
       <c r="G27" t="n">
-        <v>7.91</v>
+        <v>44.41</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -2573,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-0.79</v>
+        <v>-0.74</v>
       </c>
       <c r="M27" t="n">
-        <v>632</v>
+        <v>2035</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2585,23 +2589,23 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>12.8</v>
+        <v>16.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.26</v>
+        <v>1.13</v>
       </c>
       <c r="R27" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>28.6</v>
+        <v>118.8</v>
       </c>
       <c r="T27" t="n">
-        <v>62.1</v>
+        <v>310.9</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
@@ -2618,12 +2622,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2632,19 +2636,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E28" t="n">
-        <v>1270</v>
+        <v>680</v>
       </c>
       <c r="F28" t="n">
-        <v>72.41</v>
+        <v>56.92</v>
       </c>
       <c r="G28" t="n">
-        <v>12.47</v>
+        <v>7.67</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>12.6</v>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -2652,10 +2658,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9.960000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>1155</v>
+        <v>627</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2664,28 +2670,28 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>17.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>3.26</v>
       </c>
       <c r="R28" t="n">
-        <v>120.6</v>
+        <v>3.2</v>
       </c>
       <c r="S28" t="n">
-        <v>108.5</v>
+        <v>28.6</v>
       </c>
       <c r="T28" t="n">
-        <v>65.2</v>
+        <v>62.1</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2697,12 +2703,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2714,18 +2720,16 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>456.5</v>
+        <v>1340</v>
       </c>
       <c r="F29" t="n">
-        <v>82.55</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>15.73</v>
+        <v>11.44</v>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -2733,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-0.54</v>
+        <v>5.51</v>
       </c>
       <c r="M29" t="n">
-        <v>459</v>
+        <v>1270</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2749,24 +2753,24 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>18.9</v>
+        <v>17.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>50.3</v>
+        <v>120.6</v>
       </c>
       <c r="S29" t="n">
-        <v>21.1</v>
+        <v>108.5</v>
       </c>
       <c r="T29" t="n">
-        <v>99.8</v>
+        <v>65.2</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2778,12 +2782,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2795,17 +2799,17 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3035</v>
+        <v>474</v>
       </c>
       <c r="F30" t="n">
-        <v>89.03</v>
+        <v>82.55</v>
       </c>
       <c r="G30" t="n">
-        <v>10.15</v>
+        <v>15.73</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>454.2</v>
+        <v>27.5</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -2814,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-6.62</v>
+        <v>3.83</v>
       </c>
       <c r="M30" t="n">
-        <v>3250</v>
+        <v>456.5</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2826,23 +2830,23 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>14.1</v>
+        <v>18.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="R30" t="n">
-        <v>9.300000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="S30" t="n">
-        <v>34.1</v>
+        <v>21.1</v>
       </c>
       <c r="T30" t="n">
-        <v>95.3</v>
+        <v>99.8</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
@@ -2859,33 +2863,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E31" t="n">
-        <v>505</v>
+        <v>3035</v>
       </c>
       <c r="F31" t="n">
-        <v>157.74</v>
+        <v>89.03</v>
       </c>
       <c r="G31" t="n">
-        <v>14.8</v>
+        <v>10.15</v>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>454.2</v>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
@@ -2893,10 +2899,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-4.72</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>530</v>
+        <v>3035</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2905,23 +2911,23 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>10.7</v>
+        <v>14.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>0.99</v>
       </c>
       <c r="R31" t="n">
-        <v>4.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S31" t="n">
-        <v>49.9</v>
+        <v>34.1</v>
       </c>
       <c r="T31" t="n">
-        <v>165.8</v>
+        <v>95.3</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -2938,12 +2944,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2952,16 +2958,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>453</v>
+        <v>532</v>
       </c>
       <c r="F32" t="n">
-        <v>40.2</v>
+        <v>168.15</v>
       </c>
       <c r="G32" t="n">
-        <v>7.21</v>
+        <v>15.78</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2972,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.89</v>
+        <v>5.35</v>
       </c>
       <c r="M32" t="n">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2984,23 +2990,23 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>17.9</v>
+        <v>10.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.1</v>
+        <v>4.5</v>
       </c>
       <c r="S32" t="n">
-        <v>730.1</v>
+        <v>49.9</v>
       </c>
       <c r="T32" t="n">
-        <v>45.2</v>
+        <v>165.8</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
@@ -3017,12 +3023,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3031,20 +3037,20 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33" t="n">
-        <v>472.5</v>
+        <v>259.5</v>
       </c>
       <c r="F33" t="n">
-        <v>35.34</v>
+        <v>40.41</v>
       </c>
       <c r="G33" t="n">
-        <v>7.97</v>
+        <v>3.79</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>-2.9</v>
+        <v>-15.3</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -3053,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.73</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>455.5</v>
+        <v>236</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
@@ -3065,19 +3071,19 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>22.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="R33" t="n">
-        <v>4.9</v>
+        <v>13.2</v>
       </c>
       <c r="S33" t="n">
-        <v>32.1</v>
+        <v>34.8</v>
       </c>
       <c r="T33" t="n">
-        <v>38.6</v>
+        <v>34.5</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
@@ -3087,19 +3093,19 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3108,21 +3114,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E34" t="n">
-        <v>1040</v>
+        <v>452.5</v>
       </c>
       <c r="F34" t="n">
-        <v>79.92</v>
+        <v>41.14</v>
       </c>
       <c r="G34" t="n">
-        <v>12.51</v>
+        <v>7.38</v>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>-19.8</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -3130,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.46</v>
+        <v>-0.11</v>
       </c>
       <c r="M34" t="n">
-        <v>1015</v>
+        <v>453</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3142,23 +3146,23 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
-        <v>5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="S34" t="n">
-        <v>47.5</v>
+        <v>730.1</v>
       </c>
       <c r="T34" t="n">
-        <v>53.2</v>
+        <v>45.2</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3175,12 +3179,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3189,19 +3193,21 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>203</v>
+        <v>492</v>
       </c>
       <c r="F35" t="n">
-        <v>61.28</v>
+        <v>38.32</v>
       </c>
       <c r="G35" t="n">
-        <v>7.97</v>
+        <v>8.65</v>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
@@ -3209,35 +3215,31 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.69</v>
+        <v>4.13</v>
       </c>
       <c r="M35" t="n">
-        <v>206.5</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>472.5</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>11.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.62</v>
+        <v>0.77</v>
       </c>
       <c r="R35" t="n">
-        <v>-2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S35" t="n">
-        <v>182</v>
+        <v>32.1</v>
       </c>
       <c r="T35" t="n">
-        <v>65.90000000000001</v>
+        <v>38.6</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
@@ -3247,41 +3249,41 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>3910</v>
+        <v>1140</v>
       </c>
       <c r="F36" t="n">
-        <v>61.83</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>15.87</v>
+        <v>13.31</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>16.8</v>
+        <v>-19.8</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -3289,8 +3291,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1040</v>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -3298,23 +3304,23 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>25.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="R36" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>47.5</v>
       </c>
       <c r="T36" t="n">
-        <v>61.7</v>
+        <v>53.2</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
@@ -3331,71 +3337,71 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E37" t="n">
-        <v>1905</v>
+        <v>207.5</v>
       </c>
       <c r="F37" t="n">
-        <v>66.73999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="G37" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.32</v>
-      </c>
+        <v>8.43</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.25</v>
+        <v>2.22</v>
       </c>
       <c r="M37" t="n">
-        <v>1810</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P37" t="n">
-        <v>22.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="R37" t="n">
-        <v>15.2</v>
+        <v>-2.7</v>
       </c>
       <c r="S37" t="n">
-        <v>43.7</v>
+        <v>182</v>
       </c>
       <c r="T37" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.32</v>
-      </c>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3403,102 +3409,100 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="E38" t="n">
-        <v>638</v>
+        <v>4245</v>
       </c>
       <c r="F38" t="n">
-        <v>20.29</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="H38" t="n">
-        <v>19</v>
-      </c>
+        <v>17.95</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>10</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.09</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.31</v>
+        <v>8.57</v>
       </c>
       <c r="M38" t="n">
-        <v>636</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>3910</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>⚠️高槓桿(負債80%)</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>52.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="R38" t="n">
-        <v>9.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="S38" t="n">
-        <v>19.2</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.09</v>
-      </c>
+        <v>61.7</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3507,25 +3511,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>3320</v>
+        <v>1950</v>
       </c>
       <c r="F39" t="n">
-        <v>94.19</v>
+        <v>79.28</v>
       </c>
       <c r="G39" t="n">
-        <v>23.59</v>
+        <v>18.64</v>
       </c>
       <c r="H39" t="n">
-        <v>70.2</v>
+        <v>59.1</v>
       </c>
       <c r="I39" t="n">
-        <v>49</v>
+        <v>34.1</v>
       </c>
       <c r="J39" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3533,30 +3537,30 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-2.5</v>
+        <v>2.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3405</v>
+        <v>1905</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>25</v>
+        <v>22.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.92</v>
+        <v>1.28</v>
       </c>
       <c r="R39" t="n">
-        <v>23.2</v>
+        <v>15.2</v>
       </c>
       <c r="S39" t="n">
-        <v>37.7</v>
+        <v>43.7</v>
       </c>
       <c r="T39" t="n">
-        <v>104.6</v>
+        <v>79.3</v>
       </c>
       <c r="U39" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3572,12 +3576,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3586,25 +3590,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E40" t="n">
-        <v>5450</v>
+        <v>667</v>
       </c>
       <c r="F40" t="n">
-        <v>113.99</v>
+        <v>20.29</v>
       </c>
       <c r="G40" t="n">
-        <v>39.28</v>
+        <v>10.64</v>
       </c>
       <c r="H40" t="n">
-        <v>75.3</v>
+        <v>19</v>
       </c>
       <c r="I40" t="n">
-        <v>59.7</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3612,51 +3616,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.71</v>
+        <v>4.55</v>
       </c>
       <c r="M40" t="n">
-        <v>5255</v>
+        <v>638</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債80%)</t>
+        </is>
+      </c>
       <c r="P40" t="n">
-        <v>34.5</v>
+        <v>52.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.76</v>
+        <v>1.91</v>
       </c>
       <c r="R40" t="n">
-        <v>25.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S40" t="n">
-        <v>114.6</v>
+        <v>19.2</v>
       </c>
       <c r="T40" t="n">
-        <v>120.3</v>
+        <v>20.9</v>
       </c>
       <c r="U40" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3665,25 +3673,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>783</v>
+        <v>3430</v>
       </c>
       <c r="F41" t="n">
-        <v>53.61</v>
+        <v>109.68</v>
       </c>
       <c r="G41" t="n">
-        <v>29.91</v>
+        <v>27.47</v>
       </c>
       <c r="H41" t="n">
-        <v>47.5</v>
+        <v>70.2</v>
       </c>
       <c r="I41" t="n">
-        <v>20.2</v>
+        <v>49</v>
       </c>
       <c r="J41" t="n">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3691,34 +3699,30 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.38</v>
+        <v>3.31</v>
       </c>
       <c r="M41" t="n">
-        <v>780</v>
+        <v>3320</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>53.6</v>
+        <v>25</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.12</v>
+        <v>0.92</v>
       </c>
       <c r="R41" t="n">
-        <v>28.3</v>
+        <v>23.2</v>
       </c>
       <c r="S41" t="n">
-        <v>-9.300000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="T41" t="n">
-        <v>57.1</v>
+        <v>104.6</v>
       </c>
       <c r="U41" t="n">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3734,12 +3738,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3748,25 +3752,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E42" t="n">
-        <v>104</v>
+        <v>5390</v>
       </c>
       <c r="F42" t="n">
-        <v>12.24</v>
+        <v>121.48</v>
       </c>
       <c r="G42" t="n">
-        <v>1.92</v>
+        <v>41.85</v>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>75.3</v>
       </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>59.7</v>
       </c>
       <c r="J42" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3774,30 +3778,30 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.97</v>
+        <v>-1.1</v>
       </c>
       <c r="M42" t="n">
-        <v>103</v>
+        <v>5450</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>17.8</v>
+        <v>34.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.11</v>
+        <v>0.76</v>
       </c>
       <c r="R42" t="n">
-        <v>5.3</v>
+        <v>25.1</v>
       </c>
       <c r="S42" t="n">
-        <v>7.7</v>
+        <v>114.6</v>
       </c>
       <c r="T42" t="n">
-        <v>11.6</v>
+        <v>120.3</v>
       </c>
       <c r="U42" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3806,46 +3810,46 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E43" t="n">
-        <v>188</v>
+        <v>776</v>
       </c>
       <c r="F43" t="n">
-        <v>14.35</v>
+        <v>57.25</v>
       </c>
       <c r="G43" t="n">
-        <v>2.54</v>
+        <v>31.94</v>
       </c>
       <c r="H43" t="n">
-        <v>13.4</v>
+        <v>47.5</v>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>20.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3853,82 +3857,82 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.58</v>
+        <v>-0.89</v>
       </c>
       <c r="M43" t="n">
-        <v>181.5</v>
+        <v>783</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+          <t>月營收轉負-9%</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>17.6</v>
+        <v>53.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.7</v>
+        <v>1.12</v>
       </c>
       <c r="R43" t="n">
-        <v>8.5</v>
+        <v>28.3</v>
       </c>
       <c r="S43" t="n">
-        <v>4.2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>14.4</v>
+        <v>57.1</v>
       </c>
       <c r="U43" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E44" t="n">
-        <v>106</v>
+        <v>104.5</v>
       </c>
       <c r="F44" t="n">
-        <v>15.56</v>
+        <v>12.24</v>
       </c>
       <c r="G44" t="n">
-        <v>3.27</v>
+        <v>1.92</v>
       </c>
       <c r="H44" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3936,51 +3940,51 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M44" t="n">
-        <v>105.5</v>
+        <v>104</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>20.6</v>
+        <v>17.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.3</v>
+        <v>2.11</v>
       </c>
       <c r="R44" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="S44" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="T44" t="n">
-        <v>17.2</v>
+        <v>11.6</v>
       </c>
       <c r="U44" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3989,25 +3993,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E45" t="n">
-        <v>657</v>
+        <v>192</v>
       </c>
       <c r="F45" t="n">
-        <v>21.21</v>
+        <v>15.14</v>
       </c>
       <c r="G45" t="n">
-        <v>3.02</v>
+        <v>2.68</v>
       </c>
       <c r="H45" t="n">
-        <v>21.4</v>
+        <v>13.4</v>
       </c>
       <c r="I45" t="n">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J45" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4015,55 +4019,55 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-6.14</v>
+        <v>2.13</v>
       </c>
       <c r="M45" t="n">
-        <v>700</v>
+        <v>188</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="Q45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U45" t="n">
         <v>2.02</v>
       </c>
-      <c r="R45" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S45" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4072,25 +4076,25 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E46" t="n">
-        <v>237.5</v>
+        <v>105.5</v>
       </c>
       <c r="F46" t="n">
-        <v>34.8</v>
+        <v>17.26</v>
       </c>
       <c r="G46" t="n">
-        <v>3.2</v>
+        <v>3.63</v>
       </c>
       <c r="H46" t="n">
-        <v>30.9</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4098,82 +4102,78 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.71</v>
+        <v>-0.47</v>
       </c>
       <c r="M46" t="n">
-        <v>233.5</v>
+        <v>106</v>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>含金量0.5差</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>9.4</v>
+        <v>20.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.49</v>
+        <v>1.3</v>
       </c>
       <c r="R46" t="n">
         <v>7.6</v>
       </c>
       <c r="S46" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="T46" t="n">
-        <v>36.5</v>
+        <v>17.2</v>
       </c>
       <c r="U46" t="n">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E47" t="n">
-        <v>3985</v>
+        <v>659</v>
       </c>
       <c r="F47" t="n">
-        <v>56.72</v>
+        <v>22.82</v>
       </c>
       <c r="G47" t="n">
-        <v>7.31</v>
+        <v>3.25</v>
       </c>
       <c r="H47" t="n">
-        <v>51.7</v>
+        <v>21.4</v>
       </c>
       <c r="I47" t="n">
-        <v>23.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4181,112 +4181,118 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.97</v>
+        <v>0.3</v>
       </c>
       <c r="M47" t="n">
-        <v>3870</v>
+        <v>657</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.26</v>
+        <v>2.02</v>
       </c>
       <c r="R47" t="n">
-        <v>31.2</v>
+        <v>10.6</v>
       </c>
       <c r="S47" t="n">
-        <v>-33.5</v>
+        <v>30.2</v>
       </c>
       <c r="T47" t="n">
-        <v>63.8</v>
+        <v>23.4</v>
       </c>
       <c r="U47" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="E48" t="n">
-        <v>422.5</v>
+        <v>239.5</v>
       </c>
       <c r="F48" t="n">
-        <v>22.85</v>
+        <v>35.99</v>
       </c>
       <c r="G48" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>3.31</v>
+      </c>
+      <c r="H48" t="n">
+        <v>30.9</v>
+      </c>
       <c r="I48" t="n">
-        <v>49</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.03</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.12</v>
+        <v>0.84</v>
       </c>
       <c r="M48" t="n">
-        <v>422</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+        <v>237.5</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>含金量0.5差</t>
+        </is>
+      </c>
       <c r="P48" t="n">
-        <v>29.3</v>
+        <v>9.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.09</v>
+        <v>0.49</v>
       </c>
       <c r="R48" t="n">
-        <v>24.2</v>
+        <v>7.6</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>8.4</v>
       </c>
       <c r="T48" t="n">
-        <v>24</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
+        <v>36.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.03</v>
+      </c>
       <c r="V48" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4294,118 +4300,124 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>175.5</v>
+        <v>4180</v>
       </c>
       <c r="F49" t="n">
-        <v>21.32</v>
+        <v>64.19</v>
       </c>
       <c r="G49" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>51.7</v>
+      </c>
       <c r="I49" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.73</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3985</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>含金量0.3差、月營收轉負-34%</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R49" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="T49" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T49" t="n">
-        <v>22</v>
-      </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E50" t="n">
-        <v>126.5</v>
+        <v>430.5</v>
       </c>
       <c r="F50" t="n">
-        <v>28.83</v>
+        <v>22.85</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96</v>
+        <v>6.76</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4414,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.4</v>
+        <v>1.89</v>
       </c>
       <c r="M50" t="n">
-        <v>126</v>
+        <v>422.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4426,19 +4438,19 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>24.2</v>
       </c>
       <c r="S50" t="n">
-        <v>48.7</v>
+        <v>25</v>
       </c>
       <c r="T50" t="n">
-        <v>28.4</v>
+        <v>24</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4455,34 +4467,34 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E51" t="n">
-        <v>99.5</v>
+        <v>177</v>
       </c>
       <c r="F51" t="n">
-        <v>20.29</v>
+        <v>21.45</v>
       </c>
       <c r="G51" t="n">
-        <v>1.92</v>
+        <v>4.05</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>11.3</v>
+        <v>57.1</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4491,35 +4503,31 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="M51" t="n">
-        <v>98.8</v>
+        <v>175.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>9.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.99</v>
+        <v>2.74</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="S51" t="n">
-        <v>-2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T51" t="n">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4536,12 +4544,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4550,20 +4558,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="F52" t="n">
-        <v>34.33</v>
+        <v>28.6</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4572,40 +4580,36 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.9</v>
+        <v>2.77</v>
       </c>
       <c r="M52" t="n">
-        <v>166.5</v>
+        <v>126.5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>5.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="R52" t="n">
-        <v>22.1</v>
+        <v>3.8</v>
       </c>
       <c r="S52" t="n">
-        <v>14.6</v>
+        <v>48.7</v>
       </c>
       <c r="T52" t="n">
-        <v>34.2</v>
+        <v>28.4</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4617,12 +4621,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4631,20 +4635,20 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E53" t="n">
-        <v>279.5</v>
+        <v>102</v>
       </c>
       <c r="F53" t="n">
-        <v>31.3</v>
+        <v>22.48</v>
       </c>
       <c r="G53" t="n">
-        <v>7.62</v>
+        <v>2.13</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>9.6</v>
+        <v>11.3</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4653,36 +4657,40 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-9.98</v>
+        <v>2.51</v>
       </c>
       <c r="M53" t="n">
-        <v>310.5</v>
+        <v>99.5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P53" t="n">
-        <v>30.7</v>
+        <v>9.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="R53" t="n">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>812.4</v>
+        <v>-2.7</v>
       </c>
       <c r="T53" t="n">
-        <v>34.6</v>
+        <v>20.3</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4694,12 +4702,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4708,20 +4716,20 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E54" t="n">
-        <v>233.5</v>
+        <v>252</v>
       </c>
       <c r="F54" t="n">
-        <v>21.21</v>
+        <v>31.3</v>
       </c>
       <c r="G54" t="n">
-        <v>3.09</v>
+        <v>7.62</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>49.2</v>
+        <v>9.6</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -4730,10 +4738,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>9.880000000000001</v>
+        <v>-9.84</v>
       </c>
       <c r="M54" t="n">
-        <v>212.5</v>
+        <v>279.5</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4742,24 +4750,24 @@
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>14.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>20.4</v>
       </c>
       <c r="S54" t="n">
-        <v>10.3</v>
+        <v>812.4</v>
       </c>
       <c r="T54" t="n">
-        <v>20.2</v>
+        <v>34.6</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -4771,34 +4779,34 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F55" t="n">
-        <v>34.81</v>
+        <v>21.21</v>
       </c>
       <c r="G55" t="n">
-        <v>3.26</v>
+        <v>3.09</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>-15.3</v>
+        <v>49.2</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -4807,41 +4815,41 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M55" t="n">
-        <v>236</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+        <v>233.5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>9.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.72</v>
+        <v>1.53</v>
       </c>
       <c r="R55" t="n">
-        <v>13.2</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>34.8</v>
+        <v>10.3</v>
       </c>
       <c r="T55" t="n">
-        <v>34.5</v>
+        <v>20.2</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
@@ -4865,13 +4873,13 @@
         <v>61</v>
       </c>
       <c r="E56" t="n">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="F56" t="n">
-        <v>26.64</v>
+        <v>29.48</v>
       </c>
       <c r="G56" t="n">
-        <v>8.44</v>
+        <v>9.34</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4884,10 +4892,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>5.81</v>
+        <v>2.94</v>
       </c>
       <c r="M56" t="n">
-        <v>740</v>
+        <v>783</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4946,7 +4954,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>142</v>
+        <v>149.5</v>
       </c>
       <c r="F57" t="n">
         <v>31.91</v>
@@ -4965,10 +4973,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.71</v>
+        <v>5.28</v>
       </c>
       <c r="M57" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5027,13 +5035,13 @@
         <v>51</v>
       </c>
       <c r="E58" t="n">
-        <v>4380</v>
+        <v>4290</v>
       </c>
       <c r="F58" t="n">
-        <v>29.46</v>
+        <v>32.43</v>
       </c>
       <c r="G58" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5046,10 +5054,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-7.2</v>
+        <v>-2.05</v>
       </c>
       <c r="M58" t="n">
-        <v>4720</v>
+        <v>4380</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5091,91 +5099,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="E59" t="n">
-        <v>532</v>
+        <v>50.2</v>
       </c>
       <c r="F59" t="n">
-        <v>33.82</v>
+        <v>20.87</v>
       </c>
       <c r="G59" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H59" t="n">
-        <v>29.3</v>
-      </c>
+        <v>2.23</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.87</v>
-      </c>
+        <v>-15.4</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.19</v>
+        <v>1.93</v>
       </c>
       <c r="M59" t="n">
-        <v>531</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+        <v>49.25</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
+        </is>
+      </c>
       <c r="P59" t="n">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.94</v>
+        <v>0.58</v>
       </c>
       <c r="R59" t="n">
-        <v>10.6</v>
+        <v>-2.2</v>
       </c>
       <c r="S59" t="n">
-        <v>64.90000000000001</v>
+        <v>6</v>
       </c>
       <c r="T59" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.87</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5184,25 +5194,25 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E60" t="n">
-        <v>861</v>
+        <v>554</v>
       </c>
       <c r="F60" t="n">
-        <v>55.05</v>
+        <v>36.11</v>
       </c>
       <c r="G60" t="n">
-        <v>8.539999999999999</v>
+        <v>7.15</v>
       </c>
       <c r="H60" t="n">
-        <v>46.1</v>
+        <v>29.3</v>
       </c>
       <c r="I60" t="n">
-        <v>30.6</v>
+        <v>18.6</v>
       </c>
       <c r="J60" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5210,78 +5220,78 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>6.03</v>
+        <v>4.14</v>
       </c>
       <c r="M60" t="n">
-        <v>812</v>
+        <v>532</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R60" t="n">
-        <v>24.8</v>
+        <v>10.6</v>
       </c>
       <c r="S60" t="n">
-        <v>1.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>60.2</v>
+        <v>34.7</v>
       </c>
       <c r="U60" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E61" t="n">
-        <v>76.90000000000001</v>
+        <v>904</v>
       </c>
       <c r="F61" t="n">
-        <v>18.68</v>
+        <v>60.27</v>
       </c>
       <c r="G61" t="n">
-        <v>3.19</v>
+        <v>9.35</v>
       </c>
       <c r="H61" t="n">
-        <v>17.3</v>
+        <v>46.1</v>
       </c>
       <c r="I61" t="n">
-        <v>11.8</v>
+        <v>30.6</v>
       </c>
       <c r="J61" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5289,30 +5299,30 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.92</v>
+        <v>4.99</v>
       </c>
       <c r="M61" t="n">
-        <v>76.2</v>
+        <v>861</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>11.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="R61" t="n">
-        <v>4.4</v>
+        <v>24.8</v>
       </c>
       <c r="S61" t="n">
-        <v>768.2</v>
+        <v>1.5</v>
       </c>
       <c r="T61" t="n">
-        <v>19.4</v>
+        <v>60.2</v>
       </c>
       <c r="U61" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -5321,19 +5331,19 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5342,60 +5352,60 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E62" t="n">
-        <v>160.5</v>
+        <v>76.3</v>
       </c>
       <c r="F62" t="n">
-        <v>15.11</v>
+        <v>19.36</v>
       </c>
       <c r="G62" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H62" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J62" t="n">
         <v>1.64</v>
       </c>
-      <c r="H62" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I62" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.95</v>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-0.93</v>
+        <v>-0.78</v>
       </c>
       <c r="M62" t="n">
-        <v>162</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.03</v>
+        <v>1.15</v>
       </c>
       <c r="R62" t="n">
-        <v>30.2</v>
+        <v>4.4</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>768.2</v>
       </c>
       <c r="T62" t="n">
-        <v>16.9</v>
+        <v>19.4</v>
       </c>
       <c r="U62" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5407,12 +5417,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5421,79 +5431,77 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E63" t="n">
-        <v>22.1</v>
+        <v>162</v>
       </c>
       <c r="F63" t="n">
-        <v>17.72</v>
+        <v>15.11</v>
       </c>
       <c r="G63" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>1.64</v>
+      </c>
+      <c r="H63" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I63" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.38</v>
+        <v>0.93</v>
       </c>
       <c r="M63" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>月營收轉負-5%</t>
-        </is>
-      </c>
+        <v>160.5</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.03</v>
+        <v>4.03</v>
       </c>
       <c r="R63" t="n">
-        <v>12.8</v>
+        <v>30.2</v>
       </c>
       <c r="S63" t="n">
-        <v>-5.3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U63" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5502,20 +5510,20 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E64" t="n">
-        <v>45.2</v>
+        <v>22.6</v>
       </c>
       <c r="F64" t="n">
-        <v>14.53</v>
+        <v>18.01</v>
       </c>
       <c r="G64" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>147.4</v>
+        <v>13.7</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -5524,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="M64" t="n">
-        <v>44.75</v>
+        <v>22.1</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5536,28 +5544,28 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>含金量0.0差</t>
+          <t>月營收轉負-5%</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>29.2</v>
+        <v>10.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.04</v>
+        <v>1.03</v>
       </c>
       <c r="R64" t="n">
-        <v>36.1</v>
+        <v>12.8</v>
       </c>
       <c r="S64" t="n">
-        <v>0.4</v>
+        <v>-5.3</v>
       </c>
       <c r="T64" t="n">
-        <v>14.4</v>
+        <v>18.2</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -5569,12 +5577,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5583,20 +5591,20 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E65" t="n">
-        <v>769</v>
+        <v>46.35</v>
       </c>
       <c r="F65" t="n">
-        <v>19.05</v>
+        <v>14.53</v>
       </c>
       <c r="G65" t="n">
-        <v>18</v>
+        <v>1.28</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>-8.1</v>
+        <v>147.4</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -5605,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.22</v>
+        <v>2.54</v>
       </c>
       <c r="M65" t="n">
-        <v>745</v>
+        <v>45.2</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5617,28 +5625,28 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>含金量0.0差</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>94.5</v>
+        <v>29.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.08</v>
+        <v>0.04</v>
       </c>
       <c r="R65" t="n">
-        <v>18.2</v>
+        <v>36.1</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>0.4</v>
       </c>
       <c r="T65" t="n">
-        <v>19.6</v>
+        <v>14.4</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -5650,34 +5658,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E66" t="n">
-        <v>49.25</v>
+        <v>789</v>
       </c>
       <c r="F66" t="n">
-        <v>19.2</v>
+        <v>19.05</v>
       </c>
       <c r="G66" t="n">
-        <v>2.05</v>
+        <v>18</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>-15.4</v>
+        <v>-8.1</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -5686,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-2.48</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>50.5</v>
+        <v>769</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5698,23 +5706,23 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>11.5</v>
+        <v>94.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="R66" t="n">
-        <v>-2.2</v>
+        <v>18.2</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
@@ -5731,55 +5739,91 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(不在總表)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>97</v>
+      </c>
       <c r="E67" t="n">
-        <v>4580</v>
+        <v>159.5</v>
       </c>
       <c r="F67" t="n">
-        <v>14.35</v>
+        <v>16.43</v>
       </c>
       <c r="G67" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+        <v>4.84</v>
+      </c>
+      <c r="H67" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I67" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.29</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="M67" t="n">
+        <v>151.5</v>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R67" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="S67" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="T67" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5788,25 +5832,25 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>151.5</v>
+        <v>549</v>
       </c>
       <c r="F68" t="n">
-        <v>16.43</v>
+        <v>20.17</v>
       </c>
       <c r="G68" t="n">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="H68" t="n">
-        <v>14.7</v>
+        <v>17.9</v>
       </c>
       <c r="I68" t="n">
-        <v>12.8</v>
+        <v>19.1</v>
       </c>
       <c r="J68" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5814,51 +5858,51 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="M68" t="n">
-        <v>150</v>
+        <v>539</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>27.9</v>
+        <v>23.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="R68" t="n">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="S68" t="n">
-        <v>7.7</v>
+        <v>18.6</v>
       </c>
       <c r="T68" t="n">
-        <v>16.5</v>
+        <v>21.3</v>
       </c>
       <c r="U68" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5867,25 +5911,25 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>539</v>
+        <v>120.5</v>
       </c>
       <c r="F69" t="n">
-        <v>20.79</v>
+        <v>17.17</v>
       </c>
       <c r="G69" t="n">
-        <v>4.94</v>
+        <v>3.4</v>
       </c>
       <c r="H69" t="n">
-        <v>17.9</v>
+        <v>15</v>
       </c>
       <c r="I69" t="n">
-        <v>19.1</v>
+        <v>13.5</v>
       </c>
       <c r="J69" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5893,34 +5937,34 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>10</v>
+        <v>0.84</v>
       </c>
       <c r="M69" t="n">
-        <v>490</v>
+        <v>119.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>23.5</v>
+        <v>19.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="R69" t="n">
-        <v>12.2</v>
+        <v>7</v>
       </c>
       <c r="S69" t="n">
-        <v>18.6</v>
+        <v>0.6</v>
       </c>
       <c r="T69" t="n">
-        <v>21.3</v>
+        <v>17.1</v>
       </c>
       <c r="U69" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -5932,12 +5976,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5946,25 +5990,25 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>119.5</v>
+        <v>350</v>
       </c>
       <c r="F70" t="n">
-        <v>17.17</v>
+        <v>33.9</v>
       </c>
       <c r="G70" t="n">
-        <v>3.4</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>15</v>
+        <v>27.5</v>
       </c>
       <c r="I70" t="n">
-        <v>13.5</v>
+        <v>29.1</v>
       </c>
       <c r="J70" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5972,51 +6016,51 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M70" t="n">
-        <v>119.5</v>
+        <v>344.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>19.8</v>
+        <v>27.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.28</v>
+        <v>0.83</v>
       </c>
       <c r="R70" t="n">
-        <v>7</v>
+        <v>18.3</v>
       </c>
       <c r="S70" t="n">
-        <v>0.6</v>
+        <v>41.8</v>
       </c>
       <c r="T70" t="n">
-        <v>17.1</v>
+        <v>35.5</v>
       </c>
       <c r="U70" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6025,25 +6069,25 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>344.5</v>
+        <v>91.7</v>
       </c>
       <c r="F71" t="n">
-        <v>35.51</v>
+        <v>19.16</v>
       </c>
       <c r="G71" t="n">
-        <v>9.74</v>
+        <v>2.09</v>
       </c>
       <c r="H71" t="n">
-        <v>27.5</v>
+        <v>16.7</v>
       </c>
       <c r="I71" t="n">
-        <v>29.1</v>
+        <v>14.1</v>
       </c>
       <c r="J71" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6051,78 +6095,78 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-5.36</v>
+        <v>0.55</v>
       </c>
       <c r="M71" t="n">
-        <v>364</v>
+        <v>91.2</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>27.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.83</v>
+        <v>2.1</v>
       </c>
       <c r="R71" t="n">
-        <v>18.3</v>
+        <v>21.7</v>
       </c>
       <c r="S71" t="n">
-        <v>41.8</v>
+        <v>19.5</v>
       </c>
       <c r="T71" t="n">
-        <v>35.5</v>
+        <v>19.1</v>
       </c>
       <c r="U71" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>91.2</v>
+        <v>148</v>
       </c>
       <c r="F72" t="n">
-        <v>19.16</v>
+        <v>19.51</v>
       </c>
       <c r="G72" t="n">
-        <v>2.09</v>
+        <v>5.33</v>
       </c>
       <c r="H72" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="I72" t="n">
-        <v>14.1</v>
+        <v>17.2</v>
       </c>
       <c r="J72" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6130,34 +6174,38 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="M72" t="n">
-        <v>88.5</v>
+        <v>143</v>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>含金量-0.3差</t>
+        </is>
+      </c>
       <c r="P72" t="n">
-        <v>10.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.1</v>
+        <v>-0.28</v>
       </c>
       <c r="R72" t="n">
-        <v>21.7</v>
+        <v>17.8</v>
       </c>
       <c r="S72" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="T72" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="U72" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -6169,12 +6217,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6186,22 +6234,22 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>143</v>
+        <v>251</v>
       </c>
       <c r="F73" t="n">
-        <v>19.51</v>
+        <v>19.07</v>
       </c>
       <c r="G73" t="n">
-        <v>5.33</v>
+        <v>2.11</v>
       </c>
       <c r="H73" t="n">
-        <v>16.4</v>
+        <v>15.3</v>
       </c>
       <c r="I73" t="n">
-        <v>17.2</v>
+        <v>15.2</v>
       </c>
       <c r="J73" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6209,34 +6257,30 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="M73" t="n">
-        <v>140.5</v>
+        <v>246.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>含金量-0.3差</t>
-        </is>
-      </c>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>34.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>-0.28</v>
+        <v>1.24</v>
       </c>
       <c r="R73" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="S73" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="T73" t="n">
         <v>17.6</v>
       </c>
-      <c r="T73" t="n">
-        <v>19.2</v>
-      </c>
       <c r="U73" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -6252,12 +6296,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6266,25 +6310,23 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>246.5</v>
+        <v>1040</v>
       </c>
       <c r="F74" t="n">
-        <v>17.65</v>
+        <v>52.17</v>
       </c>
       <c r="G74" t="n">
-        <v>1.95</v>
+        <v>27.16</v>
       </c>
       <c r="H74" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="I74" t="n">
-        <v>15.2</v>
-      </c>
+        <v>38.8</v>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6292,30 +6334,34 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-0.8</v>
+        <v>4.42</v>
       </c>
       <c r="M74" t="n">
-        <v>248.5</v>
+        <v>996</v>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>EPS資料不足</t>
+        </is>
+      </c>
       <c r="P74" t="n">
-        <v>11.4</v>
+        <v>52.2</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="R74" t="n">
-        <v>7.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S74" t="n">
-        <v>39.6</v>
+        <v>99.3</v>
       </c>
       <c r="T74" t="n">
-        <v>17.6</v>
+        <v>62</v>
       </c>
       <c r="U74" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -6324,19 +6370,19 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6345,23 +6391,25 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>996</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>52.17</v>
+        <v>25.74</v>
       </c>
       <c r="G75" t="n">
-        <v>27.16</v>
+        <v>3.31</v>
       </c>
       <c r="H75" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
+        <v>21.3</v>
+      </c>
+      <c r="I75" t="n">
+        <v>18.7</v>
+      </c>
       <c r="J75" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6369,34 +6417,34 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-3.3</v>
+        <v>3.58</v>
       </c>
       <c r="M75" t="n">
-        <v>1030</v>
+        <v>64.3</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>⚠️高槓桿(負債81%)</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>52.2</v>
+        <v>13.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="R75" t="n">
-        <v>97.59999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="S75" t="n">
-        <v>99.3</v>
+        <v>35.3</v>
       </c>
       <c r="T75" t="n">
-        <v>62</v>
+        <v>25.2</v>
       </c>
       <c r="U75" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -6405,102 +6453,98 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>64.3</v>
+        <v>2525</v>
       </c>
       <c r="F76" t="n">
-        <v>24.07</v>
+        <v>39.43</v>
       </c>
       <c r="G76" t="n">
-        <v>3.09</v>
+        <v>20.86</v>
       </c>
       <c r="H76" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="I76" t="n">
-        <v>18.7</v>
+        <v>86.7</v>
       </c>
       <c r="J76" t="n">
-        <v>1.35</v>
+        <v>0.66</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R76" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="T76" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
           <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M76" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>⚠️高槓桿(負債81%)</t>
-        </is>
-      </c>
-      <c r="P76" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="S76" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="T76" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6512,22 +6556,22 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2300</v>
+        <v>923</v>
       </c>
       <c r="F77" t="n">
-        <v>37.05</v>
+        <v>22.84</v>
       </c>
       <c r="G77" t="n">
-        <v>19.6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>24.6</v>
+        <v>14.2</v>
       </c>
       <c r="I77" t="n">
-        <v>86.7</v>
+        <v>54.3</v>
       </c>
       <c r="J77" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6535,34 +6579,34 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>-3.35</v>
       </c>
       <c r="M77" t="n">
-        <v>2255</v>
+        <v>955</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>50.9</v>
+        <v>37.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="R77" t="n">
-        <v>31.1</v>
+        <v>34.4</v>
       </c>
       <c r="S77" t="n">
-        <v>60.6</v>
+        <v>103.3</v>
       </c>
       <c r="T77" t="n">
-        <v>39.3</v>
+        <v>21.9</v>
       </c>
       <c r="U77" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -6574,12 +6618,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6591,22 +6635,22 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>955</v>
+        <v>2410</v>
       </c>
       <c r="F78" t="n">
-        <v>24.37</v>
+        <v>32.4</v>
       </c>
       <c r="G78" t="n">
-        <v>9.449999999999999</v>
+        <v>10.61</v>
       </c>
       <c r="H78" t="n">
-        <v>14.2</v>
+        <v>23.6</v>
       </c>
       <c r="I78" t="n">
-        <v>54.3</v>
+        <v>43.1</v>
       </c>
       <c r="J78" t="n">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6614,30 +6658,30 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>8.77</v>
+        <v>1.69</v>
       </c>
       <c r="M78" t="n">
-        <v>878</v>
+        <v>2370</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>37.1</v>
+        <v>32.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="R78" t="n">
-        <v>34.4</v>
+        <v>24.5</v>
       </c>
       <c r="S78" t="n">
-        <v>103.3</v>
+        <v>30.1</v>
       </c>
       <c r="T78" t="n">
-        <v>21.9</v>
+        <v>33.7</v>
       </c>
       <c r="U78" t="n">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -6653,12 +6697,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6667,25 +6711,25 @@
         </is>
       </c>
       <c r="D79" t="n">
+        <v>97</v>
+      </c>
+      <c r="E79" t="n">
         <v>100</v>
       </c>
-      <c r="E79" t="n">
-        <v>2370</v>
-      </c>
       <c r="F79" t="n">
-        <v>31.46</v>
+        <v>14.93</v>
       </c>
       <c r="G79" t="n">
-        <v>10.3</v>
+        <v>3.34</v>
       </c>
       <c r="H79" t="n">
-        <v>23.6</v>
+        <v>12.4</v>
       </c>
       <c r="I79" t="n">
-        <v>43.1</v>
+        <v>20.6</v>
       </c>
       <c r="J79" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6693,34 +6737,34 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.28</v>
+        <v>2.67</v>
       </c>
       <c r="M79" t="n">
-        <v>2340</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>32.5</v>
+        <v>20.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="R79" t="n">
-        <v>24.5</v>
+        <v>17.9</v>
       </c>
       <c r="S79" t="n">
-        <v>30.1</v>
+        <v>27.4</v>
       </c>
       <c r="T79" t="n">
-        <v>33.7</v>
+        <v>14.9</v>
       </c>
       <c r="U79" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -6732,12 +6776,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6746,25 +6790,25 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>97.40000000000001</v>
+        <v>120</v>
       </c>
       <c r="F80" t="n">
-        <v>14.09</v>
+        <v>15.49</v>
       </c>
       <c r="G80" t="n">
-        <v>3.15</v>
+        <v>2.17</v>
       </c>
       <c r="H80" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="I80" t="n">
-        <v>20.6</v>
+        <v>23.9</v>
       </c>
       <c r="J80" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6772,30 +6816,30 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="M80" t="n">
-        <v>95.8</v>
+        <v>114.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>20.9</v>
+        <v>17</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="R80" t="n">
-        <v>17.9</v>
+        <v>5.7</v>
       </c>
       <c r="S80" t="n">
-        <v>27.4</v>
+        <v>20.2</v>
       </c>
       <c r="T80" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="U80" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6811,12 +6855,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6828,22 +6872,22 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>114.5</v>
+        <v>34.5</v>
       </c>
       <c r="F81" t="n">
-        <v>15.49</v>
+        <v>6.9</v>
       </c>
       <c r="G81" t="n">
-        <v>2.17</v>
+        <v>1.34</v>
       </c>
       <c r="H81" t="n">
-        <v>12.3</v>
+        <v>5.9</v>
       </c>
       <c r="I81" t="n">
-        <v>23.9</v>
+        <v>16.1</v>
       </c>
       <c r="J81" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6851,34 +6895,34 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.78</v>
+        <v>0.88</v>
       </c>
       <c r="M81" t="n">
-        <v>112.5</v>
+        <v>34.2</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>17</v>
+        <v>19.4</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.36</v>
+        <v>1.89</v>
       </c>
       <c r="R81" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="S81" t="n">
-        <v>20.2</v>
+        <v>88.7</v>
       </c>
       <c r="T81" t="n">
-        <v>15.2</v>
+        <v>6.8</v>
       </c>
       <c r="U81" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -6890,12 +6934,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6907,22 +6951,22 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>34.2</v>
+        <v>113.5</v>
       </c>
       <c r="F82" t="n">
-        <v>6.81</v>
+        <v>12.39</v>
       </c>
       <c r="G82" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="H82" t="n">
-        <v>5.9</v>
+        <v>10.7</v>
       </c>
       <c r="I82" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="J82" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6930,30 +6974,30 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.59</v>
+        <v>-1.73</v>
       </c>
       <c r="M82" t="n">
-        <v>34</v>
+        <v>115.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>19.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="R82" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="S82" t="n">
-        <v>88.7</v>
+        <v>1.7</v>
       </c>
       <c r="T82" t="n">
-        <v>6.8</v>
+        <v>12.4</v>
       </c>
       <c r="U82" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -6969,12 +7013,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6986,22 +7030,22 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>115.5</v>
+        <v>187.5</v>
       </c>
       <c r="F83" t="n">
-        <v>12.28</v>
+        <v>13.88</v>
       </c>
       <c r="G83" t="n">
-        <v>3.17</v>
+        <v>3.51</v>
       </c>
       <c r="H83" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="I83" t="n">
-        <v>16.2</v>
+        <v>24.1</v>
       </c>
       <c r="J83" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7009,30 +7053,30 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.32</v>
+        <v>-0.79</v>
       </c>
       <c r="M83" t="n">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>24.9</v>
+        <v>22.1</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="R83" t="n">
-        <v>3.4</v>
+        <v>10.2</v>
       </c>
       <c r="S83" t="n">
-        <v>1.7</v>
+        <v>13.3</v>
       </c>
       <c r="T83" t="n">
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="U83" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -7048,12 +7092,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7062,25 +7106,25 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>189</v>
+        <v>44.9</v>
       </c>
       <c r="F84" t="n">
-        <v>14.11</v>
+        <v>8.07</v>
       </c>
       <c r="G84" t="n">
-        <v>3.57</v>
+        <v>1.7</v>
       </c>
       <c r="H84" t="n">
-        <v>11.4</v>
+        <v>7.6</v>
       </c>
       <c r="I84" t="n">
-        <v>24.1</v>
+        <v>9.9</v>
       </c>
       <c r="J84" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7088,30 +7132,30 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.53</v>
+        <v>2.28</v>
       </c>
       <c r="M84" t="n">
-        <v>190</v>
+        <v>43.9</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R84" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S84" t="n">
         <v>22.1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R84" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S84" t="n">
-        <v>13.3</v>
-      </c>
       <c r="T84" t="n">
-        <v>14.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U84" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -7127,12 +7171,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7141,25 +7185,25 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>43.9</v>
+        <v>1285</v>
       </c>
       <c r="F85" t="n">
-        <v>8.31</v>
+        <v>40.47</v>
       </c>
       <c r="G85" t="n">
-        <v>1.75</v>
+        <v>13.56</v>
       </c>
       <c r="H85" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="I85" t="n">
-        <v>9.9</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7167,34 +7211,34 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.23</v>
+        <v>5.76</v>
       </c>
       <c r="M85" t="n">
-        <v>43.8</v>
+        <v>1215</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>20.9</v>
+        <v>33.9</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.16</v>
+        <v>0.84</v>
       </c>
       <c r="R85" t="n">
-        <v>20.7</v>
+        <v>23.6</v>
       </c>
       <c r="S85" t="n">
-        <v>22.1</v>
+        <v>37.3</v>
       </c>
       <c r="T85" t="n">
-        <v>8.300000000000001</v>
+        <v>40</v>
       </c>
       <c r="U85" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -7206,12 +7250,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7223,22 +7267,22 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>1215</v>
+        <v>518</v>
       </c>
       <c r="F86" t="n">
-        <v>36.47</v>
+        <v>27.84</v>
       </c>
       <c r="G86" t="n">
-        <v>12.22</v>
+        <v>5.17</v>
       </c>
       <c r="H86" t="n">
-        <v>25</v>
+        <v>21.2</v>
       </c>
       <c r="I86" t="n">
-        <v>79.40000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="J86" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7246,30 +7290,30 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-1.22</v>
+        <v>3.7</v>
       </c>
       <c r="M86" t="n">
-        <v>1230</v>
+        <v>499.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>33.9</v>
+        <v>18.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="R86" t="n">
-        <v>23.6</v>
+        <v>3.9</v>
       </c>
       <c r="S86" t="n">
-        <v>37.3</v>
+        <v>46.6</v>
       </c>
       <c r="T86" t="n">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="U86" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -7285,12 +7329,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7302,22 +7346,22 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>499.5</v>
+        <v>142</v>
       </c>
       <c r="F87" t="n">
-        <v>24.68</v>
+        <v>17.7</v>
       </c>
       <c r="G87" t="n">
-        <v>4.58</v>
+        <v>3.66</v>
       </c>
       <c r="H87" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="I87" t="n">
-        <v>29.8</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7325,34 +7369,34 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-1.67</v>
+        <v>2.9</v>
       </c>
       <c r="M87" t="n">
-        <v>508</v>
+        <v>138</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="R87" t="n">
-        <v>3.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S87" t="n">
-        <v>46.6</v>
+        <v>14.9</v>
       </c>
       <c r="T87" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="U87" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -7364,12 +7408,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7378,25 +7422,25 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>138</v>
+        <v>41.15</v>
       </c>
       <c r="F88" t="n">
-        <v>16.73</v>
+        <v>9.19</v>
       </c>
       <c r="G88" t="n">
-        <v>3.46</v>
+        <v>1.25</v>
       </c>
       <c r="H88" t="n">
-        <v>14.1</v>
+        <v>6.2</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>44.7</v>
       </c>
       <c r="J88" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7404,30 +7448,30 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="M88" t="n">
-        <v>137</v>
+        <v>40.55</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>20.7</v>
+        <v>13.6</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.16</v>
+        <v>0.89</v>
       </c>
       <c r="R88" t="n">
-        <v>8.300000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="S88" t="n">
-        <v>14.9</v>
+        <v>153.2</v>
       </c>
       <c r="T88" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="U88" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -7443,12 +7487,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7457,25 +7501,25 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>40.55</v>
+        <v>2495</v>
       </c>
       <c r="F89" t="n">
-        <v>8.699999999999999</v>
+        <v>46.05</v>
       </c>
       <c r="G89" t="n">
-        <v>1.19</v>
+        <v>20.84</v>
       </c>
       <c r="H89" t="n">
-        <v>6.2</v>
+        <v>30.7</v>
       </c>
       <c r="I89" t="n">
-        <v>44.7</v>
+        <v>71.7</v>
       </c>
       <c r="J89" t="n">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7483,34 +7527,38 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.4</v>
+        <v>6.62</v>
       </c>
       <c r="M89" t="n">
-        <v>39.6</v>
+        <v>2340</v>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P89" t="n">
-        <v>13.6</v>
+        <v>45.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="R89" t="n">
-        <v>14.5</v>
+        <v>42.9</v>
       </c>
       <c r="S89" t="n">
-        <v>153.2</v>
+        <v>56.6</v>
       </c>
       <c r="T89" t="n">
-        <v>9</v>
+        <v>49.1</v>
       </c>
       <c r="U89" t="n">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -7522,12 +7570,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7539,22 +7587,22 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>2340</v>
+        <v>1010</v>
       </c>
       <c r="F90" t="n">
-        <v>45.01</v>
+        <v>28.72</v>
       </c>
       <c r="G90" t="n">
-        <v>20.36</v>
+        <v>6.9</v>
       </c>
       <c r="H90" t="n">
-        <v>30.7</v>
+        <v>21.8</v>
       </c>
       <c r="I90" t="n">
-        <v>71.7</v>
+        <v>40.5</v>
       </c>
       <c r="J90" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7562,38 +7610,38 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M90" t="n">
-        <v>2380</v>
+        <v>995</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>含金量-0.1差</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>45.1</v>
+        <v>24.6</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.92</v>
+        <v>-0.08</v>
       </c>
       <c r="R90" t="n">
-        <v>42.9</v>
+        <v>13.1</v>
       </c>
       <c r="S90" t="n">
-        <v>56.6</v>
+        <v>93.8</v>
       </c>
       <c r="T90" t="n">
-        <v>49.1</v>
+        <v>30.6</v>
       </c>
       <c r="U90" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -7605,39 +7653,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>995</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>28.72</v>
+        <v>11.24</v>
       </c>
       <c r="G91" t="n">
-        <v>6.9</v>
+        <v>2.46</v>
       </c>
       <c r="H91" t="n">
-        <v>21.8</v>
+        <v>8.6</v>
       </c>
       <c r="I91" t="n">
-        <v>40.5</v>
+        <v>31.3</v>
       </c>
       <c r="J91" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7645,38 +7693,38 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.58</v>
+        <v>-1.51</v>
       </c>
       <c r="M91" t="n">
-        <v>970</v>
+        <v>93</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>含金量-0.1差</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>24.6</v>
+        <v>20.9</v>
       </c>
       <c r="Q91" t="n">
-        <v>-0.08</v>
+        <v>2.28</v>
       </c>
       <c r="R91" t="n">
-        <v>13.1</v>
+        <v>10.5</v>
       </c>
       <c r="S91" t="n">
-        <v>93.8</v>
+        <v>1.5</v>
       </c>
       <c r="T91" t="n">
-        <v>30.6</v>
+        <v>11.2</v>
       </c>
       <c r="U91" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -7688,12 +7736,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7702,25 +7750,25 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>93</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>11.31</v>
+        <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>2.48</v>
+        <v>1.86</v>
       </c>
       <c r="H92" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="I92" t="n">
-        <v>31.3</v>
+        <v>13.7</v>
       </c>
       <c r="J92" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7728,38 +7776,38 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1.38</v>
+        <v>0.28</v>
       </c>
       <c r="M92" t="n">
-        <v>94.3</v>
+        <v>71.7</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>含金量0.5弱</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>20.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.28</v>
+        <v>0.52</v>
       </c>
       <c r="R92" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="S92" t="n">
-        <v>1.5</v>
+        <v>11.8</v>
       </c>
       <c r="T92" t="n">
-        <v>11.2</v>
+        <v>7.7</v>
       </c>
       <c r="U92" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -7771,12 +7819,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7785,25 +7833,25 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>71.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>7.74</v>
+        <v>12.17</v>
       </c>
       <c r="G93" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="H93" t="n">
-        <v>6.8</v>
+        <v>10.4</v>
       </c>
       <c r="I93" t="n">
-        <v>13.7</v>
+        <v>17.1</v>
       </c>
       <c r="J93" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7811,34 +7859,34 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.14</v>
+        <v>2.14</v>
       </c>
       <c r="M93" t="n">
-        <v>71.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>含金量0.5弱</t>
+          <t>月營收轉負-10%</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>23.3</v>
+        <v>17.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R93" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="S93" t="n">
-        <v>11.8</v>
+        <v>-10.5</v>
       </c>
       <c r="T93" t="n">
-        <v>7.7</v>
+        <v>12.2</v>
       </c>
       <c r="U93" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -7854,12 +7902,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7868,25 +7916,25 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>65.5</v>
+        <v>368</v>
       </c>
       <c r="F94" t="n">
-        <v>12.17</v>
+        <v>18.9</v>
       </c>
       <c r="G94" t="n">
-        <v>1.49</v>
+        <v>6.98</v>
       </c>
       <c r="H94" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="I94" t="n">
-        <v>17.1</v>
+        <v>37.4</v>
       </c>
       <c r="J94" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7894,38 +7942,38 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="M94" t="n">
-        <v>65.5</v>
+        <v>367</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>月營收轉負-10%</t>
+          <t>含金量-0.9差、⚠️高槓桿(負債87%)</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>17.5</v>
+        <v>35.3</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.87</v>
       </c>
       <c r="R94" t="n">
-        <v>6.2</v>
+        <v>17.1</v>
       </c>
       <c r="S94" t="n">
-        <v>-10.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T94" t="n">
-        <v>12.2</v>
+        <v>18.2</v>
       </c>
       <c r="U94" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -7937,12 +7985,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7954,22 +8002,22 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>367</v>
+        <v>4635</v>
       </c>
       <c r="F95" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="G95" t="n">
-        <v>6.72</v>
+        <v>6.8</v>
       </c>
       <c r="H95" t="n">
-        <v>13.2</v>
+        <v>9.6</v>
       </c>
       <c r="I95" t="n">
-        <v>37.4</v>
+        <v>99.8</v>
       </c>
       <c r="J95" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7977,38 +8025,38 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="M95" t="n">
-        <v>362</v>
+        <v>4580</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>含金量-0.9差、⚠️高槓桿(負債87%)</t>
+          <t>含金量0.2差、毛利壓歷史低檔、⚠️存貨爆衝(存85%vs營18%)</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>35.3</v>
+        <v>39.6</v>
       </c>
       <c r="Q95" t="n">
-        <v>-0.87</v>
+        <v>0.16</v>
       </c>
       <c r="R95" t="n">
-        <v>17.1</v>
+        <v>49</v>
       </c>
       <c r="S95" t="n">
-        <v>94.40000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="T95" t="n">
-        <v>18.2</v>
+        <v>15.3</v>
       </c>
       <c r="U95" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -8037,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>154.5</v>
+        <v>158.5</v>
       </c>
       <c r="F96" t="n">
-        <v>15.35</v>
+        <v>16.2</v>
       </c>
       <c r="G96" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8060,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.98</v>
+        <v>2.59</v>
       </c>
       <c r="M96" t="n">
-        <v>153</v>
+        <v>154.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8120,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F97" t="n">
-        <v>16.75</v>
+        <v>17.85</v>
       </c>
       <c r="G97" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8143,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>8.06</v>
+        <v>-0.34</v>
       </c>
       <c r="M97" t="n">
-        <v>1365</v>
+        <v>1475</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8203,7 +8251,7 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="F98" t="n">
         <v>6.51</v>
@@ -8222,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="M98" t="n">
-        <v>77.3</v>
+        <v>78.3</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8280,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F99" t="n">
         <v>8.07</v>
@@ -8299,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="M99" t="n">
-        <v>397.5</v>
+        <v>404</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8380,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>23.6</v>
+        <v>23.95</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8442,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>193.5</v>
+        <v>194.5</v>
       </c>
       <c r="F101" t="n">
-        <v>9.65</v>
+        <v>10.28</v>
       </c>
       <c r="G101" t="n">
-        <v>4.02</v>
+        <v>4.28</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8461,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-2.27</v>
+        <v>0.52</v>
       </c>
       <c r="M101" t="n">
-        <v>198</v>
+        <v>193.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8514,7 +8562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8654,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2300</v>
+        <v>2525</v>
       </c>
       <c r="F2" t="n">
-        <v>37.05</v>
+        <v>39.43</v>
       </c>
       <c r="G2" t="n">
-        <v>19.6</v>
+        <v>20.86</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8677,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>2255</v>
+        <v>2300</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8733,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>955</v>
+        <v>923</v>
       </c>
       <c r="F3" t="n">
-        <v>24.37</v>
+        <v>22.84</v>
       </c>
       <c r="G3" t="n">
-        <v>9.449999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8756,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8.77</v>
+        <v>-3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>878</v>
+        <v>955</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8812,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2370</v>
+        <v>2410</v>
       </c>
       <c r="F4" t="n">
-        <v>31.46</v>
+        <v>32.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.3</v>
+        <v>10.61</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8835,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="M4" t="n">
-        <v>2340</v>
+        <v>2370</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8891,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>14.09</v>
+        <v>14.93</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8914,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="M5" t="n">
-        <v>95.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -8970,7 +9018,7 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>114.5</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
         <v>15.49</v>
@@ -8993,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>112.5</v>
+        <v>114.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9049,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.81</v>
+        <v>6.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9072,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9128,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>115.5</v>
+        <v>113.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.28</v>
+        <v>12.39</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9151,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>-1.73</v>
       </c>
       <c r="M8" t="n">
-        <v>114</v>
+        <v>115.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9207,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>189</v>
+        <v>187.5</v>
       </c>
       <c r="F9" t="n">
-        <v>14.11</v>
+        <v>13.88</v>
       </c>
       <c r="G9" t="n">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9230,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.53</v>
+        <v>-0.79</v>
       </c>
       <c r="M9" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9286,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>43.9</v>
+        <v>44.9</v>
       </c>
       <c r="F10" t="n">
-        <v>8.31</v>
+        <v>8.07</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9309,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.23</v>
+        <v>2.28</v>
       </c>
       <c r="M10" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9365,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1215</v>
+        <v>1285</v>
       </c>
       <c r="F11" t="n">
-        <v>36.47</v>
+        <v>40.47</v>
       </c>
       <c r="G11" t="n">
-        <v>12.22</v>
+        <v>13.56</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9388,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.22</v>
+        <v>5.76</v>
       </c>
       <c r="M11" t="n">
-        <v>1230</v>
+        <v>1215</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9444,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>499.5</v>
+        <v>518</v>
       </c>
       <c r="F12" t="n">
-        <v>24.68</v>
+        <v>27.84</v>
       </c>
       <c r="G12" t="n">
-        <v>4.58</v>
+        <v>5.17</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9467,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.67</v>
+        <v>3.7</v>
       </c>
       <c r="M12" t="n">
-        <v>508</v>
+        <v>499.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9523,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F13" t="n">
-        <v>16.73</v>
+        <v>17.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3.46</v>
+        <v>3.66</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9546,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.73</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9602,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>40.55</v>
+        <v>41.15</v>
       </c>
       <c r="F14" t="n">
-        <v>8.699999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G14" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9625,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>39.6</v>
+        <v>40.55</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9681,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2340</v>
+        <v>2495</v>
       </c>
       <c r="F15" t="n">
-        <v>45.01</v>
+        <v>46.05</v>
       </c>
       <c r="G15" t="n">
-        <v>20.36</v>
+        <v>20.84</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9704,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.68</v>
+        <v>6.62</v>
       </c>
       <c r="M15" t="n">
-        <v>2380</v>
+        <v>2340</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9764,7 +9812,7 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="F16" t="n">
         <v>28.72</v>
@@ -9787,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.58</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>970</v>
+        <v>995</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9847,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>11.31</v>
+        <v>11.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9870,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-1.38</v>
+        <v>-1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>94.3</v>
+        <v>93</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9930,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>7.74</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -9953,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="M18" t="n">
-        <v>71.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10013,7 +10061,7 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>65.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>12.17</v>
@@ -10036,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
         <v>65.5</v>
@@ -10096,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F20" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="G20" t="n">
-        <v>6.72</v>
+        <v>6.98</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10119,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>0.27</v>
       </c>
       <c r="M20" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10162,39 +10210,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>154.5</v>
+        <v>4635</v>
       </c>
       <c r="F21" t="n">
-        <v>15.35</v>
+        <v>17.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.56</v>
+        <v>6.8</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I21" t="n">
-        <v>48.9</v>
+        <v>99.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -10202,38 +10250,38 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.98</v>
+        <v>1.2</v>
       </c>
       <c r="M21" t="n">
-        <v>153</v>
+        <v>4580</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>含金量-3.4差、毛利壓歷史低檔、⚠️高槓桿(負債81%)</t>
+          <t>含金量0.2差、毛利壓歷史低檔、⚠️存貨爆衝(存85%vs營18%)</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>23.5</v>
+        <v>39.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.39</v>
+        <v>0.16</v>
       </c>
       <c r="R21" t="n">
-        <v>26.2</v>
+        <v>49</v>
       </c>
       <c r="S21" t="n">
-        <v>39.2</v>
+        <v>18.2</v>
       </c>
       <c r="T21" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10245,12 +10293,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10259,25 +10307,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>1475</v>
+        <v>158.5</v>
       </c>
       <c r="F22" t="n">
-        <v>16.75</v>
+        <v>16.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -10285,41 +10333,124 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.06</v>
+        <v>2.59</v>
       </c>
       <c r="M22" t="n">
-        <v>1365</v>
+        <v>154.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
+          <t>含金量-3.4差、毛利壓歷史低檔、⚠️高槓桿(負債81%)</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="R22" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1475</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>毛利壓歷史低檔、月營收轉負-19%</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>16.3</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>0.9</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>22.2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>-19.4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>17.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>0.36</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>🟢成長未反映</t>
         </is>
@@ -10476,7 +10607,7 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>151.5</v>
+        <v>159.5</v>
       </c>
       <c r="F2" t="n">
         <v>16.43</v>
@@ -10499,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>5.28</v>
       </c>
       <c r="M2" t="n">
-        <v>150</v>
+        <v>151.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10555,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="F3" t="n">
-        <v>20.79</v>
+        <v>20.17</v>
       </c>
       <c r="G3" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10578,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>490</v>
+        <v>539</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10634,7 +10765,7 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>119.5</v>
+        <v>120.5</v>
       </c>
       <c r="F4" t="n">
         <v>17.17</v>
@@ -10657,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="M4" t="n">
         <v>119.5</v>
@@ -10713,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>344.5</v>
+        <v>350</v>
       </c>
       <c r="F5" t="n">
-        <v>35.51</v>
+        <v>33.9</v>
       </c>
       <c r="G5" t="n">
-        <v>9.74</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10736,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-5.36</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>364</v>
+        <v>344.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10792,7 +10923,7 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91.2</v>
+        <v>91.7</v>
       </c>
       <c r="F6" t="n">
         <v>19.16</v>
@@ -10815,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>88.5</v>
+        <v>91.2</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -10871,7 +11002,7 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
         <v>19.51</v>
@@ -10894,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>140.5</v>
+        <v>143</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -10954,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>246.5</v>
+        <v>251</v>
       </c>
       <c r="F8" t="n">
-        <v>17.65</v>
+        <v>19.07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -10977,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.8</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11033,7 +11164,7 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="F9" t="n">
         <v>52.17</v>
@@ -11054,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-3.3</v>
+        <v>4.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1030</v>
+        <v>996</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11114,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>64.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>24.07</v>
+        <v>25.74</v>
       </c>
       <c r="G10" t="n">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11137,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.58</v>
+        <v>3.58</v>
       </c>
       <c r="M10" t="n">
-        <v>63.3</v>
+        <v>64.3</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11328,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1475</v>
+        <v>1550</v>
       </c>
       <c r="F2" t="n">
-        <v>97.72</v>
+        <v>113.41</v>
       </c>
       <c r="G2" t="n">
-        <v>27.43</v>
+        <v>31.84</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11351,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.66</v>
+        <v>5.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1370</v>
+        <v>1475</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11407,7 +11538,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.35</v>
+        <v>39.75</v>
       </c>
       <c r="F3" t="n">
         <v>11.12</v>
@@ -11430,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.13</v>
+        <v>1.02</v>
       </c>
       <c r="M3" t="n">
-        <v>39.3</v>
+        <v>39.35</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11486,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>140.5</v>
+        <v>141.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.3</v>
+        <v>16.53</v>
       </c>
       <c r="G4" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11509,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.35</v>
+        <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>141</v>
+        <v>140.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11565,7 +11696,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6060</v>
+        <v>6090</v>
       </c>
       <c r="F5" t="n">
         <v>161.34</v>
@@ -11588,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-6.77</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>6500</v>
+        <v>6060</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11648,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>24.04</v>
+        <v>24.14</v>
       </c>
       <c r="G6" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11671,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.42</v>
+        <v>-1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11727,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>34.55</v>
+        <v>35.42</v>
       </c>
       <c r="G7" t="n">
-        <v>4.91</v>
+        <v>5.03</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11750,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.42</v>
+        <v>3.36</v>
       </c>
       <c r="M7" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11810,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>185.5</v>
       </c>
       <c r="F8" t="n">
-        <v>26.03</v>
+        <v>25.95</v>
       </c>
       <c r="G8" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11833,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.88</v>
+        <v>7.85</v>
       </c>
       <c r="M8" t="n">
-        <v>170.5</v>
+        <v>172</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -11893,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>27.16</v>
+        <v>27.54</v>
       </c>
       <c r="G9" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -11916,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.93</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -11972,7 +12103,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F10" t="n">
         <v>18.99</v>
@@ -11995,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.86</v>
+        <v>3.16</v>
       </c>
       <c r="M10" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12051,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1355</v>
+        <v>1335</v>
       </c>
       <c r="F11" t="n">
-        <v>29.77</v>
+        <v>30.21</v>
       </c>
       <c r="G11" t="n">
-        <v>5.35</v>
+        <v>5.43</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12074,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.37</v>
+        <v>-1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12130,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F12" t="n">
-        <v>22.76</v>
+        <v>24.83</v>
       </c>
       <c r="G12" t="n">
-        <v>4.17</v>
+        <v>4.55</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12153,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.82</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12213,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>211.5</v>
+        <v>222</v>
       </c>
       <c r="F13" t="n">
-        <v>29.63</v>
+        <v>30.96</v>
       </c>
       <c r="G13" t="n">
-        <v>5.19</v>
+        <v>5.42</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12239,7 +12370,7 @@
         <v>4.96</v>
       </c>
       <c r="M13" t="n">
-        <v>201.5</v>
+        <v>211.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12296,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>142</v>
+        <v>141.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.43</v>
+        <v>28.63</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12319,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.7</v>
+        <v>-0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12375,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F15" t="n">
-        <v>20.33</v>
+        <v>20.37</v>
       </c>
       <c r="G15" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12398,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="M15" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12458,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4420</v>
+        <v>4845</v>
       </c>
       <c r="F16" t="n">
-        <v>132.97</v>
+        <v>146.21</v>
       </c>
       <c r="G16" t="n">
-        <v>40.61</v>
+        <v>44.66</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12480,8 +12611,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4420</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
@@ -12668,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="F2" t="n">
-        <v>66.73999999999999</v>
+        <v>79.28</v>
       </c>
       <c r="G2" t="n">
-        <v>15.7</v>
+        <v>18.64</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12691,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.25</v>
+        <v>2.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1810</v>
+        <v>1905</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12747,7 +12882,7 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="F3" t="n">
         <v>20.29</v>
@@ -12770,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.31</v>
+        <v>4.55</v>
       </c>
       <c r="M3" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12830,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3320</v>
+        <v>3430</v>
       </c>
       <c r="F4" t="n">
-        <v>94.19</v>
+        <v>109.68</v>
       </c>
       <c r="G4" t="n">
-        <v>23.59</v>
+        <v>27.47</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12853,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-2.5</v>
+        <v>3.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3405</v>
+        <v>3320</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -12909,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5450</v>
+        <v>5390</v>
       </c>
       <c r="F5" t="n">
-        <v>113.99</v>
+        <v>121.48</v>
       </c>
       <c r="G5" t="n">
-        <v>39.28</v>
+        <v>41.85</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -12932,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.71</v>
+        <v>-1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>5255</v>
+        <v>5450</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -12988,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="F6" t="n">
-        <v>53.61</v>
+        <v>57.25</v>
       </c>
       <c r="G6" t="n">
-        <v>29.91</v>
+        <v>31.94</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13011,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.38</v>
+        <v>-0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13071,7 +13206,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="F7" t="n">
         <v>12.24</v>
@@ -13094,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13150,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F8" t="n">
-        <v>14.35</v>
+        <v>15.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13173,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.58</v>
+        <v>2.13</v>
       </c>
       <c r="M8" t="n">
-        <v>181.5</v>
+        <v>188</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13233,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.56</v>
+        <v>17.26</v>
       </c>
       <c r="G9" t="n">
-        <v>3.27</v>
+        <v>3.63</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13256,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13312,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F10" t="n">
-        <v>21.21</v>
+        <v>22.82</v>
       </c>
       <c r="G10" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13335,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-6.14</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>700</v>
+        <v>657</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13395,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>237.5</v>
+        <v>239.5</v>
       </c>
       <c r="F11" t="n">
-        <v>34.8</v>
+        <v>35.99</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13418,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>0.84</v>
       </c>
       <c r="M11" t="n">
-        <v>233.5</v>
+        <v>237.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13478,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3985</v>
+        <v>4180</v>
       </c>
       <c r="F12" t="n">
-        <v>56.72</v>
+        <v>64.19</v>
       </c>
       <c r="G12" t="n">
-        <v>7.31</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13501,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.97</v>
+        <v>4.89</v>
       </c>
       <c r="M12" t="n">
-        <v>3870</v>
+        <v>3985</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="F2" t="n">
-        <v>113.41</v>
+        <v>110.91</v>
       </c>
       <c r="G2" t="n">
-        <v>31.84</v>
+        <v>31.14</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.08</v>
+        <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1475</v>
+        <v>1550</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -639,10 +639,10 @@
         <v>39.75</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12</v>
+        <v>11.23</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.35</v>
+        <v>39.75</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="F4" t="n">
-        <v>16.53</v>
+        <v>16.42</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>140.5</v>
+        <v>141.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6090</v>
+        <v>6695</v>
       </c>
       <c r="F5" t="n">
-        <v>161.34</v>
+        <v>162.14</v>
       </c>
       <c r="G5" t="n">
-        <v>37.69</v>
+        <v>37.87</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>9.93</v>
       </c>
       <c r="M5" t="n">
-        <v>6060</v>
+        <v>6090</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>116.5</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>24.14</v>
+        <v>23.94</v>
       </c>
       <c r="G6" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>118</v>
+        <v>116.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>125.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.42</v>
+        <v>36.59</v>
       </c>
       <c r="G7" t="n">
-        <v>5.03</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.36</v>
+        <v>2.03</v>
       </c>
       <c r="M7" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>185.5</v>
+        <v>204</v>
       </c>
       <c r="F8" t="n">
-        <v>25.95</v>
+        <v>31.15</v>
       </c>
       <c r="G8" t="n">
-        <v>5.03</v>
+        <v>6.04</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.85</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>185.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>103.5</v>
       </c>
       <c r="F9" t="n">
-        <v>27.54</v>
+        <v>26.27</v>
       </c>
       <c r="G9" t="n">
-        <v>4.08</v>
+        <v>3.89</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>163</v>
+        <v>158.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.99</v>
+        <v>19.59</v>
       </c>
       <c r="G10" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.16</v>
+        <v>-2.76</v>
       </c>
       <c r="M10" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1335</v>
+        <v>1375</v>
       </c>
       <c r="F11" t="n">
-        <v>30.21</v>
+        <v>30.1</v>
       </c>
       <c r="G11" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.48</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1355</v>
+        <v>1335</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
-        <v>24.83</v>
+        <v>23.31</v>
       </c>
       <c r="G12" t="n">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.19</v>
+        <v>-0.59</v>
       </c>
       <c r="M12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>222</v>
+        <v>219.5</v>
       </c>
       <c r="F13" t="n">
-        <v>30.96</v>
+        <v>32.28</v>
       </c>
       <c r="G13" t="n">
-        <v>5.42</v>
+        <v>5.65</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.96</v>
+        <v>-1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>211.5</v>
+        <v>222</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1528,10 +1528,10 @@
         <v>141.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.63</v>
+        <v>28.13</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>142</v>
+        <v>141.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>223</v>
+        <v>223.5</v>
       </c>
       <c r="F15" t="n">
         <v>20.37</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.45</v>
+        <v>0.22</v>
       </c>
       <c r="M15" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4845</v>
+        <v>5045</v>
       </c>
       <c r="F16" t="n">
-        <v>146.21</v>
+        <v>151.77</v>
       </c>
       <c r="G16" t="n">
-        <v>44.66</v>
+        <v>46.36</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="M16" t="n">
-        <v>4420</v>
+        <v>4845</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1640</v>
+        <v>1575</v>
       </c>
       <c r="F17" t="n">
-        <v>73.37</v>
+        <v>59.41</v>
       </c>
       <c r="G17" t="n">
-        <v>21.49</v>
+        <v>17.4</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>-3.96</v>
       </c>
       <c r="M17" t="n">
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7360</v>
+        <v>7655</v>
       </c>
       <c r="F18" t="n">
-        <v>60.51</v>
+        <v>67.47</v>
       </c>
       <c r="G18" t="n">
-        <v>20.75</v>
+        <v>23.14</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.52</v>
+        <v>4.01</v>
       </c>
       <c r="M18" t="n">
-        <v>7110</v>
+        <v>7360</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F19" t="n">
-        <v>69.03</v>
+        <v>75.25</v>
       </c>
       <c r="G19" t="n">
-        <v>12.66</v>
+        <v>13.79</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>0.13</v>
       </c>
       <c r="M19" t="n">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>95.7</v>
+        <v>91.3</v>
       </c>
       <c r="F20" t="n">
-        <v>65.06999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>7.72</v>
+        <v>8.23</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.57</v>
+        <v>-4.6</v>
       </c>
       <c r="M20" t="n">
-        <v>89.8</v>
+        <v>95.7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>8085</v>
+        <v>8890</v>
       </c>
       <c r="F21" t="n">
-        <v>193.65</v>
+        <v>182.17</v>
       </c>
       <c r="G21" t="n">
-        <v>52.42</v>
+        <v>49.31</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.87</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>8015</v>
+        <v>8085</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2160</v>
+        <v>2270</v>
       </c>
       <c r="F22" t="n">
-        <v>72.84999999999999</v>
+        <v>71.59</v>
       </c>
       <c r="G22" t="n">
-        <v>35.28</v>
+        <v>34.67</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.85</v>
+        <v>5.09</v>
       </c>
       <c r="M22" t="n">
-        <v>2080</v>
+        <v>2160</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>453.5</v>
+        <v>425</v>
       </c>
       <c r="F23" t="n">
-        <v>46.47</v>
+        <v>49.13</v>
       </c>
       <c r="G23" t="n">
-        <v>6.89</v>
+        <v>7.28</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>9.94</v>
+        <v>-6.28</v>
       </c>
       <c r="M23" t="n">
-        <v>412.5</v>
+        <v>453.5</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2317,13 +2317,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1680</v>
+        <v>1690</v>
       </c>
       <c r="F24" t="n">
-        <v>112.36</v>
+        <v>121.39</v>
       </c>
       <c r="G24" t="n">
-        <v>24.86</v>
+        <v>26.86</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8.039999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="M24" t="n">
-        <v>1555</v>
+        <v>1680</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>77</v>
       </c>
       <c r="E25" t="n">
-        <v>170.5</v>
+        <v>173</v>
       </c>
       <c r="F25" t="n">
-        <v>39.28</v>
+        <v>35.67</v>
       </c>
       <c r="G25" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
-        <v>168</v>
+        <v>170.5</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>75</v>
       </c>
       <c r="E26" t="n">
-        <v>38.5</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>124.63</v>
+        <v>140.74</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.5</v>
+        <v>-1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>36.15</v>
+        <v>38.5</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2560,13 +2560,13 @@
         <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>2020</v>
+        <v>1980</v>
       </c>
       <c r="F27" t="n">
-        <v>267.41</v>
+        <v>265.44</v>
       </c>
       <c r="G27" t="n">
-        <v>44.41</v>
+        <v>44.09</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-0.74</v>
+        <v>-1.98</v>
       </c>
       <c r="M27" t="n">
-        <v>2035</v>
+        <v>2020</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>68</v>
       </c>
       <c r="E28" t="n">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="F28" t="n">
-        <v>56.92</v>
+        <v>65.27</v>
       </c>
       <c r="G28" t="n">
-        <v>7.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.449999999999999</v>
+        <v>3.38</v>
       </c>
       <c r="M28" t="n">
-        <v>627</v>
+        <v>680</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2720,13 +2720,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>1340</v>
+        <v>1360</v>
       </c>
       <c r="F29" t="n">
-        <v>66.45999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="G29" t="n">
-        <v>11.44</v>
+        <v>14.68</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.51</v>
+        <v>1.49</v>
       </c>
       <c r="M29" t="n">
-        <v>1270</v>
+        <v>1340</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2799,13 +2799,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>474</v>
+        <v>450.5</v>
       </c>
       <c r="F30" t="n">
-        <v>82.55</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>15.73</v>
+        <v>16.33</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.83</v>
+        <v>-4.96</v>
       </c>
       <c r="M30" t="n">
-        <v>456.5</v>
+        <v>474</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>66</v>
       </c>
       <c r="E31" t="n">
-        <v>3035</v>
+        <v>3285</v>
       </c>
       <c r="F31" t="n">
         <v>89.03</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8.24</v>
       </c>
       <c r="M31" t="n">
         <v>3035</v>
@@ -2961,13 +2961,13 @@
         <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="F32" t="n">
-        <v>168.15</v>
+        <v>152.38</v>
       </c>
       <c r="G32" t="n">
-        <v>15.78</v>
+        <v>14.3</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.35</v>
+        <v>-3.76</v>
       </c>
       <c r="M32" t="n">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3040,13 +3040,13 @@
         <v>63</v>
       </c>
       <c r="E33" t="n">
-        <v>259.5</v>
+        <v>249</v>
       </c>
       <c r="F33" t="n">
-        <v>40.41</v>
+        <v>36.73</v>
       </c>
       <c r="G33" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>9.960000000000001</v>
+        <v>-4.05</v>
       </c>
       <c r="M33" t="n">
-        <v>236</v>
+        <v>259.5</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
@@ -3117,13 +3117,13 @@
         <v>62</v>
       </c>
       <c r="E34" t="n">
-        <v>452.5</v>
+        <v>421</v>
       </c>
       <c r="F34" t="n">
-        <v>41.14</v>
+        <v>37.69</v>
       </c>
       <c r="G34" t="n">
-        <v>7.38</v>
+        <v>6.76</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.11</v>
+        <v>-6.96</v>
       </c>
       <c r="M34" t="n">
-        <v>453</v>
+        <v>452.5</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="F35" t="n">
-        <v>38.32</v>
+        <v>39.02</v>
       </c>
       <c r="G35" t="n">
-        <v>8.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.13</v>
+        <v>2.24</v>
       </c>
       <c r="M35" t="n">
-        <v>472.5</v>
+        <v>492</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
@@ -3276,10 +3276,10 @@
         <v>1140</v>
       </c>
       <c r="F36" t="n">
-        <v>85.04000000000001</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>13.31</v>
+        <v>14.05</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3354,13 +3354,13 @@
         <v>56</v>
       </c>
       <c r="E37" t="n">
-        <v>207.5</v>
+        <v>190</v>
       </c>
       <c r="F37" t="n">
-        <v>64.84</v>
+        <v>56.38</v>
       </c>
       <c r="G37" t="n">
-        <v>8.43</v>
+        <v>7.33</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>-8.43</v>
       </c>
       <c r="M37" t="n">
-        <v>203</v>
+        <v>207.5</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3433,13 +3433,13 @@
         <v>44</v>
       </c>
       <c r="E38" t="n">
-        <v>4245</v>
+        <v>4335</v>
       </c>
       <c r="F38" t="n">
-        <v>69.95999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="G38" t="n">
-        <v>17.95</v>
+        <v>17.73</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>8.57</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>3910</v>
+        <v>4245</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3514,13 +3514,13 @@
         <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="F39" t="n">
-        <v>79.28</v>
+        <v>73.38</v>
       </c>
       <c r="G39" t="n">
-        <v>18.64</v>
+        <v>17.26</v>
       </c>
       <c r="H39" t="n">
         <v>59.1</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="M39" t="n">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3593,13 +3593,13 @@
         <v>92</v>
       </c>
       <c r="E40" t="n">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="F40" t="n">
-        <v>20.29</v>
+        <v>21.21</v>
       </c>
       <c r="G40" t="n">
-        <v>10.64</v>
+        <v>11.12</v>
       </c>
       <c r="H40" t="n">
         <v>19</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.55</v>
+        <v>2.25</v>
       </c>
       <c r="M40" t="n">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3676,13 +3676,13 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>3430</v>
+        <v>3400</v>
       </c>
       <c r="F41" t="n">
-        <v>109.68</v>
+        <v>94.05</v>
       </c>
       <c r="G41" t="n">
-        <v>27.47</v>
+        <v>23.55</v>
       </c>
       <c r="H41" t="n">
         <v>70.2</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.31</v>
+        <v>-0.87</v>
       </c>
       <c r="M41" t="n">
-        <v>3320</v>
+        <v>3430</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3755,13 +3755,13 @@
         <v>90</v>
       </c>
       <c r="E42" t="n">
-        <v>5390</v>
+        <v>5535</v>
       </c>
       <c r="F42" t="n">
-        <v>121.48</v>
+        <v>120.07</v>
       </c>
       <c r="G42" t="n">
-        <v>41.85</v>
+        <v>41.37</v>
       </c>
       <c r="H42" t="n">
         <v>75.3</v>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-1.1</v>
+        <v>2.69</v>
       </c>
       <c r="M42" t="n">
-        <v>5450</v>
+        <v>5390</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3834,13 +3834,13 @@
         <v>89</v>
       </c>
       <c r="E43" t="n">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="F43" t="n">
-        <v>57.25</v>
+        <v>52.03</v>
       </c>
       <c r="G43" t="n">
-        <v>31.94</v>
+        <v>29.03</v>
       </c>
       <c r="H43" t="n">
         <v>47.5</v>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-0.89</v>
+        <v>-2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3917,13 +3917,13 @@
         <v>80</v>
       </c>
       <c r="E44" t="n">
-        <v>104.5</v>
+        <v>103</v>
       </c>
       <c r="F44" t="n">
-        <v>12.24</v>
+        <v>12.29</v>
       </c>
       <c r="G44" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H44" t="n">
         <v>11</v>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.48</v>
+        <v>-1.44</v>
       </c>
       <c r="M44" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3996,13 +3996,13 @@
         <v>78</v>
       </c>
       <c r="E45" t="n">
-        <v>192</v>
+        <v>193.5</v>
       </c>
       <c r="F45" t="n">
-        <v>15.14</v>
+        <v>15.3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="H45" t="n">
         <v>13.4</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.13</v>
+        <v>0.78</v>
       </c>
       <c r="M45" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4079,13 +4079,13 @@
         <v>70</v>
       </c>
       <c r="E46" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="F46" t="n">
-        <v>17.26</v>
+        <v>15.49</v>
       </c>
       <c r="G46" t="n">
-        <v>3.63</v>
+        <v>3.26</v>
       </c>
       <c r="H46" t="n">
         <v>16</v>
@@ -4105,7 +4105,7 @@
         <v>-0.47</v>
       </c>
       <c r="M46" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -4158,13 +4158,13 @@
         <v>69</v>
       </c>
       <c r="E47" t="n">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="F47" t="n">
-        <v>22.82</v>
+        <v>19.42</v>
       </c>
       <c r="G47" t="n">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="H47" t="n">
         <v>21.4</v>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.3</v>
+        <v>-2.73</v>
       </c>
       <c r="M47" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4241,13 +4241,13 @@
         <v>65</v>
       </c>
       <c r="E48" t="n">
-        <v>239.5</v>
+        <v>238.5</v>
       </c>
       <c r="F48" t="n">
-        <v>35.99</v>
+        <v>35.54</v>
       </c>
       <c r="G48" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="H48" t="n">
         <v>30.9</v>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="M48" t="n">
-        <v>237.5</v>
+        <v>239.5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4324,13 +4324,13 @@
         <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>4180</v>
+        <v>4450</v>
       </c>
       <c r="F49" t="n">
-        <v>64.19</v>
+        <v>65.22</v>
       </c>
       <c r="G49" t="n">
-        <v>8.279999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="H49" t="n">
         <v>51.7</v>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.89</v>
+        <v>6.46</v>
       </c>
       <c r="M49" t="n">
-        <v>3985</v>
+        <v>4180</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
@@ -4407,13 +4407,13 @@
         <v>96</v>
       </c>
       <c r="E50" t="n">
-        <v>430.5</v>
+        <v>443.5</v>
       </c>
       <c r="F50" t="n">
-        <v>22.85</v>
+        <v>23.28</v>
       </c>
       <c r="G50" t="n">
-        <v>6.76</v>
+        <v>6.89</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.89</v>
+        <v>3.02</v>
       </c>
       <c r="M50" t="n">
-        <v>422.5</v>
+        <v>430.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4487,10 +4487,10 @@
         <v>177</v>
       </c>
       <c r="F51" t="n">
-        <v>21.45</v>
+        <v>21.51</v>
       </c>
       <c r="G51" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4561,13 +4561,13 @@
         <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>130</v>
+        <v>128.5</v>
       </c>
       <c r="F52" t="n">
-        <v>28.6</v>
+        <v>29.41</v>
       </c>
       <c r="G52" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.77</v>
+        <v>-1.15</v>
       </c>
       <c r="M52" t="n">
-        <v>126.5</v>
+        <v>130</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4638,13 +4638,13 @@
         <v>78</v>
       </c>
       <c r="E53" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F53" t="n">
-        <v>22.48</v>
+        <v>20.53</v>
       </c>
       <c r="G53" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.51</v>
+        <v>-1.96</v>
       </c>
       <c r="M53" t="n">
-        <v>99.5</v>
+        <v>102</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4719,13 +4719,13 @@
         <v>76</v>
       </c>
       <c r="E54" t="n">
-        <v>252</v>
+        <v>243.5</v>
       </c>
       <c r="F54" t="n">
-        <v>31.3</v>
+        <v>28.22</v>
       </c>
       <c r="G54" t="n">
-        <v>7.62</v>
+        <v>6.87</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-9.84</v>
+        <v>-3.37</v>
       </c>
       <c r="M54" t="n">
-        <v>279.5</v>
+        <v>252</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4796,13 +4796,13 @@
         <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>238</v>
+        <v>230.5</v>
       </c>
       <c r="F55" t="n">
-        <v>21.21</v>
+        <v>21.62</v>
       </c>
       <c r="G55" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.93</v>
+        <v>-3.15</v>
       </c>
       <c r="M55" t="n">
-        <v>233.5</v>
+        <v>238</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         <v>61</v>
       </c>
       <c r="E56" t="n">
-        <v>806</v>
+        <v>829</v>
       </c>
       <c r="F56" t="n">
-        <v>29.48</v>
+        <v>29.84</v>
       </c>
       <c r="G56" t="n">
-        <v>9.34</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4954,13 +4954,13 @@
         <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>149.5</v>
+        <v>143.5</v>
       </c>
       <c r="F57" t="n">
-        <v>31.91</v>
+        <v>33.6</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5.28</v>
+        <v>-4.01</v>
       </c>
       <c r="M57" t="n">
-        <v>142</v>
+        <v>149.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5035,13 +5035,13 @@
         <v>51</v>
       </c>
       <c r="E58" t="n">
-        <v>4290</v>
+        <v>4330</v>
       </c>
       <c r="F58" t="n">
-        <v>32.43</v>
+        <v>27.03</v>
       </c>
       <c r="G58" t="n">
-        <v>3.68</v>
+        <v>3.07</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-2.05</v>
+        <v>0.93</v>
       </c>
       <c r="M58" t="n">
-        <v>4380</v>
+        <v>4290</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5116,13 +5116,13 @@
         <v>32</v>
       </c>
       <c r="E59" t="n">
-        <v>50.2</v>
+        <v>53.2</v>
       </c>
       <c r="F59" t="n">
-        <v>20.87</v>
+        <v>20.23</v>
       </c>
       <c r="G59" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.93</v>
+        <v>5.98</v>
       </c>
       <c r="M59" t="n">
-        <v>49.25</v>
+        <v>50.2</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5197,13 +5197,13 @@
         <v>97</v>
       </c>
       <c r="E60" t="n">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="F60" t="n">
-        <v>36.11</v>
+        <v>36.37</v>
       </c>
       <c r="G60" t="n">
-        <v>7.15</v>
+        <v>7.2</v>
       </c>
       <c r="H60" t="n">
         <v>29.3</v>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.14</v>
+        <v>3.07</v>
       </c>
       <c r="M60" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
@@ -5276,13 +5276,13 @@
         <v>91</v>
       </c>
       <c r="E61" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F61" t="n">
-        <v>60.27</v>
+        <v>61.36</v>
       </c>
       <c r="G61" t="n">
-        <v>9.35</v>
+        <v>9.52</v>
       </c>
       <c r="H61" t="n">
         <v>46.1</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.99</v>
+        <v>0.11</v>
       </c>
       <c r="M61" t="n">
-        <v>861</v>
+        <v>904</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -5355,13 +5355,13 @@
         <v>79</v>
       </c>
       <c r="E62" t="n">
-        <v>76.3</v>
+        <v>74.3</v>
       </c>
       <c r="F62" t="n">
-        <v>19.36</v>
+        <v>18.21</v>
       </c>
       <c r="G62" t="n">
-        <v>3.31</v>
+        <v>3.11</v>
       </c>
       <c r="H62" t="n">
         <v>17.3</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-0.78</v>
+        <v>-2.62</v>
       </c>
       <c r="M62" t="n">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
@@ -5434,13 +5434,13 @@
         <v>77</v>
       </c>
       <c r="E63" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F63" t="n">
-        <v>15.11</v>
+        <v>15.25</v>
       </c>
       <c r="G63" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H63" t="n">
         <v>15.5</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.93</v>
+        <v>-0.62</v>
       </c>
       <c r="M63" t="n">
-        <v>160.5</v>
+        <v>162</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
@@ -5513,13 +5513,13 @@
         <v>78</v>
       </c>
       <c r="E64" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F64" t="n">
-        <v>18.01</v>
+        <v>18.29</v>
       </c>
       <c r="G64" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.26</v>
+        <v>-0.44</v>
       </c>
       <c r="M64" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>75</v>
       </c>
       <c r="E65" t="n">
-        <v>46.35</v>
+        <v>45.55</v>
       </c>
       <c r="F65" t="n">
-        <v>14.53</v>
+        <v>14.9</v>
       </c>
       <c r="G65" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.54</v>
+        <v>-1.73</v>
       </c>
       <c r="M65" t="n">
-        <v>45.2</v>
+        <v>46.35</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>66</v>
       </c>
       <c r="E66" t="n">
-        <v>789</v>
+        <v>819</v>
       </c>
       <c r="F66" t="n">
-        <v>19.05</v>
+        <v>19.54</v>
       </c>
       <c r="G66" t="n">
-        <v>18</v>
+        <v>18.47</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="M66" t="n">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>159.5</v>
+        <v>155.5</v>
       </c>
       <c r="F67" t="n">
-        <v>16.43</v>
+        <v>17.3</v>
       </c>
       <c r="G67" t="n">
-        <v>4.84</v>
+        <v>5.09</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.28</v>
+        <v>-2.51</v>
       </c>
       <c r="M67" t="n">
-        <v>151.5</v>
+        <v>159.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="F68" t="n">
-        <v>20.17</v>
+        <v>22.61</v>
       </c>
       <c r="G68" t="n">
-        <v>4.79</v>
+        <v>5.37</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.86</v>
+        <v>-2.91</v>
       </c>
       <c r="M68" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>120.5</v>
+        <v>121</v>
       </c>
       <c r="F69" t="n">
-        <v>17.17</v>
+        <v>17.31</v>
       </c>
       <c r="G69" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="M69" t="n">
-        <v>119.5</v>
+        <v>120.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F70" t="n">
-        <v>33.9</v>
+        <v>33.95</v>
       </c>
       <c r="G70" t="n">
-        <v>9.289999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.6</v>
+        <v>-0.57</v>
       </c>
       <c r="M70" t="n">
-        <v>344.5</v>
+        <v>350</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>91.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>19.16</v>
+        <v>19.26</v>
       </c>
       <c r="G71" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.55</v>
+        <v>1.31</v>
       </c>
       <c r="M71" t="n">
-        <v>91.2</v>
+        <v>91.7</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>148</v>
+        <v>148.5</v>
       </c>
       <c r="F72" t="n">
-        <v>19.51</v>
+        <v>20.19</v>
       </c>
       <c r="G72" t="n">
-        <v>5.33</v>
+        <v>5.51</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.5</v>
+        <v>0.34</v>
       </c>
       <c r="M72" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F73" t="n">
-        <v>19.07</v>
+        <v>17.61</v>
       </c>
       <c r="G73" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.83</v>
+        <v>-1.2</v>
       </c>
       <c r="M73" t="n">
-        <v>246.5</v>
+        <v>251</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1040</v>
+        <v>1095</v>
       </c>
       <c r="F74" t="n">
-        <v>52.17</v>
+        <v>54.48</v>
       </c>
       <c r="G74" t="n">
-        <v>27.16</v>
+        <v>28.36</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>4.42</v>
+        <v>5.29</v>
       </c>
       <c r="M74" t="n">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>25.74</v>
+        <v>25.44</v>
       </c>
       <c r="G75" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.58</v>
+        <v>0.45</v>
       </c>
       <c r="M75" t="n">
-        <v>64.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2525</v>
+        <v>2620</v>
       </c>
       <c r="F76" t="n">
-        <v>39.43</v>
+        <v>43.05</v>
       </c>
       <c r="G76" t="n">
-        <v>20.86</v>
+        <v>22.77</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>9.779999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="M76" t="n">
-        <v>2300</v>
+        <v>2525</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="F77" t="n">
-        <v>22.84</v>
+        <v>25.31</v>
       </c>
       <c r="G77" t="n">
-        <v>8.859999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-3.35</v>
+        <v>-1.19</v>
       </c>
       <c r="M77" t="n">
-        <v>955</v>
+        <v>923</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2410</v>
+        <v>2505</v>
       </c>
       <c r="F78" t="n">
-        <v>32.4</v>
+        <v>33.68</v>
       </c>
       <c r="G78" t="n">
-        <v>10.61</v>
+        <v>11.03</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.69</v>
+        <v>3.94</v>
       </c>
       <c r="M78" t="n">
-        <v>2370</v>
+        <v>2410</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="F79" t="n">
-        <v>14.93</v>
+        <v>14.59</v>
       </c>
       <c r="G79" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.67</v>
+        <v>-0.8</v>
       </c>
       <c r="M79" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F80" t="n">
-        <v>15.49</v>
+        <v>16.24</v>
       </c>
       <c r="G80" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="M80" t="n">
-        <v>114.5</v>
+        <v>120</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6875,7 +6875,7 @@
         <v>34.5</v>
       </c>
       <c r="F81" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="G81" t="n">
         <v>1.34</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="F82" t="n">
-        <v>12.39</v>
+        <v>12.28</v>
       </c>
       <c r="G82" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1.73</v>
+        <v>0.44</v>
       </c>
       <c r="M82" t="n">
-        <v>115.5</v>
+        <v>113.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.88</v>
+        <v>13.99</v>
       </c>
       <c r="G83" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-0.79</v>
+        <v>0.53</v>
       </c>
       <c r="M83" t="n">
-        <v>189</v>
+        <v>187.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>44.9</v>
+        <v>43.9</v>
       </c>
       <c r="F84" t="n">
-        <v>8.07</v>
+        <v>8.33</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.28</v>
+        <v>-2.23</v>
       </c>
       <c r="M84" t="n">
-        <v>43.9</v>
+        <v>44.9</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="F85" t="n">
-        <v>40.47</v>
+        <v>38.39</v>
       </c>
       <c r="G85" t="n">
-        <v>13.56</v>
+        <v>12.87</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>5.76</v>
+        <v>0.78</v>
       </c>
       <c r="M85" t="n">
-        <v>1215</v>
+        <v>1285</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="F86" t="n">
-        <v>27.84</v>
+        <v>24.59</v>
       </c>
       <c r="G86" t="n">
-        <v>5.17</v>
+        <v>4.56</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.7</v>
+        <v>-2.32</v>
       </c>
       <c r="M86" t="n">
-        <v>499.5</v>
+        <v>518</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F87" t="n">
-        <v>17.7</v>
+        <v>17.83</v>
       </c>
       <c r="G87" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="M87" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>41.15</v>
+        <v>40.75</v>
       </c>
       <c r="F88" t="n">
-        <v>9.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.48</v>
+        <v>-0.97</v>
       </c>
       <c r="M88" t="n">
-        <v>40.55</v>
+        <v>41.15</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2495</v>
+        <v>2660</v>
       </c>
       <c r="F89" t="n">
-        <v>46.05</v>
+        <v>50.3</v>
       </c>
       <c r="G89" t="n">
-        <v>20.84</v>
+        <v>22.76</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>6.62</v>
+        <v>6.61</v>
       </c>
       <c r="M89" t="n">
-        <v>2340</v>
+        <v>2495</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7590,10 +7590,10 @@
         <v>1010</v>
       </c>
       <c r="F90" t="n">
-        <v>28.72</v>
+        <v>29.15</v>
       </c>
       <c r="G90" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>91.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>11.24</v>
+        <v>10.68</v>
       </c>
       <c r="G91" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-1.51</v>
+        <v>-2.73</v>
       </c>
       <c r="M91" t="n">
-        <v>93</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>71.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="G92" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.28</v>
+        <v>2.36</v>
       </c>
       <c r="M92" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F93" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="G93" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.14</v>
+        <v>-0.3</v>
       </c>
       <c r="M93" t="n">
-        <v>65.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F94" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="G94" t="n">
-        <v>6.98</v>
+        <v>6.91</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.27</v>
+        <v>1.09</v>
       </c>
       <c r="M94" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>4635</v>
+        <v>5035</v>
       </c>
       <c r="F95" t="n">
-        <v>17.2</v>
+        <v>16.88</v>
       </c>
       <c r="G95" t="n">
-        <v>6.8</v>
+        <v>6.68</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.2</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M95" t="n">
-        <v>4580</v>
+        <v>4635</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>158.5</v>
+        <v>159.5</v>
       </c>
       <c r="F96" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.59</v>
+        <v>0.63</v>
       </c>
       <c r="M96" t="n">
-        <v>154.5</v>
+        <v>158.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8171,10 +8171,10 @@
         <v>1470</v>
       </c>
       <c r="F97" t="n">
-        <v>17.85</v>
+        <v>18.04</v>
       </c>
       <c r="G97" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
       <c r="G98" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="M98" t="n">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>409</v>
+        <v>398.5</v>
       </c>
       <c r="F99" t="n">
-        <v>8.07</v>
+        <v>8.17</v>
       </c>
       <c r="G99" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.24</v>
+        <v>-2.57</v>
       </c>
       <c r="M99" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.95</v>
+        <v>24.3</v>
       </c>
       <c r="F100" t="n">
         <v>3.97</v>
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M100" t="n">
         <v>23.95</v>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>194.5</v>
+        <v>180</v>
       </c>
       <c r="F101" t="n">
-        <v>10.28</v>
+        <v>8.77</v>
       </c>
       <c r="G101" t="n">
-        <v>4.28</v>
+        <v>3.65</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.52</v>
+        <v>-7.46</v>
       </c>
       <c r="M101" t="n">
-        <v>193.5</v>
+        <v>194.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2525</v>
+        <v>2620</v>
       </c>
       <c r="F2" t="n">
-        <v>39.43</v>
+        <v>43.05</v>
       </c>
       <c r="G2" t="n">
-        <v>20.86</v>
+        <v>22.77</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.779999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="M2" t="n">
-        <v>2300</v>
+        <v>2525</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="F3" t="n">
-        <v>22.84</v>
+        <v>25.31</v>
       </c>
       <c r="G3" t="n">
-        <v>8.859999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-3.35</v>
+        <v>-1.19</v>
       </c>
       <c r="M3" t="n">
-        <v>955</v>
+        <v>923</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2410</v>
+        <v>2505</v>
       </c>
       <c r="F4" t="n">
-        <v>32.4</v>
+        <v>33.68</v>
       </c>
       <c r="G4" t="n">
-        <v>10.61</v>
+        <v>11.03</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.69</v>
+        <v>3.94</v>
       </c>
       <c r="M4" t="n">
-        <v>2370</v>
+        <v>2410</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="F5" t="n">
-        <v>14.93</v>
+        <v>14.59</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.67</v>
+        <v>-0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F6" t="n">
-        <v>15.49</v>
+        <v>16.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>114.5</v>
+        <v>120</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9100,7 +9100,7 @@
         <v>34.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="G7" t="n">
         <v>1.34</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="F8" t="n">
-        <v>12.39</v>
+        <v>12.28</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.73</v>
+        <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>115.5</v>
+        <v>113.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.88</v>
+        <v>13.99</v>
       </c>
       <c r="G9" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.79</v>
+        <v>0.53</v>
       </c>
       <c r="M9" t="n">
-        <v>189</v>
+        <v>187.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>44.9</v>
+        <v>43.9</v>
       </c>
       <c r="F10" t="n">
-        <v>8.07</v>
+        <v>8.33</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.28</v>
+        <v>-2.23</v>
       </c>
       <c r="M10" t="n">
-        <v>43.9</v>
+        <v>44.9</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="F11" t="n">
-        <v>40.47</v>
+        <v>38.39</v>
       </c>
       <c r="G11" t="n">
-        <v>13.56</v>
+        <v>12.87</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.76</v>
+        <v>0.78</v>
       </c>
       <c r="M11" t="n">
-        <v>1215</v>
+        <v>1285</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="F12" t="n">
-        <v>27.84</v>
+        <v>24.59</v>
       </c>
       <c r="G12" t="n">
-        <v>5.17</v>
+        <v>4.56</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.7</v>
+        <v>-2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>499.5</v>
+        <v>518</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
-        <v>17.7</v>
+        <v>17.83</v>
       </c>
       <c r="G13" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="M13" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>41.15</v>
+        <v>40.75</v>
       </c>
       <c r="F14" t="n">
-        <v>9.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>-0.97</v>
       </c>
       <c r="M14" t="n">
-        <v>40.55</v>
+        <v>41.15</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2495</v>
+        <v>2660</v>
       </c>
       <c r="F15" t="n">
-        <v>46.05</v>
+        <v>50.3</v>
       </c>
       <c r="G15" t="n">
-        <v>20.84</v>
+        <v>22.76</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.62</v>
+        <v>6.61</v>
       </c>
       <c r="M15" t="n">
-        <v>2340</v>
+        <v>2495</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9815,10 +9815,10 @@
         <v>1010</v>
       </c>
       <c r="F16" t="n">
-        <v>28.72</v>
+        <v>29.15</v>
       </c>
       <c r="G16" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>91.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>11.24</v>
+        <v>10.68</v>
       </c>
       <c r="G17" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-1.51</v>
+        <v>-2.73</v>
       </c>
       <c r="M17" t="n">
-        <v>93</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>71.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="G18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.28</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F19" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="G19" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>-0.3</v>
       </c>
       <c r="M19" t="n">
-        <v>65.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F20" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="G20" t="n">
-        <v>6.98</v>
+        <v>6.91</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.27</v>
+        <v>1.09</v>
       </c>
       <c r="M20" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>4635</v>
+        <v>5035</v>
       </c>
       <c r="F21" t="n">
-        <v>17.2</v>
+        <v>16.88</v>
       </c>
       <c r="G21" t="n">
-        <v>6.8</v>
+        <v>6.68</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>4580</v>
+        <v>4635</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>158.5</v>
+        <v>159.5</v>
       </c>
       <c r="F22" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.59</v>
+        <v>0.63</v>
       </c>
       <c r="M22" t="n">
-        <v>154.5</v>
+        <v>158.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10396,10 +10396,10 @@
         <v>1470</v>
       </c>
       <c r="F23" t="n">
-        <v>17.85</v>
+        <v>18.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>159.5</v>
+        <v>155.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16.43</v>
+        <v>17.3</v>
       </c>
       <c r="G2" t="n">
-        <v>4.84</v>
+        <v>5.09</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.28</v>
+        <v>-2.51</v>
       </c>
       <c r="M2" t="n">
-        <v>151.5</v>
+        <v>159.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="F3" t="n">
-        <v>20.17</v>
+        <v>22.61</v>
       </c>
       <c r="G3" t="n">
-        <v>4.79</v>
+        <v>5.37</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.86</v>
+        <v>-2.91</v>
       </c>
       <c r="M3" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>120.5</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>17.17</v>
+        <v>17.31</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>119.5</v>
+        <v>120.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F5" t="n">
-        <v>33.9</v>
+        <v>33.95</v>
       </c>
       <c r="G5" t="n">
-        <v>9.289999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>-0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>344.5</v>
+        <v>350</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>19.16</v>
+        <v>19.26</v>
       </c>
       <c r="G6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.55</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>91.2</v>
+        <v>91.7</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>148</v>
+        <v>148.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.51</v>
+        <v>20.19</v>
       </c>
       <c r="G7" t="n">
-        <v>5.33</v>
+        <v>5.51</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F8" t="n">
-        <v>19.07</v>
+        <v>17.61</v>
       </c>
       <c r="G8" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>-1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>246.5</v>
+        <v>251</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1040</v>
+        <v>1095</v>
       </c>
       <c r="F9" t="n">
-        <v>52.17</v>
+        <v>54.48</v>
       </c>
       <c r="G9" t="n">
-        <v>27.16</v>
+        <v>28.36</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.42</v>
+        <v>5.29</v>
       </c>
       <c r="M9" t="n">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>25.74</v>
+        <v>25.44</v>
       </c>
       <c r="G10" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.58</v>
+        <v>0.45</v>
       </c>
       <c r="M10" t="n">
-        <v>64.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="F2" t="n">
-        <v>113.41</v>
+        <v>110.91</v>
       </c>
       <c r="G2" t="n">
-        <v>31.84</v>
+        <v>31.14</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.08</v>
+        <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1475</v>
+        <v>1550</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11541,10 +11541,10 @@
         <v>39.75</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12</v>
+        <v>11.23</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.35</v>
+        <v>39.75</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="F4" t="n">
-        <v>16.53</v>
+        <v>16.42</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>140.5</v>
+        <v>141.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6090</v>
+        <v>6695</v>
       </c>
       <c r="F5" t="n">
-        <v>161.34</v>
+        <v>162.14</v>
       </c>
       <c r="G5" t="n">
-        <v>37.69</v>
+        <v>37.87</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>9.93</v>
       </c>
       <c r="M5" t="n">
-        <v>6060</v>
+        <v>6090</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>116.5</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>24.14</v>
+        <v>23.94</v>
       </c>
       <c r="G6" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>118</v>
+        <v>116.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>125.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.42</v>
+        <v>36.59</v>
       </c>
       <c r="G7" t="n">
-        <v>5.03</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.36</v>
+        <v>2.03</v>
       </c>
       <c r="M7" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>185.5</v>
+        <v>204</v>
       </c>
       <c r="F8" t="n">
-        <v>25.95</v>
+        <v>31.15</v>
       </c>
       <c r="G8" t="n">
-        <v>5.03</v>
+        <v>6.04</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.85</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>185.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>103.5</v>
       </c>
       <c r="F9" t="n">
-        <v>27.54</v>
+        <v>26.27</v>
       </c>
       <c r="G9" t="n">
-        <v>4.08</v>
+        <v>3.89</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>163</v>
+        <v>158.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.99</v>
+        <v>19.59</v>
       </c>
       <c r="G10" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.16</v>
+        <v>-2.76</v>
       </c>
       <c r="M10" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1335</v>
+        <v>1375</v>
       </c>
       <c r="F11" t="n">
-        <v>30.21</v>
+        <v>30.1</v>
       </c>
       <c r="G11" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.48</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1355</v>
+        <v>1335</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
-        <v>24.83</v>
+        <v>23.31</v>
       </c>
       <c r="G12" t="n">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.19</v>
+        <v>-0.59</v>
       </c>
       <c r="M12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>222</v>
+        <v>219.5</v>
       </c>
       <c r="F13" t="n">
-        <v>30.96</v>
+        <v>32.28</v>
       </c>
       <c r="G13" t="n">
-        <v>5.42</v>
+        <v>5.65</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.96</v>
+        <v>-1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>211.5</v>
+        <v>222</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12430,10 +12430,10 @@
         <v>141.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.63</v>
+        <v>28.13</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>142</v>
+        <v>141.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,7 +12506,7 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>223</v>
+        <v>223.5</v>
       </c>
       <c r="F15" t="n">
         <v>20.37</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.45</v>
+        <v>0.22</v>
       </c>
       <c r="M15" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4845</v>
+        <v>5045</v>
       </c>
       <c r="F16" t="n">
-        <v>146.21</v>
+        <v>151.77</v>
       </c>
       <c r="G16" t="n">
-        <v>44.66</v>
+        <v>46.36</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.619999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="M16" t="n">
-        <v>4420</v>
+        <v>4845</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="F2" t="n">
-        <v>79.28</v>
+        <v>73.38</v>
       </c>
       <c r="G2" t="n">
-        <v>18.64</v>
+        <v>17.26</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="F3" t="n">
-        <v>20.29</v>
+        <v>21.21</v>
       </c>
       <c r="G3" t="n">
-        <v>10.64</v>
+        <v>11.12</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.55</v>
+        <v>2.25</v>
       </c>
       <c r="M3" t="n">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3430</v>
+        <v>3400</v>
       </c>
       <c r="F4" t="n">
-        <v>109.68</v>
+        <v>94.05</v>
       </c>
       <c r="G4" t="n">
-        <v>27.47</v>
+        <v>23.55</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.31</v>
+        <v>-0.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3320</v>
+        <v>3430</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5390</v>
+        <v>5535</v>
       </c>
       <c r="F5" t="n">
-        <v>121.48</v>
+        <v>120.07</v>
       </c>
       <c r="G5" t="n">
-        <v>41.85</v>
+        <v>41.37</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.1</v>
+        <v>2.69</v>
       </c>
       <c r="M5" t="n">
-        <v>5450</v>
+        <v>5390</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="F6" t="n">
-        <v>57.25</v>
+        <v>52.03</v>
       </c>
       <c r="G6" t="n">
-        <v>31.94</v>
+        <v>29.03</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.89</v>
+        <v>-2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>104.5</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>12.24</v>
+        <v>12.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.48</v>
+        <v>-1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>192</v>
+        <v>193.5</v>
       </c>
       <c r="F8" t="n">
-        <v>15.14</v>
+        <v>15.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.13</v>
+        <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>17.26</v>
+        <v>15.49</v>
       </c>
       <c r="G9" t="n">
-        <v>3.63</v>
+        <v>3.26</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13394,7 +13394,7 @@
         <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="F10" t="n">
-        <v>22.82</v>
+        <v>19.42</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.3</v>
+        <v>-2.73</v>
       </c>
       <c r="M10" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>239.5</v>
+        <v>238.5</v>
       </c>
       <c r="F11" t="n">
-        <v>35.99</v>
+        <v>35.54</v>
       </c>
       <c r="G11" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>237.5</v>
+        <v>239.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4180</v>
+        <v>4450</v>
       </c>
       <c r="F12" t="n">
-        <v>64.19</v>
+        <v>65.22</v>
       </c>
       <c r="G12" t="n">
-        <v>8.279999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.89</v>
+        <v>6.46</v>
       </c>
       <c r="M12" t="n">
-        <v>3985</v>
+        <v>4180</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1415</v>
+        <v>1380</v>
       </c>
       <c r="F2" t="n">
-        <v>31.12</v>
+        <v>100.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>28.33</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-9</v>
+        <v>-2.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1555</v>
+        <v>1415</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -639,7 +639,7 @@
         <v>39.85</v>
       </c>
       <c r="F3" t="n">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.75</v>
+        <v>39.85</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,7 +715,7 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>146.5</v>
       </c>
       <c r="F4" t="n">
         <v>16.8</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>7255</v>
+        <v>7380</v>
       </c>
       <c r="F5" t="n">
-        <v>178.25</v>
+        <v>193.16</v>
       </c>
       <c r="G5" t="n">
-        <v>41.64</v>
+        <v>45.12</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8.359999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>6695</v>
+        <v>7255</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>118.5</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>19.18</v>
+        <v>24.04</v>
       </c>
       <c r="G6" t="n">
-        <v>5.08</v>
+        <v>3.94</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.42</v>
+        <v>-1.69</v>
       </c>
       <c r="M6" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>121.5</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>35.31</v>
+        <v>35.42</v>
       </c>
       <c r="G7" t="n">
-        <v>0.85</v>
+        <v>5.03</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.19</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>125.5</v>
+        <v>121.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>197</v>
+        <v>216.5</v>
       </c>
       <c r="F8" t="n">
-        <v>31.15</v>
+        <v>30.08</v>
       </c>
       <c r="G8" t="n">
-        <v>6.04</v>
+        <v>5.83</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.43</v>
+        <v>9.9</v>
       </c>
       <c r="M8" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9</v>
+        <v>26.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.48</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F10" t="n">
-        <v>19.05</v>
+        <v>19.23</v>
       </c>
       <c r="G10" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.95</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1390</v>
+        <v>1440</v>
       </c>
       <c r="F11" t="n">
-        <v>33.29</v>
+        <v>30.43</v>
       </c>
       <c r="G11" t="n">
-        <v>6.25</v>
+        <v>5.47</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>173</v>
+        <v>177.5</v>
       </c>
       <c r="F12" t="n">
         <v>12.81</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>221.5</v>
+        <v>219</v>
       </c>
       <c r="F13" t="n">
-        <v>31.98</v>
+        <v>32.57</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.91</v>
+        <v>-1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>219.5</v>
+        <v>221.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1528,10 +1528,10 @@
         <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>21.47</v>
+        <v>28.03</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>228.5</v>
+        <v>231</v>
       </c>
       <c r="F15" t="n">
-        <v>27.75</v>
+        <v>20.83</v>
       </c>
       <c r="G15" t="n">
-        <v>10.19</v>
+        <v>5.11</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="M15" t="n">
-        <v>223.5</v>
+        <v>228.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>5330</v>
+        <v>5040</v>
       </c>
       <c r="F16" t="n">
-        <v>59.03</v>
+        <v>160.35</v>
       </c>
       <c r="G16" t="n">
-        <v>10.24</v>
+        <v>48.98</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.65</v>
+        <v>-5.44</v>
       </c>
       <c r="M16" t="n">
-        <v>5045</v>
+        <v>5330</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>93</v>
       </c>
       <c r="E17" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>66.16</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>7.85</v>
+        <v>7.77</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.99</v>
+        <v>-0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>84</v>
       </c>
       <c r="E18" t="n">
-        <v>9310</v>
+        <v>9900</v>
       </c>
       <c r="F18" t="n">
-        <v>182.17</v>
+        <v>190.78</v>
       </c>
       <c r="G18" t="n">
-        <v>49.31</v>
+        <v>51.64</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.72</v>
+        <v>6.34</v>
       </c>
       <c r="M18" t="n">
-        <v>8890</v>
+        <v>9310</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>1690</v>
+        <v>1790</v>
       </c>
       <c r="F19" t="n">
         <v>122.11</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="M19" t="n">
         <v>1690</v>
@@ -2009,13 +2009,13 @@
         <v>77</v>
       </c>
       <c r="E20" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F20" t="n">
-        <v>35.67</v>
+        <v>35.88</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.58</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         <v>70</v>
       </c>
       <c r="E21" t="n">
-        <v>1940</v>
+        <v>2100</v>
       </c>
       <c r="F21" t="n">
-        <v>260.18</v>
+        <v>254.93</v>
       </c>
       <c r="G21" t="n">
-        <v>43.21</v>
+        <v>42.34</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.02</v>
+        <v>8.25</v>
       </c>
       <c r="M21" t="n">
-        <v>1980</v>
+        <v>1940</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>68</v>
       </c>
       <c r="E22" t="n">
-        <v>727</v>
+        <v>682</v>
       </c>
       <c r="F22" t="n">
-        <v>65.27</v>
+        <v>67.5</v>
       </c>
       <c r="G22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.41</v>
+        <v>-6.19</v>
       </c>
       <c r="M22" t="n">
-        <v>703</v>
+        <v>727</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         <v>1395</v>
       </c>
       <c r="F23" t="n">
-        <v>85.27</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>14.68</v>
+        <v>15.06</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1360</v>
+        <v>1395</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2329,13 +2329,13 @@
         <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>468.5</v>
       </c>
       <c r="F24" t="n">
-        <v>81.45999999999999</v>
+        <v>80.47</v>
       </c>
       <c r="G24" t="n">
-        <v>15.52</v>
+        <v>15.33</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1.22</v>
+        <v>5.28</v>
       </c>
       <c r="M24" t="n">
-        <v>450.5</v>
+        <v>445</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2410,13 +2410,13 @@
         <v>66</v>
       </c>
       <c r="E25" t="n">
-        <v>3240</v>
+        <v>3320</v>
       </c>
       <c r="F25" t="n">
-        <v>96.36</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>10.98</v>
+        <v>10.83</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-1.37</v>
+        <v>2.47</v>
       </c>
       <c r="M25" t="n">
-        <v>3285</v>
+        <v>3240</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2474,71 +2474,71 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
-        <v>1970</v>
+        <v>530</v>
       </c>
       <c r="F26" t="n">
-        <v>19.02</v>
+        <v>149.11</v>
       </c>
       <c r="G26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H26" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.32</v>
-      </c>
+        <v>13.99</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-1.01</v>
+        <v>5.79</v>
       </c>
       <c r="M26" t="n">
-        <v>1990</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+        <v>501</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>EPS資料不足</t>
+        </is>
+      </c>
       <c r="P26" t="n">
-        <v>22.3</v>
+        <v>10.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>15.2</v>
+        <v>4.5</v>
       </c>
       <c r="S26" t="n">
-        <v>43.7</v>
+        <v>49.9</v>
       </c>
       <c r="T26" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.32</v>
-      </c>
+        <v>165.8</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -2546,161 +2546,155 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
-        <v>699</v>
+        <v>258</v>
       </c>
       <c r="F27" t="n">
-        <v>21.69</v>
+        <v>38.05</v>
       </c>
       <c r="G27" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="H27" t="n">
-        <v>19</v>
-      </c>
+        <v>3.57</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.09</v>
-      </c>
+        <v>-15.3</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>682</v>
+        <v>258</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>⚠️高槓桿(負債80%)</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>52.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.91</v>
+        <v>0.72</v>
       </c>
       <c r="R27" t="n">
-        <v>9.699999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="S27" t="n">
-        <v>19.2</v>
+        <v>34.8</v>
       </c>
       <c r="T27" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.09</v>
-      </c>
+        <v>34.5</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>3475</v>
+        <v>409.5</v>
       </c>
       <c r="F28" t="n">
-        <v>24.45</v>
+        <v>36.44</v>
       </c>
       <c r="G28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="H28" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>49</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.13</v>
-      </c>
+        <v>6.54</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.21</v>
+        <v>0.61</v>
       </c>
       <c r="M28" t="n">
-        <v>3400</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+        <v>407</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
+        </is>
+      </c>
       <c r="P28" t="n">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="R28" t="n">
-        <v>23.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S28" t="n">
-        <v>37.7</v>
+        <v>730.1</v>
       </c>
       <c r="T28" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.13</v>
-      </c>
+        <v>45.2</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -2708,161 +2702,157 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>5655</v>
+        <v>521</v>
       </c>
       <c r="F29" t="n">
-        <v>10.01</v>
+        <v>39.57</v>
       </c>
       <c r="G29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H29" t="n">
-        <v>75.3</v>
-      </c>
+        <v>8.93</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.01</v>
-      </c>
+        <v>-2.9</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="M29" t="n">
-        <v>5535</v>
+        <v>510</v>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>EPS單期衰退</t>
+        </is>
+      </c>
       <c r="P29" t="n">
-        <v>34.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="R29" t="n">
-        <v>25.1</v>
+        <v>4.9</v>
       </c>
       <c r="S29" t="n">
-        <v>114.6</v>
+        <v>32.1</v>
       </c>
       <c r="T29" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.01</v>
-      </c>
+        <v>38.6</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>770</v>
+        <v>4195</v>
       </c>
       <c r="F30" t="n">
-        <v>62.26</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H30" t="n">
-        <v>47.5</v>
-      </c>
+        <v>17.77</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.83</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.72</v>
+        <v>-3.45</v>
       </c>
       <c r="M30" t="n">
-        <v>757</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>4345</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>月營收轉負-9%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>53.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
-        <v>28.3</v>
+        <v>4.8</v>
       </c>
       <c r="S30" t="n">
-        <v>-9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.83</v>
-      </c>
+        <v>61.7</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -2870,19 +2860,19 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2891,25 +2881,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>103</v>
+        <v>2075</v>
       </c>
       <c r="F31" t="n">
-        <v>12.12</v>
+        <v>19.02</v>
       </c>
       <c r="G31" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>59.1</v>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>34.1</v>
       </c>
       <c r="J31" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2917,78 +2907,78 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="M31" t="n">
-        <v>103</v>
+        <v>1970</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>17.8</v>
+        <v>22.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.11</v>
+        <v>1.28</v>
       </c>
       <c r="R31" t="n">
-        <v>5.3</v>
+        <v>15.2</v>
       </c>
       <c r="S31" t="n">
-        <v>7.7</v>
+        <v>43.7</v>
       </c>
       <c r="T31" t="n">
-        <v>11.6</v>
+        <v>79.3</v>
       </c>
       <c r="U31" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E32" t="n">
-        <v>191.5</v>
+        <v>721</v>
       </c>
       <c r="F32" t="n">
-        <v>13.63</v>
+        <v>22.23</v>
       </c>
       <c r="G32" t="n">
-        <v>1.16</v>
+        <v>11.65</v>
       </c>
       <c r="H32" t="n">
-        <v>13.4</v>
+        <v>19</v>
       </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2996,34 +2986,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-1.03</v>
+        <v>3.15</v>
       </c>
       <c r="M32" t="n">
-        <v>193.5</v>
+        <v>699</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+          <t>⚠️高槓桿(負債80%)</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>17.6</v>
+        <v>52.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="R32" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>19.2</v>
       </c>
       <c r="T32" t="n">
-        <v>14.4</v>
+        <v>20.9</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3032,46 +3022,46 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E33" t="n">
-        <v>105</v>
+        <v>3420</v>
       </c>
       <c r="F33" t="n">
-        <v>39.35</v>
+        <v>96.13</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11</v>
+        <v>24.07</v>
       </c>
       <c r="H33" t="n">
-        <v>16</v>
+        <v>70.2</v>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>49</v>
       </c>
       <c r="J33" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3079,78 +3069,78 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>105</v>
+        <v>3475</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>20.6</v>
+        <v>25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.3</v>
+        <v>0.92</v>
       </c>
       <c r="R33" t="n">
-        <v>7.6</v>
+        <v>23.2</v>
       </c>
       <c r="S33" t="n">
-        <v>1.4</v>
+        <v>37.7</v>
       </c>
       <c r="T33" t="n">
-        <v>17.2</v>
+        <v>104.6</v>
       </c>
       <c r="U33" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E34" t="n">
-        <v>644</v>
+        <v>6080</v>
       </c>
       <c r="F34" t="n">
-        <v>37.94</v>
+        <v>10.01</v>
       </c>
       <c r="G34" t="n">
-        <v>4.43</v>
+        <v>2.68</v>
       </c>
       <c r="H34" t="n">
-        <v>21.4</v>
+        <v>75.3</v>
       </c>
       <c r="I34" t="n">
-        <v>9.800000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3158,82 +3148,78 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.47</v>
+        <v>7.52</v>
       </c>
       <c r="M34" t="n">
-        <v>641</v>
+        <v>5655</v>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>14.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.02</v>
+        <v>0.76</v>
       </c>
       <c r="R34" t="n">
-        <v>10.6</v>
+        <v>25.1</v>
       </c>
       <c r="S34" t="n">
-        <v>30.2</v>
+        <v>114.6</v>
       </c>
       <c r="T34" t="n">
-        <v>23.4</v>
+        <v>120.3</v>
       </c>
       <c r="U34" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E35" t="n">
-        <v>238</v>
+        <v>773</v>
       </c>
       <c r="F35" t="n">
-        <v>16.88</v>
+        <v>62.26</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>1.62</v>
       </c>
       <c r="H35" t="n">
-        <v>30.9</v>
+        <v>47.5</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>20.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3241,34 +3227,34 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-0.21</v>
+        <v>0.39</v>
       </c>
       <c r="M35" t="n">
-        <v>238.5</v>
+        <v>770</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>含金量0.5差</t>
+          <t>月營收轉負-9%</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>9.4</v>
+        <v>53.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.49</v>
+        <v>1.12</v>
       </c>
       <c r="R35" t="n">
-        <v>7.6</v>
+        <v>28.3</v>
       </c>
       <c r="S35" t="n">
-        <v>8.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>36.5</v>
+        <v>57.1</v>
       </c>
       <c r="U35" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3277,313 +3263,323 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E36" t="n">
-        <v>4895</v>
+        <v>104</v>
       </c>
       <c r="F36" t="n">
-        <v>19.34</v>
+        <v>12.12</v>
       </c>
       <c r="G36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.02</v>
       </c>
-      <c r="H36" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="I36" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.73</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>10</v>
+        <v>0.97</v>
       </c>
       <c r="M36" t="n">
-        <v>4450</v>
+        <v>103</v>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>12.9</v>
+        <v>17.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.26</v>
+        <v>2.11</v>
       </c>
       <c r="R36" t="n">
-        <v>31.2</v>
+        <v>5.3</v>
       </c>
       <c r="S36" t="n">
-        <v>-33.5</v>
+        <v>7.7</v>
       </c>
       <c r="T36" t="n">
-        <v>63.8</v>
+        <v>11.6</v>
       </c>
       <c r="U36" t="n">
-        <v>2.73</v>
+        <v>2.02</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E37" t="n">
-        <v>1635</v>
+        <v>197.5</v>
       </c>
       <c r="F37" t="n">
-        <v>24.44</v>
+        <v>13.63</v>
       </c>
       <c r="G37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>1.16</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13.4</v>
+      </c>
       <c r="I37" t="n">
-        <v>204.6</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.02</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M37" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1575</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R37" t="n">
-        <v>39</v>
-      </c>
-      <c r="S37" t="n">
-        <v>116</v>
-      </c>
-      <c r="T37" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="E38" t="n">
-        <v>7880</v>
+        <v>107</v>
       </c>
       <c r="F38" t="n">
-        <v>29.44</v>
+        <v>15.49</v>
       </c>
       <c r="G38" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>3.26</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16</v>
+      </c>
       <c r="I38" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.27</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.94</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
-        <v>7655</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>34.3</v>
+        <v>20.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="R38" t="n">
-        <v>28.8</v>
+        <v>7.6</v>
       </c>
       <c r="S38" t="n">
-        <v>172.1</v>
+        <v>1.4</v>
       </c>
       <c r="T38" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.27</v>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E39" t="n">
-        <v>440</v>
+        <v>636</v>
       </c>
       <c r="F39" t="n">
-        <v>23.99</v>
+        <v>19.52</v>
       </c>
       <c r="G39" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>2.78</v>
+      </c>
+      <c r="H39" t="n">
+        <v>21.4</v>
+      </c>
       <c r="I39" t="n">
-        <v>49</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.79</v>
+        <v>-1.24</v>
       </c>
       <c r="M39" t="n">
-        <v>443.5</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+        <v>644</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P39" t="n">
-        <v>29.3</v>
+        <v>14.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="R39" t="n">
-        <v>24.2</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>30.2</v>
       </c>
       <c r="T39" t="n">
-        <v>24</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.4</v>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3591,199 +3587,207 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="E40" t="n">
-        <v>176.5</v>
+        <v>238</v>
       </c>
       <c r="F40" t="n">
-        <v>21.6</v>
+        <v>16.88</v>
       </c>
       <c r="G40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>30.9</v>
+      </c>
       <c r="I40" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.03</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>177</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>238</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>含金量0.5差</t>
+        </is>
+      </c>
       <c r="P40" t="n">
-        <v>18.6</v>
+        <v>9.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.74</v>
+        <v>0.49</v>
       </c>
       <c r="R40" t="n">
-        <v>11.1</v>
+        <v>7.6</v>
       </c>
       <c r="S40" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="T40" t="n">
-        <v>22</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
+        <v>36.5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.03</v>
+      </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E41" t="n">
-        <v>2210</v>
+        <v>4650</v>
       </c>
       <c r="F41" t="n">
-        <v>31.25</v>
+        <v>19.34</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>2.02</v>
+      </c>
+      <c r="H41" t="n">
+        <v>51.7</v>
+      </c>
       <c r="I41" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="J41" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.73</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4895</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>含金量0.3差、月營收轉負-34%</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R41" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2270</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>含金量0.3差</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="R41" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S41" t="n">
-        <v>133.1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E42" t="n">
-        <v>239</v>
+        <v>1640</v>
       </c>
       <c r="F42" t="n">
-        <v>27.27</v>
+        <v>24.44</v>
       </c>
       <c r="G42" t="n">
-        <v>6.64</v>
+        <v>1.31</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>9.6</v>
+        <v>204.6</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -3792,10 +3796,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-1.85</v>
+        <v>0.31</v>
       </c>
       <c r="M42" t="n">
-        <v>243.5</v>
+        <v>1635</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3804,19 +3808,19 @@
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>30.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="R42" t="n">
-        <v>20.4</v>
+        <v>39</v>
       </c>
       <c r="S42" t="n">
-        <v>812.4</v>
+        <v>116</v>
       </c>
       <c r="T42" t="n">
-        <v>34.6</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
@@ -3833,34 +3837,34 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E43" t="n">
-        <v>235</v>
+        <v>8000</v>
       </c>
       <c r="F43" t="n">
-        <v>20.94</v>
+        <v>29.44</v>
       </c>
       <c r="G43" t="n">
-        <v>3.05</v>
+        <v>4.44</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>49.2</v>
+        <v>90.7</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -3869,10 +3873,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="M43" t="n">
-        <v>230.5</v>
+        <v>7880</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3881,24 +3885,24 @@
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>14.4</v>
+        <v>34.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>28.8</v>
       </c>
       <c r="S43" t="n">
-        <v>10.3</v>
+        <v>172.1</v>
       </c>
       <c r="T43" t="n">
-        <v>20.2</v>
+        <v>66.5</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -3910,34 +3914,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E44" t="n">
-        <v>800</v>
+        <v>445</v>
       </c>
       <c r="F44" t="n">
-        <v>20.29</v>
+        <v>23.8</v>
       </c>
       <c r="G44" t="n">
-        <v>19.17</v>
+        <v>7.04</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>-8.1</v>
+        <v>49</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -3946,40 +3950,36 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-2.32</v>
+        <v>1.14</v>
       </c>
       <c r="M44" t="n">
-        <v>819</v>
+        <v>440</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>94.5</v>
+        <v>29.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R44" t="n">
-        <v>18.2</v>
+        <v>24.2</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T44" t="n">
-        <v>19.6</v>
+        <v>24</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -3991,34 +3991,34 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>176.5</v>
       </c>
       <c r="F45" t="n">
-        <v>24.27</v>
+        <v>21.6</v>
       </c>
       <c r="G45" t="n">
-        <v>5.55</v>
+        <v>1.23</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>-2.9</v>
+        <v>57.1</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -4027,75 +4027,75 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>503</v>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+        <v>176.5</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>22.4</v>
+        <v>18.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.77</v>
+        <v>2.74</v>
       </c>
       <c r="R45" t="n">
-        <v>4.9</v>
+        <v>11.1</v>
       </c>
       <c r="S45" t="n">
-        <v>32.1</v>
+        <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>38.6</v>
+        <v>22</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E46" t="n">
-        <v>1055</v>
+        <v>2265</v>
       </c>
       <c r="F46" t="n">
-        <v>23.03</v>
+        <v>31.25</v>
       </c>
       <c r="G46" t="n">
-        <v>4.3</v>
+        <v>5.29</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>-19.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-7.46</v>
+        <v>2.49</v>
       </c>
       <c r="M46" t="n">
-        <v>1140</v>
+        <v>2210</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4116,23 +4116,23 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>含金量0.3差</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>15.5</v>
+        <v>48.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.24</v>
+        <v>0.31</v>
       </c>
       <c r="R46" t="n">
-        <v>5.7</v>
+        <v>12.6</v>
       </c>
       <c r="S46" t="n">
-        <v>47.5</v>
+        <v>133.1</v>
       </c>
       <c r="T46" t="n">
-        <v>53.2</v>
+        <v>72.7</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
@@ -4149,34 +4149,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>145</v>
+        <v>102.5</v>
       </c>
       <c r="F47" t="n">
-        <v>32.25</v>
+        <v>20.94</v>
       </c>
       <c r="G47" t="n">
-        <v>3.44</v>
+        <v>1.98</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>186.3</v>
+        <v>11.3</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.05</v>
+        <v>0.49</v>
       </c>
       <c r="M47" t="n">
-        <v>143.5</v>
+        <v>102</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4197,23 +4197,23 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>月營收轉負-3%</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="R47" t="n">
-        <v>-3.4</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>37</v>
+        <v>-2.7</v>
       </c>
       <c r="T47" t="n">
-        <v>35.8</v>
+        <v>20.3</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -4230,34 +4230,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E48" t="n">
-        <v>4295</v>
+        <v>236</v>
       </c>
       <c r="F48" t="n">
-        <v>22.36</v>
+        <v>26.76</v>
       </c>
       <c r="G48" t="n">
-        <v>6.86</v>
+        <v>6.52</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4266,35 +4266,31 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="M48" t="n">
-        <v>4330</v>
+        <v>239</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>11.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="R48" t="n">
-        <v>6.8</v>
+        <v>20.4</v>
       </c>
       <c r="S48" t="n">
-        <v>41.8</v>
+        <v>812.4</v>
       </c>
       <c r="T48" t="n">
-        <v>32.9</v>
+        <v>34.6</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -4311,34 +4307,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="E49" t="n">
-        <v>4345</v>
+        <v>235</v>
       </c>
       <c r="F49" t="n">
-        <v>23.55</v>
+        <v>21.34</v>
       </c>
       <c r="G49" t="n">
-        <v>1.76</v>
+        <v>3.11</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>16.8</v>
+        <v>49.2</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4347,40 +4343,36 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4335</v>
+        <v>235</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>25.3</v>
+        <v>14.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="R49" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10.3</v>
       </c>
       <c r="T49" t="n">
-        <v>61.7</v>
+        <v>20.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4392,71 +4384,73 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>588</v>
+        <v>1045</v>
       </c>
       <c r="F50" t="n">
-        <v>11.25</v>
+        <v>23.03</v>
       </c>
       <c r="G50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H50" t="n">
-        <v>29.3</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.87</v>
-      </c>
+        <v>-19.8</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.98</v>
+        <v>-0.95</v>
       </c>
       <c r="M50" t="n">
-        <v>571</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+        <v>1055</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P50" t="n">
-        <v>19.2</v>
+        <v>15.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="R50" t="n">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="S50" t="n">
-        <v>64.90000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="T50" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.87</v>
-      </c>
+        <v>53.2</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4464,78 +4458,80 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>908</v>
+        <v>144</v>
       </c>
       <c r="F51" t="n">
-        <v>26.38</v>
+        <v>32.58</v>
       </c>
       <c r="G51" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="H51" t="n">
-        <v>46.1</v>
-      </c>
+        <v>3.48</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.97</v>
-      </c>
+        <v>186.3</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.33</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>905</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+        <v>145</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>15.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R51" t="n">
-        <v>24.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S51" t="n">
-        <v>1.5</v>
+        <v>37</v>
       </c>
       <c r="T51" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.97</v>
-      </c>
+        <v>35.8</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -4543,125 +4539,127 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>4230</v>
       </c>
       <c r="F52" t="n">
-        <v>13.75</v>
+        <v>22.36</v>
       </c>
       <c r="G52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H52" t="n">
-        <v>17.3</v>
-      </c>
+        <v>6.86</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.64</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.75</v>
+        <v>-1.51</v>
       </c>
       <c r="M52" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+        <v>4295</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="R52" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="S52" t="n">
-        <v>768.2</v>
+        <v>41.8</v>
       </c>
       <c r="T52" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.64</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>164</v>
+        <v>588</v>
       </c>
       <c r="F53" t="n">
-        <v>15.16</v>
+        <v>37.45</v>
       </c>
       <c r="G53" t="n">
-        <v>1.64</v>
+        <v>7.42</v>
       </c>
       <c r="H53" t="n">
-        <v>15.5</v>
+        <v>29.3</v>
       </c>
       <c r="I53" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4669,51 +4667,51 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>161</v>
+        <v>588</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>10.8</v>
+        <v>19.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.03</v>
+        <v>1.94</v>
       </c>
       <c r="R53" t="n">
-        <v>30.2</v>
+        <v>10.6</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>16.9</v>
+        <v>34.7</v>
       </c>
       <c r="U53" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4722,75 +4720,77 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>769</v>
+        <v>851</v>
       </c>
       <c r="F54" t="n">
-        <v>15.43</v>
+        <v>61.56</v>
       </c>
       <c r="G54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>9.550000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>46.1</v>
+      </c>
       <c r="I54" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.97</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.79</v>
+        <v>-6.28</v>
       </c>
       <c r="M54" t="n">
-        <v>763</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="R54" t="n">
-        <v>7.8</v>
+        <v>24.8</v>
       </c>
       <c r="S54" t="n">
-        <v>17.8</v>
+        <v>1.5</v>
       </c>
       <c r="T54" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
+        <v>60.2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.97</v>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4802,72 +4802,74 @@
         <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>428</v>
+        <v>75</v>
       </c>
       <c r="F55" t="n">
-        <v>17.88</v>
+        <v>17.89</v>
       </c>
       <c r="G55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>3.06</v>
+      </c>
+      <c r="H55" t="n">
+        <v>17.3</v>
+      </c>
       <c r="I55" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.71</v>
+        <v>2.74</v>
       </c>
       <c r="M55" t="n">
-        <v>425</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>13.7</v>
+        <v>11.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="R55" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="S55" t="n">
-        <v>30</v>
+        <v>768.2</v>
       </c>
       <c r="T55" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.64</v>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4876,101 +4878,99 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>102</v>
+        <v>168.5</v>
       </c>
       <c r="F56" t="n">
-        <v>19.71</v>
+        <v>15.44</v>
       </c>
       <c r="G56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>1.68</v>
+      </c>
+      <c r="H56" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I56" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.99</v>
+        <v>4.03</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="S56" t="n">
-        <v>-2.7</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>45.55</v>
+        <v>756</v>
       </c>
       <c r="F57" t="n">
-        <v>14.65</v>
+        <v>15.43</v>
       </c>
       <c r="G57" t="n">
-        <v>1.29</v>
+        <v>2.91</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>147.4</v>
+        <v>25.3</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4979,40 +4979,36 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-1.69</v>
       </c>
       <c r="M57" t="n">
-        <v>45.55</v>
+        <v>769</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>含金量0.0差</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>29.2</v>
+        <v>18.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.04</v>
+        <v>1.27</v>
       </c>
       <c r="R57" t="n">
-        <v>36.1</v>
+        <v>7.8</v>
       </c>
       <c r="S57" t="n">
-        <v>0.4</v>
+        <v>17.8</v>
       </c>
       <c r="T57" t="n">
-        <v>14.4</v>
+        <v>69.5</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5024,33 +5020,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E58" t="n">
-        <v>501</v>
+        <v>425</v>
       </c>
       <c r="F58" t="n">
-        <v>19.91</v>
+        <v>17.88</v>
       </c>
       <c r="G58" t="n">
-        <v>4.61</v>
+        <v>2.85</v>
       </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>24.9</v>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
@@ -5058,35 +5056,31 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-2.15</v>
+        <v>-0.7</v>
       </c>
       <c r="M58" t="n">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>EPS資料不足</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>10.7</v>
+        <v>13.7</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="R58" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="S58" t="n">
-        <v>49.9</v>
+        <v>30</v>
       </c>
       <c r="T58" t="n">
-        <v>165.8</v>
+        <v>43.5</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5103,34 +5097,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>258</v>
+        <v>23.4</v>
       </c>
       <c r="F59" t="n">
-        <v>14.36</v>
+        <v>18.29</v>
       </c>
       <c r="G59" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>-15.3</v>
+        <v>13.7</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5139,75 +5133,79 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>249</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
+        <v>22.5</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>月營收轉負-5%</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>9.4</v>
+        <v>10.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="R59" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="S59" t="n">
-        <v>34.8</v>
+        <v>-5.3</v>
       </c>
       <c r="T59" t="n">
-        <v>34.5</v>
+        <v>18.2</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E60" t="n">
-        <v>811</v>
+        <v>47.85</v>
       </c>
       <c r="F60" t="n">
-        <v>16.15</v>
+        <v>14.65</v>
       </c>
       <c r="G60" t="n">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>147.4</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5216,10 +5214,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-2.17</v>
+        <v>5.05</v>
       </c>
       <c r="M60" t="n">
-        <v>829</v>
+        <v>45.55</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5228,28 +5226,28 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>含金量0.0差</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>31.7</v>
+        <v>29.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.5</v>
+        <v>0.04</v>
       </c>
       <c r="R60" t="n">
-        <v>3.8</v>
+        <v>36.1</v>
       </c>
       <c r="S60" t="n">
-        <v>21.9</v>
+        <v>0.4</v>
       </c>
       <c r="T60" t="n">
-        <v>32.2</v>
+        <v>14.4</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5261,33 +5259,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E61" t="n">
-        <v>183.5</v>
+        <v>797</v>
       </c>
       <c r="F61" t="n">
-        <v>19.26</v>
+        <v>19.82</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81</v>
+        <v>18.73</v>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>-8.1</v>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-3.42</v>
+        <v>-0.38</v>
       </c>
       <c r="M61" t="n">
-        <v>190</v>
+        <v>800</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5307,28 +5307,28 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>11.6</v>
+        <v>94.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="R61" t="n">
-        <v>-2.7</v>
+        <v>18.2</v>
       </c>
       <c r="S61" t="n">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="T61" t="n">
-        <v>65.90000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5340,34 +5340,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E62" t="n">
-        <v>52.5</v>
+        <v>783</v>
       </c>
       <c r="F62" t="n">
-        <v>12.74</v>
+        <v>16.15</v>
       </c>
       <c r="G62" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>-15.4</v>
+        <v>27</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1.32</v>
+        <v>-3.45</v>
       </c>
       <c r="M62" t="n">
-        <v>53.2</v>
+        <v>811</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5388,28 +5388,28 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>11.5</v>
+        <v>31.7</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.58</v>
+        <v>1.5</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.2</v>
+        <v>3.8</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>21.9</v>
       </c>
       <c r="T62" t="n">
-        <v>19.9</v>
+        <v>32.2</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5421,170 +5421,172 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E63" t="n">
-        <v>156.5</v>
+        <v>184.5</v>
       </c>
       <c r="F63" t="n">
-        <v>16.87</v>
+        <v>19.26</v>
       </c>
       <c r="G63" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="H63" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I63" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.29</v>
-      </c>
+        <v>1.81</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="M63" t="n">
-        <v>155.5</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+        <v>183.5</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P63" t="n">
-        <v>27.9</v>
+        <v>11.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="R63" t="n">
-        <v>10.8</v>
+        <v>-2.7</v>
       </c>
       <c r="S63" t="n">
-        <v>7.7</v>
+        <v>182</v>
       </c>
       <c r="T63" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.29</v>
-      </c>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="E64" t="n">
-        <v>541</v>
+        <v>53.3</v>
       </c>
       <c r="F64" t="n">
-        <v>11.53</v>
+        <v>19.96</v>
       </c>
       <c r="G64" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="H64" t="n">
-        <v>17.9</v>
-      </c>
+        <v>2.14</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.11</v>
-      </c>
+        <v>-15.4</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M64" t="n">
-        <v>533</v>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+        <v>52.5</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
+        </is>
+      </c>
       <c r="P64" t="n">
-        <v>23.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="R64" t="n">
-        <v>12.2</v>
+        <v>-2.2</v>
       </c>
       <c r="S64" t="n">
-        <v>18.6</v>
+        <v>6</v>
       </c>
       <c r="T64" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.11</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5593,25 +5595,25 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>121.5</v>
+        <v>162</v>
       </c>
       <c r="F65" t="n">
-        <v>17.39</v>
+        <v>16.97</v>
       </c>
       <c r="G65" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="I65" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="J65" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5619,30 +5621,30 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.41</v>
+        <v>3.51</v>
       </c>
       <c r="M65" t="n">
-        <v>121</v>
+        <v>156.5</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>19.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="R65" t="n">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="S65" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="T65" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="U65" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -5651,19 +5653,19 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5672,25 +5674,25 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>363.5</v>
+        <v>531</v>
       </c>
       <c r="F66" t="n">
-        <v>9.84</v>
+        <v>22.95</v>
       </c>
       <c r="G66" t="n">
-        <v>1.23</v>
+        <v>5.45</v>
       </c>
       <c r="H66" t="n">
-        <v>27.5</v>
+        <v>17.9</v>
       </c>
       <c r="I66" t="n">
-        <v>29.1</v>
+        <v>19.1</v>
       </c>
       <c r="J66" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5698,30 +5700,30 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.45</v>
+        <v>-1.85</v>
       </c>
       <c r="M66" t="n">
-        <v>348</v>
+        <v>541</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>27.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="R66" t="n">
-        <v>18.3</v>
+        <v>12.2</v>
       </c>
       <c r="S66" t="n">
-        <v>41.8</v>
+        <v>18.6</v>
       </c>
       <c r="T66" t="n">
-        <v>35.5</v>
+        <v>21.3</v>
       </c>
       <c r="U66" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -5730,19 +5732,19 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5751,25 +5753,25 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E67" t="n">
-        <v>95</v>
+        <v>123.5</v>
       </c>
       <c r="F67" t="n">
-        <v>19.52</v>
+        <v>17.46</v>
       </c>
       <c r="G67" t="n">
-        <v>2.13</v>
+        <v>3.46</v>
       </c>
       <c r="H67" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="I67" t="n">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="J67" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5777,34 +5779,34 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="M67" t="n">
-        <v>92.90000000000001</v>
+        <v>121.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="R67" t="n">
-        <v>21.7</v>
+        <v>7</v>
       </c>
       <c r="S67" t="n">
-        <v>19.5</v>
+        <v>0.6</v>
       </c>
       <c r="T67" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="U67" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -5816,39 +5818,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>153.5</v>
+        <v>372.5</v>
       </c>
       <c r="F68" t="n">
-        <v>20.26</v>
+        <v>35.46</v>
       </c>
       <c r="G68" t="n">
-        <v>5.53</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>16.4</v>
+        <v>27.5</v>
       </c>
       <c r="I68" t="n">
-        <v>17.2</v>
+        <v>29.1</v>
       </c>
       <c r="J68" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5856,34 +5858,30 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.37</v>
+        <v>2.48</v>
       </c>
       <c r="M68" t="n">
-        <v>148.5</v>
+        <v>363.5</v>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>含金量-0.3差</t>
-        </is>
-      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>34.8</v>
+        <v>27.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>-0.28</v>
+        <v>0.83</v>
       </c>
       <c r="R68" t="n">
-        <v>17.8</v>
+        <v>18.3</v>
       </c>
       <c r="S68" t="n">
-        <v>17.6</v>
+        <v>41.8</v>
       </c>
       <c r="T68" t="n">
-        <v>19.2</v>
+        <v>35.5</v>
       </c>
       <c r="U68" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -5892,46 +5890,46 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>239</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>11.94</v>
+        <v>19.96</v>
       </c>
       <c r="G69" t="n">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="H69" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="I69" t="n">
-        <v>15.2</v>
+        <v>14.1</v>
       </c>
       <c r="J69" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5939,34 +5937,34 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-3.63</v>
+        <v>-0.63</v>
       </c>
       <c r="M69" t="n">
-        <v>248</v>
+        <v>95</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="R69" t="n">
-        <v>7.8</v>
+        <v>21.7</v>
       </c>
       <c r="S69" t="n">
-        <v>39.6</v>
+        <v>19.5</v>
       </c>
       <c r="T69" t="n">
-        <v>17.6</v>
+        <v>19.1</v>
       </c>
       <c r="U69" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -5978,12 +5976,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5992,23 +5990,25 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>1200</v>
+        <v>155</v>
       </c>
       <c r="F70" t="n">
-        <v>57.36</v>
+        <v>20.94</v>
       </c>
       <c r="G70" t="n">
-        <v>29.86</v>
+        <v>5.72</v>
       </c>
       <c r="H70" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
+        <v>16.4</v>
+      </c>
+      <c r="I70" t="n">
+        <v>17.2</v>
+      </c>
       <c r="J70" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6016,34 +6016,34 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>9.59</v>
+        <v>0.98</v>
       </c>
       <c r="M70" t="n">
-        <v>1095</v>
+        <v>153.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>含金量-0.3差</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>52.2</v>
+        <v>34.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.15</v>
+        <v>-0.28</v>
       </c>
       <c r="R70" t="n">
-        <v>97.59999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="S70" t="n">
-        <v>99.3</v>
+        <v>17.6</v>
       </c>
       <c r="T70" t="n">
-        <v>62</v>
+        <v>19.2</v>
       </c>
       <c r="U70" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -6052,19 +6052,19 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6073,25 +6073,25 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>67.2</v>
+        <v>240.5</v>
       </c>
       <c r="F71" t="n">
-        <v>12.7</v>
+        <v>16.97</v>
       </c>
       <c r="G71" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="H71" t="n">
-        <v>21.3</v>
+        <v>15.3</v>
       </c>
       <c r="I71" t="n">
-        <v>18.7</v>
+        <v>15.2</v>
       </c>
       <c r="J71" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6099,34 +6099,30 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="M71" t="n">
-        <v>66.90000000000001</v>
+        <v>239</v>
       </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>⚠️高槓桿(負債81%)</t>
-        </is>
-      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="R71" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="S71" t="n">
-        <v>35.3</v>
+        <v>39.6</v>
       </c>
       <c r="T71" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="U71" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -6142,149 +6138,155 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>2740</v>
+        <v>1300</v>
       </c>
       <c r="F72" t="n">
-        <v>12.13</v>
+        <v>62.86</v>
       </c>
       <c r="G72" t="n">
-        <v>1.34</v>
+        <v>32.72</v>
       </c>
       <c r="H72" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I72" t="n">
-        <v>86.7</v>
-      </c>
+        <v>38.8</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4.58</v>
+        <v>8.33</v>
       </c>
       <c r="M72" t="n">
-        <v>2620</v>
+        <v>1200</v>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>EPS資料不足</t>
+        </is>
+      </c>
       <c r="P72" t="n">
-        <v>50.9</v>
+        <v>52.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.81</v>
+        <v>1.15</v>
       </c>
       <c r="R72" t="n">
-        <v>31.1</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S72" t="n">
-        <v>60.6</v>
+        <v>99.3</v>
       </c>
       <c r="T72" t="n">
-        <v>39.3</v>
+        <v>62</v>
       </c>
       <c r="U72" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>939</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>12.64</v>
+        <v>12.7</v>
       </c>
       <c r="G73" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="H73" t="n">
-        <v>14.2</v>
+        <v>21.3</v>
       </c>
       <c r="I73" t="n">
-        <v>54.3</v>
+        <v>18.7</v>
       </c>
       <c r="J73" t="n">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.96</v>
+        <v>0.6</v>
       </c>
       <c r="M73" t="n">
-        <v>912</v>
+        <v>67.2</v>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債81%)</t>
+        </is>
+      </c>
       <c r="P73" t="n">
-        <v>37.1</v>
+        <v>13.6</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="R73" t="n">
-        <v>34.4</v>
+        <v>7.4</v>
       </c>
       <c r="S73" t="n">
-        <v>103.3</v>
+        <v>35.3</v>
       </c>
       <c r="T73" t="n">
-        <v>21.9</v>
+        <v>25.2</v>
       </c>
       <c r="U73" t="n">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -6293,19 +6295,19 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6317,22 +6319,22 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>2465</v>
+        <v>2760</v>
       </c>
       <c r="F74" t="n">
-        <v>17.11</v>
+        <v>45.02</v>
       </c>
       <c r="G74" t="n">
-        <v>4.11</v>
+        <v>23.81</v>
       </c>
       <c r="H74" t="n">
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
       <c r="I74" t="n">
-        <v>43.1</v>
+        <v>86.7</v>
       </c>
       <c r="J74" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6340,34 +6342,34 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.6</v>
+        <v>0.73</v>
       </c>
       <c r="M74" t="n">
-        <v>2505</v>
+        <v>2740</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>32.5</v>
+        <v>50.9</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="R74" t="n">
-        <v>24.5</v>
+        <v>31.1</v>
       </c>
       <c r="S74" t="n">
-        <v>30.1</v>
+        <v>60.6</v>
       </c>
       <c r="T74" t="n">
-        <v>33.7</v>
+        <v>39.3</v>
       </c>
       <c r="U74" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -6379,12 +6381,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6393,25 +6395,25 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>102</v>
+        <v>948</v>
       </c>
       <c r="F75" t="n">
-        <v>10.74</v>
+        <v>26.06</v>
       </c>
       <c r="G75" t="n">
-        <v>1.13</v>
+        <v>10.1</v>
       </c>
       <c r="H75" t="n">
-        <v>12.4</v>
+        <v>14.2</v>
       </c>
       <c r="I75" t="n">
-        <v>20.6</v>
+        <v>54.3</v>
       </c>
       <c r="J75" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6419,34 +6421,34 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.82</v>
+        <v>0.96</v>
       </c>
       <c r="M75" t="n">
-        <v>99.2</v>
+        <v>939</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>20.9</v>
+        <v>37.1</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="R75" t="n">
-        <v>17.9</v>
+        <v>34.4</v>
       </c>
       <c r="S75" t="n">
-        <v>27.4</v>
+        <v>103.3</v>
       </c>
       <c r="T75" t="n">
-        <v>14.9</v>
+        <v>21.9</v>
       </c>
       <c r="U75" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -6458,12 +6460,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6472,25 +6474,25 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>126</v>
+        <v>2445</v>
       </c>
       <c r="F76" t="n">
-        <v>16.51</v>
+        <v>33.14</v>
       </c>
       <c r="G76" t="n">
-        <v>2.31</v>
+        <v>10.85</v>
       </c>
       <c r="H76" t="n">
-        <v>12.3</v>
+        <v>23.6</v>
       </c>
       <c r="I76" t="n">
-        <v>23.9</v>
+        <v>43.1</v>
       </c>
       <c r="J76" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6498,34 +6500,34 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.28</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>122</v>
+        <v>2465</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="R76" t="n">
-        <v>5.7</v>
+        <v>24.5</v>
       </c>
       <c r="S76" t="n">
-        <v>20.2</v>
+        <v>30.1</v>
       </c>
       <c r="T76" t="n">
-        <v>15.2</v>
+        <v>33.7</v>
       </c>
       <c r="U76" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -6537,12 +6539,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6551,25 +6553,25 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E77" t="n">
-        <v>34.5</v>
+        <v>102.5</v>
       </c>
       <c r="F77" t="n">
-        <v>9.9</v>
+        <v>10.74</v>
       </c>
       <c r="G77" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="H77" t="n">
-        <v>5.9</v>
+        <v>12.4</v>
       </c>
       <c r="I77" t="n">
-        <v>16.1</v>
+        <v>20.6</v>
       </c>
       <c r="J77" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6577,34 +6579,34 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="M77" t="n">
-        <v>34.5</v>
+        <v>102</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>19.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="R77" t="n">
-        <v>3.6</v>
+        <v>17.9</v>
       </c>
       <c r="S77" t="n">
-        <v>88.7</v>
+        <v>27.4</v>
       </c>
       <c r="T77" t="n">
-        <v>6.8</v>
+        <v>14.9</v>
       </c>
       <c r="U77" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -6616,12 +6618,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6633,22 +6635,22 @@
         <v>94</v>
       </c>
       <c r="E78" t="n">
-        <v>110.5</v>
+        <v>124</v>
       </c>
       <c r="F78" t="n">
-        <v>11.19</v>
+        <v>17.05</v>
       </c>
       <c r="G78" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="H78" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="I78" t="n">
-        <v>16.2</v>
+        <v>23.9</v>
       </c>
       <c r="J78" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6656,34 +6658,34 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-3.07</v>
+        <v>-1.59</v>
       </c>
       <c r="M78" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>24.9</v>
+        <v>17</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="R78" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="S78" t="n">
-        <v>1.7</v>
+        <v>20.2</v>
       </c>
       <c r="T78" t="n">
-        <v>12.4</v>
+        <v>15.2</v>
       </c>
       <c r="U78" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -6695,12 +6697,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6712,22 +6714,22 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>181.5</v>
+        <v>34.55</v>
       </c>
       <c r="F79" t="n">
-        <v>13.99</v>
+        <v>6.91</v>
       </c>
       <c r="G79" t="n">
-        <v>3.54</v>
+        <v>1.34</v>
       </c>
       <c r="H79" t="n">
-        <v>11.4</v>
+        <v>5.9</v>
       </c>
       <c r="I79" t="n">
-        <v>24.1</v>
+        <v>16.1</v>
       </c>
       <c r="J79" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6735,30 +6737,30 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-3.71</v>
+        <v>0.14</v>
       </c>
       <c r="M79" t="n">
-        <v>188.5</v>
+        <v>34.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R79" t="n">
-        <v>10.2</v>
+        <v>3.6</v>
       </c>
       <c r="S79" t="n">
-        <v>13.3</v>
+        <v>88.7</v>
       </c>
       <c r="T79" t="n">
-        <v>14.1</v>
+        <v>6.8</v>
       </c>
       <c r="U79" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -6774,12 +6776,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6788,25 +6790,25 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>43.9</v>
+        <v>112.5</v>
       </c>
       <c r="F80" t="n">
-        <v>15.5</v>
+        <v>11.19</v>
       </c>
       <c r="G80" t="n">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="H80" t="n">
-        <v>7.6</v>
+        <v>10.7</v>
       </c>
       <c r="I80" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="J80" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6814,30 +6816,30 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M80" t="n">
-        <v>43.9</v>
+        <v>110.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>20.9</v>
+        <v>24.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="R80" t="n">
-        <v>20.7</v>
+        <v>3.4</v>
       </c>
       <c r="S80" t="n">
-        <v>22.1</v>
+        <v>1.7</v>
       </c>
       <c r="T80" t="n">
-        <v>8.300000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="U80" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6853,12 +6855,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6867,25 +6869,25 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>1310</v>
+        <v>182.5</v>
       </c>
       <c r="F81" t="n">
-        <v>10.27</v>
+        <v>13.47</v>
       </c>
       <c r="G81" t="n">
-        <v>1.83</v>
+        <v>3.41</v>
       </c>
       <c r="H81" t="n">
-        <v>25</v>
+        <v>11.4</v>
       </c>
       <c r="I81" t="n">
-        <v>79.40000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="J81" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6893,34 +6895,34 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.16</v>
+        <v>0.55</v>
       </c>
       <c r="M81" t="n">
-        <v>1295</v>
+        <v>181.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>33.9</v>
+        <v>22.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.84</v>
+        <v>1.93</v>
       </c>
       <c r="R81" t="n">
-        <v>23.6</v>
+        <v>10.2</v>
       </c>
       <c r="S81" t="n">
-        <v>37.3</v>
+        <v>13.3</v>
       </c>
       <c r="T81" t="n">
-        <v>40</v>
+        <v>14.1</v>
       </c>
       <c r="U81" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -6932,12 +6934,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6946,25 +6948,25 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>506</v>
+        <v>43.85</v>
       </c>
       <c r="F82" t="n">
-        <v>11.17</v>
+        <v>15.5</v>
       </c>
       <c r="G82" t="n">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="H82" t="n">
-        <v>21.2</v>
+        <v>7.6</v>
       </c>
       <c r="I82" t="n">
-        <v>29.8</v>
+        <v>9.9</v>
       </c>
       <c r="J82" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6972,34 +6974,34 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="M82" t="n">
-        <v>506</v>
+        <v>43.9</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>18.5</v>
+        <v>20.9</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.13</v>
+        <v>2.16</v>
       </c>
       <c r="R82" t="n">
-        <v>3.9</v>
+        <v>20.7</v>
       </c>
       <c r="S82" t="n">
-        <v>46.6</v>
+        <v>22.1</v>
       </c>
       <c r="T82" t="n">
-        <v>27.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U82" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -7011,12 +7013,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7028,22 +7030,22 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>148</v>
+        <v>1305</v>
       </c>
       <c r="F83" t="n">
-        <v>18.47</v>
+        <v>38.84</v>
       </c>
       <c r="G83" t="n">
-        <v>3.33</v>
+        <v>13.01</v>
       </c>
       <c r="H83" t="n">
-        <v>14.1</v>
+        <v>25</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7051,34 +7053,34 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.37</v>
+        <v>-0.38</v>
       </c>
       <c r="M83" t="n">
-        <v>146</v>
+        <v>1310</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>20.7</v>
+        <v>33.9</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.16</v>
+        <v>0.84</v>
       </c>
       <c r="R83" t="n">
-        <v>8.300000000000001</v>
+        <v>23.6</v>
       </c>
       <c r="S83" t="n">
-        <v>14.9</v>
+        <v>37.3</v>
       </c>
       <c r="T83" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="U83" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -7090,12 +7092,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7104,25 +7106,25 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>40.75</v>
+        <v>520</v>
       </c>
       <c r="F84" t="n">
-        <v>33.32</v>
+        <v>11.17</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="H84" t="n">
-        <v>6.2</v>
+        <v>21.2</v>
       </c>
       <c r="I84" t="n">
-        <v>44.7</v>
+        <v>29.8</v>
       </c>
       <c r="J84" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7130,34 +7132,34 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M84" t="n">
-        <v>40.75</v>
+        <v>506</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>13.6</v>
+        <v>18.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="R84" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="S84" t="n">
-        <v>153.2</v>
+        <v>46.6</v>
       </c>
       <c r="T84" t="n">
-        <v>9</v>
+        <v>27.5</v>
       </c>
       <c r="U84" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -7169,12 +7171,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7183,25 +7185,25 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>2750</v>
+        <v>149</v>
       </c>
       <c r="F85" t="n">
-        <v>22.12</v>
+        <v>18.47</v>
       </c>
       <c r="G85" t="n">
-        <v>6.05</v>
+        <v>3.33</v>
       </c>
       <c r="H85" t="n">
-        <v>30.7</v>
+        <v>14.1</v>
       </c>
       <c r="I85" t="n">
-        <v>71.7</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7209,38 +7211,34 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.38</v>
+        <v>0.68</v>
       </c>
       <c r="M85" t="n">
-        <v>2660</v>
+        <v>148</v>
       </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>45.1</v>
+        <v>20.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="R85" t="n">
-        <v>42.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S85" t="n">
-        <v>56.6</v>
+        <v>14.9</v>
       </c>
       <c r="T85" t="n">
-        <v>49.1</v>
+        <v>17.5</v>
       </c>
       <c r="U85" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -7252,12 +7250,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7266,25 +7264,25 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>1040</v>
+        <v>41.7</v>
       </c>
       <c r="F86" t="n">
-        <v>29.15</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>7</v>
+        <v>1.22</v>
       </c>
       <c r="H86" t="n">
-        <v>21.8</v>
+        <v>6.2</v>
       </c>
       <c r="I86" t="n">
-        <v>40.5</v>
+        <v>44.7</v>
       </c>
       <c r="J86" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7292,38 +7290,34 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="M86" t="n">
-        <v>1010</v>
+        <v>40.75</v>
       </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>含金量-0.1差</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>24.6</v>
+        <v>13.6</v>
       </c>
       <c r="Q86" t="n">
-        <v>-0.08</v>
+        <v>0.89</v>
       </c>
       <c r="R86" t="n">
-        <v>13.1</v>
+        <v>14.5</v>
       </c>
       <c r="S86" t="n">
-        <v>93.8</v>
+        <v>153.2</v>
       </c>
       <c r="T86" t="n">
-        <v>30.6</v>
+        <v>9</v>
       </c>
       <c r="U86" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -7335,39 +7329,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>88.90000000000001</v>
+        <v>2735</v>
       </c>
       <c r="F87" t="n">
-        <v>6.55</v>
+        <v>52</v>
       </c>
       <c r="G87" t="n">
-        <v>0.76</v>
+        <v>23.53</v>
       </c>
       <c r="H87" t="n">
-        <v>8.6</v>
+        <v>30.7</v>
       </c>
       <c r="I87" t="n">
-        <v>31.3</v>
+        <v>71.7</v>
       </c>
       <c r="J87" t="n">
-        <v>0.36</v>
+        <v>0.82</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7375,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="M87" t="n">
-        <v>89.09999999999999</v>
+        <v>2750</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
@@ -7387,22 +7381,22 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>20.9</v>
+        <v>45.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.28</v>
+        <v>0.92</v>
       </c>
       <c r="R87" t="n">
-        <v>10.5</v>
+        <v>42.9</v>
       </c>
       <c r="S87" t="n">
-        <v>1.5</v>
+        <v>56.6</v>
       </c>
       <c r="T87" t="n">
-        <v>11.2</v>
+        <v>49.1</v>
       </c>
       <c r="U87" t="n">
-        <v>0.36</v>
+        <v>0.82</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -7418,39 +7412,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>73.8</v>
+        <v>1020</v>
       </c>
       <c r="F88" t="n">
-        <v>26.57</v>
+        <v>30.01</v>
       </c>
       <c r="G88" t="n">
-        <v>1.21</v>
+        <v>7.21</v>
       </c>
       <c r="H88" t="n">
-        <v>6.8</v>
+        <v>21.8</v>
       </c>
       <c r="I88" t="n">
-        <v>13.7</v>
+        <v>40.5</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7458,34 +7452,34 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.27</v>
+        <v>-1.92</v>
       </c>
       <c r="M88" t="n">
-        <v>73.59999999999999</v>
+        <v>1040</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>含金量0.5弱</t>
+          <t>含金量-0.1差</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>23.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.52</v>
+        <v>-0.08</v>
       </c>
       <c r="R88" t="n">
-        <v>4.1</v>
+        <v>13.1</v>
       </c>
       <c r="S88" t="n">
-        <v>11.8</v>
+        <v>93.8</v>
       </c>
       <c r="T88" t="n">
-        <v>7.7</v>
+        <v>30.6</v>
       </c>
       <c r="U88" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -7501,12 +7495,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7515,25 +7509,25 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>67.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F89" t="n">
-        <v>12.4</v>
+        <v>6.55</v>
       </c>
       <c r="G89" t="n">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="H89" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="I89" t="n">
-        <v>17.1</v>
+        <v>31.3</v>
       </c>
       <c r="J89" t="n">
-        <v>0.71</v>
+        <v>0.36</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7541,38 +7535,38 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M89" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>月營收轉負-10%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>17.5</v>
+        <v>20.9</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="R89" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="S89" t="n">
-        <v>-10.5</v>
+        <v>1.5</v>
       </c>
       <c r="T89" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="U89" t="n">
-        <v>0.71</v>
+        <v>0.36</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -7584,12 +7578,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7598,25 +7592,25 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>369</v>
+        <v>76.2</v>
       </c>
       <c r="F90" t="n">
-        <v>15.84</v>
+        <v>7.98</v>
       </c>
       <c r="G90" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H90" t="n">
-        <v>13.2</v>
+        <v>6.8</v>
       </c>
       <c r="I90" t="n">
-        <v>37.4</v>
+        <v>13.7</v>
       </c>
       <c r="J90" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7624,38 +7618,38 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.8100000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="M90" t="n">
-        <v>372</v>
+        <v>73.8</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>含金量-0.9差、⚠️高槓桿(負債87%)</t>
+          <t>含金量0.5弱</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>35.3</v>
+        <v>23.3</v>
       </c>
       <c r="Q90" t="n">
-        <v>-0.87</v>
+        <v>0.52</v>
       </c>
       <c r="R90" t="n">
-        <v>17.1</v>
+        <v>4.1</v>
       </c>
       <c r="S90" t="n">
-        <v>94.40000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="T90" t="n">
-        <v>18.2</v>
+        <v>7.7</v>
       </c>
       <c r="U90" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -7667,12 +7661,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7681,25 +7675,25 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E91" t="n">
-        <v>5200</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F91" t="n">
-        <v>16.88</v>
+        <v>12.47</v>
       </c>
       <c r="G91" t="n">
-        <v>6.68</v>
+        <v>1.53</v>
       </c>
       <c r="H91" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="I91" t="n">
-        <v>99.8</v>
+        <v>17.1</v>
       </c>
       <c r="J91" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7707,38 +7701,38 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.28</v>
+        <v>1.94</v>
       </c>
       <c r="M91" t="n">
-        <v>5035</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>含金量0.2差、毛利壓歷史低檔、⚠️存貨爆衝(存85%vs營18%)</t>
+          <t>月營收轉負-10%</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>39.6</v>
+        <v>17.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R91" t="n">
-        <v>49</v>
+        <v>6.2</v>
       </c>
       <c r="S91" t="n">
-        <v>18.2</v>
+        <v>-10.5</v>
       </c>
       <c r="T91" t="n">
-        <v>15.3</v>
+        <v>12.2</v>
       </c>
       <c r="U91" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -7750,39 +7744,39 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>158.5</v>
+        <v>377</v>
       </c>
       <c r="F92" t="n">
-        <v>16.25</v>
+        <v>15.84</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="H92" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="I92" t="n">
-        <v>48.9</v>
+        <v>37.4</v>
       </c>
       <c r="J92" t="n">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7790,38 +7784,38 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.63</v>
+        <v>2.17</v>
       </c>
       <c r="M92" t="n">
-        <v>159.5</v>
+        <v>369</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>含金量-3.4差、毛利壓歷史低檔、⚠️高槓桿(負債81%)</t>
+          <t>含金量-0.9差、⚠️高槓桿(負債87%)</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>23.5</v>
+        <v>35.3</v>
       </c>
       <c r="Q92" t="n">
-        <v>-3.39</v>
+        <v>-0.87</v>
       </c>
       <c r="R92" t="n">
-        <v>26.2</v>
+        <v>17.1</v>
       </c>
       <c r="S92" t="n">
-        <v>39.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T92" t="n">
-        <v>15</v>
+        <v>18.2</v>
       </c>
       <c r="U92" t="n">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -7833,39 +7827,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>1520</v>
+        <v>5265</v>
       </c>
       <c r="F93" t="n">
-        <v>50.63</v>
+        <v>17.43</v>
       </c>
       <c r="G93" t="n">
-        <v>13.47</v>
+        <v>6.89</v>
       </c>
       <c r="H93" t="n">
-        <v>11.9</v>
+        <v>9.6</v>
       </c>
       <c r="I93" t="n">
-        <v>50.3</v>
+        <v>99.8</v>
       </c>
       <c r="J93" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7873,34 +7867,34 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="M93" t="n">
-        <v>1470</v>
+        <v>5200</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔、月營收轉負-19%</t>
+          <t>含金量0.2差、毛利壓歷史低檔、⚠️存貨爆衝(存85%vs營18%)</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>16.3</v>
+        <v>39.6</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.9</v>
+        <v>0.16</v>
       </c>
       <c r="R93" t="n">
-        <v>22.2</v>
+        <v>49</v>
       </c>
       <c r="S93" t="n">
-        <v>-19.4</v>
+        <v>18.2</v>
       </c>
       <c r="T93" t="n">
-        <v>17.9</v>
+        <v>15.3</v>
       </c>
       <c r="U93" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -7916,166 +7910,178 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E94" t="n">
-        <v>80.40000000000001</v>
+        <v>159</v>
       </c>
       <c r="F94" t="n">
-        <v>6.61</v>
+        <v>15.9</v>
       </c>
       <c r="G94" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>2.65</v>
+      </c>
+      <c r="H94" t="n">
+        <v>10</v>
+      </c>
       <c r="I94" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J94" t="inlineStr"/>
+        <v>48.9</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.31</v>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.26</v>
+        <v>0.32</v>
       </c>
       <c r="M94" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
+        <v>158.5</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>含金量-3.4差、毛利壓歷史低檔、⚠️高槓桿(負債81%)</t>
+        </is>
+      </c>
       <c r="P94" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.99</v>
+        <v>-3.39</v>
       </c>
       <c r="R94" t="n">
-        <v>23</v>
+        <v>26.2</v>
       </c>
       <c r="S94" t="n">
-        <v>13.7</v>
+        <v>39.2</v>
       </c>
       <c r="T94" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="U94" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0.31</v>
+      </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E95" t="n">
-        <v>134</v>
+        <v>1530</v>
       </c>
       <c r="F95" t="n">
-        <v>10.81</v>
+        <v>50.63</v>
       </c>
       <c r="G95" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>13.47</v>
+      </c>
+      <c r="H95" t="n">
+        <v>11.9</v>
+      </c>
       <c r="I95" t="n">
-        <v>11</v>
-      </c>
-      <c r="J95" t="inlineStr"/>
+        <v>50.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.36</v>
+      </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1520</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔、月營收轉負-19%</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R95" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S95" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="T95" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L95" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="M95" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R95" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S95" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="T95" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8084,20 +8090,20 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>408</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>7.96</v>
+        <v>6.69</v>
       </c>
       <c r="G96" t="n">
-        <v>4.59</v>
+        <v>1.27</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>110.7</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
@@ -8106,40 +8112,36 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>398.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>含金量-0.5差</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>55.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>-0.46</v>
+        <v>0.99</v>
       </c>
       <c r="R96" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="S96" t="n">
-        <v>210.4</v>
+        <v>13.7</v>
       </c>
       <c r="T96" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -8151,12 +8153,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8165,20 +8167,20 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E97" t="n">
-        <v>24.3</v>
+        <v>133</v>
       </c>
       <c r="F97" t="n">
-        <v>4.03</v>
+        <v>10.81</v>
       </c>
       <c r="G97" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>40.9</v>
+        <v>11</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -8187,40 +8189,36 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="M97" t="n">
-        <v>24.3</v>
+        <v>134</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>含金量0.4差</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>51.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.39</v>
+        <v>1.4</v>
       </c>
       <c r="R97" t="n">
-        <v>30.3</v>
+        <v>3.8</v>
       </c>
       <c r="S97" t="n">
-        <v>826.2</v>
+        <v>48.7</v>
       </c>
       <c r="T97" t="n">
-        <v>3.9</v>
+        <v>28.4</v>
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -8232,12 +8230,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8246,20 +8244,20 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>37.6</v>
+        <v>411.5</v>
       </c>
       <c r="F98" t="n">
-        <v>3.18</v>
+        <v>8.15</v>
       </c>
       <c r="G98" t="n">
-        <v>0.85</v>
+        <v>4.7</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>158.2</v>
+        <v>110.7</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
@@ -8268,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.05</v>
+        <v>0.86</v>
       </c>
       <c r="M98" t="n">
-        <v>38</v>
+        <v>408</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8280,23 +8278,23 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>ROE4低</t>
+          <t>含金量-0.5差</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>4.5</v>
+        <v>55.8</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.77</v>
+        <v>-0.46</v>
       </c>
       <c r="R98" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="S98" t="n">
-        <v>97.8</v>
+        <v>210.4</v>
       </c>
       <c r="T98" t="n">
-        <v>130</v>
+        <v>8.4</v>
       </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
@@ -8313,12 +8311,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8327,20 +8325,20 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>192.5</v>
+        <v>24.45</v>
       </c>
       <c r="F99" t="n">
-        <v>10.12</v>
+        <v>4.03</v>
       </c>
       <c r="G99" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>21.9</v>
+        <v>40.9</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
@@ -8349,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>6.94</v>
+        <v>0.62</v>
       </c>
       <c r="M99" t="n">
-        <v>180</v>
+        <v>24.3</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8361,28 +8359,28 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>含金量-1.3差</t>
+          <t>含金量0.4差</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>41.3</v>
+        <v>51.6</v>
       </c>
       <c r="Q99" t="n">
-        <v>-1.31</v>
+        <v>0.39</v>
       </c>
       <c r="R99" t="n">
-        <v>6.4</v>
+        <v>30.3</v>
       </c>
       <c r="S99" t="n">
-        <v>224.4</v>
+        <v>826.2</v>
       </c>
       <c r="T99" t="n">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -8394,33 +8392,35 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>407</v>
+        <v>38.8</v>
       </c>
       <c r="F100" t="n">
-        <v>5.64</v>
+        <v>3.18</v>
       </c>
       <c r="G100" t="n">
-        <v>1.9</v>
+        <v>0.85</v>
       </c>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>158.2</v>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-3.33</v>
+        <v>3.19</v>
       </c>
       <c r="M100" t="n">
-        <v>421</v>
+        <v>37.6</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8440,28 +8440,28 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>ROE4低</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>17.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.5</v>
+        <v>0.77</v>
       </c>
       <c r="R100" t="n">
-        <v>-6.1</v>
+        <v>5.2</v>
       </c>
       <c r="S100" t="n">
-        <v>730.1</v>
+        <v>97.8</v>
       </c>
       <c r="T100" t="n">
-        <v>45.2</v>
+        <v>130</v>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -8473,12 +8473,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8487,30 +8487,32 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
+        <v>193</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9.380000000000001</v>
+      </c>
       <c r="G101" t="n">
-        <v>0.63</v>
+        <v>3.91</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>13.7</v>
+        <v>21.9</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="M101" t="n">
-        <v>22.5</v>
+        <v>192.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8519,28 +8521,28 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>月營收轉負-5%</t>
+          <t>含金量-1.3差</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>10.3</v>
+        <v>41.3</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.03</v>
+        <v>-1.31</v>
       </c>
       <c r="R101" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="S101" t="n">
-        <v>-5.3</v>
+        <v>224.4</v>
       </c>
       <c r="T101" t="n">
-        <v>18.2</v>
+        <v>10.5</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -8700,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2740</v>
+        <v>2760</v>
       </c>
       <c r="F2" t="n">
-        <v>12.13</v>
+        <v>45.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.34</v>
+        <v>23.81</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8723,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.58</v>
+        <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>2620</v>
+        <v>2740</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8779,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="F3" t="n">
-        <v>12.64</v>
+        <v>26.06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.02</v>
+        <v>10.1</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8802,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.96</v>
+        <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>912</v>
+        <v>939</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8858,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2465</v>
+        <v>2445</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>33.14</v>
       </c>
       <c r="G4" t="n">
-        <v>4.11</v>
+        <v>10.85</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8881,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.6</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2505</v>
+        <v>2465</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8937,7 +8939,7 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F5" t="n">
         <v>10.74</v>
@@ -8960,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.82</v>
+        <v>0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>99.2</v>
+        <v>102</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9016,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>16.51</v>
+        <v>17.05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9039,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.28</v>
+        <v>-1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9095,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>34.5</v>
+        <v>34.55</v>
       </c>
       <c r="F7" t="n">
-        <v>9.9</v>
+        <v>6.91</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>1.34</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9118,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M7" t="n">
         <v>34.5</v>
@@ -9174,7 +9176,7 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>110.5</v>
+        <v>112.5</v>
       </c>
       <c r="F8" t="n">
         <v>11.19</v>
@@ -9197,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.07</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>114</v>
+        <v>110.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9253,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5</v>
+        <v>182.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.99</v>
+        <v>13.47</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54</v>
+        <v>3.41</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9276,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-3.71</v>
+        <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>188.5</v>
+        <v>181.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9332,7 +9334,7 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>43.9</v>
+        <v>43.85</v>
       </c>
       <c r="F10" t="n">
         <v>15.5</v>
@@ -9355,7 +9357,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="M10" t="n">
         <v>43.9</v>
@@ -9411,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="F11" t="n">
-        <v>10.27</v>
+        <v>38.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.83</v>
+        <v>13.01</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9434,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.16</v>
+        <v>-0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1295</v>
+        <v>1310</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9490,7 +9492,7 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="F12" t="n">
         <v>11.17</v>
@@ -9513,7 +9515,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M12" t="n">
         <v>506</v>
@@ -9569,7 +9571,7 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F13" t="n">
         <v>18.47</v>
@@ -9592,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>0.68</v>
       </c>
       <c r="M13" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9648,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>40.75</v>
+        <v>41.7</v>
       </c>
       <c r="F14" t="n">
-        <v>33.32</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9671,7 +9673,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M14" t="n">
         <v>40.75</v>
@@ -9727,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2750</v>
+        <v>2735</v>
       </c>
       <c r="F15" t="n">
-        <v>22.12</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>6.05</v>
+        <v>23.53</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9750,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.38</v>
+        <v>-0.55</v>
       </c>
       <c r="M15" t="n">
-        <v>2660</v>
+        <v>2750</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9810,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="F16" t="n">
-        <v>29.15</v>
+        <v>30.01</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>7.21</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9833,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.97</v>
+        <v>-1.92</v>
       </c>
       <c r="M16" t="n">
-        <v>1010</v>
+        <v>1040</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9893,7 +9895,7 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="F17" t="n">
         <v>6.55</v>
@@ -9916,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.22</v>
+        <v>0.45</v>
       </c>
       <c r="M17" t="n">
-        <v>89.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9976,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>73.8</v>
+        <v>76.2</v>
       </c>
       <c r="F18" t="n">
-        <v>26.57</v>
+        <v>7.98</v>
       </c>
       <c r="G18" t="n">
-        <v>1.21</v>
+        <v>1.86</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -9999,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.27</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>73.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10059,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>67.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>12.4</v>
+        <v>12.47</v>
       </c>
       <c r="G19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10082,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.6</v>
+        <v>1.94</v>
       </c>
       <c r="M19" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10142,7 +10144,7 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F20" t="n">
         <v>15.84</v>
@@ -10165,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="M20" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10225,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5200</v>
+        <v>5265</v>
       </c>
       <c r="F21" t="n">
-        <v>16.88</v>
+        <v>17.43</v>
       </c>
       <c r="G21" t="n">
-        <v>6.68</v>
+        <v>6.89</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10248,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.28</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>5035</v>
+        <v>5200</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10308,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>158.5</v>
+        <v>159</v>
       </c>
       <c r="F22" t="n">
-        <v>16.25</v>
+        <v>15.9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10331,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.63</v>
+        <v>0.32</v>
       </c>
       <c r="M22" t="n">
-        <v>159.5</v>
+        <v>158.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10391,7 +10393,7 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="F23" t="n">
         <v>50.63</v>
@@ -10414,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.4</v>
+        <v>0.66</v>
       </c>
       <c r="M23" t="n">
-        <v>1470</v>
+        <v>1520</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10605,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>156.5</v>
+        <v>162</v>
       </c>
       <c r="F2" t="n">
-        <v>16.87</v>
+        <v>16.97</v>
       </c>
       <c r="G2" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10628,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.64</v>
+        <v>3.51</v>
       </c>
       <c r="M2" t="n">
-        <v>155.5</v>
+        <v>156.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10684,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="F3" t="n">
-        <v>11.53</v>
+        <v>22.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.01</v>
+        <v>5.45</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10707,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>-1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10763,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>121.5</v>
+        <v>123.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.39</v>
+        <v>17.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10786,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.41</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10842,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>363.5</v>
+        <v>372.5</v>
       </c>
       <c r="F5" t="n">
-        <v>9.84</v>
+        <v>35.46</v>
       </c>
       <c r="G5" t="n">
-        <v>1.23</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10865,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.45</v>
+        <v>2.48</v>
       </c>
       <c r="M5" t="n">
-        <v>348</v>
+        <v>363.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10921,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>19.52</v>
+        <v>19.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10944,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.26</v>
+        <v>-0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>92.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11000,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>153.5</v>
+        <v>155</v>
       </c>
       <c r="F7" t="n">
-        <v>20.26</v>
+        <v>20.94</v>
       </c>
       <c r="G7" t="n">
-        <v>5.53</v>
+        <v>5.72</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11023,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.37</v>
+        <v>0.98</v>
       </c>
       <c r="M7" t="n">
-        <v>148.5</v>
+        <v>153.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11083,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>239</v>
+        <v>240.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.94</v>
+        <v>16.97</v>
       </c>
       <c r="G8" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11106,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.63</v>
+        <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11162,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F9" t="n">
-        <v>57.36</v>
+        <v>62.86</v>
       </c>
       <c r="G9" t="n">
-        <v>29.86</v>
+        <v>32.72</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11183,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9.59</v>
+        <v>8.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1095</v>
+        <v>1200</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11243,7 +11245,7 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>67.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>12.7</v>
@@ -11266,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>66.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11457,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1415</v>
+        <v>1380</v>
       </c>
       <c r="F2" t="n">
-        <v>31.12</v>
+        <v>100.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>28.33</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11480,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-9</v>
+        <v>-2.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1555</v>
+        <v>1415</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11539,7 +11541,7 @@
         <v>39.85</v>
       </c>
       <c r="F3" t="n">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
@@ -11559,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.75</v>
+        <v>39.85</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11615,7 +11617,7 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>146.5</v>
       </c>
       <c r="F4" t="n">
         <v>16.8</v>
@@ -11638,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11694,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>7255</v>
+        <v>7380</v>
       </c>
       <c r="F5" t="n">
-        <v>178.25</v>
+        <v>193.16</v>
       </c>
       <c r="G5" t="n">
-        <v>41.64</v>
+        <v>45.12</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11717,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8.359999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>6695</v>
+        <v>7255</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11777,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>118.5</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>19.18</v>
+        <v>24.04</v>
       </c>
       <c r="G6" t="n">
-        <v>5.08</v>
+        <v>3.94</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11800,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.42</v>
+        <v>-1.69</v>
       </c>
       <c r="M6" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11856,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>121.5</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>35.31</v>
+        <v>35.42</v>
       </c>
       <c r="G7" t="n">
-        <v>0.85</v>
+        <v>5.03</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11879,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.19</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>125.5</v>
+        <v>121.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11939,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>197</v>
+        <v>216.5</v>
       </c>
       <c r="F8" t="n">
-        <v>31.15</v>
+        <v>30.08</v>
       </c>
       <c r="G8" t="n">
-        <v>6.04</v>
+        <v>5.83</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11962,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.43</v>
+        <v>9.9</v>
       </c>
       <c r="M8" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12022,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9</v>
+        <v>26.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12045,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.48</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12101,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F10" t="n">
-        <v>19.05</v>
+        <v>19.23</v>
       </c>
       <c r="G10" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12124,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.95</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12180,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1390</v>
+        <v>1440</v>
       </c>
       <c r="F11" t="n">
-        <v>33.29</v>
+        <v>30.43</v>
       </c>
       <c r="G11" t="n">
-        <v>6.25</v>
+        <v>5.47</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12203,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12259,7 +12261,7 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>173</v>
+        <v>177.5</v>
       </c>
       <c r="F12" t="n">
         <v>12.81</v>
@@ -12282,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12342,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>221.5</v>
+        <v>219</v>
       </c>
       <c r="F13" t="n">
-        <v>31.98</v>
+        <v>32.57</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12365,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.91</v>
+        <v>-1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>219.5</v>
+        <v>221.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12428,10 +12430,10 @@
         <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>21.47</v>
+        <v>28.03</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12448,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12504,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>228.5</v>
+        <v>231</v>
       </c>
       <c r="F15" t="n">
-        <v>27.75</v>
+        <v>20.83</v>
       </c>
       <c r="G15" t="n">
-        <v>10.19</v>
+        <v>5.11</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12527,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="M15" t="n">
-        <v>223.5</v>
+        <v>228.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12587,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>5330</v>
+        <v>5040</v>
       </c>
       <c r="F16" t="n">
-        <v>59.03</v>
+        <v>160.35</v>
       </c>
       <c r="G16" t="n">
-        <v>10.24</v>
+        <v>48.98</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12610,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.65</v>
+        <v>-5.44</v>
       </c>
       <c r="M16" t="n">
-        <v>5045</v>
+        <v>5330</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12801,7 +12803,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1970</v>
+        <v>2075</v>
       </c>
       <c r="F2" t="n">
         <v>19.02</v>
@@ -12824,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.01</v>
+        <v>5.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1990</v>
+        <v>1970</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12880,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>699</v>
+        <v>721</v>
       </c>
       <c r="F3" t="n">
-        <v>21.69</v>
+        <v>22.23</v>
       </c>
       <c r="G3" t="n">
-        <v>11.37</v>
+        <v>11.65</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12903,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.49</v>
+        <v>3.15</v>
       </c>
       <c r="M3" t="n">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12963,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3475</v>
+        <v>3420</v>
       </c>
       <c r="F4" t="n">
-        <v>24.45</v>
+        <v>96.13</v>
       </c>
       <c r="G4" t="n">
-        <v>1.69</v>
+        <v>24.07</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12986,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.21</v>
+        <v>-1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3400</v>
+        <v>3475</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13042,7 +13044,7 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5655</v>
+        <v>6080</v>
       </c>
       <c r="F5" t="n">
         <v>10.01</v>
@@ -13065,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.17</v>
+        <v>7.52</v>
       </c>
       <c r="M5" t="n">
-        <v>5535</v>
+        <v>5655</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13121,7 +13123,7 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="F6" t="n">
         <v>62.26</v>
@@ -13144,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13204,7 +13206,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
         <v>12.12</v>
@@ -13227,7 +13229,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="M7" t="n">
         <v>103</v>
@@ -13283,7 +13285,7 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>191.5</v>
+        <v>197.5</v>
       </c>
       <c r="F8" t="n">
         <v>13.63</v>
@@ -13306,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.03</v>
+        <v>3.13</v>
       </c>
       <c r="M8" t="n">
-        <v>193.5</v>
+        <v>191.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13366,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>39.35</v>
+        <v>15.49</v>
       </c>
       <c r="G9" t="n">
-        <v>4.11</v>
+        <v>3.26</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13389,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
         <v>105</v>
@@ -13445,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="F10" t="n">
-        <v>37.94</v>
+        <v>19.52</v>
       </c>
       <c r="G10" t="n">
-        <v>4.43</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13468,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.47</v>
+        <v>-1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13551,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>238.5</v>
+        <v>238</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13611,7 +13613,7 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4895</v>
+        <v>4650</v>
       </c>
       <c r="F12" t="n">
         <v>19.34</v>
@@ -13634,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>-5.01</v>
       </c>
       <c r="M12" t="n">
-        <v>4450</v>
+        <v>4895</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,7 +557,7 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1425</v>
+        <v>1335</v>
       </c>
       <c r="F2" t="n">
         <v>101.64</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.26</v>
+        <v>-6.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1380</v>
+        <v>1425</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,7 +636,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.65</v>
+        <v>39.35</v>
       </c>
       <c r="F3" t="n">
         <v>11.2</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>39.85</v>
+        <v>39.65</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>146.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.23</v>
+        <v>16.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.71</v>
+        <v>-1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>146.5</v>
+        <v>149</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,7 +794,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6855</v>
+        <v>6310</v>
       </c>
       <c r="F5" t="n">
         <v>182.51</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-7.11</v>
+        <v>-7.95</v>
       </c>
       <c r="M5" t="n">
-        <v>7380</v>
+        <v>6855</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>117.5</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.83</v>
+        <v>23.63</v>
       </c>
       <c r="G6" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.86</v>
+        <v>-0.85</v>
       </c>
       <c r="M6" t="n">
-        <v>116.5</v>
+        <v>117.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>126.5</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>36.88</v>
+        <v>35.28</v>
       </c>
       <c r="G7" t="n">
-        <v>5.24</v>
+        <v>5.01</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>-4.35</v>
       </c>
       <c r="M7" t="n">
-        <v>123</v>
+        <v>126.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>238</v>
+        <v>214.5</v>
       </c>
       <c r="F8" t="n">
-        <v>36.34</v>
+        <v>32.75</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04</v>
+        <v>6.35</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9.93</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>216.5</v>
+        <v>238</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F10" t="n">
         <v>20.19</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M10" t="n">
         <v>168</v>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="n">
-        <v>30.32</v>
+        <v>30.21</v>
       </c>
       <c r="G11" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-3.82</v>
+        <v>-0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>1440</v>
+        <v>1385</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>175.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25.52</v>
+        <v>24.21</v>
       </c>
       <c r="G12" t="n">
-        <v>4.68</v>
+        <v>4.44</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.23</v>
+        <v>-5.14</v>
       </c>
       <c r="M12" t="n">
-        <v>177.5</v>
+        <v>185</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F13" t="n">
-        <v>32.94</v>
+        <v>31.32</v>
       </c>
       <c r="G13" t="n">
-        <v>5.77</v>
+        <v>5.49</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.28</v>
+        <v>-4.91</v>
       </c>
       <c r="M13" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>28.13</v>
+        <v>28.03</v>
       </c>
       <c r="G14" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>141</v>
+        <v>141.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4605</v>
+        <v>4480</v>
       </c>
       <c r="F16" t="n">
-        <v>138.54</v>
+        <v>134.78</v>
       </c>
       <c r="G16" t="n">
-        <v>42.31</v>
+        <v>41.17</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-8.630000000000001</v>
+        <v>-2.71</v>
       </c>
       <c r="M16" t="n">
-        <v>5040</v>
+        <v>4605</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1595</v>
+        <v>1540</v>
       </c>
       <c r="F17" t="n">
         <v>60.17</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-2.74</v>
+        <v>-3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>1640</v>
+        <v>1595</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7785</v>
+        <v>8260</v>
       </c>
       <c r="F18" t="n">
-        <v>68.62</v>
+        <v>72.81</v>
       </c>
       <c r="G18" t="n">
-        <v>23.53</v>
+        <v>24.97</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-2.69</v>
+        <v>6.1</v>
       </c>
       <c r="M18" t="n">
-        <v>8000</v>
+        <v>7785</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>745</v>
+        <v>700</v>
       </c>
       <c r="F19" t="n">
         <v>73.47</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.46</v>
+        <v>-6.04</v>
       </c>
       <c r="M19" t="n">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>88.8</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
         <v>64.34999999999999</v>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1.44</v>
+        <v>-5.41</v>
       </c>
       <c r="M20" t="n">
-        <v>90.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>8915</v>
+        <v>8025</v>
       </c>
       <c r="F21" t="n">
         <v>182.68</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-9.949999999999999</v>
+        <v>-9.98</v>
       </c>
       <c r="M21" t="n">
-        <v>9900</v>
+        <v>8915</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>1965</v>
       </c>
       <c r="F22" t="n">
-        <v>68.75</v>
+        <v>61.97</v>
       </c>
       <c r="G22" t="n">
-        <v>33.3</v>
+        <v>30.01</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-3.75</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>2265</v>
+        <v>2180</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="F23" t="n">
-        <v>46.82</v>
+        <v>42.66</v>
       </c>
       <c r="G23" t="n">
-        <v>6.94</v>
+        <v>6.32</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-4.71</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1630</v>
+        <v>1575</v>
       </c>
       <c r="F24" t="n">
         <v>117.77</v>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-8.94</v>
+        <v>-3.37</v>
       </c>
       <c r="M24" t="n">
-        <v>1790</v>
+        <v>1630</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2381,12 +2381,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2395,20 +2395,20 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>176</v>
+        <v>38.4</v>
       </c>
       <c r="F25" t="n">
-        <v>36.29</v>
+        <v>142.22</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96</v>
+        <v>3.31</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>12.4</v>
+        <v>158.2</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>177</v>
+        <v>42.65</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2429,23 +2429,23 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ROE5低</t>
+          <t>ROE4低</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>0.77</v>
       </c>
       <c r="R25" t="n">
-        <v>22.1</v>
+        <v>5.2</v>
       </c>
       <c r="S25" t="n">
-        <v>14.6</v>
+        <v>97.8</v>
       </c>
       <c r="T25" t="n">
-        <v>34.2</v>
+        <v>130</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
@@ -2462,12 +2462,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2476,21 +2476,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>42.65</v>
+        <v>1905</v>
       </c>
       <c r="F26" t="n">
-        <v>157.96</v>
+        <v>262.81</v>
       </c>
       <c r="G26" t="n">
-        <v>3.68</v>
+        <v>43.65</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>158.2</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2498,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9.92</v>
+        <v>-4.75</v>
       </c>
       <c r="M26" t="n">
-        <v>38.8</v>
+        <v>2000</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2510,28 +2508,28 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>ROE4低</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="R26" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>97.8</v>
+        <v>118.8</v>
       </c>
       <c r="T26" t="n">
-        <v>130</v>
+        <v>310.9</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2543,12 +2541,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2557,19 +2555,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>2000</v>
+        <v>651</v>
       </c>
       <c r="F27" t="n">
-        <v>262.81</v>
+        <v>60.45</v>
       </c>
       <c r="G27" t="n">
-        <v>43.65</v>
+        <v>8.15</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>12.6</v>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-4.76</v>
+        <v>-4.12</v>
       </c>
       <c r="M27" t="n">
-        <v>2100</v>
+        <v>679</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>16.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.13</v>
+        <v>3.26</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="S27" t="n">
-        <v>118.8</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>310.9</v>
+        <v>62.1</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
@@ -2622,12 +2622,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2636,21 +2636,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>679</v>
+        <v>1495</v>
       </c>
       <c r="F28" t="n">
-        <v>63.05</v>
+        <v>93.73</v>
       </c>
       <c r="G28" t="n">
-        <v>8.5</v>
+        <v>16.14</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -2658,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-0.44</v>
+        <v>3.46</v>
       </c>
       <c r="M28" t="n">
-        <v>682</v>
+        <v>1445</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2670,28 +2668,28 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>12.8</v>
+        <v>17.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.26</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>3.2</v>
+        <v>120.6</v>
       </c>
       <c r="S28" t="n">
-        <v>28.6</v>
+        <v>108.5</v>
       </c>
       <c r="T28" t="n">
-        <v>62.1</v>
+        <v>65.2</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2703,12 +2701,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2720,16 +2718,18 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>1445</v>
+        <v>428</v>
       </c>
       <c r="F29" t="n">
-        <v>90.59999999999999</v>
+        <v>82.64</v>
       </c>
       <c r="G29" t="n">
-        <v>15.6</v>
+        <v>15.74</v>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>27.5</v>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.58</v>
+        <v>-6.35</v>
       </c>
       <c r="M29" t="n">
-        <v>1395</v>
+        <v>457</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2753,24 +2753,24 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>17.2</v>
+        <v>18.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="R29" t="n">
-        <v>120.6</v>
+        <v>50.3</v>
       </c>
       <c r="S29" t="n">
-        <v>108.5</v>
+        <v>21.1</v>
       </c>
       <c r="T29" t="n">
-        <v>65.2</v>
+        <v>99.8</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2799,17 +2799,17 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>457</v>
+        <v>2835</v>
       </c>
       <c r="F30" t="n">
-        <v>82.64</v>
+        <v>89.91</v>
       </c>
       <c r="G30" t="n">
-        <v>15.74</v>
+        <v>10.25</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>27.5</v>
+        <v>454.2</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-2.45</v>
+        <v>-7.5</v>
       </c>
       <c r="M30" t="n">
-        <v>468.5</v>
+        <v>3065</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2830,23 +2830,23 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>18.9</v>
+        <v>14.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="R30" t="n">
-        <v>50.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>21.1</v>
+        <v>34.1</v>
       </c>
       <c r="T30" t="n">
-        <v>99.8</v>
+        <v>95.3</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
@@ -2863,35 +2863,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>3065</v>
+        <v>495</v>
       </c>
       <c r="F31" t="n">
-        <v>89.91</v>
+        <v>147.32</v>
       </c>
       <c r="G31" t="n">
-        <v>10.25</v>
+        <v>13.83</v>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>454.2</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
@@ -2899,10 +2897,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-7.68</v>
+        <v>-4.81</v>
       </c>
       <c r="M31" t="n">
-        <v>3320</v>
+        <v>520</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2911,23 +2909,23 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>14.1</v>
+        <v>10.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="S31" t="n">
-        <v>34.1</v>
+        <v>49.9</v>
       </c>
       <c r="T31" t="n">
-        <v>95.3</v>
+        <v>165.8</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -2944,12 +2942,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2958,19 +2956,21 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>520</v>
+        <v>243.5</v>
       </c>
       <c r="F32" t="n">
-        <v>154.76</v>
+        <v>35.91</v>
       </c>
       <c r="G32" t="n">
-        <v>14.53</v>
+        <v>3.37</v>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>-15.3</v>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -2978,35 +2978,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-1.89</v>
+        <v>-5.8</v>
       </c>
       <c r="M32" t="n">
-        <v>530</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>258.5</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.73</v>
+        <v>0.72</v>
       </c>
       <c r="R32" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="S32" t="n">
-        <v>49.9</v>
+        <v>34.8</v>
       </c>
       <c r="T32" t="n">
-        <v>165.8</v>
+        <v>34.5</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
@@ -3016,19 +3012,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3037,21 +3033,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>258.5</v>
+        <v>403</v>
       </c>
       <c r="F33" t="n">
-        <v>38.13</v>
+        <v>36.08</v>
       </c>
       <c r="G33" t="n">
-        <v>3.57</v>
+        <v>6.47</v>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>-15.3</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -3059,31 +3053,35 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.19</v>
+        <v>-4.16</v>
       </c>
       <c r="M33" t="n">
-        <v>258</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
+        <v>420.5</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>9.4</v>
+        <v>17.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>13.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S33" t="n">
-        <v>34.8</v>
+        <v>730.1</v>
       </c>
       <c r="T33" t="n">
-        <v>34.5</v>
+        <v>45.2</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
@@ -3093,19 +3091,19 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3114,19 +3112,21 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>420.5</v>
+        <v>496.5</v>
       </c>
       <c r="F34" t="n">
-        <v>37.65</v>
+        <v>38.52</v>
       </c>
       <c r="G34" t="n">
-        <v>6.76</v>
+        <v>8.69</v>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -3134,35 +3134,31 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.69</v>
+        <v>-3.59</v>
       </c>
       <c r="M34" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>0.77</v>
       </c>
       <c r="R34" t="n">
-        <v>-6.1</v>
+        <v>4.9</v>
       </c>
       <c r="S34" t="n">
-        <v>730.1</v>
+        <v>32.1</v>
       </c>
       <c r="T34" t="n">
-        <v>45.2</v>
+        <v>38.6</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3172,19 +3168,19 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3193,20 +3189,20 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>515</v>
+        <v>905</v>
       </c>
       <c r="F35" t="n">
-        <v>39.95</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>9.01</v>
+        <v>11.15</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>-2.9</v>
+        <v>-19.8</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -3215,31 +3211,35 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.15</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>521</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>1005</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.77</v>
+        <v>1.24</v>
       </c>
       <c r="R35" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="S35" t="n">
-        <v>32.1</v>
+        <v>47.5</v>
       </c>
       <c r="T35" t="n">
-        <v>38.6</v>
+        <v>53.2</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
@@ -3249,19 +3249,19 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3270,21 +3270,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>1005</v>
+        <v>174</v>
       </c>
       <c r="F36" t="n">
-        <v>79.13</v>
+        <v>51.63</v>
       </c>
       <c r="G36" t="n">
-        <v>12.38</v>
+        <v>6.71</v>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>-19.8</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -3292,10 +3290,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-3.83</v>
+        <v>-4.92</v>
       </c>
       <c r="M36" t="n">
-        <v>1045</v>
+        <v>183</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3304,23 +3302,23 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="R36" t="n">
-        <v>5.7</v>
+        <v>-2.7</v>
       </c>
       <c r="S36" t="n">
-        <v>47.5</v>
+        <v>182</v>
       </c>
       <c r="T36" t="n">
-        <v>53.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
@@ -3337,33 +3335,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>183</v>
+        <v>4030</v>
       </c>
       <c r="F37" t="n">
-        <v>54.3</v>
+        <v>64.22</v>
       </c>
       <c r="G37" t="n">
-        <v>7.06</v>
+        <v>16.48</v>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>16.8</v>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>184.5</v>
+        <v>4125</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3383,23 +3383,23 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>11.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.7</v>
+        <v>4.8</v>
       </c>
       <c r="S37" t="n">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>65.90000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
@@ -3416,93 +3416,91 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>4125</v>
+        <v>1890</v>
       </c>
       <c r="F38" t="n">
-        <v>65.73999999999999</v>
+        <v>69.69</v>
       </c>
       <c r="G38" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>16.39</v>
+      </c>
+      <c r="H38" t="n">
+        <v>59.1</v>
+      </c>
       <c r="I38" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>34.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.32</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1995</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R38" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4195</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3511,25 +3509,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>1995</v>
+        <v>725</v>
       </c>
       <c r="F39" t="n">
-        <v>73.56</v>
+        <v>23.43</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3</v>
+        <v>12.29</v>
       </c>
       <c r="H39" t="n">
-        <v>59.1</v>
+        <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>34.1</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3537,51 +3535,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-3.86</v>
+        <v>-1.63</v>
       </c>
       <c r="M39" t="n">
-        <v>2075</v>
+        <v>737</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債80%)</t>
+        </is>
+      </c>
       <c r="P39" t="n">
-        <v>22.3</v>
+        <v>52.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="R39" t="n">
-        <v>15.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S39" t="n">
-        <v>43.7</v>
+        <v>19.2</v>
       </c>
       <c r="T39" t="n">
-        <v>79.3</v>
+        <v>20.9</v>
       </c>
       <c r="U39" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3590,25 +3592,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>737</v>
+        <v>3195</v>
       </c>
       <c r="F40" t="n">
-        <v>23.43</v>
+        <v>88.38</v>
       </c>
       <c r="G40" t="n">
-        <v>12.29</v>
+        <v>22.13</v>
       </c>
       <c r="H40" t="n">
-        <v>19</v>
+        <v>70.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="J40" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3616,55 +3618,51 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.22</v>
+        <v>-3.77</v>
       </c>
       <c r="M40" t="n">
-        <v>721</v>
+        <v>3320</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>⚠️高槓桿(負債80%)</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>52.4</v>
+        <v>25</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.91</v>
+        <v>0.92</v>
       </c>
       <c r="R40" t="n">
-        <v>9.699999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="S40" t="n">
-        <v>19.2</v>
+        <v>37.7</v>
       </c>
       <c r="T40" t="n">
-        <v>20.9</v>
+        <v>104.6</v>
       </c>
       <c r="U40" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3676,22 +3674,22 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>3320</v>
+        <v>5220</v>
       </c>
       <c r="F41" t="n">
-        <v>91.84</v>
+        <v>113.23</v>
       </c>
       <c r="G41" t="n">
-        <v>23</v>
+        <v>39.01</v>
       </c>
       <c r="H41" t="n">
-        <v>70.2</v>
+        <v>75.3</v>
       </c>
       <c r="I41" t="n">
-        <v>49</v>
+        <v>59.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3699,34 +3697,34 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-2.92</v>
+        <v>-4.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3420</v>
+        <v>5475</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="R41" t="n">
-        <v>23.2</v>
+        <v>25.1</v>
       </c>
       <c r="S41" t="n">
-        <v>37.7</v>
+        <v>114.6</v>
       </c>
       <c r="T41" t="n">
-        <v>104.6</v>
+        <v>120.3</v>
       </c>
       <c r="U41" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -3738,12 +3736,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3752,25 +3750,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>5475</v>
+        <v>748</v>
       </c>
       <c r="F42" t="n">
-        <v>118.76</v>
+        <v>51.41</v>
       </c>
       <c r="G42" t="n">
-        <v>40.92</v>
+        <v>28.68</v>
       </c>
       <c r="H42" t="n">
-        <v>75.3</v>
+        <v>47.5</v>
       </c>
       <c r="I42" t="n">
-        <v>59.7</v>
+        <v>20.2</v>
       </c>
       <c r="J42" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3778,34 +3776,38 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-9.949999999999999</v>
+        <v>-3.23</v>
       </c>
       <c r="M42" t="n">
-        <v>6080</v>
+        <v>773</v>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>月營收轉負-9%</t>
+        </is>
+      </c>
       <c r="P42" t="n">
-        <v>34.5</v>
+        <v>53.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.76</v>
+        <v>1.12</v>
       </c>
       <c r="R42" t="n">
-        <v>25.1</v>
+        <v>28.3</v>
       </c>
       <c r="S42" t="n">
-        <v>114.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>120.3</v>
+        <v>57.1</v>
       </c>
       <c r="U42" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -3817,12 +3819,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3831,25 +3833,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>773</v>
+        <v>102</v>
       </c>
       <c r="F43" t="n">
-        <v>53.13</v>
+        <v>12.24</v>
       </c>
       <c r="G43" t="n">
-        <v>29.64</v>
+        <v>1.92</v>
       </c>
       <c r="H43" t="n">
-        <v>47.5</v>
+        <v>11</v>
       </c>
       <c r="I43" t="n">
-        <v>20.2</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3857,79 +3859,75 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>773</v>
+        <v>104</v>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>53.6</v>
+        <v>17.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.12</v>
+        <v>2.11</v>
       </c>
       <c r="R43" t="n">
-        <v>28.3</v>
+        <v>5.3</v>
       </c>
       <c r="S43" t="n">
-        <v>-9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="T43" t="n">
-        <v>57.1</v>
+        <v>11.6</v>
       </c>
       <c r="U43" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>104</v>
+        <v>193.5</v>
       </c>
       <c r="F44" t="n">
-        <v>12.24</v>
+        <v>15.3</v>
       </c>
       <c r="G44" t="n">
-        <v>1.92</v>
+        <v>2.71</v>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="J44" t="n">
         <v>2.02</v>
@@ -3940,34 +3938,38 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
       <c r="M44" t="n">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+        </is>
+      </c>
       <c r="P44" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R44" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="S44" t="n">
-        <v>7.7</v>
+        <v>4.2</v>
       </c>
       <c r="T44" t="n">
-        <v>11.6</v>
+        <v>14.4</v>
       </c>
       <c r="U44" t="n">
         <v>2.02</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -3979,12 +3981,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3993,25 +3995,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="F45" t="n">
-        <v>15.57</v>
+        <v>15.49</v>
       </c>
       <c r="G45" t="n">
-        <v>2.76</v>
+        <v>3.26</v>
       </c>
       <c r="H45" t="n">
-        <v>13.4</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4019,55 +4021,51 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.25</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>197.5</v>
+        <v>106</v>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
-        </is>
-      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>17.6</v>
+        <v>20.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="R45" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="S45" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="T45" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="U45" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4076,25 +4074,25 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>106</v>
+        <v>609</v>
       </c>
       <c r="F46" t="n">
-        <v>15.63</v>
+        <v>18.45</v>
       </c>
       <c r="G46" t="n">
-        <v>3.29</v>
+        <v>2.63</v>
       </c>
       <c r="H46" t="n">
-        <v>16</v>
+        <v>21.4</v>
       </c>
       <c r="I46" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4102,34 +4100,38 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-0.93</v>
+        <v>-6.74</v>
       </c>
       <c r="M46" t="n">
-        <v>107</v>
+        <v>653</v>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P46" t="n">
-        <v>20.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="R46" t="n">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="S46" t="n">
-        <v>1.4</v>
+        <v>30.2</v>
       </c>
       <c r="T46" t="n">
-        <v>17.2</v>
+        <v>23.4</v>
       </c>
       <c r="U46" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -4141,12 +4143,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4155,25 +4157,25 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>653</v>
+        <v>230</v>
       </c>
       <c r="F47" t="n">
-        <v>19.79</v>
+        <v>34.28</v>
       </c>
       <c r="G47" t="n">
-        <v>2.82</v>
+        <v>3.16</v>
       </c>
       <c r="H47" t="n">
-        <v>21.4</v>
+        <v>30.9</v>
       </c>
       <c r="I47" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4181,34 +4183,34 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.67</v>
+        <v>-4.76</v>
       </c>
       <c r="M47" t="n">
-        <v>636</v>
+        <v>241.5</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>含金量0.5差</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>14.3</v>
+        <v>9.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.02</v>
+        <v>0.49</v>
       </c>
       <c r="R47" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="S47" t="n">
-        <v>30.2</v>
+        <v>8.4</v>
       </c>
       <c r="T47" t="n">
-        <v>23.4</v>
+        <v>36.5</v>
       </c>
       <c r="U47" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4217,46 +4219,46 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>241.5</v>
+        <v>4035</v>
       </c>
       <c r="F48" t="n">
-        <v>35.99</v>
+        <v>59.14</v>
       </c>
       <c r="G48" t="n">
-        <v>3.31</v>
+        <v>7.62</v>
       </c>
       <c r="H48" t="n">
-        <v>30.9</v>
+        <v>51.7</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>23.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4264,138 +4266,132 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>-4.27</v>
       </c>
       <c r="M48" t="n">
-        <v>238</v>
+        <v>4215</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>含金量0.5差</t>
+          <t>含金量0.3差、月營收轉負-34%</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>9.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="R48" t="n">
-        <v>7.6</v>
+        <v>31.2</v>
       </c>
       <c r="S48" t="n">
-        <v>8.4</v>
+        <v>-33.5</v>
       </c>
       <c r="T48" t="n">
-        <v>36.5</v>
+        <v>63.8</v>
       </c>
       <c r="U48" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>4215</v>
+        <v>419</v>
       </c>
       <c r="F49" t="n">
-        <v>61.78</v>
+        <v>23.58</v>
       </c>
       <c r="G49" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="H49" t="n">
-        <v>51.7</v>
-      </c>
+        <v>6.98</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.73</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-9.35</v>
+        <v>-3.9</v>
       </c>
       <c r="M49" t="n">
-        <v>4650</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
-        </is>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>12.9</v>
+        <v>29.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.26</v>
+        <v>1.09</v>
       </c>
       <c r="R49" t="n">
-        <v>31.2</v>
+        <v>24.2</v>
       </c>
       <c r="S49" t="n">
-        <v>-33.5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.73</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4404,20 +4400,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E50" t="n">
-        <v>436</v>
+        <v>175</v>
       </c>
       <c r="F50" t="n">
-        <v>23.58</v>
+        <v>21.26</v>
       </c>
       <c r="G50" t="n">
-        <v>6.98</v>
+        <v>4.02</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>49</v>
+        <v>57.1</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4426,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-2.02</v>
+        <v>-1.96</v>
       </c>
       <c r="M50" t="n">
-        <v>445</v>
+        <v>178.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4438,24 +4434,24 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>29.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="R50" t="n">
-        <v>24.2</v>
+        <v>11.1</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="T50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4467,34 +4463,34 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E51" t="n">
-        <v>178.5</v>
+        <v>131</v>
       </c>
       <c r="F51" t="n">
-        <v>21.69</v>
+        <v>29.98</v>
       </c>
       <c r="G51" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>57.1</v>
+        <v>11</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4503,10 +4499,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.13</v>
+        <v>-3.68</v>
       </c>
       <c r="M51" t="n">
-        <v>176.5</v>
+        <v>136</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4515,24 +4511,24 @@
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>18.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="R51" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>48.7</v>
       </c>
       <c r="T51" t="n">
-        <v>22</v>
+        <v>28.4</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4544,12 +4540,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4561,17 +4557,17 @@
         <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="F52" t="n">
-        <v>31.12</v>
+        <v>20.12</v>
       </c>
       <c r="G52" t="n">
-        <v>3.19</v>
+        <v>1.9</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4580,36 +4576,40 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.26</v>
+        <v>-5.31</v>
       </c>
       <c r="M52" t="n">
-        <v>133</v>
+        <v>103.5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="R52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>48.7</v>
+        <v>-2.7</v>
       </c>
       <c r="T52" t="n">
-        <v>28.4</v>
+        <v>20.3</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4635,20 +4635,20 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E53" t="n">
-        <v>103.5</v>
+        <v>168.5</v>
       </c>
       <c r="F53" t="n">
-        <v>21.25</v>
+        <v>34.74</v>
       </c>
       <c r="G53" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.98</v>
+        <v>-4.26</v>
       </c>
       <c r="M53" t="n">
-        <v>102.5</v>
+        <v>176</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4669,23 +4669,23 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S53" t="n">
-        <v>-2.7</v>
+        <v>14.6</v>
       </c>
       <c r="T53" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
@@ -4719,7 +4719,7 @@
         <v>76</v>
       </c>
       <c r="E54" t="n">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="F54" t="n">
         <v>27.32</v>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.39</v>
+        <v>-7.79</v>
       </c>
       <c r="M54" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>235.5</v>
+        <v>232</v>
       </c>
       <c r="F55" t="n">
         <v>21.39</v>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.21</v>
+        <v>-1.49</v>
       </c>
       <c r="M55" t="n">
-        <v>235</v>
+        <v>235.5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         <v>61</v>
       </c>
       <c r="E56" t="n">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="F56" t="n">
-        <v>27.68</v>
+        <v>27.93</v>
       </c>
       <c r="G56" t="n">
-        <v>8.77</v>
+        <v>8.85</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
       <c r="M56" t="n">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>144.5</v>
+        <v>136</v>
       </c>
       <c r="F57" t="n">
         <v>32.47</v>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.35</v>
+        <v>-5.88</v>
       </c>
       <c r="M57" t="n">
-        <v>144</v>
+        <v>144.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5035,13 +5035,13 @@
         <v>51</v>
       </c>
       <c r="E58" t="n">
-        <v>4135</v>
+        <v>3890</v>
       </c>
       <c r="F58" t="n">
-        <v>25.81</v>
+        <v>24.28</v>
       </c>
       <c r="G58" t="n">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-2.25</v>
+        <v>-5.93</v>
       </c>
       <c r="M58" t="n">
-        <v>4230</v>
+        <v>4135</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5099,93 +5099,91 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="E59" t="n">
-        <v>52.7</v>
+        <v>562</v>
       </c>
       <c r="F59" t="n">
-        <v>20.04</v>
+        <v>35.8</v>
       </c>
       <c r="G59" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>7.09</v>
+      </c>
+      <c r="H59" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I59" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1.13</v>
+        <v>-1.4</v>
       </c>
       <c r="M59" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
-        </is>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>11.5</v>
+        <v>19.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.58</v>
+        <v>1.94</v>
       </c>
       <c r="R59" t="n">
-        <v>-2.2</v>
+        <v>10.6</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T59" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5194,25 +5192,25 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E60" t="n">
-        <v>570</v>
+        <v>808</v>
       </c>
       <c r="F60" t="n">
-        <v>36.31</v>
+        <v>54.78</v>
       </c>
       <c r="G60" t="n">
-        <v>7.19</v>
+        <v>8.5</v>
       </c>
       <c r="H60" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I60" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J60" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5220,78 +5218,78 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-3.06</v>
+        <v>-6.05</v>
       </c>
       <c r="M60" t="n">
-        <v>588</v>
+        <v>860</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R60" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S60" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T60" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U60" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E61" t="n">
-        <v>860</v>
+        <v>78.5</v>
       </c>
       <c r="F61" t="n">
-        <v>58.31</v>
+        <v>19.24</v>
       </c>
       <c r="G61" t="n">
-        <v>9.050000000000001</v>
+        <v>3.29</v>
       </c>
       <c r="H61" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I61" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J61" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5299,30 +5297,30 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.06</v>
+        <v>-3.09</v>
       </c>
       <c r="M61" t="n">
-        <v>851</v>
+        <v>81</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R61" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S61" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T61" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U61" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -5331,19 +5329,19 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5352,25 +5350,25 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E62" t="n">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="F62" t="n">
-        <v>19.85</v>
+        <v>15.68</v>
       </c>
       <c r="G62" t="n">
-        <v>3.39</v>
+        <v>1.7</v>
       </c>
       <c r="H62" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I62" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J62" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5378,34 +5376,34 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>8</v>
+        <v>-0.3</v>
       </c>
       <c r="M62" t="n">
-        <v>75</v>
+        <v>166.5</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R62" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S62" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U62" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5417,12 +5415,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5431,77 +5429,79 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E63" t="n">
-        <v>166.5</v>
+        <v>23.5</v>
       </c>
       <c r="F63" t="n">
-        <v>15.68</v>
+        <v>19.11</v>
       </c>
       <c r="G63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H63" t="n">
-        <v>15.5</v>
-      </c>
+        <v>1.96</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.95</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1.19</v>
+        <v>-0.63</v>
       </c>
       <c r="M63" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+        <v>23.65</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>月營收轉負-5%</t>
+        </is>
+      </c>
       <c r="P63" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.03</v>
+        <v>1.03</v>
       </c>
       <c r="R63" t="n">
-        <v>30.2</v>
+        <v>12.8</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>-5.3</v>
       </c>
       <c r="T63" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.95</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5510,20 +5510,20 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>23.65</v>
+        <v>45.85</v>
       </c>
       <c r="F64" t="n">
-        <v>19.23</v>
+        <v>15.18</v>
       </c>
       <c r="G64" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>13.7</v>
+        <v>147.4</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.07</v>
+        <v>-2.86</v>
       </c>
       <c r="M64" t="n">
-        <v>23.4</v>
+        <v>47.2</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5544,28 +5544,28 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>月營收轉負-5%</t>
+          <t>含金量0.0差</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>10.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.03</v>
+        <v>0.04</v>
       </c>
       <c r="R64" t="n">
-        <v>12.8</v>
+        <v>36.1</v>
       </c>
       <c r="S64" t="n">
-        <v>-5.3</v>
+        <v>0.4</v>
       </c>
       <c r="T64" t="n">
-        <v>18.2</v>
+        <v>14.4</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -5577,12 +5577,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5591,20 +5591,20 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>47.2</v>
+        <v>770</v>
       </c>
       <c r="F65" t="n">
-        <v>15.18</v>
+        <v>19.67</v>
       </c>
       <c r="G65" t="n">
-        <v>1.33</v>
+        <v>18.59</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>147.4</v>
+        <v>-8.1</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-1.36</v>
+        <v>-3.02</v>
       </c>
       <c r="M65" t="n">
-        <v>47.85</v>
+        <v>794</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5625,28 +5625,28 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>含金量0.0差</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>29.2</v>
+        <v>94.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.04</v>
+        <v>1.08</v>
       </c>
       <c r="R65" t="n">
-        <v>36.1</v>
+        <v>18.2</v>
       </c>
       <c r="S65" t="n">
-        <v>0.4</v>
+        <v>12</v>
       </c>
       <c r="T65" t="n">
-        <v>14.4</v>
+        <v>19.6</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -5658,34 +5658,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>794</v>
+        <v>51.5</v>
       </c>
       <c r="F66" t="n">
-        <v>19.67</v>
+        <v>19.58</v>
       </c>
       <c r="G66" t="n">
-        <v>18.59</v>
+        <v>2.09</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>-8.1</v>
+        <v>-15.4</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.38</v>
+        <v>-2.28</v>
       </c>
       <c r="M66" t="n">
-        <v>797</v>
+        <v>52.7</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5706,23 +5706,23 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>94.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.08</v>
+        <v>0.58</v>
       </c>
       <c r="R66" t="n">
-        <v>18.2</v>
+        <v>-2.2</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T66" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
@@ -5756,7 +5756,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="F67" t="n">
         <v>17.52</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.31</v>
+        <v>-1.86</v>
       </c>
       <c r="M67" t="n">
-        <v>162</v>
+        <v>161.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F68" t="n">
-        <v>22.15</v>
+        <v>21.89</v>
       </c>
       <c r="G68" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.69</v>
+        <v>-1.15</v>
       </c>
       <c r="M68" t="n">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F69" t="n">
         <v>17.6</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="M69" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>372.5</v>
+        <v>360</v>
       </c>
       <c r="F70" t="n">
-        <v>36.34</v>
+        <v>35.12</v>
       </c>
       <c r="G70" t="n">
-        <v>9.960000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>-3.36</v>
       </c>
       <c r="M70" t="n">
         <v>372.5</v>
@@ -6072,7 +6072,7 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>94.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="F71" t="n">
         <v>19.87</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.21</v>
+        <v>-0.95</v>
       </c>
       <c r="M71" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,7 +6151,7 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F72" t="n">
         <v>20.87</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.29</v>
+        <v>-3.92</v>
       </c>
       <c r="M72" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F73" t="n">
-        <v>17.19</v>
+        <v>16.83</v>
       </c>
       <c r="G73" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.62</v>
+        <v>-2.07</v>
       </c>
       <c r="M73" t="n">
-        <v>240.5</v>
+        <v>242</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,7 +6313,7 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1315</v>
+        <v>1185</v>
       </c>
       <c r="F74" t="n">
         <v>68.88</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.15</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M74" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>25.55</v>
+        <v>24.87</v>
       </c>
       <c r="G75" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-0.59</v>
+        <v>-2.68</v>
       </c>
       <c r="M75" t="n">
-        <v>67.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2670</v>
+        <v>2450</v>
       </c>
       <c r="F76" t="n">
-        <v>43.87</v>
+        <v>40.26</v>
       </c>
       <c r="G76" t="n">
-        <v>23.21</v>
+        <v>21.29</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-3.26</v>
+        <v>-8.24</v>
       </c>
       <c r="M76" t="n">
-        <v>2760</v>
+        <v>2670</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="F77" t="n">
-        <v>25.87</v>
+        <v>24.51</v>
       </c>
       <c r="G77" t="n">
-        <v>10.03</v>
+        <v>9.5</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1.69</v>
+        <v>-5.26</v>
       </c>
       <c r="M77" t="n">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="F78" t="n">
-        <v>33.07</v>
+        <v>32.8</v>
       </c>
       <c r="G78" t="n">
-        <v>10.83</v>
+        <v>10.74</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.61</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>2445</v>
+        <v>2460</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="F79" t="n">
-        <v>15.22</v>
+        <v>15.15</v>
       </c>
       <c r="G79" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.98</v>
+        <v>-0.48</v>
       </c>
       <c r="M79" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6872,13 +6872,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>34.55</v>
+        <v>34.15</v>
       </c>
       <c r="F81" t="n">
-        <v>6.92</v>
+        <v>6.84</v>
       </c>
       <c r="G81" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="M81" t="n">
         <v>34.55</v>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>113</v>
+        <v>111.5</v>
       </c>
       <c r="F82" t="n">
-        <v>12.18</v>
+        <v>12.02</v>
       </c>
       <c r="G82" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.44</v>
+        <v>-1.33</v>
       </c>
       <c r="M82" t="n">
-        <v>112.5</v>
+        <v>113</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>180.5</v>
+        <v>178.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.4</v>
+        <v>13.25</v>
       </c>
       <c r="G83" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.1</v>
+        <v>-1.11</v>
       </c>
       <c r="M83" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>43.55</v>
+        <v>42.4</v>
       </c>
       <c r="F84" t="n">
-        <v>8.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.68</v>
+        <v>-2.64</v>
       </c>
       <c r="M84" t="n">
-        <v>43.85</v>
+        <v>43.55</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1290</v>
+        <v>1175</v>
       </c>
       <c r="F85" t="n">
-        <v>38.24</v>
+        <v>34.84</v>
       </c>
       <c r="G85" t="n">
-        <v>12.82</v>
+        <v>11.67</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-1.15</v>
+        <v>-8.91</v>
       </c>
       <c r="M85" t="n">
-        <v>1305</v>
+        <v>1290</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>506</v>
+        <v>475.5</v>
       </c>
       <c r="F86" t="n">
         <v>24.59</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-2.69</v>
+        <v>-6.03</v>
       </c>
       <c r="M86" t="n">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>148.5</v>
+        <v>144</v>
       </c>
       <c r="F87" t="n">
-        <v>18.13</v>
+        <v>17.58</v>
       </c>
       <c r="G87" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.34</v>
+        <v>-3.03</v>
       </c>
       <c r="M87" t="n">
-        <v>149</v>
+        <v>148.5</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>42.2</v>
+        <v>40.95</v>
       </c>
       <c r="F88" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="G88" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.2</v>
+        <v>-2.96</v>
       </c>
       <c r="M88" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2645</v>
+        <v>2455</v>
       </c>
       <c r="F89" t="n">
-        <v>50.02</v>
+        <v>46.43</v>
       </c>
       <c r="G89" t="n">
-        <v>22.63</v>
+        <v>21.01</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-3.29</v>
+        <v>-7.18</v>
       </c>
       <c r="M89" t="n">
-        <v>2735</v>
+        <v>2645</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,7 +7587,7 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>1010</v>
+        <v>970</v>
       </c>
       <c r="F90" t="n">
         <v>29.15</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.98</v>
+        <v>-3.96</v>
       </c>
       <c r="M90" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>90</v>
+        <v>87.8</v>
       </c>
       <c r="F91" t="n">
-        <v>10.79</v>
+        <v>10.53</v>
       </c>
       <c r="G91" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.78</v>
+        <v>-2.44</v>
       </c>
       <c r="M91" t="n">
-        <v>89.3</v>
+        <v>90</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>76.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>8.279999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="G92" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.52</v>
+        <v>-1.57</v>
       </c>
       <c r="M92" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,7 +7836,7 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="F93" t="n">
         <v>12.75</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.29</v>
+        <v>-3.5</v>
       </c>
       <c r="M93" t="n">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F94" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
       <c r="G94" t="n">
-        <v>7.02</v>
+        <v>6.93</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.27</v>
+        <v>-1.32</v>
       </c>
       <c r="M94" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,7 +8002,7 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5035</v>
+        <v>5015</v>
       </c>
       <c r="F95" t="n">
         <v>16.88</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-4.37</v>
+        <v>-0.4</v>
       </c>
       <c r="M95" t="n">
-        <v>5265</v>
+        <v>5035</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>158</v>
+        <v>155.5</v>
       </c>
       <c r="F96" t="n">
-        <v>15.85</v>
+        <v>15.6</v>
       </c>
       <c r="G96" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-0.63</v>
+        <v>-1.58</v>
       </c>
       <c r="M96" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1520</v>
+        <v>1500</v>
       </c>
       <c r="F97" t="n">
-        <v>18.65</v>
+        <v>18.41</v>
       </c>
       <c r="G97" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.65</v>
+        <v>-1.32</v>
       </c>
       <c r="M97" t="n">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,7 +8251,7 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>80.2</v>
+        <v>79.3</v>
       </c>
       <c r="F98" t="n">
         <v>6.67</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.25</v>
+        <v>-1.12</v>
       </c>
       <c r="M98" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>410.5</v>
+        <v>404</v>
       </c>
       <c r="F99" t="n">
         <v>8.199999999999999</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-0.24</v>
+        <v>-1.58</v>
       </c>
       <c r="M99" t="n">
-        <v>411.5</v>
+        <v>410.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>24.25</v>
+        <v>23.85</v>
       </c>
       <c r="F100" t="n">
         <v>4.02</v>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.82</v>
+        <v>-1.65</v>
       </c>
       <c r="M100" t="n">
-        <v>24.45</v>
+        <v>24.25</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>196</v>
+        <v>185.5</v>
       </c>
       <c r="F101" t="n">
         <v>9.550000000000001</v>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.55</v>
+        <v>-5.36</v>
       </c>
       <c r="M101" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2670</v>
+        <v>2450</v>
       </c>
       <c r="F2" t="n">
-        <v>43.87</v>
+        <v>40.26</v>
       </c>
       <c r="G2" t="n">
-        <v>23.21</v>
+        <v>21.29</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.26</v>
+        <v>-8.24</v>
       </c>
       <c r="M2" t="n">
-        <v>2760</v>
+        <v>2670</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="F3" t="n">
-        <v>25.87</v>
+        <v>24.51</v>
       </c>
       <c r="G3" t="n">
-        <v>10.03</v>
+        <v>9.5</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.69</v>
+        <v>-5.26</v>
       </c>
       <c r="M3" t="n">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="F4" t="n">
-        <v>33.07</v>
+        <v>32.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.83</v>
+        <v>10.74</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.61</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2445</v>
+        <v>2460</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>15.22</v>
+        <v>15.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.98</v>
+        <v>-0.48</v>
       </c>
       <c r="M5" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>34.55</v>
+        <v>34.15</v>
       </c>
       <c r="F7" t="n">
-        <v>6.92</v>
+        <v>6.84</v>
       </c>
       <c r="G7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="M7" t="n">
         <v>34.55</v>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
+        <v>111.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.18</v>
+        <v>12.02</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>-1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>112.5</v>
+        <v>113</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>180.5</v>
+        <v>178.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.4</v>
+        <v>13.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.1</v>
+        <v>-1.11</v>
       </c>
       <c r="M9" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>43.55</v>
+        <v>42.4</v>
       </c>
       <c r="F10" t="n">
-        <v>8.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.68</v>
+        <v>-2.64</v>
       </c>
       <c r="M10" t="n">
-        <v>43.85</v>
+        <v>43.55</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1290</v>
+        <v>1175</v>
       </c>
       <c r="F11" t="n">
-        <v>38.24</v>
+        <v>34.84</v>
       </c>
       <c r="G11" t="n">
-        <v>12.82</v>
+        <v>11.67</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.15</v>
+        <v>-8.91</v>
       </c>
       <c r="M11" t="n">
-        <v>1305</v>
+        <v>1290</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,7 +9492,7 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>506</v>
+        <v>475.5</v>
       </c>
       <c r="F12" t="n">
         <v>24.59</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-2.69</v>
+        <v>-6.03</v>
       </c>
       <c r="M12" t="n">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>148.5</v>
+        <v>144</v>
       </c>
       <c r="F13" t="n">
-        <v>18.13</v>
+        <v>17.58</v>
       </c>
       <c r="G13" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.34</v>
+        <v>-3.03</v>
       </c>
       <c r="M13" t="n">
-        <v>149</v>
+        <v>148.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>42.2</v>
+        <v>40.95</v>
       </c>
       <c r="F14" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.2</v>
+        <v>-2.96</v>
       </c>
       <c r="M14" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2645</v>
+        <v>2455</v>
       </c>
       <c r="F15" t="n">
-        <v>50.02</v>
+        <v>46.43</v>
       </c>
       <c r="G15" t="n">
-        <v>22.63</v>
+        <v>21.01</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-3.29</v>
+        <v>-7.18</v>
       </c>
       <c r="M15" t="n">
-        <v>2735</v>
+        <v>2645</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,7 +9812,7 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1010</v>
+        <v>970</v>
       </c>
       <c r="F16" t="n">
         <v>29.15</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-0.98</v>
+        <v>-3.96</v>
       </c>
       <c r="M16" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>87.8</v>
       </c>
       <c r="F17" t="n">
-        <v>10.79</v>
+        <v>10.53</v>
       </c>
       <c r="G17" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.78</v>
+        <v>-2.44</v>
       </c>
       <c r="M17" t="n">
-        <v>89.3</v>
+        <v>90</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>76.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8.279999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="G18" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.52</v>
+        <v>-1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,7 +10061,7 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="F19" t="n">
         <v>12.75</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.29</v>
+        <v>-3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
       <c r="G20" t="n">
-        <v>7.02</v>
+        <v>6.93</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.27</v>
+        <v>-1.32</v>
       </c>
       <c r="M20" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,7 +10227,7 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5035</v>
+        <v>5015</v>
       </c>
       <c r="F21" t="n">
         <v>16.88</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-4.37</v>
+        <v>-0.4</v>
       </c>
       <c r="M21" t="n">
-        <v>5265</v>
+        <v>5035</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>158</v>
+        <v>155.5</v>
       </c>
       <c r="F22" t="n">
-        <v>15.85</v>
+        <v>15.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.63</v>
+        <v>-1.58</v>
       </c>
       <c r="M22" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1520</v>
+        <v>1500</v>
       </c>
       <c r="F23" t="n">
-        <v>18.65</v>
+        <v>18.41</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.65</v>
+        <v>-1.32</v>
       </c>
       <c r="M23" t="n">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,7 +10607,7 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="F2" t="n">
         <v>17.52</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.31</v>
+        <v>-1.86</v>
       </c>
       <c r="M2" t="n">
-        <v>162</v>
+        <v>161.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F3" t="n">
-        <v>22.15</v>
+        <v>21.89</v>
       </c>
       <c r="G3" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.69</v>
+        <v>-1.15</v>
       </c>
       <c r="M3" t="n">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,7 +10765,7 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
         <v>17.6</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>372.5</v>
+        <v>360</v>
       </c>
       <c r="F5" t="n">
-        <v>36.34</v>
+        <v>35.12</v>
       </c>
       <c r="G5" t="n">
-        <v>9.960000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-3.36</v>
       </c>
       <c r="M5" t="n">
         <v>372.5</v>
@@ -10923,7 +10923,7 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>94.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="F6" t="n">
         <v>19.87</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.21</v>
+        <v>-0.95</v>
       </c>
       <c r="M6" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,7 +11002,7 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F7" t="n">
         <v>20.87</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.29</v>
+        <v>-3.92</v>
       </c>
       <c r="M7" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F8" t="n">
-        <v>17.19</v>
+        <v>16.83</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.62</v>
+        <v>-2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>240.5</v>
+        <v>242</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,7 +11164,7 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1315</v>
+        <v>1185</v>
       </c>
       <c r="F9" t="n">
         <v>68.88</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>25.55</v>
+        <v>24.87</v>
       </c>
       <c r="G10" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.59</v>
+        <v>-2.68</v>
       </c>
       <c r="M10" t="n">
-        <v>67.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,7 +11459,7 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1425</v>
+        <v>1335</v>
       </c>
       <c r="F2" t="n">
         <v>101.64</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.26</v>
+        <v>-6.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1380</v>
+        <v>1425</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,7 +11538,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.65</v>
+        <v>39.35</v>
       </c>
       <c r="F3" t="n">
         <v>11.2</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>39.85</v>
+        <v>39.65</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>146.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.23</v>
+        <v>16.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.71</v>
+        <v>-1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>146.5</v>
+        <v>149</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,7 +11696,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6855</v>
+        <v>6310</v>
       </c>
       <c r="F5" t="n">
         <v>182.51</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-7.11</v>
+        <v>-7.95</v>
       </c>
       <c r="M5" t="n">
-        <v>7380</v>
+        <v>6855</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>117.5</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.83</v>
+        <v>23.63</v>
       </c>
       <c r="G6" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.86</v>
+        <v>-0.85</v>
       </c>
       <c r="M6" t="n">
-        <v>116.5</v>
+        <v>117.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>126.5</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>36.88</v>
+        <v>35.28</v>
       </c>
       <c r="G7" t="n">
-        <v>5.24</v>
+        <v>5.01</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>-4.35</v>
       </c>
       <c r="M7" t="n">
-        <v>123</v>
+        <v>126.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>238</v>
+        <v>214.5</v>
       </c>
       <c r="F8" t="n">
-        <v>36.34</v>
+        <v>32.75</v>
       </c>
       <c r="G8" t="n">
-        <v>7.04</v>
+        <v>6.35</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9.93</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>216.5</v>
+        <v>238</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,7 +12103,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F10" t="n">
         <v>20.19</v>
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M10" t="n">
         <v>168</v>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="n">
-        <v>30.32</v>
+        <v>30.21</v>
       </c>
       <c r="G11" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-3.82</v>
+        <v>-0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>1440</v>
+        <v>1385</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>175.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25.52</v>
+        <v>24.21</v>
       </c>
       <c r="G12" t="n">
-        <v>4.68</v>
+        <v>4.44</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.23</v>
+        <v>-5.14</v>
       </c>
       <c r="M12" t="n">
-        <v>177.5</v>
+        <v>185</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F13" t="n">
-        <v>32.94</v>
+        <v>31.32</v>
       </c>
       <c r="G13" t="n">
-        <v>5.77</v>
+        <v>5.49</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.28</v>
+        <v>-4.91</v>
       </c>
       <c r="M13" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>28.13</v>
+        <v>28.03</v>
       </c>
       <c r="G14" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>141</v>
+        <v>141.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4605</v>
+        <v>4480</v>
       </c>
       <c r="F16" t="n">
-        <v>138.54</v>
+        <v>134.78</v>
       </c>
       <c r="G16" t="n">
-        <v>42.31</v>
+        <v>41.17</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-8.630000000000001</v>
+        <v>-2.71</v>
       </c>
       <c r="M16" t="n">
-        <v>5040</v>
+        <v>4605</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1995</v>
+        <v>1890</v>
       </c>
       <c r="F2" t="n">
-        <v>73.56</v>
+        <v>69.69</v>
       </c>
       <c r="G2" t="n">
-        <v>17.3</v>
+        <v>16.39</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.86</v>
+        <v>-5.26</v>
       </c>
       <c r="M2" t="n">
-        <v>2075</v>
+        <v>1995</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,7 +12882,7 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="F3" t="n">
         <v>23.43</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.22</v>
+        <v>-1.63</v>
       </c>
       <c r="M3" t="n">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3320</v>
+        <v>3195</v>
       </c>
       <c r="F4" t="n">
-        <v>91.84</v>
+        <v>88.38</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>22.13</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-2.92</v>
+        <v>-3.77</v>
       </c>
       <c r="M4" t="n">
-        <v>3420</v>
+        <v>3320</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5475</v>
+        <v>5220</v>
       </c>
       <c r="F5" t="n">
-        <v>118.76</v>
+        <v>113.23</v>
       </c>
       <c r="G5" t="n">
-        <v>40.92</v>
+        <v>39.01</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-9.949999999999999</v>
+        <v>-4.66</v>
       </c>
       <c r="M5" t="n">
-        <v>6080</v>
+        <v>5475</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>773</v>
+        <v>748</v>
       </c>
       <c r="F6" t="n">
-        <v>53.13</v>
+        <v>51.41</v>
       </c>
       <c r="G6" t="n">
-        <v>29.64</v>
+        <v>28.68</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,7 +13146,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.23</v>
       </c>
       <c r="M6" t="n">
         <v>773</v>
@@ -13206,7 +13206,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
         <v>12.24</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.92</v>
       </c>
       <c r="M7" t="n">
         <v>104</v>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>197</v>
+        <v>193.5</v>
       </c>
       <c r="F8" t="n">
-        <v>15.57</v>
+        <v>15.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.25</v>
+        <v>-1.78</v>
       </c>
       <c r="M8" t="n">
-        <v>197.5</v>
+        <v>197</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>15.63</v>
+        <v>15.49</v>
       </c>
       <c r="G9" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.93</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>653</v>
+        <v>609</v>
       </c>
       <c r="F10" t="n">
-        <v>19.79</v>
+        <v>18.45</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.67</v>
+        <v>-6.74</v>
       </c>
       <c r="M10" t="n">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>241.5</v>
+        <v>230</v>
       </c>
       <c r="F11" t="n">
-        <v>35.99</v>
+        <v>34.28</v>
       </c>
       <c r="G11" t="n">
-        <v>3.31</v>
+        <v>3.16</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>-4.76</v>
       </c>
       <c r="M11" t="n">
-        <v>238</v>
+        <v>241.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4215</v>
+        <v>4035</v>
       </c>
       <c r="F12" t="n">
-        <v>61.78</v>
+        <v>59.14</v>
       </c>
       <c r="G12" t="n">
-        <v>7.96</v>
+        <v>7.62</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-9.35</v>
+        <v>-4.27</v>
       </c>
       <c r="M12" t="n">
-        <v>4650</v>
+        <v>4215</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1335</v>
+        <v>1320</v>
       </c>
       <c r="F2" t="n">
-        <v>101.64</v>
+        <v>56.03</v>
       </c>
       <c r="G2" t="n">
-        <v>28.53</v>
+        <v>9.23</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-6.32</v>
+        <v>-1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>1425</v>
+        <v>1335</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.35</v>
+        <v>39.25</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2</v>
+        <v>11.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>39.65</v>
+        <v>39.35</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>146.5</v>
+        <v>145.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94</v>
+        <v>18.07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.73</v>
+        <v>4.4</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.68</v>
+        <v>-0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>149</v>
+        <v>146.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6310</v>
+        <v>6460</v>
       </c>
       <c r="F5" t="n">
-        <v>182.51</v>
+        <v>168</v>
       </c>
       <c r="G5" t="n">
-        <v>42.63</v>
+        <v>39.24</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-7.95</v>
+        <v>2.38</v>
       </c>
       <c r="M5" t="n">
-        <v>6855</v>
+        <v>6310</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>116.5</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
-        <v>23.63</v>
+        <v>24.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.88</v>
+        <v>4.24</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.85</v>
+        <v>-3</v>
       </c>
       <c r="M6" t="n">
-        <v>117.5</v>
+        <v>116.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.28</v>
+        <v>30.67</v>
       </c>
       <c r="G7" t="n">
-        <v>5.01</v>
+        <v>4.83</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-4.35</v>
+        <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>126.5</v>
+        <v>121</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>214.5</v>
+        <v>235.5</v>
       </c>
       <c r="F8" t="n">
-        <v>32.75</v>
+        <v>20.78</v>
       </c>
       <c r="G8" t="n">
-        <v>6.35</v>
+        <v>2.75</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-9.869999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>238</v>
+        <v>214.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>93.2</v>
       </c>
       <c r="F9" t="n">
-        <v>26.14</v>
+        <v>27.03</v>
       </c>
       <c r="G9" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-9.51</v>
       </c>
       <c r="M9" t="n">
         <v>103</v>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F10" t="n">
-        <v>20.19</v>
+        <v>20.55</v>
       </c>
       <c r="G10" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.79</v>
+        <v>-1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1345</v>
       </c>
       <c r="F11" t="n">
-        <v>30.21</v>
+        <v>22.33</v>
       </c>
       <c r="G11" t="n">
-        <v>5.43</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.36</v>
+        <v>-2.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>24.21</v>
+        <v>22.33</v>
       </c>
       <c r="G12" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-5.14</v>
+        <v>-0.28</v>
       </c>
       <c r="M12" t="n">
-        <v>185</v>
+        <v>175.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F13" t="n">
-        <v>31.32</v>
+        <v>18.99</v>
       </c>
       <c r="G13" t="n">
-        <v>5.49</v>
+        <v>2.73</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-4.91</v>
+        <v>0.47</v>
       </c>
       <c r="M13" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>139.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.03</v>
+        <v>26.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>-1.06</v>
       </c>
       <c r="M14" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F15" t="n">
-        <v>21.88</v>
+        <v>24.25</v>
       </c>
       <c r="G15" t="n">
-        <v>5.37</v>
+        <v>7.16</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M15" t="n">
         <v>240</v>
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4480</v>
+        <v>4400</v>
       </c>
       <c r="F16" t="n">
-        <v>134.78</v>
+        <v>53.56</v>
       </c>
       <c r="G16" t="n">
-        <v>41.17</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2.71</v>
+        <v>-1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>4605</v>
+        <v>4480</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1540</v>
+        <v>1485</v>
       </c>
       <c r="F17" t="n">
-        <v>60.17</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>17.62</v>
+        <v>15.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.45</v>
+        <v>-3.57</v>
       </c>
       <c r="M17" t="n">
-        <v>1595</v>
+        <v>1540</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1830,12 +1830,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1844,20 +1844,20 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E18" t="n">
-        <v>8260</v>
+        <v>698</v>
       </c>
       <c r="F18" t="n">
-        <v>72.81</v>
+        <v>44.89</v>
       </c>
       <c r="G18" t="n">
-        <v>24.97</v>
+        <v>6.27</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>90.7</v>
+        <v>25.3</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.1</v>
+        <v>-0.29</v>
       </c>
       <c r="M18" t="n">
-        <v>7785</v>
+        <v>700</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1878,19 +1878,19 @@
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>34.3</v>
+        <v>18.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="R18" t="n">
-        <v>28.8</v>
+        <v>7.8</v>
       </c>
       <c r="S18" t="n">
-        <v>172.1</v>
+        <v>17.8</v>
       </c>
       <c r="T18" t="n">
-        <v>66.5</v>
+        <v>69.5</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
@@ -1907,12 +1907,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1921,20 +1921,20 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" t="n">
-        <v>700</v>
+        <v>82.8</v>
       </c>
       <c r="F19" t="n">
-        <v>73.47</v>
+        <v>60.87</v>
       </c>
       <c r="G19" t="n">
-        <v>13.47</v>
+        <v>7.22</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>25.3</v>
+        <v>203.8</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-6.04</v>
+        <v>-1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>745</v>
+        <v>84</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1955,24 +1955,24 @@
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>18.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="R19" t="n">
-        <v>7.8</v>
+        <v>19.4</v>
       </c>
       <c r="S19" t="n">
-        <v>17.8</v>
+        <v>25.3</v>
       </c>
       <c r="T19" t="n">
-        <v>69.5</v>
+        <v>62.5</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1998,20 +1998,20 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>7705</v>
       </c>
       <c r="F20" t="n">
-        <v>64.34999999999999</v>
+        <v>44.65</v>
       </c>
       <c r="G20" t="n">
-        <v>7.64</v>
+        <v>8.82</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>203.8</v>
+        <v>86.3</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -2020,36 +2020,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-5.41</v>
+        <v>-3.99</v>
       </c>
       <c r="M20" t="n">
-        <v>88.8</v>
+        <v>8025</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>含金量0.6弱</t>
+        </is>
+      </c>
       <c r="P20" t="n">
-        <v>15.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.18</v>
+        <v>0.63</v>
       </c>
       <c r="R20" t="n">
-        <v>19.4</v>
+        <v>28.5</v>
       </c>
       <c r="S20" t="n">
-        <v>25.3</v>
+        <v>119.8</v>
       </c>
       <c r="T20" t="n">
-        <v>62.5</v>
+        <v>192</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2061,12 +2065,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2075,20 +2079,20 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E21" t="n">
-        <v>8025</v>
+        <v>1855</v>
       </c>
       <c r="F21" t="n">
-        <v>182.68</v>
+        <v>37.4</v>
       </c>
       <c r="G21" t="n">
-        <v>49.45</v>
+        <v>7.38</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>86.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -2097,10 +2101,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-9.98</v>
+        <v>-5.6</v>
       </c>
       <c r="M21" t="n">
-        <v>8915</v>
+        <v>1965</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2109,23 +2113,23 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>含金量0.6弱</t>
+          <t>含金量0.3差</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>27.1</v>
+        <v>48.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="R21" t="n">
-        <v>28.5</v>
+        <v>12.6</v>
       </c>
       <c r="S21" t="n">
-        <v>119.8</v>
+        <v>133.1</v>
       </c>
       <c r="T21" t="n">
-        <v>192</v>
+        <v>72.7</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
@@ -2142,34 +2146,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>1965</v>
+        <v>1645</v>
       </c>
       <c r="F22" t="n">
-        <v>61.97</v>
+        <v>113.8</v>
       </c>
       <c r="G22" t="n">
-        <v>30.01</v>
+        <v>25.18</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>71.09999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -2178,10 +2182,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-9.859999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="M22" t="n">
-        <v>2180</v>
+        <v>1575</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2190,23 +2194,23 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>含金量0.3差</t>
+          <t>含金量-0.4差</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>48.1</v>
+        <v>22.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.31</v>
+        <v>-0.38</v>
       </c>
       <c r="R22" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="S22" t="n">
-        <v>133.1</v>
+        <v>124.4</v>
       </c>
       <c r="T22" t="n">
-        <v>72.7</v>
+        <v>135.1</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -2223,12 +2227,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2237,20 +2241,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
-        <v>369</v>
+        <v>35.15</v>
       </c>
       <c r="F23" t="n">
-        <v>42.66</v>
+        <v>186.25</v>
       </c>
       <c r="G23" t="n">
-        <v>6.32</v>
+        <v>1.33</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>24.9</v>
+        <v>158.2</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -2259,36 +2263,40 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>405</v>
+        <v>38.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ROE4低</t>
+        </is>
+      </c>
       <c r="P23" t="n">
-        <v>13.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="R23" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>97.8</v>
       </c>
       <c r="T23" t="n">
-        <v>43.5</v>
+        <v>130</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2300,12 +2308,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2314,21 +2322,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
-        <v>1575</v>
+        <v>2095</v>
       </c>
       <c r="F24" t="n">
-        <v>117.77</v>
+        <v>250.33</v>
       </c>
       <c r="G24" t="n">
-        <v>26.06</v>
+        <v>41.58</v>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>99.8</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -2336,10 +2342,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-3.37</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>1630</v>
+        <v>1905</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2348,23 +2354,23 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>含金量-0.4差</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>22.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.38</v>
+        <v>1.13</v>
       </c>
       <c r="R24" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>124.4</v>
+        <v>118.8</v>
       </c>
       <c r="T24" t="n">
-        <v>135.1</v>
+        <v>310.9</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
@@ -2381,12 +2387,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2395,21 +2401,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E25" t="n">
-        <v>38.4</v>
+        <v>1530</v>
       </c>
       <c r="F25" t="n">
-        <v>142.22</v>
+        <v>105.22</v>
       </c>
       <c r="G25" t="n">
-        <v>3.31</v>
+        <v>7.45</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>158.2</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -2417,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-9.960000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="M25" t="n">
-        <v>42.65</v>
+        <v>1495</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2429,23 +2433,23 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ROE4低</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>17.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>5.2</v>
+        <v>120.6</v>
       </c>
       <c r="S25" t="n">
-        <v>97.8</v>
+        <v>108.5</v>
       </c>
       <c r="T25" t="n">
-        <v>130</v>
+        <v>65.2</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
@@ -2462,12 +2466,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2476,19 +2480,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E26" t="n">
-        <v>1905</v>
+        <v>434.5</v>
       </c>
       <c r="F26" t="n">
-        <v>262.81</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>43.65</v>
+        <v>14.74</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>27.5</v>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2496,10 +2502,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-4.75</v>
+        <v>1.52</v>
       </c>
       <c r="M26" t="n">
-        <v>2000</v>
+        <v>428</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2512,19 +2518,19 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>16.6</v>
+        <v>18.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>50.3</v>
       </c>
       <c r="S26" t="n">
-        <v>118.8</v>
+        <v>21.1</v>
       </c>
       <c r="T26" t="n">
-        <v>310.9</v>
+        <v>99.8</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
@@ -2541,12 +2547,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2555,20 +2561,20 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E27" t="n">
-        <v>651</v>
+        <v>2840</v>
       </c>
       <c r="F27" t="n">
-        <v>60.45</v>
+        <v>83.16</v>
       </c>
       <c r="G27" t="n">
-        <v>8.15</v>
+        <v>9.48</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>12.6</v>
+        <v>454.2</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -2577,10 +2583,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-4.12</v>
+        <v>0.18</v>
       </c>
       <c r="M27" t="n">
-        <v>679</v>
+        <v>2835</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2589,23 +2595,23 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>12.8</v>
+        <v>14.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.26</v>
+        <v>0.99</v>
       </c>
       <c r="R27" t="n">
-        <v>3.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>28.6</v>
+        <v>34.1</v>
       </c>
       <c r="T27" t="n">
-        <v>62.1</v>
+        <v>95.3</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
@@ -2622,30 +2628,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>1495</v>
+        <v>510</v>
       </c>
       <c r="F28" t="n">
-        <v>93.73</v>
+        <v>143.06</v>
       </c>
       <c r="G28" t="n">
-        <v>16.14</v>
+        <v>9.1</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2656,10 +2662,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.46</v>
+        <v>3.03</v>
       </c>
       <c r="M28" t="n">
-        <v>1445</v>
+        <v>495</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2672,24 +2678,24 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>17.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
-        <v>120.6</v>
+        <v>4.5</v>
       </c>
       <c r="S28" t="n">
-        <v>108.5</v>
+        <v>49.9</v>
       </c>
       <c r="T28" t="n">
-        <v>65.2</v>
+        <v>165.8</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2701,34 +2707,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>428</v>
+        <v>546</v>
       </c>
       <c r="F29" t="n">
-        <v>82.64</v>
+        <v>35.18</v>
       </c>
       <c r="G29" t="n">
-        <v>15.74</v>
+        <v>6.28</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>27.5</v>
+        <v>-2.9</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -2737,35 +2743,31 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-6.35</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>457</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>496.5</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>18.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.07</v>
+        <v>0.77</v>
       </c>
       <c r="R29" t="n">
-        <v>50.3</v>
+        <v>4.9</v>
       </c>
       <c r="S29" t="n">
-        <v>21.1</v>
+        <v>32.1</v>
       </c>
       <c r="T29" t="n">
-        <v>99.8</v>
+        <v>38.6</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
@@ -2775,42 +2777,40 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E30" t="n">
-        <v>2835</v>
+        <v>168.5</v>
       </c>
       <c r="F30" t="n">
-        <v>89.91</v>
+        <v>78.95</v>
       </c>
       <c r="G30" t="n">
-        <v>10.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>454.2</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-7.5</v>
+        <v>-3.16</v>
       </c>
       <c r="M30" t="n">
-        <v>3065</v>
+        <v>174</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2830,23 +2830,23 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>14.1</v>
+        <v>11.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.99</v>
+        <v>1.62</v>
       </c>
       <c r="R30" t="n">
-        <v>9.300000000000001</v>
+        <v>-2.7</v>
       </c>
       <c r="S30" t="n">
-        <v>34.1</v>
+        <v>182</v>
       </c>
       <c r="T30" t="n">
-        <v>95.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
@@ -2863,592 +2863,604 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>495</v>
+        <v>1885</v>
       </c>
       <c r="F31" t="n">
-        <v>147.32</v>
+        <v>29.68</v>
       </c>
       <c r="G31" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+        <v>5.03</v>
+      </c>
+      <c r="H31" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.32</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1890</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R31" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>-4.81</v>
-      </c>
-      <c r="M31" t="n">
-        <v>520</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>EPS資料不足</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="T31" t="n">
-        <v>165.8</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E32" t="n">
-        <v>243.5</v>
+        <v>717</v>
       </c>
       <c r="F32" t="n">
-        <v>35.91</v>
+        <v>23.05</v>
       </c>
       <c r="G32" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>12.09</v>
+      </c>
+      <c r="H32" t="n">
+        <v>19</v>
+      </c>
       <c r="I32" t="n">
-        <v>-15.3</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.09</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-5.8</v>
+        <v>-1.1</v>
       </c>
       <c r="M32" t="n">
-        <v>258.5</v>
+        <v>725</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>⚠️高槓桿(負債80%)</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>9.4</v>
+        <v>52.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.72</v>
+        <v>1.91</v>
       </c>
       <c r="R32" t="n">
-        <v>13.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>34.8</v>
+        <v>19.2</v>
       </c>
       <c r="T32" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>20.9</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.09</v>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="E33" t="n">
-        <v>403</v>
+        <v>3200</v>
       </c>
       <c r="F33" t="n">
-        <v>36.08</v>
+        <v>74.7</v>
       </c>
       <c r="G33" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+        <v>15.67</v>
+      </c>
+      <c r="H33" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>49</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.13</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3195</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R33" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="M33" t="n">
-        <v>420.5</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>730.1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E34" t="n">
-        <v>496.5</v>
+        <v>5315</v>
       </c>
       <c r="F34" t="n">
-        <v>38.52</v>
+        <v>23.19</v>
       </c>
       <c r="G34" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>6.44</v>
+      </c>
+      <c r="H34" t="n">
+        <v>75.3</v>
+      </c>
       <c r="I34" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>59.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.01</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-3.59</v>
+        <v>1.82</v>
       </c>
       <c r="M34" t="n">
-        <v>515</v>
+        <v>5220</v>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>22.4</v>
+        <v>34.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="R34" t="n">
-        <v>4.9</v>
+        <v>25.1</v>
       </c>
       <c r="S34" t="n">
-        <v>32.1</v>
+        <v>114.6</v>
       </c>
       <c r="T34" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
+        <v>120.3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.01</v>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E35" t="n">
-        <v>905</v>
+        <v>740</v>
       </c>
       <c r="F35" t="n">
-        <v>71.26000000000001</v>
+        <v>39.6</v>
       </c>
       <c r="G35" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>21.08</v>
+      </c>
+      <c r="H35" t="n">
+        <v>47.5</v>
+      </c>
       <c r="I35" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.83</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="M35" t="n">
+        <v>748</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>月營收轉負-9%</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R35" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="T35" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1005</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R35" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="S35" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E36" t="n">
-        <v>174</v>
+        <v>101.5</v>
       </c>
       <c r="F36" t="n">
-        <v>51.63</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+        <v>1.88</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.02</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-4.92</v>
+        <v>-0.49</v>
       </c>
       <c r="M36" t="n">
-        <v>183</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
-        </is>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="T36" t="n">
         <v>11.6</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="S36" t="n">
-        <v>182</v>
-      </c>
-      <c r="T36" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>2.02</v>
+      </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E37" t="n">
-        <v>4030</v>
+        <v>195.5</v>
       </c>
       <c r="F37" t="n">
-        <v>64.22</v>
+        <v>14.65</v>
       </c>
       <c r="G37" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>2.43</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13.4</v>
+      </c>
       <c r="I37" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.02</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-2.3</v>
+        <v>1.03</v>
       </c>
       <c r="M37" t="n">
-        <v>4125</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>193.5</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>25.3</v>
+        <v>17.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="R37" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="T37" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.02</v>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E38" t="n">
-        <v>1890</v>
+        <v>105.5</v>
       </c>
       <c r="F38" t="n">
-        <v>69.69</v>
+        <v>20.6</v>
       </c>
       <c r="G38" t="n">
-        <v>16.39</v>
+        <v>4.7</v>
       </c>
       <c r="H38" t="n">
-        <v>59.1</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>34.1</v>
+        <v>7.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3456,78 +3468,78 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-5.26</v>
+        <v>0.48</v>
       </c>
       <c r="M38" t="n">
-        <v>1995</v>
+        <v>105</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R38" t="n">
-        <v>15.2</v>
+        <v>7.6</v>
       </c>
       <c r="S38" t="n">
-        <v>43.7</v>
+        <v>1.4</v>
       </c>
       <c r="T38" t="n">
-        <v>79.3</v>
+        <v>17.2</v>
       </c>
       <c r="U38" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E39" t="n">
-        <v>725</v>
+        <v>612</v>
       </c>
       <c r="F39" t="n">
-        <v>23.43</v>
+        <v>11.26</v>
       </c>
       <c r="G39" t="n">
-        <v>12.29</v>
+        <v>2.16</v>
       </c>
       <c r="H39" t="n">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3535,38 +3547,38 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-1.63</v>
+        <v>0.49</v>
       </c>
       <c r="M39" t="n">
-        <v>737</v>
+        <v>609</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>⚠️高槓桿(負債80%)</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>52.4</v>
+        <v>14.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="R39" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
-        <v>19.2</v>
+        <v>30.2</v>
       </c>
       <c r="T39" t="n">
-        <v>20.9</v>
+        <v>23.4</v>
       </c>
       <c r="U39" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -3578,39 +3590,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E40" t="n">
-        <v>3195</v>
+        <v>225.5</v>
       </c>
       <c r="F40" t="n">
-        <v>88.38</v>
+        <v>34.63</v>
       </c>
       <c r="G40" t="n">
-        <v>22.13</v>
+        <v>2.61</v>
       </c>
       <c r="H40" t="n">
-        <v>70.2</v>
+        <v>30.9</v>
       </c>
       <c r="I40" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3618,30 +3630,34 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-3.77</v>
+        <v>-1.96</v>
       </c>
       <c r="M40" t="n">
-        <v>3320</v>
+        <v>230</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>含金量0.5差</t>
+        </is>
+      </c>
       <c r="P40" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="R40" t="n">
-        <v>23.2</v>
+        <v>7.6</v>
       </c>
       <c r="S40" t="n">
-        <v>37.7</v>
+        <v>8.4</v>
       </c>
       <c r="T40" t="n">
-        <v>104.6</v>
+        <v>36.5</v>
       </c>
       <c r="U40" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3650,46 +3666,46 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="E41" t="n">
-        <v>5220</v>
+        <v>4065</v>
       </c>
       <c r="F41" t="n">
-        <v>113.23</v>
+        <v>40.44</v>
       </c>
       <c r="G41" t="n">
-        <v>39.01</v>
+        <v>6.57</v>
       </c>
       <c r="H41" t="n">
-        <v>75.3</v>
+        <v>51.7</v>
       </c>
       <c r="I41" t="n">
-        <v>59.7</v>
+        <v>23.4</v>
       </c>
       <c r="J41" t="n">
-        <v>2.01</v>
+        <v>2.73</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3697,34 +3713,38 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-4.66</v>
+        <v>0.74</v>
       </c>
       <c r="M41" t="n">
-        <v>5475</v>
+        <v>4035</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>含金量0.3差、月營收轉負-34%</t>
+        </is>
+      </c>
       <c r="P41" t="n">
-        <v>34.5</v>
+        <v>12.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.76</v>
+        <v>0.26</v>
       </c>
       <c r="R41" t="n">
-        <v>25.1</v>
+        <v>31.2</v>
       </c>
       <c r="S41" t="n">
-        <v>114.6</v>
+        <v>-33.5</v>
       </c>
       <c r="T41" t="n">
-        <v>120.3</v>
+        <v>63.8</v>
       </c>
       <c r="U41" t="n">
-        <v>2.01</v>
+        <v>2.73</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -3736,12 +3756,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3750,61 +3770,55 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E42" t="n">
-        <v>748</v>
+        <v>8095</v>
       </c>
       <c r="F42" t="n">
-        <v>51.41</v>
+        <v>32.37</v>
       </c>
       <c r="G42" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="H42" t="n">
-        <v>47.5</v>
-      </c>
+        <v>7.71</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.83</v>
-      </c>
+        <v>90.7</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-3.23</v>
+        <v>-2</v>
       </c>
       <c r="M42" t="n">
-        <v>773</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
+        <v>8260</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>53.6</v>
+        <v>34.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="R42" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="S42" t="n">
-        <v>-9.300000000000001</v>
+        <v>172.1</v>
       </c>
       <c r="T42" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.83</v>
-      </c>
+        <v>66.5</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3812,19 +3826,19 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3833,140 +3847,132 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E43" t="n">
-        <v>102</v>
+        <v>408</v>
       </c>
       <c r="F43" t="n">
-        <v>12.24</v>
+        <v>22.66</v>
       </c>
       <c r="G43" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11</v>
-      </c>
+        <v>6.71</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.02</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-1.92</v>
+        <v>-2.63</v>
       </c>
       <c r="M43" t="n">
-        <v>104</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>419</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>17.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.11</v>
+        <v>1.09</v>
       </c>
       <c r="R43" t="n">
-        <v>5.3</v>
+        <v>24.2</v>
       </c>
       <c r="S43" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="T43" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.02</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E44" t="n">
-        <v>193.5</v>
+        <v>171.5</v>
       </c>
       <c r="F44" t="n">
-        <v>15.3</v>
+        <v>21.22</v>
       </c>
       <c r="G44" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="H44" t="n">
-        <v>13.4</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.02</v>
-      </c>
+        <v>57.1</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1.78</v>
+        <v>-2</v>
       </c>
       <c r="M44" t="n">
-        <v>197</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
-        </is>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R44" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="S44" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.02</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -3974,19 +3980,19 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3995,77 +4001,79 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E45" t="n">
-        <v>105</v>
+        <v>98.8</v>
       </c>
       <c r="F45" t="n">
-        <v>15.49</v>
+        <v>22.09</v>
       </c>
       <c r="G45" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="H45" t="n">
-        <v>16</v>
-      </c>
+        <v>1.43</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.27</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="M45" t="n">
-        <v>106</v>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P45" t="n">
-        <v>20.6</v>
+        <v>9.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="R45" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.4</v>
+        <v>-2.7</v>
       </c>
       <c r="T45" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2.27</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4074,81 +4082,79 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E46" t="n">
-        <v>609</v>
+        <v>169.5</v>
       </c>
       <c r="F46" t="n">
-        <v>18.45</v>
+        <v>31.21</v>
       </c>
       <c r="G46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H46" t="n">
-        <v>21.4</v>
-      </c>
+        <v>2.09</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.4</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-6.74</v>
+        <v>0.59</v>
       </c>
       <c r="M46" t="n">
-        <v>653</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
+        <v>168.5</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>14.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="R46" t="n">
-        <v>10.6</v>
+        <v>22.1</v>
       </c>
       <c r="S46" t="n">
-        <v>30.2</v>
+        <v>14.6</v>
       </c>
       <c r="T46" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.4</v>
-      </c>
+        <v>34.2</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4157,61 +4163,55 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E47" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F47" t="n">
-        <v>34.28</v>
+        <v>25.2</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="H47" t="n">
-        <v>30.9</v>
-      </c>
+        <v>6.13</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>18</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.03</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-4.76</v>
+        <v>0.44</v>
       </c>
       <c r="M47" t="n">
-        <v>241.5</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>含金量0.5差</t>
-        </is>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>9.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.49</v>
+        <v>1.44</v>
       </c>
       <c r="R47" t="n">
-        <v>7.6</v>
+        <v>20.4</v>
       </c>
       <c r="S47" t="n">
-        <v>8.4</v>
+        <v>812.4</v>
       </c>
       <c r="T47" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.03</v>
-      </c>
+        <v>34.6</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4219,82 +4219,76 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E48" t="n">
-        <v>4035</v>
+        <v>228</v>
       </c>
       <c r="F48" t="n">
-        <v>59.14</v>
+        <v>21.07</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="H48" t="n">
-        <v>51.7</v>
-      </c>
+        <v>3.07</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.73</v>
-      </c>
+        <v>49.2</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-4.27</v>
+        <v>-1.72</v>
       </c>
       <c r="M48" t="n">
-        <v>4215</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
-        </is>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.26</v>
+        <v>1.53</v>
       </c>
       <c r="R48" t="n">
-        <v>31.2</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>-33.5</v>
+        <v>10.3</v>
       </c>
       <c r="T48" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.73</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -4302,41 +4296,41 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="E49" t="n">
-        <v>419</v>
+        <v>625</v>
       </c>
       <c r="F49" t="n">
-        <v>23.58</v>
+        <v>21.16</v>
       </c>
       <c r="G49" t="n">
-        <v>6.98</v>
+        <v>2.22</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>49</v>
+        <v>12.6</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4345,31 +4339,35 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-3.9</v>
+        <v>-3.99</v>
       </c>
       <c r="M49" t="n">
-        <v>436</v>
+        <v>651</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P49" t="n">
-        <v>29.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.09</v>
+        <v>3.26</v>
       </c>
       <c r="R49" t="n">
-        <v>24.2</v>
+        <v>3.2</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="T49" t="n">
-        <v>24</v>
+        <v>62.1</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -4386,34 +4384,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="F50" t="n">
-        <v>21.26</v>
+        <v>30.56</v>
       </c>
       <c r="G50" t="n">
-        <v>4.02</v>
+        <v>3.26</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>57.1</v>
+        <v>186.3</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4422,31 +4420,35 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-1.96</v>
+        <v>2.21</v>
       </c>
       <c r="M50" t="n">
-        <v>178.5</v>
+        <v>136</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P50" t="n">
-        <v>18.6</v>
+        <v>10.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="R50" t="n">
-        <v>11.1</v>
+        <v>-3.4</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>37</v>
       </c>
       <c r="T50" t="n">
-        <v>22</v>
+        <v>35.8</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4463,34 +4465,34 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="E51" t="n">
-        <v>131</v>
+        <v>3995</v>
       </c>
       <c r="F51" t="n">
-        <v>29.98</v>
+        <v>20.76</v>
       </c>
       <c r="G51" t="n">
-        <v>3.08</v>
+        <v>5.41</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>16.8</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4499,31 +4501,35 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-3.68</v>
+        <v>-0.87</v>
       </c>
       <c r="M51" t="n">
-        <v>136</v>
+        <v>4030</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>10.8</v>
+        <v>25.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="S51" t="n">
-        <v>48.7</v>
+        <v>5</v>
       </c>
       <c r="T51" t="n">
-        <v>28.4</v>
+        <v>61.7</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4540,174 +4546,170 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E52" t="n">
-        <v>98</v>
+        <v>546</v>
       </c>
       <c r="F52" t="n">
-        <v>20.12</v>
+        <v>17.26</v>
       </c>
       <c r="G52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>2.57</v>
+      </c>
+      <c r="H52" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I52" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-5.31</v>
+        <v>-2.85</v>
       </c>
       <c r="M52" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>9.5</v>
+        <v>19.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S52" t="n">
-        <v>-2.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E53" t="n">
-        <v>168.5</v>
+        <v>785</v>
       </c>
       <c r="F53" t="n">
-        <v>34.74</v>
+        <v>38.6</v>
       </c>
       <c r="G53" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>7.03</v>
+      </c>
+      <c r="H53" t="n">
+        <v>46.1</v>
+      </c>
       <c r="I53" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.97</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="M53" t="n">
+        <v>808</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R53" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T53" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>-4.26</v>
-      </c>
-      <c r="M53" t="n">
-        <v>176</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R53" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="T53" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4716,75 +4718,77 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>225</v>
+        <v>77.7</v>
       </c>
       <c r="F54" t="n">
-        <v>27.32</v>
+        <v>26.26</v>
       </c>
       <c r="G54" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>2.03</v>
+      </c>
+      <c r="H54" t="n">
+        <v>17.3</v>
+      </c>
       <c r="I54" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-7.79</v>
+        <v>-1.02</v>
       </c>
       <c r="M54" t="n">
-        <v>244</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>78.5</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>30.7</v>
+        <v>11.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="R54" t="n">
-        <v>20.4</v>
+        <v>4.4</v>
       </c>
       <c r="S54" t="n">
-        <v>812.4</v>
+        <v>768.2</v>
       </c>
       <c r="T54" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.64</v>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4793,134 +4797,132 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E55" t="n">
-        <v>232</v>
+        <v>166.5</v>
       </c>
       <c r="F55" t="n">
-        <v>21.39</v>
+        <v>15.63</v>
       </c>
       <c r="G55" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="H55" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I55" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-1.49</v>
+        <v>0.3</v>
       </c>
       <c r="M55" t="n">
-        <v>235.5</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>14.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.53</v>
+        <v>4.03</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>30.2</v>
       </c>
       <c r="S55" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E56" t="n">
-        <v>776</v>
+        <v>351</v>
       </c>
       <c r="F56" t="n">
-        <v>27.93</v>
+        <v>12.49</v>
       </c>
       <c r="G56" t="n">
-        <v>8.85</v>
+        <v>1.71</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.91</v>
+        <v>-4.88</v>
       </c>
       <c r="M56" t="n">
-        <v>769</v>
+        <v>369</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>31.7</v>
+        <v>13.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="R56" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="S56" t="n">
-        <v>21.9</v>
+        <v>30</v>
       </c>
       <c r="T56" t="n">
-        <v>32.2</v>
+        <v>43.5</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
@@ -4937,76 +4939,72 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E57" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F57" t="n">
-        <v>32.47</v>
+        <v>18.93</v>
       </c>
       <c r="G57" t="n">
-        <v>3.46</v>
+        <v>2.24</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>186.3</v>
+        <v>11</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-5.88</v>
+        <v>0.76</v>
       </c>
       <c r="M57" t="n">
-        <v>144.5</v>
+        <v>131</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S57" t="n">
-        <v>37</v>
+        <v>48.7</v>
       </c>
       <c r="T57" t="n">
-        <v>35.8</v>
+        <v>28.4</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5018,46 +5016,46 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>3890</v>
+        <v>23.25</v>
       </c>
       <c r="F58" t="n">
-        <v>24.28</v>
+        <v>17.94</v>
       </c>
       <c r="G58" t="n">
-        <v>2.76</v>
+        <v>1.94</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>13.7</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-5.93</v>
+        <v>-1.06</v>
       </c>
       <c r="M58" t="n">
-        <v>4135</v>
+        <v>23.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5066,28 +5064,28 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>月營收轉負-5%</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="R58" t="n">
-        <v>6.8</v>
+        <v>12.8</v>
       </c>
       <c r="S58" t="n">
-        <v>41.8</v>
+        <v>-5.3</v>
       </c>
       <c r="T58" t="n">
-        <v>32.9</v>
+        <v>18.2</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5099,150 +5097,154 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="E59" t="n">
-        <v>562</v>
+        <v>45.55</v>
       </c>
       <c r="F59" t="n">
-        <v>35.8</v>
+        <v>14.74</v>
       </c>
       <c r="G59" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="H59" t="n">
-        <v>29.3</v>
-      </c>
+        <v>1.29</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.87</v>
-      </c>
+        <v>147.4</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1.4</v>
+        <v>-0.65</v>
       </c>
       <c r="M59" t="n">
-        <v>570</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+        <v>45.85</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>含金量0.0差</t>
+        </is>
+      </c>
       <c r="P59" t="n">
-        <v>19.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.94</v>
+        <v>0.04</v>
       </c>
       <c r="R59" t="n">
-        <v>10.6</v>
+        <v>36.1</v>
       </c>
       <c r="S59" t="n">
-        <v>64.90000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="T59" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.87</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E60" t="n">
-        <v>808</v>
+        <v>181</v>
       </c>
       <c r="F60" t="n">
-        <v>54.78</v>
+        <v>14.09</v>
       </c>
       <c r="G60" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>46.1</v>
-      </c>
+        <v>1.29</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1.97</v>
-      </c>
+        <v>21.9</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-6.05</v>
+        <v>-2.43</v>
       </c>
       <c r="M60" t="n">
-        <v>860</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+        <v>185.5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>含金量-1.3差</t>
+        </is>
+      </c>
       <c r="P60" t="n">
-        <v>15.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.83</v>
+        <v>-1.31</v>
       </c>
       <c r="R60" t="n">
-        <v>24.8</v>
+        <v>6.4</v>
       </c>
       <c r="S60" t="n">
-        <v>1.5</v>
+        <v>224.4</v>
       </c>
       <c r="T60" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.97</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -5250,19 +5252,19 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5271,57 +5273,59 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E61" t="n">
-        <v>78.5</v>
+        <v>748</v>
       </c>
       <c r="F61" t="n">
-        <v>19.24</v>
+        <v>19.07</v>
       </c>
       <c r="G61" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="H61" t="n">
-        <v>17.3</v>
-      </c>
+        <v>18.02</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.64</v>
-      </c>
+        <v>-8.1</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-3.09</v>
+        <v>-2.86</v>
       </c>
       <c r="M61" t="n">
-        <v>81</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+        <v>770</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P61" t="n">
-        <v>11.3</v>
+        <v>94.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="R61" t="n">
-        <v>4.4</v>
+        <v>18.2</v>
       </c>
       <c r="S61" t="n">
-        <v>768.2</v>
+        <v>12</v>
       </c>
       <c r="T61" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.64</v>
-      </c>
+        <v>19.6</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -5329,120 +5333,118 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E62" t="n">
-        <v>166</v>
+        <v>251.5</v>
       </c>
       <c r="F62" t="n">
-        <v>15.68</v>
+        <v>17.4</v>
       </c>
       <c r="G62" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H62" t="n">
-        <v>15.5</v>
-      </c>
+        <v>1.87</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.95</v>
-      </c>
+        <v>-15.3</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-0.3</v>
+        <v>3.29</v>
       </c>
       <c r="M62" t="n">
-        <v>166.5</v>
+        <v>243.5</v>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>EPS單期衰退</t>
+        </is>
+      </c>
       <c r="P62" t="n">
-        <v>10.8</v>
+        <v>9.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.03</v>
+        <v>0.72</v>
       </c>
       <c r="R62" t="n">
-        <v>30.2</v>
+        <v>13.2</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>34.8</v>
       </c>
       <c r="T62" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.95</v>
-      </c>
+        <v>34.5</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E63" t="n">
-        <v>23.5</v>
+        <v>817</v>
       </c>
       <c r="F63" t="n">
-        <v>19.11</v>
+        <v>19.46</v>
       </c>
       <c r="G63" t="n">
-        <v>1.96</v>
+        <v>5.71</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>13.7</v>
+        <v>27</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -5451,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-0.63</v>
+        <v>5.28</v>
       </c>
       <c r="M63" t="n">
-        <v>23.65</v>
+        <v>776</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5463,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>月營收轉負-5%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>10.3</v>
+        <v>31.7</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="R63" t="n">
-        <v>12.8</v>
+        <v>3.8</v>
       </c>
       <c r="S63" t="n">
-        <v>-5.3</v>
+        <v>21.9</v>
       </c>
       <c r="T63" t="n">
-        <v>18.2</v>
+        <v>32.2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5496,34 +5498,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E64" t="n">
-        <v>45.85</v>
+        <v>891</v>
       </c>
       <c r="F64" t="n">
-        <v>15.18</v>
+        <v>12.68</v>
       </c>
       <c r="G64" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>147.4</v>
+        <v>-19.8</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -5532,10 +5534,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-2.86</v>
+        <v>-1.55</v>
       </c>
       <c r="M64" t="n">
-        <v>47.2</v>
+        <v>905</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5544,28 +5546,28 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>含金量0.0差</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>29.2</v>
+        <v>15.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.04</v>
+        <v>1.24</v>
       </c>
       <c r="R64" t="n">
-        <v>36.1</v>
+        <v>5.7</v>
       </c>
       <c r="S64" t="n">
-        <v>0.4</v>
+        <v>47.5</v>
       </c>
       <c r="T64" t="n">
-        <v>14.4</v>
+        <v>53.2</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -5577,34 +5579,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E65" t="n">
-        <v>770</v>
+        <v>3950</v>
       </c>
       <c r="F65" t="n">
-        <v>19.67</v>
+        <v>15.27</v>
       </c>
       <c r="G65" t="n">
-        <v>18.59</v>
+        <v>1.95</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>-8.1</v>
+        <v>9</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -5613,10 +5615,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-3.02</v>
+        <v>1.54</v>
       </c>
       <c r="M65" t="n">
-        <v>794</v>
+        <v>3890</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5625,28 +5627,28 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>94.5</v>
+        <v>11.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="R65" t="n">
-        <v>18.2</v>
+        <v>6.8</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>41.8</v>
       </c>
       <c r="T65" t="n">
-        <v>19.6</v>
+        <v>32.9</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -5675,13 +5677,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F66" t="n">
-        <v>19.58</v>
+        <v>14.91</v>
       </c>
       <c r="G66" t="n">
-        <v>2.09</v>
+        <v>2.88</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5696,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-2.28</v>
+        <v>-0.58</v>
       </c>
       <c r="M66" t="n">
-        <v>52.7</v>
+        <v>51.5</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,13 +5758,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>158.5</v>
+        <v>156.5</v>
       </c>
       <c r="F67" t="n">
-        <v>17.52</v>
+        <v>17.19</v>
       </c>
       <c r="G67" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5781,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.86</v>
+        <v>-1.26</v>
       </c>
       <c r="M67" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5837,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="F68" t="n">
-        <v>21.89</v>
+        <v>16.99</v>
       </c>
       <c r="G68" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5860,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.15</v>
+        <v>-1.36</v>
       </c>
       <c r="M68" t="n">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5916,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F69" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="G69" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5939,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.41</v>
+        <v>-0.41</v>
       </c>
       <c r="M69" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5995,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F70" t="n">
-        <v>35.12</v>
+        <v>18.48</v>
       </c>
       <c r="G70" t="n">
-        <v>9.630000000000001</v>
+        <v>4.61</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6018,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-3.36</v>
+        <v>2.5</v>
       </c>
       <c r="M70" t="n">
-        <v>372.5</v>
+        <v>360</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6074,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="F71" t="n">
-        <v>19.87</v>
+        <v>19.68</v>
       </c>
       <c r="G71" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6097,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.95</v>
+        <v>-0.75</v>
       </c>
       <c r="M71" t="n">
-        <v>94.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>147</v>
+        <v>143.5</v>
       </c>
       <c r="F72" t="n">
-        <v>20.87</v>
+        <v>20.05</v>
       </c>
       <c r="G72" t="n">
-        <v>5.7</v>
+        <v>5.47</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-3.92</v>
+        <v>-2.38</v>
       </c>
       <c r="M72" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6236,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>237</v>
+        <v>237.5</v>
       </c>
       <c r="F73" t="n">
-        <v>16.83</v>
+        <v>16.2</v>
       </c>
       <c r="G73" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6259,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-2.07</v>
+        <v>0.21</v>
       </c>
       <c r="M73" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6315,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1185</v>
+        <v>1110</v>
       </c>
       <c r="F74" t="n">
-        <v>68.88</v>
+        <v>62.07</v>
       </c>
       <c r="G74" t="n">
-        <v>35.86</v>
+        <v>32.32</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-9.890000000000001</v>
+        <v>-6.33</v>
       </c>
       <c r="M74" t="n">
-        <v>1315</v>
+        <v>1185</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6396,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F75" t="n">
-        <v>24.87</v>
+        <v>25.83</v>
       </c>
       <c r="G75" t="n">
-        <v>3.19</v>
+        <v>2.65</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-2.68</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6479,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2450</v>
+        <v>2325</v>
       </c>
       <c r="F76" t="n">
-        <v>40.26</v>
+        <v>35.42</v>
       </c>
       <c r="G76" t="n">
-        <v>21.29</v>
+        <v>9.98</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6502,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-8.24</v>
+        <v>-5.1</v>
       </c>
       <c r="M76" t="n">
-        <v>2670</v>
+        <v>2450</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6558,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="F77" t="n">
-        <v>24.51</v>
+        <v>12.06</v>
       </c>
       <c r="G77" t="n">
-        <v>9.5</v>
+        <v>3.75</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6581,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-5.26</v>
+        <v>-1.93</v>
       </c>
       <c r="M77" t="n">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6637,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2440</v>
+        <v>2465</v>
       </c>
       <c r="F78" t="n">
-        <v>32.8</v>
+        <v>26.63</v>
       </c>
       <c r="G78" t="n">
-        <v>10.74</v>
+        <v>6.92</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6660,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="M78" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6716,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="F79" t="n">
-        <v>15.15</v>
+        <v>32.98</v>
       </c>
       <c r="G79" t="n">
-        <v>3.39</v>
+        <v>4.88</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6739,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.48</v>
+        <v>0.49</v>
       </c>
       <c r="M79" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,7 +6795,7 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>123</v>
+        <v>123.5</v>
       </c>
       <c r="F80" t="n">
         <v>16.64</v>
@@ -6816,7 +6818,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M80" t="n">
         <v>123</v>
@@ -6872,13 +6874,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>34.15</v>
+        <v>34.2</v>
       </c>
       <c r="F81" t="n">
-        <v>6.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6897,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1.16</v>
+        <v>0.15</v>
       </c>
       <c r="M81" t="n">
-        <v>34.55</v>
+        <v>34.15</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6954,10 +6956,10 @@
         <v>111.5</v>
       </c>
       <c r="F82" t="n">
-        <v>12.02</v>
+        <v>15.6</v>
       </c>
       <c r="G82" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6976,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1.33</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>113</v>
+        <v>111.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7032,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="F83" t="n">
-        <v>13.25</v>
+        <v>17.43</v>
       </c>
       <c r="G83" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7055,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.11</v>
+        <v>0.28</v>
       </c>
       <c r="M83" t="n">
-        <v>180.5</v>
+        <v>178.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7111,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>42.4</v>
+        <v>39.85</v>
       </c>
       <c r="F84" t="n">
-        <v>8.050000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G84" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7134,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-2.64</v>
+        <v>-6.01</v>
       </c>
       <c r="M84" t="n">
-        <v>43.55</v>
+        <v>42.4</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7190,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1175</v>
+        <v>1195</v>
       </c>
       <c r="F85" t="n">
-        <v>34.84</v>
+        <v>16.92</v>
       </c>
       <c r="G85" t="n">
-        <v>11.67</v>
+        <v>5.14</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7213,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-8.91</v>
+        <v>1.7</v>
       </c>
       <c r="M85" t="n">
-        <v>1290</v>
+        <v>1175</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7269,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>475.5</v>
+        <v>472</v>
       </c>
       <c r="F86" t="n">
-        <v>24.59</v>
+        <v>12.85</v>
       </c>
       <c r="G86" t="n">
-        <v>4.56</v>
+        <v>2.17</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7292,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-6.03</v>
+        <v>-0.74</v>
       </c>
       <c r="M86" t="n">
-        <v>506</v>
+        <v>475.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7348,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="F87" t="n">
-        <v>17.58</v>
+        <v>21.56</v>
       </c>
       <c r="G87" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7371,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-3.03</v>
+        <v>-0.35</v>
       </c>
       <c r="M87" t="n">
-        <v>148.5</v>
+        <v>144</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7427,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>40.95</v>
+        <v>40.5</v>
       </c>
       <c r="F88" t="n">
-        <v>9</v>
+        <v>11.95</v>
       </c>
       <c r="G88" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7450,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-2.96</v>
+        <v>-1.1</v>
       </c>
       <c r="M88" t="n">
-        <v>42.2</v>
+        <v>40.95</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2455</v>
+        <v>2415</v>
       </c>
       <c r="F89" t="n">
-        <v>46.43</v>
+        <v>42.85</v>
       </c>
       <c r="G89" t="n">
-        <v>21.01</v>
+        <v>14.31</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-7.18</v>
+        <v>-1.63</v>
       </c>
       <c r="M89" t="n">
-        <v>2645</v>
+        <v>2455</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7589,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="F90" t="n">
-        <v>29.15</v>
+        <v>27.99</v>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-3.96</v>
+        <v>-4.64</v>
       </c>
       <c r="M90" t="n">
-        <v>1010</v>
+        <v>970</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7672,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="F91" t="n">
-        <v>10.53</v>
+        <v>11.41</v>
       </c>
       <c r="G91" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-2.44</v>
+        <v>-0.68</v>
       </c>
       <c r="M91" t="n">
-        <v>90</v>
+        <v>87.8</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7755,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="F92" t="n">
-        <v>8.15</v>
+        <v>10.58</v>
       </c>
       <c r="G92" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1.57</v>
+        <v>-0.53</v>
       </c>
       <c r="M92" t="n">
-        <v>76.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7838,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>66.2</v>
+        <v>65.2</v>
       </c>
       <c r="F93" t="n">
-        <v>12.75</v>
+        <v>12.3</v>
       </c>
       <c r="G93" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-3.5</v>
+        <v>-1.51</v>
       </c>
       <c r="M93" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F94" t="n">
-        <v>18.75</v>
+        <v>20.33</v>
       </c>
       <c r="G94" t="n">
-        <v>6.93</v>
+        <v>5.47</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-1.32</v>
+        <v>1.07</v>
       </c>
       <c r="M94" t="n">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8004,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5015</v>
+        <v>5050</v>
       </c>
       <c r="F95" t="n">
-        <v>16.88</v>
+        <v>24.29</v>
       </c>
       <c r="G95" t="n">
-        <v>6.68</v>
+        <v>5.85</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-0.4</v>
+        <v>0.7</v>
       </c>
       <c r="M95" t="n">
-        <v>5035</v>
+        <v>5015</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8087,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>155.5</v>
+        <v>146.5</v>
       </c>
       <c r="F96" t="n">
-        <v>15.6</v>
+        <v>20.8</v>
       </c>
       <c r="G96" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.58</v>
+        <v>-5.79</v>
       </c>
       <c r="M96" t="n">
-        <v>158</v>
+        <v>155.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8170,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="F97" t="n">
-        <v>18.41</v>
+        <v>41.42</v>
       </c>
       <c r="G97" t="n">
-        <v>3.01</v>
+        <v>4.62</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8193,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-1.32</v>
+        <v>1.67</v>
       </c>
       <c r="M97" t="n">
-        <v>1520</v>
+        <v>1500</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8253,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="F98" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="G98" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8272,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.12</v>
+        <v>0.5</v>
       </c>
       <c r="M98" t="n">
-        <v>80.2</v>
+        <v>79.3</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8331,10 +8333,10 @@
         <v>404</v>
       </c>
       <c r="F99" t="n">
-        <v>8.199999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="G99" t="n">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8349,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.58</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>410.5</v>
+        <v>404</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8411,13 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.85</v>
+        <v>23.7</v>
       </c>
       <c r="F100" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="G100" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8430,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-1.65</v>
+        <v>-0.63</v>
       </c>
       <c r="M100" t="n">
-        <v>24.25</v>
+        <v>23.85</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8473,46 +8475,42 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E101" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="F101" t="n">
-        <v>9.550000000000001</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>3.98</v>
+        <v>0.55</v>
       </c>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-5.36</v>
+        <v>-1.74</v>
       </c>
       <c r="M101" t="n">
-        <v>196</v>
+        <v>403</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8521,28 +8519,28 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>含金量-1.3差</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>41.3</v>
+        <v>17.9</v>
       </c>
       <c r="Q101" t="n">
-        <v>-1.31</v>
+        <v>1.5</v>
       </c>
       <c r="R101" t="n">
-        <v>6.4</v>
+        <v>-6.1</v>
       </c>
       <c r="S101" t="n">
-        <v>224.4</v>
+        <v>730.1</v>
       </c>
       <c r="T101" t="n">
-        <v>10.5</v>
+        <v>45.2</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -8702,13 +8700,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2450</v>
+        <v>2325</v>
       </c>
       <c r="F2" t="n">
-        <v>40.26</v>
+        <v>35.42</v>
       </c>
       <c r="G2" t="n">
-        <v>21.29</v>
+        <v>9.98</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8723,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-8.24</v>
+        <v>-5.1</v>
       </c>
       <c r="M2" t="n">
-        <v>2670</v>
+        <v>2450</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8779,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="F3" t="n">
-        <v>24.51</v>
+        <v>12.06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.5</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8802,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-5.26</v>
+        <v>-1.93</v>
       </c>
       <c r="M3" t="n">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8858,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2440</v>
+        <v>2465</v>
       </c>
       <c r="F4" t="n">
-        <v>32.8</v>
+        <v>26.63</v>
       </c>
       <c r="G4" t="n">
-        <v>10.74</v>
+        <v>6.92</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8881,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8937,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="F5" t="n">
-        <v>15.15</v>
+        <v>32.98</v>
       </c>
       <c r="G5" t="n">
-        <v>3.39</v>
+        <v>4.88</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8960,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.48</v>
+        <v>0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,7 +9016,7 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>123.5</v>
       </c>
       <c r="F6" t="n">
         <v>16.64</v>
@@ -9041,7 +9039,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M6" t="n">
         <v>123</v>
@@ -9097,13 +9095,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>34.15</v>
+        <v>34.2</v>
       </c>
       <c r="F7" t="n">
-        <v>6.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9118,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.16</v>
+        <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>34.55</v>
+        <v>34.15</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9179,10 +9177,10 @@
         <v>111.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.02</v>
+        <v>15.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9197,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.33</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>113</v>
+        <v>111.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9253,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>13.25</v>
+        <v>17.43</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9276,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.11</v>
+        <v>0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>180.5</v>
+        <v>178.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9332,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.4</v>
+        <v>39.85</v>
       </c>
       <c r="F10" t="n">
-        <v>8.050000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9355,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.64</v>
+        <v>-6.01</v>
       </c>
       <c r="M10" t="n">
-        <v>43.55</v>
+        <v>42.4</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9411,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1175</v>
+        <v>1195</v>
       </c>
       <c r="F11" t="n">
-        <v>34.84</v>
+        <v>16.92</v>
       </c>
       <c r="G11" t="n">
-        <v>11.67</v>
+        <v>5.14</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9434,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-8.91</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>1290</v>
+        <v>1175</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9490,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>475.5</v>
+        <v>472</v>
       </c>
       <c r="F12" t="n">
-        <v>24.59</v>
+        <v>12.85</v>
       </c>
       <c r="G12" t="n">
-        <v>4.56</v>
+        <v>2.17</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9513,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-6.03</v>
+        <v>-0.74</v>
       </c>
       <c r="M12" t="n">
-        <v>506</v>
+        <v>475.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9569,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.58</v>
+        <v>21.56</v>
       </c>
       <c r="G13" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9592,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-3.03</v>
+        <v>-0.35</v>
       </c>
       <c r="M13" t="n">
-        <v>148.5</v>
+        <v>144</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9648,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>40.95</v>
+        <v>40.5</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>11.95</v>
       </c>
       <c r="G14" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9671,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-2.96</v>
+        <v>-1.1</v>
       </c>
       <c r="M14" t="n">
-        <v>42.2</v>
+        <v>40.95</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9727,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2455</v>
+        <v>2415</v>
       </c>
       <c r="F15" t="n">
-        <v>46.43</v>
+        <v>42.85</v>
       </c>
       <c r="G15" t="n">
-        <v>21.01</v>
+        <v>14.31</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9750,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-7.18</v>
+        <v>-1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>2645</v>
+        <v>2455</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9810,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="F16" t="n">
-        <v>29.15</v>
+        <v>27.99</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9833,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-3.96</v>
+        <v>-4.64</v>
       </c>
       <c r="M16" t="n">
-        <v>1010</v>
+        <v>970</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9893,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="F17" t="n">
-        <v>10.53</v>
+        <v>11.41</v>
       </c>
       <c r="G17" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9916,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-2.44</v>
+        <v>-0.68</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>87.8</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9976,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>8.15</v>
+        <v>10.58</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +9999,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.57</v>
+        <v>-0.53</v>
       </c>
       <c r="M18" t="n">
-        <v>76.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10059,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>66.2</v>
+        <v>65.2</v>
       </c>
       <c r="F19" t="n">
-        <v>12.75</v>
+        <v>12.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10082,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-3.5</v>
+        <v>-1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10142,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F20" t="n">
-        <v>18.75</v>
+        <v>20.33</v>
       </c>
       <c r="G20" t="n">
-        <v>6.93</v>
+        <v>5.47</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10165,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1.32</v>
+        <v>1.07</v>
       </c>
       <c r="M20" t="n">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10225,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5015</v>
+        <v>5050</v>
       </c>
       <c r="F21" t="n">
-        <v>16.88</v>
+        <v>24.29</v>
       </c>
       <c r="G21" t="n">
-        <v>6.68</v>
+        <v>5.85</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10248,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.4</v>
+        <v>0.7</v>
       </c>
       <c r="M21" t="n">
-        <v>5035</v>
+        <v>5015</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10308,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>155.5</v>
+        <v>146.5</v>
       </c>
       <c r="F22" t="n">
-        <v>15.6</v>
+        <v>20.8</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10331,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-1.58</v>
+        <v>-5.79</v>
       </c>
       <c r="M22" t="n">
-        <v>158</v>
+        <v>155.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10391,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="F23" t="n">
-        <v>18.41</v>
+        <v>41.42</v>
       </c>
       <c r="G23" t="n">
-        <v>3.01</v>
+        <v>4.62</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10414,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.32</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>1520</v>
+        <v>1500</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10605,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>158.5</v>
+        <v>156.5</v>
       </c>
       <c r="F2" t="n">
-        <v>17.52</v>
+        <v>17.19</v>
       </c>
       <c r="G2" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10628,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.86</v>
+        <v>-1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10684,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="F3" t="n">
-        <v>21.89</v>
+        <v>16.99</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10707,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.15</v>
+        <v>-1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10763,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="G4" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10786,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.41</v>
+        <v>-0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10842,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F5" t="n">
-        <v>35.12</v>
+        <v>18.48</v>
       </c>
       <c r="G5" t="n">
-        <v>9.630000000000001</v>
+        <v>4.61</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10865,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.36</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>372.5</v>
+        <v>360</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10921,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>19.87</v>
+        <v>19.68</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10944,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.95</v>
+        <v>-0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>94.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11000,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>147</v>
+        <v>143.5</v>
       </c>
       <c r="F7" t="n">
-        <v>20.87</v>
+        <v>20.05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.47</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11023,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.92</v>
+        <v>-2.38</v>
       </c>
       <c r="M7" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11083,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>237</v>
+        <v>237.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.83</v>
+        <v>16.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11106,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-2.07</v>
+        <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11162,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1185</v>
+        <v>1110</v>
       </c>
       <c r="F9" t="n">
-        <v>68.88</v>
+        <v>62.07</v>
       </c>
       <c r="G9" t="n">
-        <v>35.86</v>
+        <v>32.32</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11183,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-9.890000000000001</v>
+        <v>-6.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1315</v>
+        <v>1185</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11243,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F10" t="n">
-        <v>24.87</v>
+        <v>25.83</v>
       </c>
       <c r="G10" t="n">
-        <v>3.19</v>
+        <v>2.65</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11266,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.68</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11457,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1335</v>
+        <v>1320</v>
       </c>
       <c r="F2" t="n">
-        <v>101.64</v>
+        <v>56.03</v>
       </c>
       <c r="G2" t="n">
-        <v>28.53</v>
+        <v>9.23</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11480,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-6.32</v>
+        <v>-1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>1425</v>
+        <v>1335</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11536,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.35</v>
+        <v>39.25</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2</v>
+        <v>11.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11559,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>39.65</v>
+        <v>39.35</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11615,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>146.5</v>
+        <v>145.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94</v>
+        <v>18.07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.73</v>
+        <v>4.4</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11638,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.68</v>
+        <v>-0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>149</v>
+        <v>146.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11694,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6310</v>
+        <v>6460</v>
       </c>
       <c r="F5" t="n">
-        <v>182.51</v>
+        <v>168</v>
       </c>
       <c r="G5" t="n">
-        <v>42.63</v>
+        <v>39.24</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11717,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-7.95</v>
+        <v>2.38</v>
       </c>
       <c r="M5" t="n">
-        <v>6855</v>
+        <v>6310</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11777,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>116.5</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
-        <v>23.63</v>
+        <v>24.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.88</v>
+        <v>4.24</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11800,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.85</v>
+        <v>-3</v>
       </c>
       <c r="M6" t="n">
-        <v>117.5</v>
+        <v>116.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11856,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.28</v>
+        <v>30.67</v>
       </c>
       <c r="G7" t="n">
-        <v>5.01</v>
+        <v>4.83</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11879,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-4.35</v>
+        <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>126.5</v>
+        <v>121</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11939,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>214.5</v>
+        <v>235.5</v>
       </c>
       <c r="F8" t="n">
-        <v>32.75</v>
+        <v>20.78</v>
       </c>
       <c r="G8" t="n">
-        <v>6.35</v>
+        <v>2.75</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11962,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-9.869999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>238</v>
+        <v>214.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12022,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>93.2</v>
       </c>
       <c r="F9" t="n">
-        <v>26.14</v>
+        <v>27.03</v>
       </c>
       <c r="G9" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,7 +12045,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-9.51</v>
       </c>
       <c r="M9" t="n">
         <v>103</v>
@@ -12103,13 +12101,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F10" t="n">
-        <v>20.19</v>
+        <v>20.55</v>
       </c>
       <c r="G10" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12124,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.79</v>
+        <v>-1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12180,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1345</v>
       </c>
       <c r="F11" t="n">
-        <v>30.21</v>
+        <v>22.33</v>
       </c>
       <c r="G11" t="n">
-        <v>5.43</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12203,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.36</v>
+        <v>-2.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12259,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>24.21</v>
+        <v>22.33</v>
       </c>
       <c r="G12" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12282,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-5.14</v>
+        <v>-0.28</v>
       </c>
       <c r="M12" t="n">
-        <v>185</v>
+        <v>175.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12342,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F13" t="n">
-        <v>31.32</v>
+        <v>18.99</v>
       </c>
       <c r="G13" t="n">
-        <v>5.49</v>
+        <v>2.73</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12365,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-4.91</v>
+        <v>0.47</v>
       </c>
       <c r="M13" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12425,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>139.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.03</v>
+        <v>26.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12448,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>-1.06</v>
       </c>
       <c r="M14" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12504,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F15" t="n">
-        <v>21.88</v>
+        <v>24.25</v>
       </c>
       <c r="G15" t="n">
-        <v>5.37</v>
+        <v>7.16</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,7 +12527,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M15" t="n">
         <v>240</v>
@@ -12589,13 +12587,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4480</v>
+        <v>4400</v>
       </c>
       <c r="F16" t="n">
-        <v>134.78</v>
+        <v>53.56</v>
       </c>
       <c r="G16" t="n">
-        <v>41.17</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12610,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2.71</v>
+        <v>-1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>4605</v>
+        <v>4480</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12801,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="F2" t="n">
-        <v>69.69</v>
+        <v>29.68</v>
       </c>
       <c r="G2" t="n">
-        <v>16.39</v>
+        <v>5.03</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12824,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.26</v>
+        <v>-0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>1995</v>
+        <v>1890</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12880,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="F3" t="n">
-        <v>23.43</v>
+        <v>23.05</v>
       </c>
       <c r="G3" t="n">
-        <v>12.29</v>
+        <v>12.09</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12903,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.63</v>
+        <v>-1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12963,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="F4" t="n">
-        <v>88.38</v>
+        <v>74.7</v>
       </c>
       <c r="G4" t="n">
-        <v>22.13</v>
+        <v>15.67</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12986,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-3.77</v>
+        <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>3320</v>
+        <v>3195</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13042,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5220</v>
+        <v>5315</v>
       </c>
       <c r="F5" t="n">
-        <v>113.23</v>
+        <v>23.19</v>
       </c>
       <c r="G5" t="n">
-        <v>39.01</v>
+        <v>6.44</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13065,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-4.66</v>
+        <v>1.82</v>
       </c>
       <c r="M5" t="n">
-        <v>5475</v>
+        <v>5220</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13121,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="F6" t="n">
-        <v>51.41</v>
+        <v>39.6</v>
       </c>
       <c r="G6" t="n">
-        <v>28.68</v>
+        <v>21.08</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13144,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3.23</v>
+        <v>-1.07</v>
       </c>
       <c r="M6" t="n">
-        <v>773</v>
+        <v>748</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13204,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12.24</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13227,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.92</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13283,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>193.5</v>
+        <v>195.5</v>
       </c>
       <c r="F8" t="n">
-        <v>15.3</v>
+        <v>14.65</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13306,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.78</v>
+        <v>1.03</v>
       </c>
       <c r="M8" t="n">
-        <v>197</v>
+        <v>193.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13366,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.49</v>
+        <v>20.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.26</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13389,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13445,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F10" t="n">
-        <v>18.45</v>
+        <v>11.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13468,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-6.74</v>
+        <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>653</v>
+        <v>609</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13528,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>230</v>
+        <v>225.5</v>
       </c>
       <c r="F11" t="n">
-        <v>34.28</v>
+        <v>34.63</v>
       </c>
       <c r="G11" t="n">
-        <v>3.16</v>
+        <v>2.61</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13551,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-4.76</v>
+        <v>-1.96</v>
       </c>
       <c r="M11" t="n">
-        <v>241.5</v>
+        <v>230</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13611,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4035</v>
+        <v>4065</v>
       </c>
       <c r="F12" t="n">
-        <v>59.14</v>
+        <v>40.44</v>
       </c>
       <c r="G12" t="n">
-        <v>7.62</v>
+        <v>6.57</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13634,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-4.27</v>
+        <v>0.74</v>
       </c>
       <c r="M12" t="n">
-        <v>4215</v>
+        <v>4035</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="F2" t="n">
-        <v>56.03</v>
+        <v>87.73</v>
       </c>
       <c r="G2" t="n">
-        <v>9.23</v>
+        <v>24.63</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.12</v>
+        <v>-6.82</v>
       </c>
       <c r="M2" t="n">
-        <v>1335</v>
+        <v>1320</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -639,10 +639,10 @@
         <v>39.25</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12</v>
+        <v>11.09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.35</v>
+        <v>39.25</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -718,10 +718,10 @@
         <v>145.5</v>
       </c>
       <c r="F4" t="n">
-        <v>18.07</v>
+        <v>16.82</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>146.5</v>
+        <v>145.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6460</v>
+        <v>7080</v>
       </c>
       <c r="F5" t="n">
-        <v>168</v>
+        <v>171.99</v>
       </c>
       <c r="G5" t="n">
-        <v>39.24</v>
+        <v>40.17</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.38</v>
+        <v>9.6</v>
       </c>
       <c r="M5" t="n">
-        <v>6310</v>
+        <v>6460</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>108.5</v>
       </c>
       <c r="F6" t="n">
-        <v>24.84</v>
+        <v>22.01</v>
       </c>
       <c r="G6" t="n">
-        <v>4.24</v>
+        <v>3.61</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3</v>
+        <v>-3.98</v>
       </c>
       <c r="M6" t="n">
-        <v>116.5</v>
+        <v>113</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="F7" t="n">
-        <v>30.67</v>
+        <v>35.71</v>
       </c>
       <c r="G7" t="n">
-        <v>4.83</v>
+        <v>5.07</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>235.5</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>20.78</v>
+        <v>36.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.75</v>
+        <v>7.1</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9.789999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>214.5</v>
+        <v>235.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>93.2</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>27.03</v>
+        <v>24.11</v>
       </c>
       <c r="G9" t="n">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-9.51</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>103</v>
+        <v>93.2</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>20.55</v>
+        <v>20.31</v>
       </c>
       <c r="G10" t="n">
-        <v>5.65</v>
+        <v>5.58</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="M10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1345</v>
+        <v>1280</v>
       </c>
       <c r="F11" t="n">
-        <v>22.33</v>
+        <v>28.02</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>5.03</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.54</v>
+        <v>-4.83</v>
       </c>
       <c r="M11" t="n">
-        <v>1380</v>
+        <v>1345</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>174.5</v>
       </c>
       <c r="F12" t="n">
-        <v>22.33</v>
+        <v>24.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>214</v>
+        <v>213.5</v>
       </c>
       <c r="F13" t="n">
-        <v>18.99</v>
+        <v>31.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="M13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>139.5</v>
+        <v>133.5</v>
       </c>
       <c r="F14" t="n">
-        <v>26.28</v>
+        <v>26.54</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-1.06</v>
+        <v>-4.3</v>
       </c>
       <c r="M14" t="n">
-        <v>141</v>
+        <v>139.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         <v>241</v>
       </c>
       <c r="F15" t="n">
-        <v>24.25</v>
+        <v>21.97</v>
       </c>
       <c r="G15" t="n">
-        <v>7.16</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4400</v>
+        <v>4340</v>
       </c>
       <c r="F16" t="n">
-        <v>53.56</v>
+        <v>130.57</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>39.88</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.79</v>
+        <v>-1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>4480</v>
+        <v>4400</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F17" t="n">
-        <v>72.73999999999999</v>
+        <v>55.83</v>
       </c>
       <c r="G17" t="n">
-        <v>15.1</v>
+        <v>16.35</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.57</v>
+        <v>-0.34</v>
       </c>
       <c r="M17" t="n">
-        <v>1540</v>
+        <v>1485</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1830,12 +1830,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1844,20 +1844,20 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>698</v>
+        <v>8250</v>
       </c>
       <c r="F18" t="n">
-        <v>44.89</v>
+        <v>72.72</v>
       </c>
       <c r="G18" t="n">
-        <v>6.27</v>
+        <v>24.94</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>25.3</v>
+        <v>90.7</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.29</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>700</v>
+        <v>8095</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1878,19 +1878,19 @@
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>18.1</v>
+        <v>34.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="R18" t="n">
-        <v>7.8</v>
+        <v>28.8</v>
       </c>
       <c r="S18" t="n">
-        <v>17.8</v>
+        <v>172.1</v>
       </c>
       <c r="T18" t="n">
-        <v>69.5</v>
+        <v>66.5</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
@@ -1907,12 +1907,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1921,20 +1921,20 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>82.8</v>
+        <v>709</v>
       </c>
       <c r="F19" t="n">
-        <v>60.87</v>
+        <v>69.92</v>
       </c>
       <c r="G19" t="n">
-        <v>7.22</v>
+        <v>12.82</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>203.8</v>
+        <v>25.3</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.43</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>84</v>
+        <v>698</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1955,24 +1955,24 @@
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>15.4</v>
+        <v>18.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="R19" t="n">
-        <v>19.4</v>
+        <v>7.8</v>
       </c>
       <c r="S19" t="n">
-        <v>25.3</v>
+        <v>17.8</v>
       </c>
       <c r="T19" t="n">
-        <v>62.5</v>
+        <v>69.5</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1998,20 +1998,20 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>7705</v>
+        <v>82.8</v>
       </c>
       <c r="F20" t="n">
-        <v>44.65</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>8.82</v>
+        <v>7.12</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>86.3</v>
+        <v>203.8</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -2020,40 +2020,36 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-3.99</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>8025</v>
+        <v>82.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>含金量0.6弱</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>27.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.63</v>
+        <v>1.18</v>
       </c>
       <c r="R20" t="n">
-        <v>28.5</v>
+        <v>19.4</v>
       </c>
       <c r="S20" t="n">
-        <v>119.8</v>
+        <v>25.3</v>
       </c>
       <c r="T20" t="n">
-        <v>192</v>
+        <v>62.5</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2065,12 +2061,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2079,20 +2075,20 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>1855</v>
+        <v>7765</v>
       </c>
       <c r="F21" t="n">
-        <v>37.4</v>
+        <v>159.12</v>
       </c>
       <c r="G21" t="n">
-        <v>7.38</v>
+        <v>43.07</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>71.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -2101,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-5.6</v>
+        <v>0.78</v>
       </c>
       <c r="M21" t="n">
-        <v>1965</v>
+        <v>7705</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2113,23 +2109,23 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>含金量0.3差</t>
+          <t>含金量0.6弱</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>48.1</v>
+        <v>27.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="R21" t="n">
-        <v>12.6</v>
+        <v>28.5</v>
       </c>
       <c r="S21" t="n">
-        <v>133.1</v>
+        <v>119.8</v>
       </c>
       <c r="T21" t="n">
-        <v>72.7</v>
+        <v>192</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
@@ -2146,34 +2142,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1645</v>
+        <v>1820</v>
       </c>
       <c r="F22" t="n">
-        <v>113.8</v>
+        <v>57.4</v>
       </c>
       <c r="G22" t="n">
-        <v>25.18</v>
+        <v>27.8</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>99.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -2182,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.44</v>
+        <v>-1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>1575</v>
+        <v>1855</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2194,23 +2190,23 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>含金量-0.4差</t>
+          <t>含金量0.3差</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>22.1</v>
+        <v>48.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.38</v>
+        <v>0.31</v>
       </c>
       <c r="R22" t="n">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="S22" t="n">
-        <v>124.4</v>
+        <v>133.1</v>
       </c>
       <c r="T22" t="n">
-        <v>135.1</v>
+        <v>72.7</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -2227,12 +2223,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2241,20 +2237,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>35.15</v>
+        <v>376</v>
       </c>
       <c r="F23" t="n">
-        <v>186.25</v>
+        <v>43.47</v>
       </c>
       <c r="G23" t="n">
-        <v>1.33</v>
+        <v>6.44</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>158.2</v>
+        <v>24.9</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -2263,40 +2259,36 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-8.460000000000001</v>
+        <v>7.12</v>
       </c>
       <c r="M23" t="n">
-        <v>38.4</v>
+        <v>351</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>ROE4低</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>4.5</v>
+        <v>13.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="R23" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="S23" t="n">
-        <v>97.8</v>
+        <v>30</v>
       </c>
       <c r="T23" t="n">
-        <v>130</v>
+        <v>43.5</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2308,12 +2300,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2322,19 +2314,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>2095</v>
+        <v>1570</v>
       </c>
       <c r="F24" t="n">
-        <v>250.33</v>
+        <v>118.86</v>
       </c>
       <c r="G24" t="n">
-        <v>41.58</v>
+        <v>26.3</v>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>99.8</v>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -2342,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9.970000000000001</v>
+        <v>-4.56</v>
       </c>
       <c r="M24" t="n">
-        <v>1905</v>
+        <v>1645</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2354,23 +2348,23 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>含金量-0.4差</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>16.6</v>
+        <v>22.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.13</v>
+        <v>-0.38</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="S24" t="n">
-        <v>118.8</v>
+        <v>124.4</v>
       </c>
       <c r="T24" t="n">
-        <v>310.9</v>
+        <v>135.1</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
@@ -2387,12 +2381,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2401,19 +2395,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>1530</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>105.22</v>
+        <v>133.33</v>
       </c>
       <c r="G25" t="n">
-        <v>7.45</v>
+        <v>3.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>158.2</v>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -2421,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1495</v>
+        <v>35.15</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2433,23 +2429,23 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>ROE4低</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>17.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="R25" t="n">
-        <v>120.6</v>
+        <v>5.2</v>
       </c>
       <c r="S25" t="n">
-        <v>108.5</v>
+        <v>97.8</v>
       </c>
       <c r="T25" t="n">
-        <v>65.2</v>
+        <v>130</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
@@ -2466,12 +2462,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2480,21 +2476,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>434.5</v>
+        <v>2005</v>
       </c>
       <c r="F26" t="n">
-        <v>77.40000000000001</v>
+        <v>275.3</v>
       </c>
       <c r="G26" t="n">
-        <v>14.74</v>
+        <v>45.72</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2502,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.52</v>
+        <v>-4.3</v>
       </c>
       <c r="M26" t="n">
-        <v>428</v>
+        <v>2095</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2518,19 +2512,19 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>18.9</v>
+        <v>16.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="R26" t="n">
-        <v>50.3</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>21.1</v>
+        <v>118.8</v>
       </c>
       <c r="T26" t="n">
-        <v>99.8</v>
+        <v>310.9</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
@@ -2547,12 +2541,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2561,20 +2555,20 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>2840</v>
+        <v>677</v>
       </c>
       <c r="F27" t="n">
-        <v>83.16</v>
+        <v>62.86</v>
       </c>
       <c r="G27" t="n">
-        <v>9.48</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>454.2</v>
+        <v>12.6</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -2583,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.18</v>
+        <v>8.32</v>
       </c>
       <c r="M27" t="n">
-        <v>2835</v>
+        <v>625</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2595,23 +2589,23 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>14.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.99</v>
+        <v>3.26</v>
       </c>
       <c r="R27" t="n">
-        <v>9.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="S27" t="n">
-        <v>34.1</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>95.3</v>
+        <v>62.1</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
@@ -2628,30 +2622,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>1285</v>
       </c>
       <c r="F28" t="n">
-        <v>143.06</v>
+        <v>80.56</v>
       </c>
       <c r="G28" t="n">
-        <v>9.1</v>
+        <v>13.87</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2662,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.03</v>
+        <v>-16.01</v>
       </c>
       <c r="M28" t="n">
-        <v>495</v>
+        <v>1530</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2678,24 +2672,24 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>10.7</v>
+        <v>17.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.73</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>4.5</v>
+        <v>120.6</v>
       </c>
       <c r="S28" t="n">
-        <v>49.9</v>
+        <v>108.5</v>
       </c>
       <c r="T28" t="n">
-        <v>165.8</v>
+        <v>65.2</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2707,34 +2701,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>546</v>
+        <v>432.5</v>
       </c>
       <c r="F29" t="n">
-        <v>35.18</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>6.28</v>
+        <v>14.97</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>-2.9</v>
+        <v>27.5</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -2743,31 +2737,35 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9.970000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="M29" t="n">
-        <v>496.5</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+        <v>434.5</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>22.4</v>
+        <v>18.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="R29" t="n">
-        <v>4.9</v>
+        <v>50.3</v>
       </c>
       <c r="S29" t="n">
-        <v>32.1</v>
+        <v>21.1</v>
       </c>
       <c r="T29" t="n">
-        <v>38.6</v>
+        <v>99.8</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
@@ -2777,40 +2775,42 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>168.5</v>
+        <v>2855</v>
       </c>
       <c r="F30" t="n">
-        <v>78.95</v>
+        <v>83.31</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>454.2</v>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-3.16</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>174</v>
+        <v>2840</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2830,23 +2830,23 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>11.6</v>
+        <v>14.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.62</v>
+        <v>0.99</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>182</v>
+        <v>34.1</v>
       </c>
       <c r="T30" t="n">
-        <v>65.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
@@ -2863,71 +2863,71 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>1885</v>
+        <v>502</v>
       </c>
       <c r="F31" t="n">
-        <v>29.68</v>
+        <v>149.4</v>
       </c>
       <c r="G31" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="H31" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.32</v>
-      </c>
+        <v>14.02</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-0.26</v>
+        <v>-1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>1890</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+        <v>510</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>EPS資料不足</t>
+        </is>
+      </c>
       <c r="P31" t="n">
-        <v>22.3</v>
+        <v>10.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>15.2</v>
+        <v>4.5</v>
       </c>
       <c r="S31" t="n">
-        <v>43.7</v>
+        <v>49.9</v>
       </c>
       <c r="T31" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.32</v>
-      </c>
+        <v>165.8</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -2935,161 +2935,155 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>717</v>
+        <v>260.5</v>
       </c>
       <c r="F32" t="n">
-        <v>23.05</v>
+        <v>38.42</v>
       </c>
       <c r="G32" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="H32" t="n">
-        <v>19</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.09</v>
-      </c>
+        <v>-15.3</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-1.1</v>
+        <v>3.58</v>
       </c>
       <c r="M32" t="n">
-        <v>725</v>
+        <v>251.5</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>⚠️高槓桿(負債80%)</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>52.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.91</v>
+        <v>0.72</v>
       </c>
       <c r="R32" t="n">
-        <v>9.699999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="S32" t="n">
-        <v>19.2</v>
+        <v>34.8</v>
       </c>
       <c r="T32" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.09</v>
-      </c>
+        <v>34.5</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>3200</v>
+        <v>435.5</v>
       </c>
       <c r="F33" t="n">
-        <v>74.7</v>
+        <v>38.99</v>
       </c>
       <c r="G33" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="H33" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>49</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.13</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.16</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>3195</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+        <v>396</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
+        </is>
+      </c>
       <c r="P33" t="n">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>23.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S33" t="n">
-        <v>37.7</v>
+        <v>730.1</v>
       </c>
       <c r="T33" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.13</v>
-      </c>
+        <v>45.2</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3097,161 +3091,157 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>5315</v>
+        <v>540</v>
       </c>
       <c r="F34" t="n">
-        <v>23.19</v>
+        <v>41.89</v>
       </c>
       <c r="G34" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="H34" t="n">
-        <v>75.3</v>
-      </c>
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.01</v>
-      </c>
+        <v>-2.9</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>-1.1</v>
       </c>
       <c r="M34" t="n">
-        <v>5220</v>
+        <v>546</v>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>EPS單期衰退</t>
+        </is>
+      </c>
       <c r="P34" t="n">
-        <v>34.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="R34" t="n">
-        <v>25.1</v>
+        <v>4.9</v>
       </c>
       <c r="S34" t="n">
-        <v>114.6</v>
+        <v>32.1</v>
       </c>
       <c r="T34" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.01</v>
-      </c>
+        <v>38.6</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>740</v>
+        <v>900</v>
       </c>
       <c r="F35" t="n">
-        <v>39.6</v>
+        <v>70.87</v>
       </c>
       <c r="G35" t="n">
-        <v>21.08</v>
-      </c>
-      <c r="H35" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>891</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S35" t="n">
         <v>47.5</v>
       </c>
-      <c r="I35" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="M35" t="n">
-        <v>748</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R35" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>-9.300000000000001</v>
-      </c>
       <c r="T35" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.83</v>
-      </c>
+        <v>53.2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3259,208 +3249,206 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>101.5</v>
+        <v>176.5</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>52.37</v>
       </c>
       <c r="G36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H36" t="n">
-        <v>11</v>
-      </c>
-      <c r="I36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.02</v>
-      </c>
+        <v>6.81</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-0.49</v>
+        <v>4.75</v>
       </c>
       <c r="M36" t="n">
-        <v>102</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+        <v>168.5</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P36" t="n">
-        <v>17.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="R36" t="n">
-        <v>5.3</v>
+        <v>-2.7</v>
       </c>
       <c r="S36" t="n">
-        <v>7.7</v>
+        <v>182</v>
       </c>
       <c r="T36" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.02</v>
-      </c>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>195.5</v>
+        <v>3925</v>
       </c>
       <c r="F37" t="n">
-        <v>14.65</v>
+        <v>62.55</v>
       </c>
       <c r="G37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="H37" t="n">
-        <v>13.4</v>
-      </c>
+        <v>16.05</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.02</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.03</v>
+        <v>-1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>3995</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>17.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="R37" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="S37" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.02</v>
-      </c>
+        <v>61.7</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>105.5</v>
+        <v>1880</v>
       </c>
       <c r="F38" t="n">
-        <v>20.6</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>4.7</v>
+        <v>16.3</v>
       </c>
       <c r="H38" t="n">
-        <v>16</v>
+        <v>59.1</v>
       </c>
       <c r="I38" t="n">
-        <v>7.6</v>
+        <v>34.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3468,78 +3456,78 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.48</v>
+        <v>-0.27</v>
       </c>
       <c r="M38" t="n">
-        <v>105</v>
+        <v>1885</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R38" t="n">
-        <v>7.6</v>
+        <v>15.2</v>
       </c>
       <c r="S38" t="n">
-        <v>1.4</v>
+        <v>43.7</v>
       </c>
       <c r="T38" t="n">
-        <v>17.2</v>
+        <v>79.3</v>
       </c>
       <c r="U38" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>612</v>
+        <v>720</v>
       </c>
       <c r="F39" t="n">
-        <v>11.26</v>
+        <v>22.8</v>
       </c>
       <c r="G39" t="n">
-        <v>2.16</v>
+        <v>11.95</v>
       </c>
       <c r="H39" t="n">
-        <v>21.4</v>
+        <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3547,38 +3535,38 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="M39" t="n">
-        <v>609</v>
+        <v>717</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>⚠️高槓桿(負債80%)</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>14.3</v>
+        <v>52.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S39" t="n">
-        <v>30.2</v>
+        <v>19.2</v>
       </c>
       <c r="T39" t="n">
-        <v>23.4</v>
+        <v>20.9</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -3590,39 +3578,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>225.5</v>
+        <v>3205</v>
       </c>
       <c r="F40" t="n">
-        <v>34.63</v>
+        <v>88.66</v>
       </c>
       <c r="G40" t="n">
-        <v>2.61</v>
+        <v>22.2</v>
       </c>
       <c r="H40" t="n">
-        <v>30.9</v>
+        <v>70.2</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="J40" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3630,34 +3618,30 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-1.96</v>
+        <v>0.16</v>
       </c>
       <c r="M40" t="n">
-        <v>230</v>
+        <v>3200</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>含金量0.5差</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.49</v>
+        <v>0.92</v>
       </c>
       <c r="R40" t="n">
-        <v>7.6</v>
+        <v>23.2</v>
       </c>
       <c r="S40" t="n">
-        <v>8.4</v>
+        <v>37.7</v>
       </c>
       <c r="T40" t="n">
-        <v>36.5</v>
+        <v>104.6</v>
       </c>
       <c r="U40" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3666,46 +3650,46 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>4065</v>
+        <v>5295</v>
       </c>
       <c r="F41" t="n">
-        <v>40.44</v>
+        <v>114.86</v>
       </c>
       <c r="G41" t="n">
-        <v>6.57</v>
+        <v>39.57</v>
       </c>
       <c r="H41" t="n">
-        <v>51.7</v>
+        <v>75.3</v>
       </c>
       <c r="I41" t="n">
-        <v>23.4</v>
+        <v>59.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3713,38 +3697,34 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.74</v>
+        <v>-0.38</v>
       </c>
       <c r="M41" t="n">
-        <v>4035</v>
+        <v>5315</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>12.9</v>
+        <v>34.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.26</v>
+        <v>0.76</v>
       </c>
       <c r="R41" t="n">
-        <v>31.2</v>
+        <v>25.1</v>
       </c>
       <c r="S41" t="n">
-        <v>-33.5</v>
+        <v>114.6</v>
       </c>
       <c r="T41" t="n">
-        <v>63.8</v>
+        <v>120.3</v>
       </c>
       <c r="U41" t="n">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -3756,12 +3736,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3770,55 +3750,61 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>8095</v>
+        <v>721</v>
       </c>
       <c r="F42" t="n">
-        <v>32.37</v>
+        <v>49.55</v>
       </c>
       <c r="G42" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>27.65</v>
+      </c>
+      <c r="H42" t="n">
+        <v>47.5</v>
+      </c>
       <c r="I42" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="J42" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.83</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-2</v>
+        <v>-2.57</v>
       </c>
       <c r="M42" t="n">
-        <v>8260</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+        <v>740</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>月營收轉負-9%</t>
+        </is>
+      </c>
       <c r="P42" t="n">
-        <v>34.3</v>
+        <v>53.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="R42" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="S42" t="n">
-        <v>172.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
+        <v>57.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.83</v>
+      </c>
       <c r="V42" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3826,19 +3812,19 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3847,152 +3833,160 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>408</v>
+        <v>101.5</v>
       </c>
       <c r="F43" t="n">
-        <v>22.66</v>
+        <v>11.94</v>
       </c>
       <c r="G43" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>1.87</v>
+      </c>
+      <c r="H43" t="n">
+        <v>11</v>
+      </c>
       <c r="I43" t="n">
-        <v>49</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.02</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-2.63</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>419</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>101.5</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>29.3</v>
+        <v>17.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.09</v>
+        <v>2.11</v>
       </c>
       <c r="R43" t="n">
-        <v>24.2</v>
+        <v>5.3</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>7.7</v>
       </c>
       <c r="T43" t="n">
-        <v>24</v>
-      </c>
-      <c r="U43" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.02</v>
+      </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>171.5</v>
+        <v>194</v>
       </c>
       <c r="F44" t="n">
-        <v>21.22</v>
+        <v>15.34</v>
       </c>
       <c r="G44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>2.72</v>
+      </c>
+      <c r="H44" t="n">
+        <v>13.4</v>
+      </c>
       <c r="I44" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.02</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M44" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R44" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M44" t="n">
-        <v>175</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T44" t="n">
-        <v>22</v>
-      </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4001,79 +3995,77 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>98.8</v>
+        <v>107.5</v>
       </c>
       <c r="F45" t="n">
-        <v>22.09</v>
+        <v>15.86</v>
       </c>
       <c r="G45" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>3.33</v>
+      </c>
+      <c r="H45" t="n">
+        <v>16</v>
+      </c>
       <c r="I45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.27</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.82</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>98</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+        <v>105.5</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>9.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S45" t="n">
-        <v>-2.7</v>
+        <v>1.4</v>
       </c>
       <c r="T45" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U45" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.27</v>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4082,79 +4074,81 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>169.5</v>
+        <v>616</v>
       </c>
       <c r="F46" t="n">
-        <v>31.21</v>
+        <v>18.67</v>
       </c>
       <c r="G46" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>2.66</v>
+      </c>
+      <c r="H46" t="n">
+        <v>21.4</v>
+      </c>
       <c r="I46" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="M46" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>ROE5低</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5.4</v>
+        <v>14.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="R46" t="n">
-        <v>22.1</v>
+        <v>10.6</v>
       </c>
       <c r="S46" t="n">
-        <v>14.6</v>
+        <v>30.2</v>
       </c>
       <c r="T46" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="U46" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.4</v>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4163,55 +4157,61 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>226</v>
+        <v>221.5</v>
       </c>
       <c r="F47" t="n">
-        <v>25.2</v>
+        <v>33.01</v>
       </c>
       <c r="G47" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30.9</v>
+      </c>
       <c r="I47" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.03</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.44</v>
+        <v>-1.77</v>
       </c>
       <c r="M47" t="n">
-        <v>225</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+        <v>225.5</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>含金量0.5差</t>
+        </is>
+      </c>
       <c r="P47" t="n">
-        <v>30.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.44</v>
+        <v>0.49</v>
       </c>
       <c r="R47" t="n">
-        <v>20.4</v>
+        <v>7.6</v>
       </c>
       <c r="S47" t="n">
-        <v>812.4</v>
+        <v>8.4</v>
       </c>
       <c r="T47" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
+        <v>36.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.03</v>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4219,118 +4219,124 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>228</v>
+        <v>4210</v>
       </c>
       <c r="F48" t="n">
-        <v>21.07</v>
+        <v>61.7</v>
       </c>
       <c r="G48" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>7.95</v>
+      </c>
+      <c r="H48" t="n">
+        <v>51.7</v>
+      </c>
       <c r="I48" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.73</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4065</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>含金量0.3差、月營收轉負-34%</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R48" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="M48" t="n">
-        <v>232</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>625</v>
+        <v>403.5</v>
       </c>
       <c r="F49" t="n">
-        <v>21.16</v>
+        <v>22.07</v>
       </c>
       <c r="G49" t="n">
-        <v>2.22</v>
+        <v>6.53</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>12.6</v>
+        <v>49</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4339,35 +4345,31 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-3.99</v>
+        <v>-1.1</v>
       </c>
       <c r="M49" t="n">
-        <v>651</v>
+        <v>408</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>12.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.26</v>
+        <v>1.09</v>
       </c>
       <c r="R49" t="n">
-        <v>3.2</v>
+        <v>24.2</v>
       </c>
       <c r="S49" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="T49" t="n">
-        <v>62.1</v>
+        <v>24</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -4384,34 +4386,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="E50" t="n">
-        <v>139</v>
+        <v>168.5</v>
       </c>
       <c r="F50" t="n">
-        <v>30.56</v>
+        <v>20.47</v>
       </c>
       <c r="G50" t="n">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>186.3</v>
+        <v>57.1</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4420,35 +4422,31 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.21</v>
+        <v>-1.75</v>
       </c>
       <c r="M50" t="n">
-        <v>136</v>
+        <v>171.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>10.7</v>
+        <v>18.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.85</v>
+        <v>2.74</v>
       </c>
       <c r="R50" t="n">
-        <v>-3.4</v>
+        <v>11.1</v>
       </c>
       <c r="S50" t="n">
-        <v>37</v>
+        <v>3.6</v>
       </c>
       <c r="T50" t="n">
-        <v>35.8</v>
+        <v>22</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4465,34 +4463,34 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E51" t="n">
-        <v>3995</v>
+        <v>129</v>
       </c>
       <c r="F51" t="n">
-        <v>20.76</v>
+        <v>29.52</v>
       </c>
       <c r="G51" t="n">
-        <v>5.41</v>
+        <v>3.03</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4501,35 +4499,31 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-0.87</v>
+        <v>-2.27</v>
       </c>
       <c r="M51" t="n">
-        <v>4030</v>
+        <v>132</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>25.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R51" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>48.7</v>
       </c>
       <c r="T51" t="n">
-        <v>61.7</v>
+        <v>28.4</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4546,150 +4540,154 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>546</v>
+        <v>97.8</v>
       </c>
       <c r="F52" t="n">
-        <v>17.26</v>
+        <v>20.08</v>
       </c>
       <c r="G52" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="H52" t="n">
-        <v>29.3</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.87</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-2.85</v>
+        <v>-1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>562</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+        <v>98.8</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>19.2</v>
+        <v>9.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R52" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>64.90000000000001</v>
+        <v>-2.7</v>
       </c>
       <c r="T52" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.87</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E53" t="n">
-        <v>785</v>
+        <v>168</v>
       </c>
       <c r="F53" t="n">
-        <v>38.6</v>
+        <v>34.64</v>
       </c>
       <c r="G53" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="H53" t="n">
-        <v>46.1</v>
-      </c>
+        <v>1.87</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.97</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.85</v>
+        <v>-0.88</v>
       </c>
       <c r="M53" t="n">
-        <v>808</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+        <v>169.5</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P53" t="n">
-        <v>15.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="R53" t="n">
-        <v>24.8</v>
+        <v>22.1</v>
       </c>
       <c r="S53" t="n">
-        <v>1.5</v>
+        <v>14.6</v>
       </c>
       <c r="T53" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.97</v>
-      </c>
+        <v>34.2</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -4697,19 +4695,19 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4718,77 +4716,75 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E54" t="n">
-        <v>77.7</v>
+        <v>232</v>
       </c>
       <c r="F54" t="n">
-        <v>26.26</v>
+        <v>25.31</v>
       </c>
       <c r="G54" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="H54" t="n">
-        <v>17.3</v>
-      </c>
+        <v>6.16</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.64</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1.02</v>
+        <v>2.65</v>
       </c>
       <c r="M54" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>11.3</v>
+        <v>30.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="R54" t="n">
-        <v>4.4</v>
+        <v>20.4</v>
       </c>
       <c r="S54" t="n">
-        <v>768.2</v>
+        <v>812.4</v>
       </c>
       <c r="T54" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.64</v>
-      </c>
+        <v>34.6</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4797,132 +4793,134 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>166.5</v>
+        <v>221.5</v>
       </c>
       <c r="F55" t="n">
-        <v>15.63</v>
+        <v>20.71</v>
       </c>
       <c r="G55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>15.5</v>
-      </c>
+        <v>3.02</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.95</v>
-      </c>
+        <v>49.2</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.3</v>
+        <v>-2.85</v>
       </c>
       <c r="M55" t="n">
-        <v>166</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
+        <v>228</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.03</v>
+        <v>1.53</v>
       </c>
       <c r="R55" t="n">
-        <v>30.2</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="T55" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.95</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E56" t="n">
-        <v>351</v>
+        <v>840</v>
       </c>
       <c r="F56" t="n">
-        <v>12.49</v>
+        <v>30.24</v>
       </c>
       <c r="G56" t="n">
-        <v>1.71</v>
+        <v>9.58</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>24.9</v>
+        <v>27</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-4.88</v>
+        <v>2.82</v>
       </c>
       <c r="M56" t="n">
-        <v>369</v>
+        <v>817</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P56" t="n">
-        <v>13.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="R56" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="S56" t="n">
-        <v>30</v>
+        <v>21.9</v>
       </c>
       <c r="T56" t="n">
-        <v>43.5</v>
+        <v>32.2</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
@@ -4939,72 +4937,76 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F57" t="n">
-        <v>18.93</v>
+        <v>31.24</v>
       </c>
       <c r="G57" t="n">
-        <v>2.24</v>
+        <v>3.33</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>11</v>
+        <v>186.3</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.76</v>
+        <v>-2.16</v>
       </c>
       <c r="M57" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P57" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="R57" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S57" t="n">
-        <v>48.7</v>
+        <v>37</v>
       </c>
       <c r="T57" t="n">
-        <v>28.4</v>
+        <v>35.8</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5016,46 +5018,46 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E58" t="n">
-        <v>23.25</v>
+        <v>3950</v>
       </c>
       <c r="F58" t="n">
-        <v>17.94</v>
+        <v>24.66</v>
       </c>
       <c r="G58" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>13.7</v>
+        <v>9</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-1.06</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>23.5</v>
+        <v>3950</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5064,28 +5066,28 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>月營收轉負-5%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="R58" t="n">
-        <v>12.8</v>
+        <v>6.8</v>
       </c>
       <c r="S58" t="n">
-        <v>-5.3</v>
+        <v>41.8</v>
       </c>
       <c r="T58" t="n">
-        <v>18.2</v>
+        <v>32.9</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5097,154 +5099,150 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E59" t="n">
-        <v>45.55</v>
+        <v>549</v>
       </c>
       <c r="F59" t="n">
-        <v>14.74</v>
+        <v>34.97</v>
       </c>
       <c r="G59" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>6.92</v>
+      </c>
+      <c r="H59" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I59" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-0.65</v>
+        <v>0.55</v>
       </c>
       <c r="M59" t="n">
-        <v>45.85</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>含金量0.0差</t>
-        </is>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>29.2</v>
+        <v>19.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.04</v>
+        <v>1.94</v>
       </c>
       <c r="R59" t="n">
-        <v>36.1</v>
+        <v>10.6</v>
       </c>
       <c r="S59" t="n">
-        <v>0.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T59" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E60" t="n">
-        <v>181</v>
+        <v>817</v>
       </c>
       <c r="F60" t="n">
-        <v>14.09</v>
+        <v>55.39</v>
       </c>
       <c r="G60" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>8.59</v>
+      </c>
+      <c r="H60" t="n">
+        <v>46.1</v>
+      </c>
       <c r="I60" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.97</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-2.43</v>
+        <v>4.08</v>
       </c>
       <c r="M60" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>含金量-1.3差</t>
-        </is>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>41.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>-1.31</v>
+        <v>1.83</v>
       </c>
       <c r="R60" t="n">
-        <v>6.4</v>
+        <v>24.8</v>
       </c>
       <c r="S60" t="n">
-        <v>224.4</v>
+        <v>1.5</v>
       </c>
       <c r="T60" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="U60" t="inlineStr"/>
+        <v>60.2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.97</v>
+      </c>
       <c r="V60" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -5252,19 +5250,19 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5273,59 +5271,57 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E61" t="n">
-        <v>748</v>
+        <v>76</v>
       </c>
       <c r="F61" t="n">
-        <v>19.07</v>
+        <v>18.63</v>
       </c>
       <c r="G61" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="H61" t="n">
+        <v>17.3</v>
+      </c>
       <c r="I61" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-2.86</v>
+        <v>-2.19</v>
       </c>
       <c r="M61" t="n">
-        <v>770</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+        <v>77.7</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>94.5</v>
+        <v>11.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="R61" t="n">
-        <v>18.2</v>
+        <v>4.4</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>768.2</v>
       </c>
       <c r="T61" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.64</v>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -5333,118 +5329,120 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E62" t="n">
-        <v>251.5</v>
+        <v>166.5</v>
       </c>
       <c r="F62" t="n">
-        <v>17.4</v>
+        <v>15.68</v>
       </c>
       <c r="G62" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="H62" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I62" t="n">
-        <v>-15.3</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>243.5</v>
+        <v>166.5</v>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.72</v>
+        <v>4.03</v>
       </c>
       <c r="R62" t="n">
-        <v>13.2</v>
+        <v>30.2</v>
       </c>
       <c r="S62" t="n">
-        <v>34.8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E63" t="n">
-        <v>817</v>
+        <v>21.8</v>
       </c>
       <c r="F63" t="n">
-        <v>19.46</v>
+        <v>17.72</v>
       </c>
       <c r="G63" t="n">
-        <v>5.71</v>
+        <v>1.82</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>13.7</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -5453,10 +5451,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5.28</v>
+        <v>-6.24</v>
       </c>
       <c r="M63" t="n">
-        <v>776</v>
+        <v>23.25</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5463,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>月營收轉負-5%</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>31.7</v>
+        <v>10.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="R63" t="n">
-        <v>3.8</v>
+        <v>12.8</v>
       </c>
       <c r="S63" t="n">
-        <v>21.9</v>
+        <v>-5.3</v>
       </c>
       <c r="T63" t="n">
-        <v>32.2</v>
+        <v>18.2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5498,34 +5496,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>891</v>
+        <v>45.6</v>
       </c>
       <c r="F64" t="n">
-        <v>12.68</v>
+        <v>14.65</v>
       </c>
       <c r="G64" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>-19.8</v>
+        <v>147.4</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -5534,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.55</v>
+        <v>0.11</v>
       </c>
       <c r="M64" t="n">
-        <v>905</v>
+        <v>45.55</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5546,28 +5544,28 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>含金量0.0差</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>15.5</v>
+        <v>29.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.24</v>
+        <v>0.04</v>
       </c>
       <c r="R64" t="n">
-        <v>5.7</v>
+        <v>36.1</v>
       </c>
       <c r="S64" t="n">
-        <v>47.5</v>
+        <v>0.4</v>
       </c>
       <c r="T64" t="n">
-        <v>53.2</v>
+        <v>14.4</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -5579,34 +5577,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>3950</v>
+        <v>744</v>
       </c>
       <c r="F65" t="n">
-        <v>15.27</v>
+        <v>18.53</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95</v>
+        <v>17.51</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>-8.1</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -5615,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.54</v>
+        <v>-0.53</v>
       </c>
       <c r="M65" t="n">
-        <v>3890</v>
+        <v>748</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5627,28 +5625,28 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>11.4</v>
+        <v>94.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="R65" t="n">
-        <v>6.8</v>
+        <v>18.2</v>
       </c>
       <c r="S65" t="n">
-        <v>41.8</v>
+        <v>12</v>
       </c>
       <c r="T65" t="n">
-        <v>32.9</v>
+        <v>19.6</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -5677,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="F66" t="n">
-        <v>14.91</v>
+        <v>19.16</v>
       </c>
       <c r="G66" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5696,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.58</v>
+        <v>-1.56</v>
       </c>
       <c r="M66" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5758,13 +5756,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>156.5</v>
+        <v>158</v>
       </c>
       <c r="F67" t="n">
-        <v>17.19</v>
+        <v>16.97</v>
       </c>
       <c r="G67" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5781,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.26</v>
+        <v>0.96</v>
       </c>
       <c r="M67" t="n">
-        <v>158.5</v>
+        <v>156.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5840,10 +5838,10 @@
         <v>509</v>
       </c>
       <c r="F68" t="n">
-        <v>16.99</v>
+        <v>21.6</v>
       </c>
       <c r="G68" t="n">
-        <v>3.4</v>
+        <v>5.13</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5860,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5916,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F69" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="G69" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5939,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.41</v>
+        <v>0.41</v>
       </c>
       <c r="M69" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5995,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>369</v>
+        <v>358.5</v>
       </c>
       <c r="F70" t="n">
-        <v>18.48</v>
+        <v>34.98</v>
       </c>
       <c r="G70" t="n">
-        <v>4.61</v>
+        <v>9.59</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6018,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>-2.85</v>
       </c>
       <c r="M70" t="n">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6074,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="F71" t="n">
-        <v>19.68</v>
+        <v>19.54</v>
       </c>
       <c r="G71" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6097,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.75</v>
+        <v>-0.86</v>
       </c>
       <c r="M71" t="n">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6153,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>143.5</v>
+        <v>143</v>
       </c>
       <c r="F72" t="n">
-        <v>20.05</v>
+        <v>19.58</v>
       </c>
       <c r="G72" t="n">
-        <v>5.47</v>
+        <v>5.34</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6176,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-2.38</v>
+        <v>-0.35</v>
       </c>
       <c r="M72" t="n">
-        <v>147</v>
+        <v>143.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6239,10 +6237,10 @@
         <v>237.5</v>
       </c>
       <c r="F73" t="n">
-        <v>16.2</v>
+        <v>16.87</v>
       </c>
       <c r="G73" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6259,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>237</v>
+        <v>237.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6315,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1110</v>
+        <v>1055</v>
       </c>
       <c r="F74" t="n">
-        <v>62.07</v>
+        <v>58.15</v>
       </c>
       <c r="G74" t="n">
-        <v>32.32</v>
+        <v>30.27</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6336,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-6.33</v>
+        <v>-4.95</v>
       </c>
       <c r="M74" t="n">
-        <v>1185</v>
+        <v>1110</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>66.2</v>
+        <v>69.8</v>
       </c>
       <c r="F75" t="n">
-        <v>25.83</v>
+        <v>26.54</v>
       </c>
       <c r="G75" t="n">
-        <v>2.65</v>
+        <v>3.41</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6419,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>5.44</v>
       </c>
       <c r="M75" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6479,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="F76" t="n">
-        <v>35.42</v>
+        <v>38.61</v>
       </c>
       <c r="G76" t="n">
-        <v>9.98</v>
+        <v>20.42</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6502,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-5.1</v>
+        <v>1.08</v>
       </c>
       <c r="M76" t="n">
-        <v>2450</v>
+        <v>2325</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6558,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="F77" t="n">
-        <v>12.06</v>
+        <v>24.29</v>
       </c>
       <c r="G77" t="n">
-        <v>3.75</v>
+        <v>9.41</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6581,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1.93</v>
+        <v>1.04</v>
       </c>
       <c r="M77" t="n">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6637,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2465</v>
+        <v>2415</v>
       </c>
       <c r="F78" t="n">
-        <v>26.63</v>
+        <v>32.47</v>
       </c>
       <c r="G78" t="n">
-        <v>6.92</v>
+        <v>10.63</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6660,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.02</v>
+        <v>-2.03</v>
       </c>
       <c r="M78" t="n">
-        <v>2440</v>
+        <v>2465</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6716,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="F79" t="n">
-        <v>32.98</v>
+        <v>15.15</v>
       </c>
       <c r="G79" t="n">
-        <v>4.88</v>
+        <v>3.39</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6739,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="M79" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6795,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="F80" t="n">
-        <v>16.64</v>
+        <v>16.71</v>
       </c>
       <c r="G80" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6818,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.41</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>123</v>
+        <v>123.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6874,13 +6872,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>34.2</v>
+        <v>34.45</v>
       </c>
       <c r="F81" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="G81" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6897,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.15</v>
+        <v>0.73</v>
       </c>
       <c r="M81" t="n">
-        <v>34.15</v>
+        <v>34.2</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6953,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="F82" t="n">
-        <v>15.6</v>
+        <v>12.07</v>
       </c>
       <c r="G82" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6976,7 +6974,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="M82" t="n">
         <v>111.5</v>
@@ -7032,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F83" t="n">
-        <v>17.43</v>
+        <v>13.07</v>
       </c>
       <c r="G83" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7055,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.28</v>
+        <v>-1.68</v>
       </c>
       <c r="M83" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7111,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>39.85</v>
+        <v>39.6</v>
       </c>
       <c r="F84" t="n">
-        <v>8.98</v>
+        <v>7.51</v>
       </c>
       <c r="G84" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7134,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-6.01</v>
+        <v>-0.63</v>
       </c>
       <c r="M84" t="n">
-        <v>42.4</v>
+        <v>39.85</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7190,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="F85" t="n">
-        <v>16.92</v>
+        <v>34.84</v>
       </c>
       <c r="G85" t="n">
-        <v>5.14</v>
+        <v>11.67</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7213,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="M85" t="n">
-        <v>1175</v>
+        <v>1195</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7269,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>472</v>
+        <v>448.5</v>
       </c>
       <c r="F86" t="n">
-        <v>12.85</v>
+        <v>21.79</v>
       </c>
       <c r="G86" t="n">
-        <v>2.17</v>
+        <v>4.04</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7292,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.74</v>
+        <v>-4.98</v>
       </c>
       <c r="M86" t="n">
-        <v>475.5</v>
+        <v>472</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7348,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="F87" t="n">
-        <v>21.56</v>
+        <v>17.4</v>
       </c>
       <c r="G87" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7371,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.35</v>
+        <v>-0.7</v>
       </c>
       <c r="M87" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7427,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="F88" t="n">
-        <v>11.95</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7450,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1.1</v>
+        <v>-4.2</v>
       </c>
       <c r="M88" t="n">
-        <v>40.95</v>
+        <v>40.5</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7506,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2415</v>
+        <v>2470</v>
       </c>
       <c r="F89" t="n">
-        <v>42.85</v>
+        <v>46.71</v>
       </c>
       <c r="G89" t="n">
-        <v>14.31</v>
+        <v>21.13</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7529,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-1.63</v>
+        <v>2.28</v>
       </c>
       <c r="M89" t="n">
-        <v>2455</v>
+        <v>2415</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="F90" t="n">
-        <v>27.99</v>
+        <v>26.7</v>
       </c>
       <c r="G90" t="n">
-        <v>6.73</v>
+        <v>6.41</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7612,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-4.64</v>
+        <v>-0.54</v>
       </c>
       <c r="M90" t="n">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>87.2</v>
+        <v>88.5</v>
       </c>
       <c r="F91" t="n">
-        <v>11.41</v>
+        <v>10.61</v>
       </c>
       <c r="G91" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7695,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-0.68</v>
+        <v>1.49</v>
       </c>
       <c r="M91" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>10.58</v>
+        <v>7.99</v>
       </c>
       <c r="G92" t="n">
-        <v>2.82</v>
+        <v>1.86</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7778,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.53</v>
+        <v>-1.47</v>
       </c>
       <c r="M92" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="F93" t="n">
-        <v>12.3</v>
+        <v>12.12</v>
       </c>
       <c r="G93" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7861,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.51</v>
+        <v>-3.99</v>
       </c>
       <c r="M93" t="n">
-        <v>66.2</v>
+        <v>65.2</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>377</v>
+        <v>373.5</v>
       </c>
       <c r="F94" t="n">
-        <v>20.33</v>
+        <v>18.78</v>
       </c>
       <c r="G94" t="n">
-        <v>5.47</v>
+        <v>6.94</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7944,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="M94" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="F95" t="n">
-        <v>24.29</v>
+        <v>16.89</v>
       </c>
       <c r="G95" t="n">
-        <v>5.85</v>
+        <v>6.68</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8027,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="M95" t="n">
-        <v>5015</v>
+        <v>5050</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>146.5</v>
+        <v>144.5</v>
       </c>
       <c r="F96" t="n">
-        <v>20.8</v>
+        <v>14.49</v>
       </c>
       <c r="G96" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8110,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-5.79</v>
+        <v>-1.37</v>
       </c>
       <c r="M96" t="n">
-        <v>155.5</v>
+        <v>146.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1525</v>
+        <v>1480</v>
       </c>
       <c r="F97" t="n">
-        <v>41.42</v>
+        <v>18.16</v>
       </c>
       <c r="G97" t="n">
-        <v>4.62</v>
+        <v>2.97</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8193,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.67</v>
+        <v>-2.95</v>
       </c>
       <c r="M97" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8253,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>79.7</v>
+        <v>63.3</v>
       </c>
       <c r="F98" t="n">
-        <v>6.6</v>
+        <v>6.63</v>
       </c>
       <c r="G98" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8272,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.5</v>
+        <v>-20.58</v>
       </c>
       <c r="M98" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8330,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F99" t="n">
         <v>8.07</v>
@@ -8349,7 +8347,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M99" t="n">
         <v>404</v>
@@ -8411,13 +8409,13 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="F100" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="G100" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8430,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.63</v>
+        <v>-0.42</v>
       </c>
       <c r="M100" t="n">
-        <v>23.85</v>
+        <v>23.7</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8475,42 +8473,46 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>396</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8.82</v>
+      </c>
       <c r="G101" t="n">
-        <v>0.55</v>
+        <v>3.67</v>
       </c>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>21.9</v>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-1.74</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>403</v>
+        <v>181</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8519,28 +8521,28 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>含金量-1.3差</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>17.9</v>
+        <v>41.3</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.5</v>
+        <v>-1.31</v>
       </c>
       <c r="R101" t="n">
-        <v>-6.1</v>
+        <v>6.4</v>
       </c>
       <c r="S101" t="n">
-        <v>730.1</v>
+        <v>224.4</v>
       </c>
       <c r="T101" t="n">
-        <v>45.2</v>
+        <v>10.5</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -8700,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="F2" t="n">
-        <v>35.42</v>
+        <v>38.61</v>
       </c>
       <c r="G2" t="n">
-        <v>9.98</v>
+        <v>20.42</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8723,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.1</v>
+        <v>1.08</v>
       </c>
       <c r="M2" t="n">
-        <v>2450</v>
+        <v>2325</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8779,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="F3" t="n">
-        <v>12.06</v>
+        <v>24.29</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>9.41</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8802,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.93</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8858,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2465</v>
+        <v>2415</v>
       </c>
       <c r="F4" t="n">
-        <v>26.63</v>
+        <v>32.47</v>
       </c>
       <c r="G4" t="n">
-        <v>6.92</v>
+        <v>10.63</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8881,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.02</v>
+        <v>-2.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2440</v>
+        <v>2465</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8937,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>32.98</v>
+        <v>15.15</v>
       </c>
       <c r="G5" t="n">
-        <v>4.88</v>
+        <v>3.39</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8960,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="M5" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9016,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>16.64</v>
+        <v>16.71</v>
       </c>
       <c r="G6" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9039,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.41</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>123</v>
+        <v>123.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9095,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>34.2</v>
+        <v>34.45</v>
       </c>
       <c r="F7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9118,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.15</v>
+        <v>0.73</v>
       </c>
       <c r="M7" t="n">
-        <v>34.15</v>
+        <v>34.2</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9174,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>15.6</v>
+        <v>12.07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9197,7 +9199,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="M8" t="n">
         <v>111.5</v>
@@ -9253,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>17.43</v>
+        <v>13.07</v>
       </c>
       <c r="G9" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9276,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.28</v>
+        <v>-1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9332,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>39.85</v>
+        <v>39.6</v>
       </c>
       <c r="F10" t="n">
-        <v>8.98</v>
+        <v>7.51</v>
       </c>
       <c r="G10" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9355,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-6.01</v>
+        <v>-0.63</v>
       </c>
       <c r="M10" t="n">
-        <v>42.4</v>
+        <v>39.85</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9411,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="F11" t="n">
-        <v>16.92</v>
+        <v>34.84</v>
       </c>
       <c r="G11" t="n">
-        <v>5.14</v>
+        <v>11.67</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9434,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>1175</v>
+        <v>1195</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9490,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>472</v>
+        <v>448.5</v>
       </c>
       <c r="F12" t="n">
-        <v>12.85</v>
+        <v>21.79</v>
       </c>
       <c r="G12" t="n">
-        <v>2.17</v>
+        <v>4.04</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9513,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.74</v>
+        <v>-4.98</v>
       </c>
       <c r="M12" t="n">
-        <v>475.5</v>
+        <v>472</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9569,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="F13" t="n">
-        <v>21.56</v>
+        <v>17.4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9592,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.35</v>
+        <v>-0.7</v>
       </c>
       <c r="M13" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9648,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="F14" t="n">
-        <v>11.95</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9671,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-1.1</v>
+        <v>-4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>40.95</v>
+        <v>40.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9727,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2415</v>
+        <v>2470</v>
       </c>
       <c r="F15" t="n">
-        <v>42.85</v>
+        <v>46.71</v>
       </c>
       <c r="G15" t="n">
-        <v>14.31</v>
+        <v>21.13</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9750,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.63</v>
+        <v>2.28</v>
       </c>
       <c r="M15" t="n">
-        <v>2455</v>
+        <v>2415</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9810,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="F16" t="n">
-        <v>27.99</v>
+        <v>26.7</v>
       </c>
       <c r="G16" t="n">
-        <v>6.73</v>
+        <v>6.41</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9833,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-4.64</v>
+        <v>-0.54</v>
       </c>
       <c r="M16" t="n">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9893,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>87.2</v>
+        <v>88.5</v>
       </c>
       <c r="F17" t="n">
-        <v>11.41</v>
+        <v>10.61</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9916,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.68</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9976,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>10.58</v>
+        <v>7.99</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>1.86</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -9999,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.53</v>
+        <v>-1.47</v>
       </c>
       <c r="M18" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10059,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="F19" t="n">
-        <v>12.3</v>
+        <v>12.12</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10082,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.51</v>
+        <v>-3.99</v>
       </c>
       <c r="M19" t="n">
-        <v>66.2</v>
+        <v>65.2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10142,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>377</v>
+        <v>373.5</v>
       </c>
       <c r="F20" t="n">
-        <v>20.33</v>
+        <v>18.78</v>
       </c>
       <c r="G20" t="n">
-        <v>5.47</v>
+        <v>6.94</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10165,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="M20" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10225,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="F21" t="n">
-        <v>24.29</v>
+        <v>16.89</v>
       </c>
       <c r="G21" t="n">
-        <v>5.85</v>
+        <v>6.68</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10248,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="M21" t="n">
-        <v>5015</v>
+        <v>5050</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10308,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>146.5</v>
+        <v>144.5</v>
       </c>
       <c r="F22" t="n">
-        <v>20.8</v>
+        <v>14.49</v>
       </c>
       <c r="G22" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10331,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-5.79</v>
+        <v>-1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>155.5</v>
+        <v>146.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10391,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1525</v>
+        <v>1480</v>
       </c>
       <c r="F23" t="n">
-        <v>41.42</v>
+        <v>18.16</v>
       </c>
       <c r="G23" t="n">
-        <v>4.62</v>
+        <v>2.97</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10414,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>-2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10605,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>156.5</v>
+        <v>158</v>
       </c>
       <c r="F2" t="n">
-        <v>17.19</v>
+        <v>16.97</v>
       </c>
       <c r="G2" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10628,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.26</v>
+        <v>0.96</v>
       </c>
       <c r="M2" t="n">
-        <v>158.5</v>
+        <v>156.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10687,10 +10689,10 @@
         <v>509</v>
       </c>
       <c r="F3" t="n">
-        <v>16.99</v>
+        <v>21.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>5.13</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10707,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10763,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10786,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.41</v>
+        <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10842,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>369</v>
+        <v>358.5</v>
       </c>
       <c r="F5" t="n">
-        <v>18.48</v>
+        <v>34.98</v>
       </c>
       <c r="G5" t="n">
-        <v>4.61</v>
+        <v>9.59</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10865,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>-2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10921,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="F6" t="n">
-        <v>19.68</v>
+        <v>19.54</v>
       </c>
       <c r="G6" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10944,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.75</v>
+        <v>-0.86</v>
       </c>
       <c r="M6" t="n">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11000,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>143.5</v>
+        <v>143</v>
       </c>
       <c r="F7" t="n">
-        <v>20.05</v>
+        <v>19.58</v>
       </c>
       <c r="G7" t="n">
-        <v>5.47</v>
+        <v>5.34</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11023,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.38</v>
+        <v>-0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>147</v>
+        <v>143.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11086,10 +11088,10 @@
         <v>237.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.2</v>
+        <v>16.87</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11106,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>237</v>
+        <v>237.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11162,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1110</v>
+        <v>1055</v>
       </c>
       <c r="F9" t="n">
-        <v>62.07</v>
+        <v>58.15</v>
       </c>
       <c r="G9" t="n">
-        <v>32.32</v>
+        <v>30.27</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11183,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-6.33</v>
+        <v>-4.95</v>
       </c>
       <c r="M9" t="n">
-        <v>1185</v>
+        <v>1110</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11243,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>66.2</v>
+        <v>69.8</v>
       </c>
       <c r="F10" t="n">
-        <v>25.83</v>
+        <v>26.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.65</v>
+        <v>3.41</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11266,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>5.44</v>
       </c>
       <c r="M10" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11457,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="F2" t="n">
-        <v>56.03</v>
+        <v>87.73</v>
       </c>
       <c r="G2" t="n">
-        <v>9.23</v>
+        <v>24.63</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11480,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.12</v>
+        <v>-6.82</v>
       </c>
       <c r="M2" t="n">
-        <v>1335</v>
+        <v>1320</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11539,10 +11541,10 @@
         <v>39.25</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12</v>
+        <v>11.09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11559,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.35</v>
+        <v>39.25</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11618,10 +11620,10 @@
         <v>145.5</v>
       </c>
       <c r="F4" t="n">
-        <v>18.07</v>
+        <v>16.82</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11638,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>146.5</v>
+        <v>145.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11694,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6460</v>
+        <v>7080</v>
       </c>
       <c r="F5" t="n">
-        <v>168</v>
+        <v>171.99</v>
       </c>
       <c r="G5" t="n">
-        <v>39.24</v>
+        <v>40.17</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11717,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.38</v>
+        <v>9.6</v>
       </c>
       <c r="M5" t="n">
-        <v>6310</v>
+        <v>6460</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11777,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>108.5</v>
       </c>
       <c r="F6" t="n">
-        <v>24.84</v>
+        <v>22.01</v>
       </c>
       <c r="G6" t="n">
-        <v>4.24</v>
+        <v>3.61</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11800,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3</v>
+        <v>-3.98</v>
       </c>
       <c r="M6" t="n">
-        <v>116.5</v>
+        <v>113</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11856,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="F7" t="n">
-        <v>30.67</v>
+        <v>35.71</v>
       </c>
       <c r="G7" t="n">
-        <v>4.83</v>
+        <v>5.07</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11879,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>121</v>
+        <v>121.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11939,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>235.5</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>20.78</v>
+        <v>36.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.75</v>
+        <v>7.1</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11962,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9.789999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>214.5</v>
+        <v>235.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12022,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>93.2</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>27.03</v>
+        <v>24.11</v>
       </c>
       <c r="G9" t="n">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12045,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-9.51</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>103</v>
+        <v>93.2</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12101,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>20.55</v>
+        <v>20.31</v>
       </c>
       <c r="G10" t="n">
-        <v>5.65</v>
+        <v>5.58</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12124,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="M10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12180,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1345</v>
+        <v>1280</v>
       </c>
       <c r="F11" t="n">
-        <v>22.33</v>
+        <v>28.02</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>5.03</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12203,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.54</v>
+        <v>-4.83</v>
       </c>
       <c r="M11" t="n">
-        <v>1380</v>
+        <v>1345</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12259,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>174.5</v>
       </c>
       <c r="F12" t="n">
-        <v>22.33</v>
+        <v>24.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12282,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12342,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>214</v>
+        <v>213.5</v>
       </c>
       <c r="F13" t="n">
-        <v>18.99</v>
+        <v>31.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12365,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="M13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12425,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>139.5</v>
+        <v>133.5</v>
       </c>
       <c r="F14" t="n">
-        <v>26.28</v>
+        <v>26.54</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12448,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-1.06</v>
+        <v>-4.3</v>
       </c>
       <c r="M14" t="n">
-        <v>141</v>
+        <v>139.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12507,10 +12509,10 @@
         <v>241</v>
       </c>
       <c r="F15" t="n">
-        <v>24.25</v>
+        <v>21.97</v>
       </c>
       <c r="G15" t="n">
-        <v>7.16</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12527,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12587,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4400</v>
+        <v>4340</v>
       </c>
       <c r="F16" t="n">
-        <v>53.56</v>
+        <v>130.57</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>39.88</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12610,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.79</v>
+        <v>-1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>4480</v>
+        <v>4400</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12801,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="F2" t="n">
-        <v>29.68</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>5.03</v>
+        <v>16.3</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12824,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12880,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="F3" t="n">
-        <v>23.05</v>
+        <v>22.8</v>
       </c>
       <c r="G3" t="n">
-        <v>12.09</v>
+        <v>11.95</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12903,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.1</v>
+        <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12963,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3200</v>
+        <v>3205</v>
       </c>
       <c r="F4" t="n">
-        <v>74.7</v>
+        <v>88.66</v>
       </c>
       <c r="G4" t="n">
-        <v>15.67</v>
+        <v>22.2</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12989,7 +12991,7 @@
         <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13042,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5315</v>
+        <v>5295</v>
       </c>
       <c r="F5" t="n">
-        <v>23.19</v>
+        <v>114.86</v>
       </c>
       <c r="G5" t="n">
-        <v>6.44</v>
+        <v>39.57</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13065,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.82</v>
+        <v>-0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>5220</v>
+        <v>5315</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13121,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="F6" t="n">
-        <v>39.6</v>
+        <v>49.55</v>
       </c>
       <c r="G6" t="n">
-        <v>21.08</v>
+        <v>27.65</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13144,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.07</v>
+        <v>-2.57</v>
       </c>
       <c r="M6" t="n">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13207,10 +13209,10 @@
         <v>101.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11.94</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13227,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13283,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>195.5</v>
+        <v>194</v>
       </c>
       <c r="F8" t="n">
-        <v>14.65</v>
+        <v>15.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13306,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.03</v>
+        <v>-0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>193.5</v>
+        <v>195.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13366,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>107.5</v>
       </c>
       <c r="F9" t="n">
-        <v>20.6</v>
+        <v>15.86</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>3.33</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13389,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.48</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13445,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F10" t="n">
-        <v>11.26</v>
+        <v>18.67</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13468,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="M10" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13528,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>225.5</v>
+        <v>221.5</v>
       </c>
       <c r="F11" t="n">
-        <v>34.63</v>
+        <v>33.01</v>
       </c>
       <c r="G11" t="n">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13551,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.96</v>
+        <v>-1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>230</v>
+        <v>225.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13611,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4065</v>
+        <v>4210</v>
       </c>
       <c r="F12" t="n">
-        <v>40.44</v>
+        <v>61.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.57</v>
+        <v>7.95</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13634,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.74</v>
+        <v>3.57</v>
       </c>
       <c r="M12" t="n">
-        <v>4035</v>
+        <v>4065</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-6.82</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -797,10 +797,10 @@
         <v>7080</v>
       </c>
       <c r="F5" t="n">
-        <v>171.99</v>
+        <v>188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>40.17</v>
+        <v>44.03</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6460</v>
+        <v>7080</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>113</v>
+        <v>108.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>235.5</v>
+        <v>240</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>93.2</v>
+        <v>95</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>20.31</v>
+        <v>20.07</v>
       </c>
       <c r="G10" t="n">
-        <v>5.58</v>
+        <v>5.52</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-4.83</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1345</v>
+        <v>1280</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>175</v>
+        <v>174.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>214</v>
+        <v>213.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>139.5</v>
+        <v>133.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4400</v>
+        <v>4340</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>8095</v>
+        <v>8250</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7705</v>
+        <v>7765</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1855</v>
+        <v>1820</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         <v>1570</v>
       </c>
       <c r="F24" t="n">
-        <v>118.86</v>
+        <v>113.44</v>
       </c>
       <c r="G24" t="n">
-        <v>26.3</v>
+        <v>25.1</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-4.56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1645</v>
+        <v>1570</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>35.15</v>
+        <v>36</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         <v>2005</v>
       </c>
       <c r="F26" t="n">
-        <v>275.3</v>
+        <v>263.47</v>
       </c>
       <c r="G26" t="n">
-        <v>45.72</v>
+        <v>43.76</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2095</v>
+        <v>2005</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8.32</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>625</v>
+        <v>677</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-16.01</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1530</v>
+        <v>1285</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         <v>432.5</v>
       </c>
       <c r="F29" t="n">
-        <v>78.56999999999999</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>14.97</v>
+        <v>14.9</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>434.5</v>
+        <v>432.5</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
         <v>2855</v>
       </c>
       <c r="F30" t="n">
-        <v>83.31</v>
+        <v>83.75</v>
       </c>
       <c r="G30" t="n">
-        <v>9.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2840</v>
+        <v>2855</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-1.57</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>251.5</v>
+        <v>260.5</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>396</v>
+        <v>435.5</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>168.5</v>
+        <v>176.5</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3995</v>
+        <v>3925</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         <v>720</v>
       </c>
       <c r="F39" t="n">
-        <v>22.8</v>
+        <v>22.89</v>
       </c>
       <c r="G39" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3200</v>
+        <v>3205</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>5315</v>
+        <v>5295</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-2.57</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>195.5</v>
+        <v>194</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>105.5</v>
+        <v>107.5</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>225.5</v>
+        <v>221.5</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4065</v>
+        <v>4210</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4329,10 +4329,10 @@
         <v>403.5</v>
       </c>
       <c r="F49" t="n">
-        <v>22.07</v>
+        <v>21.82</v>
       </c>
       <c r="G49" t="n">
-        <v>6.53</v>
+        <v>6.46</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>408</v>
+        <v>403.5</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>171.5</v>
+        <v>168.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>98.8</v>
+        <v>97.8</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>169.5</v>
+        <v>168</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4722,10 +4722,10 @@
         <v>232</v>
       </c>
       <c r="F54" t="n">
-        <v>25.31</v>
+        <v>25.98</v>
       </c>
       <c r="G54" t="n">
-        <v>6.16</v>
+        <v>6.32</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
         <v>221.5</v>
       </c>
       <c r="F55" t="n">
-        <v>20.71</v>
+        <v>20.12</v>
       </c>
       <c r="G55" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>228</v>
+        <v>221.5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>817</v>
+        <v>840</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         <v>136</v>
       </c>
       <c r="F57" t="n">
-        <v>31.24</v>
+        <v>30.56</v>
       </c>
       <c r="G57" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>785</v>
+        <v>817</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-2.19</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>77.7</v>
+        <v>76</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-6.24</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>23.25</v>
+        <v>21.8</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>45.6</v>
       </c>
       <c r="F64" t="n">
-        <v>14.65</v>
+        <v>14.66</v>
       </c>
       <c r="G64" t="n">
         <v>1.29</v>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>45.55</v>
+        <v>45.6</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>744</v>
       </c>
       <c r="F65" t="n">
-        <v>18.53</v>
+        <v>18.43</v>
       </c>
       <c r="G65" t="n">
-        <v>17.51</v>
+        <v>17.42</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5759,10 +5759,10 @@
         <v>158</v>
       </c>
       <c r="F67" t="n">
-        <v>16.97</v>
+        <v>17.14</v>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>156.5</v>
+        <v>158</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         <v>123</v>
       </c>
       <c r="F69" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="G69" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>369</v>
+        <v>358.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         <v>92.2</v>
       </c>
       <c r="F71" t="n">
-        <v>19.54</v>
+        <v>19.37</v>
       </c>
       <c r="G71" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         <v>143</v>
       </c>
       <c r="F72" t="n">
-        <v>19.58</v>
+        <v>19.51</v>
       </c>
       <c r="G72" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>143.5</v>
+        <v>143</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6316,10 +6316,10 @@
         <v>1055</v>
       </c>
       <c r="F74" t="n">
-        <v>58.15</v>
+        <v>55.26</v>
       </c>
       <c r="G74" t="n">
-        <v>30.27</v>
+        <v>28.77</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-4.95</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1110</v>
+        <v>1055</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>66.2</v>
+        <v>69.8</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-2.03</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2465</v>
+        <v>2415</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6796,10 +6796,10 @@
         <v>122.5</v>
       </c>
       <c r="F80" t="n">
-        <v>16.71</v>
+        <v>16.58</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>34.2</v>
+        <v>34.45</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>39.85</v>
+        <v>39.6</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-4.98</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>472</v>
+        <v>448.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2415</v>
+        <v>2470</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7590,10 +7590,10 @@
         <v>920</v>
       </c>
       <c r="F90" t="n">
-        <v>26.7</v>
+        <v>26.55</v>
       </c>
       <c r="G90" t="n">
-        <v>6.41</v>
+        <v>6.38</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>87.2</v>
+        <v>88.5</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1.47</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7839,10 +7839,10 @@
         <v>62.6</v>
       </c>
       <c r="F93" t="n">
-        <v>12.12</v>
+        <v>11.64</v>
       </c>
       <c r="G93" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-3.99</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>377</v>
+        <v>373.5</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.37</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>146.5</v>
+        <v>144.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-2.95</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1525</v>
+        <v>1480</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8254,10 +8254,10 @@
         <v>63.3</v>
       </c>
       <c r="F98" t="n">
-        <v>6.63</v>
+        <v>5.27</v>
       </c>
       <c r="G98" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-20.58</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>79.7</v>
+        <v>63.3</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         <v>410</v>
       </c>
       <c r="F99" t="n">
-        <v>8.07</v>
+        <v>8.19</v>
       </c>
       <c r="G99" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8412,10 +8412,10 @@
         <v>23.6</v>
       </c>
       <c r="F100" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="G100" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-2.03</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2465</v>
+        <v>2415</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>16.71</v>
+        <v>16.58</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>34.2</v>
+        <v>34.45</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>39.85</v>
+        <v>39.6</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-4.98</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>472</v>
+        <v>448.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2415</v>
+        <v>2470</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9815,10 +9815,10 @@
         <v>920</v>
       </c>
       <c r="F16" t="n">
-        <v>26.7</v>
+        <v>26.55</v>
       </c>
       <c r="G16" t="n">
-        <v>6.41</v>
+        <v>6.38</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>87.2</v>
+        <v>88.5</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10064,10 +10064,10 @@
         <v>62.6</v>
       </c>
       <c r="F19" t="n">
-        <v>12.12</v>
+        <v>11.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-3.99</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>377</v>
+        <v>373.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-1.37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>146.5</v>
+        <v>144.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-2.95</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1525</v>
+        <v>1480</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>158</v>
       </c>
       <c r="F2" t="n">
-        <v>16.97</v>
+        <v>17.14</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>156.5</v>
+        <v>158</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="G4" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>369</v>
+        <v>358.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10926,10 +10926,10 @@
         <v>92.2</v>
       </c>
       <c r="F6" t="n">
-        <v>19.54</v>
+        <v>19.37</v>
       </c>
       <c r="G6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11005,10 +11005,10 @@
         <v>143</v>
       </c>
       <c r="F7" t="n">
-        <v>19.58</v>
+        <v>19.51</v>
       </c>
       <c r="G7" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>143.5</v>
+        <v>143</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11167,10 +11167,10 @@
         <v>1055</v>
       </c>
       <c r="F9" t="n">
-        <v>58.15</v>
+        <v>55.26</v>
       </c>
       <c r="G9" t="n">
-        <v>30.27</v>
+        <v>28.77</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-4.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1110</v>
+        <v>1055</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>66.2</v>
+        <v>69.8</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-6.82</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         <v>7080</v>
       </c>
       <c r="F5" t="n">
-        <v>171.99</v>
+        <v>188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>40.17</v>
+        <v>44.03</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6460</v>
+        <v>7080</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>113</v>
+        <v>108.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>235.5</v>
+        <v>240</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>93.2</v>
+        <v>95</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12106,10 +12106,10 @@
         <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>20.31</v>
+        <v>20.07</v>
       </c>
       <c r="G10" t="n">
-        <v>5.58</v>
+        <v>5.52</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-4.83</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1345</v>
+        <v>1280</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>175</v>
+        <v>174.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>214</v>
+        <v>213.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>139.5</v>
+        <v>133.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4400</v>
+        <v>4340</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12885,10 +12885,10 @@
         <v>720</v>
       </c>
       <c r="F3" t="n">
-        <v>22.8</v>
+        <v>22.89</v>
       </c>
       <c r="G3" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3200</v>
+        <v>3205</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5315</v>
+        <v>5295</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-2.57</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>195.5</v>
+        <v>194</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>107.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>225.5</v>
+        <v>221.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4065</v>
+        <v>4210</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,7 +557,7 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="F2" t="n">
         <v>87.73</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>1230</v>
@@ -636,7 +636,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.25</v>
+        <v>39.55</v>
       </c>
       <c r="F3" t="n">
         <v>11.09</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="M3" t="n">
         <v>39.25</v>
@@ -715,7 +715,7 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>145.5</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
         <v>16.82</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="M4" t="n">
         <v>145.5</v>
@@ -794,7 +794,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>7080</v>
+        <v>6640</v>
       </c>
       <c r="F5" t="n">
         <v>188.5</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-6.21</v>
       </c>
       <c r="M5" t="n">
         <v>7080</v>
@@ -877,7 +877,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>108.5</v>
+        <v>109.5</v>
       </c>
       <c r="F6" t="n">
         <v>22.01</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="M6" t="n">
         <v>108.5</v>
@@ -956,7 +956,7 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>122.5</v>
+        <v>120.5</v>
       </c>
       <c r="F7" t="n">
         <v>35.71</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="M7" t="n">
         <v>122.5</v>
@@ -1039,7 +1039,7 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>240</v>
+        <v>251.5</v>
       </c>
       <c r="F8" t="n">
         <v>36.64</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="M8" t="n">
         <v>240</v>
@@ -1122,7 +1122,7 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>24.11</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M9" t="n">
         <v>95</v>
@@ -1201,7 +1201,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>167</v>
+        <v>162.5</v>
       </c>
       <c r="F10" t="n">
         <v>20.07</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.69</v>
       </c>
       <c r="M10" t="n">
         <v>167</v>
@@ -1280,7 +1280,7 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1280</v>
+        <v>1320</v>
       </c>
       <c r="F11" t="n">
         <v>28.02</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M11" t="n">
         <v>1280</v>
@@ -1359,7 +1359,7 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174.5</v>
+        <v>176.5</v>
       </c>
       <c r="F12" t="n">
         <v>24.07</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
         <v>174.5</v>
@@ -1442,7 +1442,7 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>213.5</v>
+        <v>222</v>
       </c>
       <c r="F13" t="n">
         <v>31.4</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M13" t="n">
         <v>213.5</v>
@@ -1604,7 +1604,7 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="F15" t="n">
         <v>21.97</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="M15" t="n">
         <v>241</v>
@@ -1687,7 +1687,7 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4340</v>
+        <v>4270</v>
       </c>
       <c r="F16" t="n">
         <v>130.57</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="M16" t="n">
         <v>4340</v>
@@ -1770,7 +1770,7 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1480</v>
+        <v>1375</v>
       </c>
       <c r="F17" t="n">
         <v>55.83</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-7.09</v>
       </c>
       <c r="M17" t="n">
         <v>1480</v>
@@ -1847,7 +1847,7 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>8250</v>
+        <v>8080</v>
       </c>
       <c r="F18" t="n">
         <v>72.72</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="M18" t="n">
         <v>8250</v>
@@ -1924,7 +1924,7 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="F19" t="n">
         <v>69.92</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="M19" t="n">
         <v>709</v>
@@ -2001,7 +2001,7 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.29</v>
       </c>
       <c r="M20" t="n">
         <v>82.8</v>
@@ -2078,7 +2078,7 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>7765</v>
+        <v>7375</v>
       </c>
       <c r="F21" t="n">
         <v>159.12</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-5.02</v>
       </c>
       <c r="M21" t="n">
         <v>7765</v>
@@ -2159,7 +2159,7 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1820</v>
+        <v>1850</v>
       </c>
       <c r="F22" t="n">
         <v>57.4</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
         <v>1820</v>
@@ -2240,7 +2240,7 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="F23" t="n">
         <v>43.47</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>376</v>
@@ -2317,7 +2317,7 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1570</v>
+        <v>1550</v>
       </c>
       <c r="F24" t="n">
         <v>113.44</v>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="M24" t="n">
         <v>1570</v>
@@ -2398,7 +2398,7 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>39.6</v>
       </c>
       <c r="F25" t="n">
         <v>133.33</v>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M25" t="n">
         <v>36</v>
@@ -2479,7 +2479,7 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2005</v>
+        <v>1990</v>
       </c>
       <c r="F26" t="n">
         <v>263.47</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="M26" t="n">
         <v>2005</v>
@@ -2558,7 +2558,7 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="F27" t="n">
         <v>62.86</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="M27" t="n">
         <v>677</v>
@@ -2639,7 +2639,7 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1285</v>
+        <v>1250</v>
       </c>
       <c r="F28" t="n">
         <v>80.56</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>-2.72</v>
       </c>
       <c r="M28" t="n">
         <v>1285</v>
@@ -2718,7 +2718,7 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>432.5</v>
+        <v>419</v>
       </c>
       <c r="F29" t="n">
         <v>78.20999999999999</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-3.12</v>
       </c>
       <c r="M29" t="n">
         <v>432.5</v>
@@ -2799,7 +2799,7 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>2855</v>
+        <v>2775</v>
       </c>
       <c r="F30" t="n">
         <v>83.75</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="M30" t="n">
         <v>2855</v>
@@ -2880,7 +2880,7 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="F31" t="n">
         <v>149.4</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M31" t="n">
         <v>502</v>
@@ -2959,7 +2959,7 @@
         <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>260.5</v>
+        <v>259</v>
       </c>
       <c r="F32" t="n">
         <v>38.42</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="M32" t="n">
         <v>260.5</v>
@@ -3036,7 +3036,7 @@
         <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>435.5</v>
+        <v>423</v>
       </c>
       <c r="F33" t="n">
         <v>38.99</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-2.87</v>
       </c>
       <c r="M33" t="n">
         <v>435.5</v>
@@ -3115,7 +3115,7 @@
         <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F34" t="n">
         <v>41.89</v>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="M34" t="n">
         <v>540</v>
@@ -3192,7 +3192,7 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>900</v>
+        <v>816</v>
       </c>
       <c r="F35" t="n">
         <v>70.87</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-9.33</v>
       </c>
       <c r="M35" t="n">
         <v>900</v>
@@ -3273,7 +3273,7 @@
         <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>176.5</v>
+        <v>167</v>
       </c>
       <c r="F36" t="n">
         <v>52.37</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-5.38</v>
       </c>
       <c r="M36" t="n">
         <v>176.5</v>
@@ -3352,7 +3352,7 @@
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>3925</v>
+        <v>3825</v>
       </c>
       <c r="F37" t="n">
         <v>62.55</v>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-2.55</v>
       </c>
       <c r="M37" t="n">
         <v>3925</v>
@@ -3433,7 +3433,7 @@
         <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="F38" t="n">
         <v>69.31999999999999</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M38" t="n">
         <v>1880</v>
@@ -3512,7 +3512,7 @@
         <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="F39" t="n">
         <v>22.89</v>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>-7.08</v>
       </c>
       <c r="M39" t="n">
         <v>720</v>
@@ -3595,7 +3595,7 @@
         <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>3205</v>
+        <v>3195</v>
       </c>
       <c r="F40" t="n">
         <v>88.66</v>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M40" t="n">
         <v>3205</v>
@@ -3674,7 +3674,7 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>5295</v>
+        <v>5125</v>
       </c>
       <c r="F41" t="n">
         <v>114.86</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-3.21</v>
       </c>
       <c r="M41" t="n">
         <v>5295</v>
@@ -3753,7 +3753,7 @@
         <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="F42" t="n">
         <v>49.55</v>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="M42" t="n">
         <v>721</v>
@@ -3836,7 +3836,7 @@
         <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="F43" t="n">
         <v>11.94</v>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="M43" t="n">
         <v>101.5</v>
@@ -3915,7 +3915,7 @@
         <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F44" t="n">
         <v>15.34</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M44" t="n">
         <v>194</v>
@@ -4077,7 +4077,7 @@
         <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F46" t="n">
         <v>18.67</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="M46" t="n">
         <v>616</v>
@@ -4160,7 +4160,7 @@
         <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>221.5</v>
+        <v>220</v>
       </c>
       <c r="F47" t="n">
         <v>33.01</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="M47" t="n">
         <v>221.5</v>
@@ -4243,7 +4243,7 @@
         <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>4210</v>
+        <v>4135</v>
       </c>
       <c r="F48" t="n">
         <v>61.7</v>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
       <c r="M48" t="n">
         <v>4210</v>
@@ -4326,7 +4326,7 @@
         <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>403.5</v>
+        <v>394.5</v>
       </c>
       <c r="F49" t="n">
         <v>21.82</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="M49" t="n">
         <v>403.5</v>
@@ -4403,7 +4403,7 @@
         <v>94</v>
       </c>
       <c r="E50" t="n">
-        <v>168.5</v>
+        <v>168</v>
       </c>
       <c r="F50" t="n">
         <v>20.47</v>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="M50" t="n">
         <v>168.5</v>
@@ -4480,7 +4480,7 @@
         <v>78</v>
       </c>
       <c r="E51" t="n">
-        <v>129</v>
+        <v>126.5</v>
       </c>
       <c r="F51" t="n">
         <v>29.52</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="M51" t="n">
         <v>129</v>
@@ -4557,7 +4557,7 @@
         <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>97.8</v>
+        <v>95.3</v>
       </c>
       <c r="F52" t="n">
         <v>20.08</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
       <c r="M52" t="n">
         <v>97.8</v>
@@ -4638,7 +4638,7 @@
         <v>77</v>
       </c>
       <c r="E53" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F53" t="n">
         <v>34.64</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>-2.98</v>
       </c>
       <c r="M53" t="n">
         <v>168</v>
@@ -4719,7 +4719,7 @@
         <v>76</v>
       </c>
       <c r="E54" t="n">
-        <v>232</v>
+        <v>240.5</v>
       </c>
       <c r="F54" t="n">
         <v>25.98</v>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="M54" t="n">
         <v>232</v>
@@ -4796,7 +4796,7 @@
         <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>221.5</v>
+        <v>201</v>
       </c>
       <c r="F55" t="n">
         <v>20.12</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-9.26</v>
       </c>
       <c r="M55" t="n">
         <v>221.5</v>
@@ -4873,7 +4873,7 @@
         <v>61</v>
       </c>
       <c r="E56" t="n">
-        <v>840</v>
+        <v>756</v>
       </c>
       <c r="F56" t="n">
         <v>30.24</v>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M56" t="n">
         <v>840</v>
@@ -4954,7 +4954,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F57" t="n">
         <v>30.56</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="M57" t="n">
         <v>136</v>
@@ -5035,7 +5035,7 @@
         <v>51</v>
       </c>
       <c r="E58" t="n">
-        <v>3950</v>
+        <v>4345</v>
       </c>
       <c r="F58" t="n">
         <v>24.66</v>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M58" t="n">
         <v>3950</v>
@@ -5116,7 +5116,7 @@
         <v>97</v>
       </c>
       <c r="E59" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F59" t="n">
         <v>34.97</v>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="M59" t="n">
         <v>549</v>
@@ -5195,7 +5195,7 @@
         <v>91</v>
       </c>
       <c r="E60" t="n">
-        <v>817</v>
+        <v>794</v>
       </c>
       <c r="F60" t="n">
         <v>55.39</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-2.82</v>
       </c>
       <c r="M60" t="n">
         <v>817</v>
@@ -5274,7 +5274,7 @@
         <v>79</v>
       </c>
       <c r="E61" t="n">
-        <v>76</v>
+        <v>69.3</v>
       </c>
       <c r="F61" t="n">
         <v>18.63</v>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-8.82</v>
       </c>
       <c r="M61" t="n">
         <v>76</v>
@@ -5353,7 +5353,7 @@
         <v>77</v>
       </c>
       <c r="E62" t="n">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="F62" t="n">
         <v>15.68</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="M62" t="n">
         <v>166.5</v>
@@ -5432,7 +5432,7 @@
         <v>78</v>
       </c>
       <c r="E63" t="n">
-        <v>21.8</v>
+        <v>21.25</v>
       </c>
       <c r="F63" t="n">
         <v>17.72</v>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="M63" t="n">
         <v>21.8</v>
@@ -5594,7 +5594,7 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="F65" t="n">
         <v>18.43</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>-2.02</v>
       </c>
       <c r="M65" t="n">
         <v>744</v>
@@ -5675,7 +5675,7 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="F66" t="n">
         <v>19.16</v>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="M66" t="n">
         <v>50.4</v>
@@ -5756,7 +5756,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>158</v>
+        <v>157.5</v>
       </c>
       <c r="F67" t="n">
         <v>17.14</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M67" t="n">
         <v>158</v>
@@ -5835,7 +5835,7 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="F68" t="n">
         <v>21.6</v>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>9.82</v>
       </c>
       <c r="M68" t="n">
         <v>509</v>
@@ -5914,7 +5914,7 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F69" t="n">
         <v>17.67</v>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="M69" t="n">
         <v>123</v>
@@ -5993,7 +5993,7 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>358.5</v>
+        <v>328.5</v>
       </c>
       <c r="F70" t="n">
         <v>34.98</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M70" t="n">
         <v>358.5</v>
@@ -6072,7 +6072,7 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="F71" t="n">
         <v>19.37</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="M71" t="n">
         <v>92.2</v>
@@ -6151,7 +6151,7 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F72" t="n">
         <v>19.51</v>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M72" t="n">
         <v>143</v>
@@ -6234,7 +6234,7 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>237.5</v>
+        <v>236.5</v>
       </c>
       <c r="F73" t="n">
         <v>16.87</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M73" t="n">
         <v>237.5</v>
@@ -6313,7 +6313,7 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="F74" t="n">
         <v>55.26</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M74" t="n">
         <v>1055</v>
@@ -6394,7 +6394,7 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>69.8</v>
+        <v>64.7</v>
       </c>
       <c r="F75" t="n">
         <v>26.54</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
       <c r="M75" t="n">
         <v>69.8</v>
@@ -6477,7 +6477,7 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2350</v>
+        <v>2225</v>
       </c>
       <c r="F76" t="n">
         <v>38.61</v>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>-5.32</v>
       </c>
       <c r="M76" t="n">
         <v>2350</v>
@@ -6556,7 +6556,7 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="F77" t="n">
         <v>24.29</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="M77" t="n">
         <v>875</v>
@@ -6635,7 +6635,7 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2415</v>
+        <v>2440</v>
       </c>
       <c r="F78" t="n">
         <v>32.47</v>
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M78" t="n">
         <v>2415</v>
@@ -6714,7 +6714,7 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F79" t="n">
         <v>15.15</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="M79" t="n">
         <v>103</v>
@@ -6793,7 +6793,7 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>122.5</v>
+        <v>119.5</v>
       </c>
       <c r="F80" t="n">
         <v>16.58</v>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="M80" t="n">
         <v>122.5</v>
@@ -6872,7 +6872,7 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>34.45</v>
+        <v>28.9</v>
       </c>
       <c r="F81" t="n">
         <v>6.9</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-16.11</v>
       </c>
       <c r="M81" t="n">
         <v>34.45</v>
@@ -6951,7 +6951,7 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="F82" t="n">
         <v>12.07</v>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M82" t="n">
         <v>112</v>
@@ -7030,7 +7030,7 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F83" t="n">
         <v>13.07</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="M83" t="n">
         <v>176</v>
@@ -7109,7 +7109,7 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>39.6</v>
+        <v>40.75</v>
       </c>
       <c r="F84" t="n">
         <v>7.51</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M84" t="n">
         <v>39.6</v>
@@ -7188,7 +7188,7 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1175</v>
+        <v>1135</v>
       </c>
       <c r="F85" t="n">
         <v>34.84</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
       <c r="M85" t="n">
         <v>1175</v>
@@ -7267,7 +7267,7 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>448.5</v>
+        <v>439</v>
       </c>
       <c r="F86" t="n">
         <v>21.79</v>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>-2.12</v>
       </c>
       <c r="M86" t="n">
         <v>448.5</v>
@@ -7346,7 +7346,7 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>142.5</v>
+        <v>138</v>
       </c>
       <c r="F87" t="n">
         <v>17.4</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>-3.16</v>
       </c>
       <c r="M87" t="n">
         <v>142.5</v>
@@ -7425,7 +7425,7 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>38.8</v>
+        <v>38.65</v>
       </c>
       <c r="F88" t="n">
         <v>8.529999999999999</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M88" t="n">
         <v>38.8</v>
@@ -7504,7 +7504,7 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2470</v>
+        <v>2405</v>
       </c>
       <c r="F89" t="n">
         <v>46.71</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>-2.63</v>
       </c>
       <c r="M89" t="n">
         <v>2470</v>
@@ -7587,7 +7587,7 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="F90" t="n">
         <v>26.55</v>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="M90" t="n">
         <v>920</v>
@@ -7670,7 +7670,7 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>88.5</v>
+        <v>89.3</v>
       </c>
       <c r="F91" t="n">
         <v>10.61</v>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M91" t="n">
         <v>88.5</v>
@@ -7753,7 +7753,7 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F92" t="n">
         <v>7.99</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="M92" t="n">
         <v>73.90000000000001</v>
@@ -7836,7 +7836,7 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>62.6</v>
+        <v>61.6</v>
       </c>
       <c r="F93" t="n">
         <v>11.64</v>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M93" t="n">
         <v>62.6</v>
@@ -7919,7 +7919,7 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>373.5</v>
+        <v>378</v>
       </c>
       <c r="F94" t="n">
         <v>18.78</v>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M94" t="n">
         <v>373.5</v>
@@ -8002,7 +8002,7 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5040</v>
+        <v>4960</v>
       </c>
       <c r="F95" t="n">
         <v>16.89</v>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="M95" t="n">
         <v>5040</v>
@@ -8085,7 +8085,7 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>144.5</v>
+        <v>143.5</v>
       </c>
       <c r="F96" t="n">
         <v>14.49</v>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M96" t="n">
         <v>144.5</v>
@@ -8168,7 +8168,7 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="F97" t="n">
         <v>18.16</v>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M97" t="n">
         <v>1480</v>
@@ -8251,7 +8251,7 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>63.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F98" t="n">
         <v>5.27</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M98" t="n">
         <v>63.3</v>
@@ -8328,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F99" t="n">
         <v>8.19</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>-1.22</v>
       </c>
       <c r="M99" t="n">
         <v>410</v>
@@ -8409,7 +8409,7 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="F100" t="n">
         <v>3.91</v>
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M100" t="n">
         <v>23.6</v>
@@ -8490,7 +8490,7 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F101" t="n">
         <v>8.82</v>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M101" t="n">
         <v>181</v>
@@ -8702,7 +8702,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2350</v>
+        <v>2225</v>
       </c>
       <c r="F2" t="n">
         <v>38.61</v>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-5.32</v>
       </c>
       <c r="M2" t="n">
         <v>2350</v>
@@ -8781,7 +8781,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="F3" t="n">
         <v>24.29</v>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="M3" t="n">
         <v>875</v>
@@ -8860,7 +8860,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2415</v>
+        <v>2440</v>
       </c>
       <c r="F4" t="n">
         <v>32.47</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
         <v>2415</v>
@@ -8939,7 +8939,7 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" t="n">
         <v>15.15</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="M5" t="n">
         <v>103</v>
@@ -9018,7 +9018,7 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>119.5</v>
       </c>
       <c r="F6" t="n">
         <v>16.58</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="M6" t="n">
         <v>122.5</v>
@@ -9097,7 +9097,7 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>34.45</v>
+        <v>28.9</v>
       </c>
       <c r="F7" t="n">
         <v>6.9</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-16.11</v>
       </c>
       <c r="M7" t="n">
         <v>34.45</v>
@@ -9176,7 +9176,7 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="F8" t="n">
         <v>12.07</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>112</v>
@@ -9255,7 +9255,7 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F9" t="n">
         <v>13.07</v>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="M9" t="n">
         <v>176</v>
@@ -9334,7 +9334,7 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>39.6</v>
+        <v>40.75</v>
       </c>
       <c r="F10" t="n">
         <v>7.51</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
         <v>39.6</v>
@@ -9413,7 +9413,7 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1175</v>
+        <v>1135</v>
       </c>
       <c r="F11" t="n">
         <v>34.84</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
       <c r="M11" t="n">
         <v>1175</v>
@@ -9492,7 +9492,7 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>448.5</v>
+        <v>439</v>
       </c>
       <c r="F12" t="n">
         <v>21.79</v>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-2.12</v>
       </c>
       <c r="M12" t="n">
         <v>448.5</v>
@@ -9571,7 +9571,7 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>142.5</v>
+        <v>138</v>
       </c>
       <c r="F13" t="n">
         <v>17.4</v>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-3.16</v>
       </c>
       <c r="M13" t="n">
         <v>142.5</v>
@@ -9650,7 +9650,7 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.8</v>
+        <v>38.65</v>
       </c>
       <c r="F14" t="n">
         <v>8.529999999999999</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M14" t="n">
         <v>38.8</v>
@@ -9729,7 +9729,7 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2470</v>
+        <v>2405</v>
       </c>
       <c r="F15" t="n">
         <v>46.71</v>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-2.63</v>
       </c>
       <c r="M15" t="n">
         <v>2470</v>
@@ -9812,7 +9812,7 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="F16" t="n">
         <v>26.55</v>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="M16" t="n">
         <v>920</v>
@@ -9895,7 +9895,7 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.5</v>
+        <v>89.3</v>
       </c>
       <c r="F17" t="n">
         <v>10.61</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M17" t="n">
         <v>88.5</v>
@@ -9978,7 +9978,7 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>7.99</v>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="M18" t="n">
         <v>73.90000000000001</v>
@@ -10061,7 +10061,7 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>62.6</v>
+        <v>61.6</v>
       </c>
       <c r="F19" t="n">
         <v>11.64</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M19" t="n">
         <v>62.6</v>
@@ -10144,7 +10144,7 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>373.5</v>
+        <v>378</v>
       </c>
       <c r="F20" t="n">
         <v>18.78</v>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M20" t="n">
         <v>373.5</v>
@@ -10227,7 +10227,7 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5040</v>
+        <v>4960</v>
       </c>
       <c r="F21" t="n">
         <v>16.89</v>
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="M21" t="n">
         <v>5040</v>
@@ -10310,7 +10310,7 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>144.5</v>
+        <v>143.5</v>
       </c>
       <c r="F22" t="n">
         <v>14.49</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>144.5</v>
@@ -10393,7 +10393,7 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="F23" t="n">
         <v>18.16</v>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
         <v>1480</v>
@@ -10607,7 +10607,7 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>158</v>
+        <v>157.5</v>
       </c>
       <c r="F2" t="n">
         <v>17.14</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M2" t="n">
         <v>158</v>
@@ -10686,7 +10686,7 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="F3" t="n">
         <v>21.6</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>9.82</v>
       </c>
       <c r="M3" t="n">
         <v>509</v>
@@ -10765,7 +10765,7 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F4" t="n">
         <v>17.67</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="M4" t="n">
         <v>123</v>
@@ -10844,7 +10844,7 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>358.5</v>
+        <v>328.5</v>
       </c>
       <c r="F5" t="n">
         <v>34.98</v>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>358.5</v>
@@ -10923,7 +10923,7 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="F6" t="n">
         <v>19.37</v>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="M6" t="n">
         <v>92.2</v>
@@ -11002,7 +11002,7 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
         <v>19.51</v>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
         <v>143</v>
@@ -11085,7 +11085,7 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>237.5</v>
+        <v>236.5</v>
       </c>
       <c r="F8" t="n">
         <v>16.87</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M8" t="n">
         <v>237.5</v>
@@ -11164,7 +11164,7 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="F9" t="n">
         <v>55.26</v>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
         <v>1055</v>
@@ -11245,7 +11245,7 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>69.8</v>
+        <v>64.7</v>
       </c>
       <c r="F10" t="n">
         <v>26.54</v>
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
       <c r="M10" t="n">
         <v>69.8</v>
@@ -11459,7 +11459,7 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="F2" t="n">
         <v>87.73</v>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>1230</v>
@@ -11538,7 +11538,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.25</v>
+        <v>39.55</v>
       </c>
       <c r="F3" t="n">
         <v>11.09</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="M3" t="n">
         <v>39.25</v>
@@ -11617,7 +11617,7 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>145.5</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
         <v>16.82</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="M4" t="n">
         <v>145.5</v>
@@ -11696,7 +11696,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>7080</v>
+        <v>6640</v>
       </c>
       <c r="F5" t="n">
         <v>188.5</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-6.21</v>
       </c>
       <c r="M5" t="n">
         <v>7080</v>
@@ -11779,7 +11779,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>108.5</v>
+        <v>109.5</v>
       </c>
       <c r="F6" t="n">
         <v>22.01</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="M6" t="n">
         <v>108.5</v>
@@ -11858,7 +11858,7 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>122.5</v>
+        <v>120.5</v>
       </c>
       <c r="F7" t="n">
         <v>35.71</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="M7" t="n">
         <v>122.5</v>
@@ -11941,7 +11941,7 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>240</v>
+        <v>251.5</v>
       </c>
       <c r="F8" t="n">
         <v>36.64</v>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="M8" t="n">
         <v>240</v>
@@ -12024,7 +12024,7 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>24.11</v>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M9" t="n">
         <v>95</v>
@@ -12103,7 +12103,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>167</v>
+        <v>162.5</v>
       </c>
       <c r="F10" t="n">
         <v>20.07</v>
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.69</v>
       </c>
       <c r="M10" t="n">
         <v>167</v>
@@ -12182,7 +12182,7 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1280</v>
+        <v>1320</v>
       </c>
       <c r="F11" t="n">
         <v>28.02</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M11" t="n">
         <v>1280</v>
@@ -12261,7 +12261,7 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174.5</v>
+        <v>176.5</v>
       </c>
       <c r="F12" t="n">
         <v>24.07</v>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
         <v>174.5</v>
@@ -12344,7 +12344,7 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>213.5</v>
+        <v>222</v>
       </c>
       <c r="F13" t="n">
         <v>31.4</v>
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="M13" t="n">
         <v>213.5</v>
@@ -12506,7 +12506,7 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="F15" t="n">
         <v>21.97</v>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="M15" t="n">
         <v>241</v>
@@ -12589,7 +12589,7 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4340</v>
+        <v>4270</v>
       </c>
       <c r="F16" t="n">
         <v>130.57</v>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="M16" t="n">
         <v>4340</v>
@@ -12803,7 +12803,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="F2" t="n">
         <v>69.31999999999999</v>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M2" t="n">
         <v>1880</v>
@@ -12882,7 +12882,7 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="F3" t="n">
         <v>22.89</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-7.08</v>
       </c>
       <c r="M3" t="n">
         <v>720</v>
@@ -12965,7 +12965,7 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3205</v>
+        <v>3195</v>
       </c>
       <c r="F4" t="n">
         <v>88.66</v>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M4" t="n">
         <v>3205</v>
@@ -13044,7 +13044,7 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5295</v>
+        <v>5125</v>
       </c>
       <c r="F5" t="n">
         <v>114.86</v>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-3.21</v>
       </c>
       <c r="M5" t="n">
         <v>5295</v>
@@ -13123,7 +13123,7 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="F6" t="n">
         <v>49.55</v>
@@ -13146,7 +13146,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="M6" t="n">
         <v>721</v>
@@ -13206,7 +13206,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="F7" t="n">
         <v>11.94</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="M7" t="n">
         <v>101.5</v>
@@ -13285,7 +13285,7 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F8" t="n">
         <v>15.34</v>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
         <v>194</v>
@@ -13447,7 +13447,7 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F10" t="n">
         <v>18.67</v>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="M10" t="n">
         <v>616</v>
@@ -13530,7 +13530,7 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>221.5</v>
+        <v>220</v>
       </c>
       <c r="F11" t="n">
         <v>33.01</v>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="M11" t="n">
         <v>221.5</v>
@@ -13613,7 +13613,7 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4210</v>
+        <v>4135</v>
       </c>
       <c r="F12" t="n">
         <v>61.7</v>
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
       <c r="M12" t="n">
         <v>4210</v>

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1240</v>
+        <v>1175</v>
       </c>
       <c r="F2" t="n">
-        <v>87.73</v>
+        <v>88.45</v>
       </c>
       <c r="G2" t="n">
-        <v>24.63</v>
+        <v>24.83</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8100000000000001</v>
+        <v>-5.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.55</v>
+        <v>39.35</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09</v>
+        <v>11.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.76</v>
+        <v>-0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>39.25</v>
+        <v>39.55</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>151.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.82</v>
+        <v>17.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.78</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>145.5</v>
+        <v>151</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6640</v>
+        <v>6340</v>
       </c>
       <c r="F5" t="n">
-        <v>188.5</v>
+        <v>176.78</v>
       </c>
       <c r="G5" t="n">
-        <v>44.03</v>
+        <v>41.29</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-6.21</v>
+        <v>-4.52</v>
       </c>
       <c r="M5" t="n">
-        <v>7080</v>
+        <v>6640</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>22.01</v>
+        <v>22.21</v>
       </c>
       <c r="G6" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>108.5</v>
+        <v>109.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>120.5</v>
+        <v>109.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.71</v>
+        <v>35.13</v>
       </c>
       <c r="G7" t="n">
-        <v>5.07</v>
+        <v>4.99</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.63</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>122.5</v>
+        <v>120.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>251.5</v>
+        <v>241</v>
       </c>
       <c r="F8" t="n">
-        <v>36.64</v>
+        <v>38.4</v>
       </c>
       <c r="G8" t="n">
-        <v>7.1</v>
+        <v>7.44</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.79</v>
+        <v>-4.17</v>
       </c>
       <c r="M8" t="n">
-        <v>240</v>
+        <v>251.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>96.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>24.11</v>
+        <v>24.39</v>
       </c>
       <c r="G9" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.16</v>
+        <v>-1.04</v>
       </c>
       <c r="M9" t="n">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>162.5</v>
+        <v>159</v>
       </c>
       <c r="F10" t="n">
-        <v>20.07</v>
+        <v>19.53</v>
       </c>
       <c r="G10" t="n">
-        <v>5.52</v>
+        <v>5.37</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.69</v>
+        <v>-2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>167</v>
+        <v>162.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1320</v>
+        <v>1290</v>
       </c>
       <c r="F11" t="n">
-        <v>28.02</v>
+        <v>28.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5.03</v>
+        <v>5.19</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.12</v>
+        <v>-2.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1280</v>
+        <v>1320</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>176.5</v>
+        <v>174</v>
       </c>
       <c r="F12" t="n">
-        <v>24.07</v>
+        <v>24.34</v>
       </c>
       <c r="G12" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>-1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>174.5</v>
+        <v>176.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>222</v>
+        <v>212.5</v>
       </c>
       <c r="F13" t="n">
-        <v>31.4</v>
+        <v>32.65</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>5.72</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.98</v>
+        <v>-4.28</v>
       </c>
       <c r="M13" t="n">
-        <v>213.5</v>
+        <v>222</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,7 +1525,7 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>133.5</v>
+        <v>133</v>
       </c>
       <c r="F14" t="n">
         <v>26.54</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="M14" t="n">
         <v>133.5</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>239.5</v>
+        <v>242</v>
       </c>
       <c r="F15" t="n">
-        <v>21.97</v>
+        <v>21.83</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.36</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.62</v>
+        <v>1.04</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4270</v>
+        <v>4020</v>
       </c>
       <c r="F16" t="n">
-        <v>130.57</v>
+        <v>128.46</v>
       </c>
       <c r="G16" t="n">
-        <v>39.88</v>
+        <v>39.24</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.61</v>
+        <v>-5.85</v>
       </c>
       <c r="M16" t="n">
-        <v>4340</v>
+        <v>4270</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1375</v>
+        <v>1315</v>
       </c>
       <c r="F17" t="n">
-        <v>55.83</v>
+        <v>51.87</v>
       </c>
       <c r="G17" t="n">
-        <v>16.35</v>
+        <v>15.19</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-7.09</v>
+        <v>-4.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1480</v>
+        <v>1375</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>8080</v>
+        <v>7995</v>
       </c>
       <c r="F18" t="n">
-        <v>72.72</v>
+        <v>71.22</v>
       </c>
       <c r="G18" t="n">
-        <v>24.94</v>
+        <v>24.42</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-2.06</v>
+        <v>-1.05</v>
       </c>
       <c r="M18" t="n">
-        <v>8250</v>
+        <v>8080</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="F19" t="n">
-        <v>69.92</v>
+        <v>69.03</v>
       </c>
       <c r="G19" t="n">
-        <v>12.82</v>
+        <v>12.66</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.27</v>
+        <v>-3.57</v>
       </c>
       <c r="M19" t="n">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>80.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>58.62</v>
       </c>
       <c r="G20" t="n">
-        <v>7.12</v>
+        <v>6.96</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.29</v>
+        <v>-4.33</v>
       </c>
       <c r="M20" t="n">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>7375</v>
+        <v>7040</v>
       </c>
       <c r="F21" t="n">
-        <v>159.12</v>
+        <v>151.13</v>
       </c>
       <c r="G21" t="n">
-        <v>43.07</v>
+        <v>40.91</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-5.02</v>
+        <v>-4.54</v>
       </c>
       <c r="M21" t="n">
-        <v>7765</v>
+        <v>7375</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1850</v>
+        <v>1820</v>
       </c>
       <c r="F22" t="n">
-        <v>57.4</v>
+        <v>58.34</v>
       </c>
       <c r="G22" t="n">
-        <v>27.8</v>
+        <v>28.26</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>-1.62</v>
       </c>
       <c r="M22" t="n">
-        <v>1820</v>
+        <v>1850</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="F23" t="n">
-        <v>43.47</v>
+        <v>39.65</v>
       </c>
       <c r="G23" t="n">
-        <v>6.44</v>
+        <v>5.88</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-8.779999999999999</v>
+        <v>-6.41</v>
       </c>
       <c r="M23" t="n">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2317,13 +2317,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1550</v>
+        <v>1395</v>
       </c>
       <c r="F24" t="n">
-        <v>113.44</v>
+        <v>111.99</v>
       </c>
       <c r="G24" t="n">
-        <v>25.1</v>
+        <v>24.78</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1.27</v>
+        <v>-10</v>
       </c>
       <c r="M24" t="n">
-        <v>1570</v>
+        <v>1550</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>39.6</v>
+        <v>36.95</v>
       </c>
       <c r="F25" t="n">
-        <v>133.33</v>
+        <v>146.67</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>-6.69</v>
       </c>
       <c r="M25" t="n">
-        <v>36</v>
+        <v>39.6</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>1990</v>
+        <v>1925</v>
       </c>
       <c r="F26" t="n">
-        <v>263.47</v>
+        <v>261.5</v>
       </c>
       <c r="G26" t="n">
-        <v>43.76</v>
+        <v>43.43</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-0.75</v>
+        <v>-3.27</v>
       </c>
       <c r="M26" t="n">
-        <v>2005</v>
+        <v>1990</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2558,13 +2558,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="F27" t="n">
-        <v>62.86</v>
+        <v>62.21</v>
       </c>
       <c r="G27" t="n">
-        <v>8.470000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1.03</v>
+        <v>-4.33</v>
       </c>
       <c r="M27" t="n">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="F28" t="n">
-        <v>80.56</v>
+        <v>78.37</v>
       </c>
       <c r="G28" t="n">
-        <v>13.87</v>
+        <v>13.49</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-2.72</v>
+        <v>-4</v>
       </c>
       <c r="M28" t="n">
-        <v>1285</v>
+        <v>1250</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="F29" t="n">
-        <v>78.20999999999999</v>
+        <v>75.77</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9</v>
+        <v>14.43</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-3.12</v>
+        <v>-3.82</v>
       </c>
       <c r="M29" t="n">
-        <v>432.5</v>
+        <v>419</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2799,13 +2799,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>2775</v>
+        <v>2700</v>
       </c>
       <c r="F30" t="n">
-        <v>83.75</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>9.550000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>2855</v>
+        <v>2775</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2880,13 +2880,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="F31" t="n">
-        <v>149.4</v>
+        <v>153.27</v>
       </c>
       <c r="G31" t="n">
-        <v>14.02</v>
+        <v>14.39</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.59</v>
+        <v>-7.57</v>
       </c>
       <c r="M31" t="n">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2959,13 +2959,13 @@
         <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>259</v>
+        <v>247.5</v>
       </c>
       <c r="F32" t="n">
-        <v>38.42</v>
+        <v>38.2</v>
       </c>
       <c r="G32" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.58</v>
+        <v>-4.44</v>
       </c>
       <c r="M32" t="n">
-        <v>260.5</v>
+        <v>259</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3036,13 +3036,13 @@
         <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="F33" t="n">
-        <v>38.99</v>
+        <v>37.87</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-2.87</v>
+        <v>5.91</v>
       </c>
       <c r="M33" t="n">
-        <v>435.5</v>
+        <v>423</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3115,13 +3115,13 @@
         <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="F34" t="n">
-        <v>41.89</v>
+        <v>41.58</v>
       </c>
       <c r="G34" t="n">
-        <v>9.449999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.74</v>
+        <v>-1.31</v>
       </c>
       <c r="M34" t="n">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
@@ -3192,13 +3192,13 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>816</v>
+        <v>778</v>
       </c>
       <c r="F35" t="n">
-        <v>70.87</v>
+        <v>64.25</v>
       </c>
       <c r="G35" t="n">
-        <v>11.09</v>
+        <v>10.06</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-9.33</v>
+        <v>-4.66</v>
       </c>
       <c r="M35" t="n">
-        <v>900</v>
+        <v>816</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="F36" t="n">
-        <v>52.37</v>
+        <v>49.55</v>
       </c>
       <c r="G36" t="n">
-        <v>6.81</v>
+        <v>6.44</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-5.38</v>
+        <v>-1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>176.5</v>
+        <v>167</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3352,13 +3352,13 @@
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>3825</v>
+        <v>3660</v>
       </c>
       <c r="F37" t="n">
-        <v>62.55</v>
+        <v>60.96</v>
       </c>
       <c r="G37" t="n">
-        <v>16.05</v>
+        <v>15.64</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-2.55</v>
+        <v>-4.31</v>
       </c>
       <c r="M37" t="n">
-        <v>3925</v>
+        <v>3825</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>1890</v>
+        <v>1855</v>
       </c>
       <c r="F38" t="n">
-        <v>69.31999999999999</v>
+        <v>69.69</v>
       </c>
       <c r="G38" t="n">
-        <v>16.3</v>
+        <v>16.39</v>
       </c>
       <c r="H38" t="n">
         <v>59.1</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.53</v>
+        <v>-1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3512,13 +3512,13 @@
         <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="F39" t="n">
-        <v>22.89</v>
+        <v>21.27</v>
       </c>
       <c r="G39" t="n">
-        <v>12</v>
+        <v>11.15</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-7.08</v>
+        <v>-1.94</v>
       </c>
       <c r="M39" t="n">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3595,13 +3595,13 @@
         <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>3195</v>
+        <v>3070</v>
       </c>
       <c r="F40" t="n">
-        <v>88.66</v>
+        <v>88.38</v>
       </c>
       <c r="G40" t="n">
-        <v>22.2</v>
+        <v>22.13</v>
       </c>
       <c r="H40" t="n">
         <v>70.2</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.31</v>
+        <v>-3.91</v>
       </c>
       <c r="M40" t="n">
-        <v>3205</v>
+        <v>3195</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>5125</v>
+        <v>4970</v>
       </c>
       <c r="F41" t="n">
-        <v>114.86</v>
+        <v>111.17</v>
       </c>
       <c r="G41" t="n">
-        <v>39.57</v>
+        <v>38.3</v>
       </c>
       <c r="H41" t="n">
         <v>75.3</v>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-3.21</v>
+        <v>-3.02</v>
       </c>
       <c r="M41" t="n">
-        <v>5295</v>
+        <v>5125</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3753,13 +3753,13 @@
         <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>727</v>
+        <v>692</v>
       </c>
       <c r="F42" t="n">
-        <v>49.55</v>
+        <v>49.97</v>
       </c>
       <c r="G42" t="n">
-        <v>27.65</v>
+        <v>27.88</v>
       </c>
       <c r="H42" t="n">
         <v>47.5</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.83</v>
+        <v>-4.81</v>
       </c>
       <c r="M42" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3836,13 +3836,13 @@
         <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>100.5</v>
+        <v>99</v>
       </c>
       <c r="F43" t="n">
-        <v>11.94</v>
+        <v>11.82</v>
       </c>
       <c r="G43" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H43" t="n">
         <v>11</v>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-0.99</v>
+        <v>-1.49</v>
       </c>
       <c r="M43" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3915,13 +3915,13 @@
         <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>197</v>
+        <v>189.5</v>
       </c>
       <c r="F44" t="n">
-        <v>15.34</v>
+        <v>15.57</v>
       </c>
       <c r="G44" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H44" t="n">
         <v>13.4</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.55</v>
+        <v>-3.81</v>
       </c>
       <c r="M44" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -3998,7 +3998,7 @@
         <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>107.5</v>
+        <v>106.5</v>
       </c>
       <c r="F45" t="n">
         <v>15.86</v>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="M45" t="n">
         <v>107.5</v>
@@ -4077,13 +4077,13 @@
         <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="F46" t="n">
-        <v>18.67</v>
+        <v>18.45</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="H46" t="n">
         <v>21.4</v>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-1.14</v>
+        <v>-3.61</v>
       </c>
       <c r="M46" t="n">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4160,13 +4160,13 @@
         <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="F47" t="n">
-        <v>33.01</v>
+        <v>32.79</v>
       </c>
       <c r="G47" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="H47" t="n">
         <v>30.9</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-0.68</v>
+        <v>-6.82</v>
       </c>
       <c r="M47" t="n">
-        <v>221.5</v>
+        <v>220</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4243,13 +4243,13 @@
         <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>4135</v>
+        <v>3725</v>
       </c>
       <c r="F48" t="n">
-        <v>61.7</v>
+        <v>60.6</v>
       </c>
       <c r="G48" t="n">
-        <v>7.95</v>
+        <v>7.81</v>
       </c>
       <c r="H48" t="n">
         <v>51.7</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1.78</v>
+        <v>-9.92</v>
       </c>
       <c r="M48" t="n">
-        <v>4210</v>
+        <v>4135</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4326,13 +4326,13 @@
         <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>394.5</v>
+        <v>373</v>
       </c>
       <c r="F49" t="n">
-        <v>21.82</v>
+        <v>21.34</v>
       </c>
       <c r="G49" t="n">
-        <v>6.46</v>
+        <v>6.32</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-2.23</v>
+        <v>-5.45</v>
       </c>
       <c r="M49" t="n">
-        <v>403.5</v>
+        <v>394.5</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4403,13 +4403,13 @@
         <v>94</v>
       </c>
       <c r="E50" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F50" t="n">
-        <v>20.47</v>
+        <v>20.41</v>
       </c>
       <c r="G50" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.3</v>
+        <v>-2.38</v>
       </c>
       <c r="M50" t="n">
-        <v>168.5</v>
+        <v>168</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4480,13 +4480,13 @@
         <v>78</v>
       </c>
       <c r="E51" t="n">
-        <v>126.5</v>
+        <v>122</v>
       </c>
       <c r="F51" t="n">
-        <v>29.52</v>
+        <v>28.95</v>
       </c>
       <c r="G51" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1.94</v>
+        <v>-3.56</v>
       </c>
       <c r="M51" t="n">
-        <v>129</v>
+        <v>126.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4540,12 +4540,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4554,20 +4554,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E52" t="n">
-        <v>95.3</v>
+        <v>162</v>
       </c>
       <c r="F52" t="n">
-        <v>20.08</v>
+        <v>33.61</v>
       </c>
       <c r="G52" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-2.56</v>
+        <v>-0.61</v>
       </c>
       <c r="M52" t="n">
-        <v>97.8</v>
+        <v>163</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4588,23 +4588,23 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S52" t="n">
-        <v>-2.7</v>
+        <v>14.6</v>
       </c>
       <c r="T52" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4635,20 +4635,20 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E53" t="n">
-        <v>163</v>
+        <v>222.5</v>
       </c>
       <c r="F53" t="n">
-        <v>34.64</v>
+        <v>26.93</v>
       </c>
       <c r="G53" t="n">
-        <v>1.87</v>
+        <v>6.56</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4657,40 +4657,36 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.98</v>
+        <v>-7.48</v>
       </c>
       <c r="M53" t="n">
-        <v>168</v>
+        <v>240.5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R53" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S53" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T53" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4702,34 +4698,34 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E54" t="n">
-        <v>240.5</v>
+        <v>754</v>
       </c>
       <c r="F54" t="n">
-        <v>25.98</v>
+        <v>27.21</v>
       </c>
       <c r="G54" t="n">
-        <v>6.32</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -4738,31 +4734,35 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.66</v>
+        <v>-0.26</v>
       </c>
       <c r="M54" t="n">
-        <v>232</v>
+        <v>756</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P54" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R54" t="n">
-        <v>20.4</v>
+        <v>3.8</v>
       </c>
       <c r="S54" t="n">
-        <v>812.4</v>
+        <v>21.9</v>
       </c>
       <c r="T54" t="n">
-        <v>34.6</v>
+        <v>32.2</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
@@ -4779,34 +4779,34 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>201</v>
+        <v>128.5</v>
       </c>
       <c r="F55" t="n">
-        <v>20.12</v>
+        <v>30.34</v>
       </c>
       <c r="G55" t="n">
-        <v>2.93</v>
+        <v>3.24</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>49.2</v>
+        <v>186.3</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -4815,31 +4815,35 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-9.26</v>
+        <v>-4.81</v>
       </c>
       <c r="M55" t="n">
-        <v>221.5</v>
+        <v>135</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P55" t="n">
-        <v>14.4</v>
+        <v>10.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>-3.4</v>
       </c>
       <c r="S55" t="n">
-        <v>10.3</v>
+        <v>37</v>
       </c>
       <c r="T55" t="n">
-        <v>20.2</v>
+        <v>35.8</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
@@ -4856,12 +4860,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4870,20 +4874,20 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E56" t="n">
-        <v>756</v>
+        <v>4265</v>
       </c>
       <c r="F56" t="n">
-        <v>30.24</v>
+        <v>27.12</v>
       </c>
       <c r="G56" t="n">
-        <v>9.58</v>
+        <v>3.08</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -4892,10 +4896,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-10</v>
+        <v>-1.84</v>
       </c>
       <c r="M56" t="n">
-        <v>840</v>
+        <v>4345</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4904,23 +4908,23 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>31.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="R56" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="S56" t="n">
-        <v>21.9</v>
+        <v>41.8</v>
       </c>
       <c r="T56" t="n">
-        <v>32.2</v>
+        <v>32.9</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
@@ -4937,201 +4941,197 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E57" t="n">
-        <v>135</v>
+        <v>539</v>
       </c>
       <c r="F57" t="n">
-        <v>30.56</v>
+        <v>35.1</v>
       </c>
       <c r="G57" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>6.95</v>
+      </c>
+      <c r="H57" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I57" t="n">
-        <v>186.3</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-0.74</v>
+        <v>-2.18</v>
       </c>
       <c r="M57" t="n">
-        <v>136</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>10.7</v>
+        <v>19.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.4</v>
+        <v>10.6</v>
       </c>
       <c r="S57" t="n">
-        <v>37</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T57" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="U57" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E58" t="n">
-        <v>4345</v>
+        <v>766</v>
       </c>
       <c r="F58" t="n">
-        <v>24.66</v>
+        <v>53.83</v>
       </c>
       <c r="G58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>8.35</v>
+      </c>
+      <c r="H58" t="n">
+        <v>46.1</v>
+      </c>
       <c r="I58" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.97</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="M58" t="n">
+        <v>794</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R58" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L58" t="n">
-        <v>10</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3950</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R58" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="S58" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="T58" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E59" t="n">
-        <v>551</v>
+        <v>67.3</v>
       </c>
       <c r="F59" t="n">
-        <v>34.97</v>
+        <v>16.99</v>
       </c>
       <c r="G59" t="n">
-        <v>6.92</v>
+        <v>2.9</v>
       </c>
       <c r="H59" t="n">
-        <v>29.3</v>
+        <v>17.3</v>
       </c>
       <c r="I59" t="n">
-        <v>18.6</v>
+        <v>11.8</v>
       </c>
       <c r="J59" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5139,78 +5139,78 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.36</v>
+        <v>-2.89</v>
       </c>
       <c r="M59" t="n">
-        <v>549</v>
+        <v>69.3</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>19.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.94</v>
+        <v>1.15</v>
       </c>
       <c r="R59" t="n">
-        <v>10.6</v>
+        <v>4.4</v>
       </c>
       <c r="S59" t="n">
-        <v>64.90000000000001</v>
+        <v>768.2</v>
       </c>
       <c r="T59" t="n">
-        <v>34.7</v>
+        <v>19.4</v>
       </c>
       <c r="U59" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>794</v>
+        <v>162.5</v>
       </c>
       <c r="F60" t="n">
-        <v>55.39</v>
+        <v>15.54</v>
       </c>
       <c r="G60" t="n">
-        <v>8.59</v>
+        <v>1.69</v>
       </c>
       <c r="H60" t="n">
-        <v>46.1</v>
+        <v>15.5</v>
       </c>
       <c r="I60" t="n">
-        <v>30.6</v>
+        <v>8.6</v>
       </c>
       <c r="J60" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5218,51 +5218,51 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-2.82</v>
+        <v>-1.52</v>
       </c>
       <c r="M60" t="n">
-        <v>817</v>
+        <v>165</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>15.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.83</v>
+        <v>4.03</v>
       </c>
       <c r="R60" t="n">
-        <v>24.8</v>
+        <v>30.2</v>
       </c>
       <c r="S60" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="n">
-        <v>60.2</v>
+        <v>16.9</v>
       </c>
       <c r="U60" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5271,77 +5271,79 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>69.3</v>
+        <v>20.6</v>
       </c>
       <c r="F61" t="n">
-        <v>18.63</v>
+        <v>17.28</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="H61" t="n">
-        <v>17.3</v>
-      </c>
+        <v>1.77</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.64</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-8.82</v>
+        <v>-3.06</v>
       </c>
       <c r="M61" t="n">
-        <v>76</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+        <v>21.25</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>月營收轉負-5%</t>
+        </is>
+      </c>
       <c r="P61" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="R61" t="n">
-        <v>4.4</v>
+        <v>12.8</v>
       </c>
       <c r="S61" t="n">
-        <v>768.2</v>
+        <v>-5.3</v>
       </c>
       <c r="T61" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.64</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5350,77 +5352,79 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>165</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>15.68</v>
+        <v>19.57</v>
       </c>
       <c r="G62" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H62" t="n">
-        <v>15.5</v>
-      </c>
+        <v>1.85</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.95</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-0.9</v>
+        <v>-2.52</v>
       </c>
       <c r="M62" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+        <v>95.3</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P62" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R62" t="n">
-        <v>30.2</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>-2.7</v>
       </c>
       <c r="T62" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.95</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5429,20 +5433,20 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>21.25</v>
+        <v>44.5</v>
       </c>
       <c r="F63" t="n">
-        <v>17.72</v>
+        <v>14.66</v>
       </c>
       <c r="G63" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>13.7</v>
+        <v>147.4</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -5451,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-2.52</v>
+        <v>-2.41</v>
       </c>
       <c r="M63" t="n">
-        <v>21.8</v>
+        <v>45.6</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5463,28 +5467,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>月營收轉負-5%</t>
+          <t>含金量0.0差</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>10.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.03</v>
+        <v>0.04</v>
       </c>
       <c r="R63" t="n">
-        <v>12.8</v>
+        <v>36.1</v>
       </c>
       <c r="S63" t="n">
-        <v>-5.3</v>
+        <v>0.4</v>
       </c>
       <c r="T63" t="n">
-        <v>18.2</v>
+        <v>14.4</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5496,12 +5500,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5510,20 +5514,20 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>45.6</v>
+        <v>198.5</v>
       </c>
       <c r="F64" t="n">
-        <v>14.66</v>
+        <v>18.26</v>
       </c>
       <c r="G64" t="n">
-        <v>1.29</v>
+        <v>2.66</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>147.4</v>
+        <v>49.2</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -5532,40 +5536,36 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>-1.24</v>
       </c>
       <c r="M64" t="n">
-        <v>45.6</v>
+        <v>201</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>含金量0.0差</t>
-        </is>
-      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>29.2</v>
+        <v>14.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.04</v>
+        <v>1.53</v>
       </c>
       <c r="R64" t="n">
-        <v>36.1</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.4</v>
+        <v>10.3</v>
       </c>
       <c r="T64" t="n">
-        <v>14.4</v>
+        <v>20.2</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -5594,13 +5594,13 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="F65" t="n">
-        <v>18.43</v>
+        <v>18.06</v>
       </c>
       <c r="G65" t="n">
-        <v>17.42</v>
+        <v>17.06</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-2.02</v>
+        <v>-2.47</v>
       </c>
       <c r="M65" t="n">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
       <c r="F66" t="n">
-        <v>19.16</v>
+        <v>18.97</v>
       </c>
       <c r="G66" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.99</v>
+        <v>-2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>157.5</v>
+        <v>156</v>
       </c>
       <c r="F67" t="n">
-        <v>17.14</v>
+        <v>17.08</v>
       </c>
       <c r="G67" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.32</v>
+        <v>-0.95</v>
       </c>
       <c r="M67" t="n">
-        <v>158</v>
+        <v>157.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="F68" t="n">
-        <v>21.6</v>
+        <v>23.72</v>
       </c>
       <c r="G68" t="n">
-        <v>5.13</v>
+        <v>5.63</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>9.82</v>
+        <v>-1.61</v>
       </c>
       <c r="M68" t="n">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="F69" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="G69" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.41</v>
+        <v>-0.82</v>
       </c>
       <c r="M69" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>328.5</v>
+        <v>322</v>
       </c>
       <c r="F70" t="n">
-        <v>34.98</v>
+        <v>32.05</v>
       </c>
       <c r="G70" t="n">
-        <v>9.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-8.369999999999999</v>
+        <v>-1.98</v>
       </c>
       <c r="M70" t="n">
-        <v>358.5</v>
+        <v>328.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>19.37</v>
+        <v>19.22</v>
       </c>
       <c r="G71" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.76</v>
+        <v>-0.11</v>
       </c>
       <c r="M71" t="n">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>148</v>
+        <v>145.5</v>
       </c>
       <c r="F72" t="n">
-        <v>19.51</v>
+        <v>20.19</v>
       </c>
       <c r="G72" t="n">
-        <v>5.33</v>
+        <v>5.51</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.5</v>
+        <v>-1.69</v>
       </c>
       <c r="M72" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>236.5</v>
+        <v>235.5</v>
       </c>
       <c r="F73" t="n">
-        <v>16.87</v>
+        <v>16.8</v>
       </c>
       <c r="G73" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6260,7 +6260,7 @@
         <v>-0.42</v>
       </c>
       <c r="M73" t="n">
-        <v>237.5</v>
+        <v>236.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1050</v>
+        <v>1085</v>
       </c>
       <c r="F74" t="n">
-        <v>55.26</v>
+        <v>55</v>
       </c>
       <c r="G74" t="n">
-        <v>28.77</v>
+        <v>28.63</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-0.47</v>
+        <v>3.33</v>
       </c>
       <c r="M74" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
       <c r="F75" t="n">
-        <v>26.54</v>
+        <v>24.6</v>
       </c>
       <c r="G75" t="n">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-7.31</v>
+        <v>-1.55</v>
       </c>
       <c r="M75" t="n">
-        <v>69.8</v>
+        <v>64.7</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2225</v>
+        <v>2120</v>
       </c>
       <c r="F76" t="n">
-        <v>38.61</v>
+        <v>36.56</v>
       </c>
       <c r="G76" t="n">
-        <v>20.42</v>
+        <v>19.34</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-5.32</v>
+        <v>-4.72</v>
       </c>
       <c r="M76" t="n">
-        <v>2350</v>
+        <v>2225</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>883</v>
+        <v>834</v>
       </c>
       <c r="F77" t="n">
-        <v>24.29</v>
+        <v>24.51</v>
       </c>
       <c r="G77" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.91</v>
+        <v>-5.55</v>
       </c>
       <c r="M77" t="n">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="F78" t="n">
-        <v>32.47</v>
+        <v>32.8</v>
       </c>
       <c r="G78" t="n">
-        <v>10.63</v>
+        <v>10.74</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.04</v>
+        <v>-0.82</v>
       </c>
       <c r="M78" t="n">
-        <v>2415</v>
+        <v>2440</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="F79" t="n">
-        <v>15.15</v>
+        <v>15</v>
       </c>
       <c r="G79" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.97</v>
+        <v>-0.49</v>
       </c>
       <c r="M79" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>119.5</v>
+        <v>115.5</v>
       </c>
       <c r="F80" t="n">
-        <v>16.58</v>
+        <v>16.17</v>
       </c>
       <c r="G80" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-2.45</v>
+        <v>-3.35</v>
       </c>
       <c r="M80" t="n">
-        <v>122.5</v>
+        <v>119.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6872,13 +6872,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="F81" t="n">
-        <v>6.9</v>
+        <v>5.79</v>
       </c>
       <c r="G81" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-16.11</v>
+        <v>-2.08</v>
       </c>
       <c r="M81" t="n">
-        <v>34.45</v>
+        <v>28.9</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>113.5</v>
+        <v>113</v>
       </c>
       <c r="F82" t="n">
-        <v>12.07</v>
+        <v>12.23</v>
       </c>
       <c r="G82" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.34</v>
+        <v>-0.44</v>
       </c>
       <c r="M82" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.07</v>
+        <v>13.14</v>
       </c>
       <c r="G83" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.57</v>
+        <v>-0.85</v>
       </c>
       <c r="M83" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="F84" t="n">
-        <v>7.51</v>
+        <v>7.73</v>
       </c>
       <c r="G84" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.9</v>
+        <v>0.12</v>
       </c>
       <c r="M84" t="n">
-        <v>39.6</v>
+        <v>40.75</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1135</v>
+        <v>1110</v>
       </c>
       <c r="F85" t="n">
-        <v>34.84</v>
+        <v>33.65</v>
       </c>
       <c r="G85" t="n">
-        <v>11.67</v>
+        <v>11.28</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="M85" t="n">
-        <v>1175</v>
+        <v>1135</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>439</v>
+        <v>421.5</v>
       </c>
       <c r="F86" t="n">
-        <v>21.79</v>
+        <v>21.33</v>
       </c>
       <c r="G86" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-2.12</v>
+        <v>-3.99</v>
       </c>
       <c r="M86" t="n">
-        <v>448.5</v>
+        <v>439</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>138</v>
+        <v>133.5</v>
       </c>
       <c r="F87" t="n">
-        <v>17.4</v>
+        <v>16.85</v>
       </c>
       <c r="G87" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-3.16</v>
+        <v>-3.26</v>
       </c>
       <c r="M87" t="n">
-        <v>142.5</v>
+        <v>138</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,10 +7425,10 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>38.65</v>
+        <v>37.9</v>
       </c>
       <c r="F88" t="n">
-        <v>8.529999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="G88" t="n">
         <v>1.16</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-0.39</v>
+        <v>-1.94</v>
       </c>
       <c r="M88" t="n">
-        <v>38.8</v>
+        <v>38.65</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2405</v>
+        <v>2280</v>
       </c>
       <c r="F89" t="n">
-        <v>46.71</v>
+        <v>45.48</v>
       </c>
       <c r="G89" t="n">
-        <v>21.13</v>
+        <v>20.58</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-2.63</v>
+        <v>-5.2</v>
       </c>
       <c r="M89" t="n">
-        <v>2470</v>
+        <v>2405</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>905</v>
+        <v>864</v>
       </c>
       <c r="F90" t="n">
-        <v>26.55</v>
+        <v>26.12</v>
       </c>
       <c r="G90" t="n">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-1.63</v>
+        <v>-4.53</v>
       </c>
       <c r="M90" t="n">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="F91" t="n">
-        <v>10.61</v>
+        <v>10.71</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.9</v>
+        <v>-1.79</v>
       </c>
       <c r="M91" t="n">
-        <v>88.5</v>
+        <v>89.3</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>72.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F92" t="n">
-        <v>7.99</v>
+        <v>7.85</v>
       </c>
       <c r="G92" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1.76</v>
+        <v>-1.52</v>
       </c>
       <c r="M92" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>61.6</v>
+        <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>11.64</v>
+        <v>11.45</v>
       </c>
       <c r="G93" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.6</v>
+        <v>-2.6</v>
       </c>
       <c r="M93" t="n">
-        <v>62.6</v>
+        <v>61.6</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F94" t="n">
-        <v>18.78</v>
+        <v>19</v>
       </c>
       <c r="G94" t="n">
-        <v>6.94</v>
+        <v>7.02</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="M94" t="n">
-        <v>373.5</v>
+        <v>378</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>4960</v>
+        <v>4905</v>
       </c>
       <c r="F95" t="n">
-        <v>16.89</v>
+        <v>16.63</v>
       </c>
       <c r="G95" t="n">
-        <v>6.68</v>
+        <v>6.58</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-1.59</v>
+        <v>-1.11</v>
       </c>
       <c r="M95" t="n">
-        <v>5040</v>
+        <v>4960</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="F96" t="n">
-        <v>14.49</v>
+        <v>14.39</v>
       </c>
       <c r="G96" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="M96" t="n">
-        <v>144.5</v>
+        <v>143.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="F97" t="n">
-        <v>18.16</v>
+        <v>18.53</v>
       </c>
       <c r="G97" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.03</v>
+        <v>0.99</v>
       </c>
       <c r="M97" t="n">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>69.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="F98" t="n">
-        <v>5.27</v>
+        <v>5.79</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>9.949999999999999</v>
+        <v>-3.3</v>
       </c>
       <c r="M98" t="n">
-        <v>63.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F99" t="n">
-        <v>8.19</v>
+        <v>8.09</v>
       </c>
       <c r="G99" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.22</v>
+        <v>-0.49</v>
       </c>
       <c r="M99" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="F100" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="G100" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.12</v>
+        <v>-0.83</v>
       </c>
       <c r="M100" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>183</v>
+        <v>173.5</v>
       </c>
       <c r="F101" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="G101" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.1</v>
+        <v>-5.19</v>
       </c>
       <c r="M101" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2225</v>
+        <v>2120</v>
       </c>
       <c r="F2" t="n">
-        <v>38.61</v>
+        <v>36.56</v>
       </c>
       <c r="G2" t="n">
-        <v>20.42</v>
+        <v>19.34</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.32</v>
+        <v>-4.72</v>
       </c>
       <c r="M2" t="n">
-        <v>2350</v>
+        <v>2225</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>883</v>
+        <v>834</v>
       </c>
       <c r="F3" t="n">
-        <v>24.29</v>
+        <v>24.51</v>
       </c>
       <c r="G3" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.91</v>
+        <v>-5.55</v>
       </c>
       <c r="M3" t="n">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="F4" t="n">
-        <v>32.47</v>
+        <v>32.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.63</v>
+        <v>10.74</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>-0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>2415</v>
+        <v>2440</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="F5" t="n">
-        <v>15.15</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.97</v>
+        <v>-0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>119.5</v>
+        <v>115.5</v>
       </c>
       <c r="F6" t="n">
-        <v>16.58</v>
+        <v>16.17</v>
       </c>
       <c r="G6" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-2.45</v>
+        <v>-3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>119.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="F7" t="n">
-        <v>6.9</v>
+        <v>5.79</v>
       </c>
       <c r="G7" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-16.11</v>
+        <v>-2.08</v>
       </c>
       <c r="M7" t="n">
-        <v>34.45</v>
+        <v>28.9</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>113.5</v>
+        <v>113</v>
       </c>
       <c r="F8" t="n">
-        <v>12.07</v>
+        <v>12.23</v>
       </c>
       <c r="G8" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>-0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.07</v>
+        <v>13.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.57</v>
+        <v>-0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="F10" t="n">
-        <v>7.51</v>
+        <v>7.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>39.6</v>
+        <v>40.75</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1135</v>
+        <v>1110</v>
       </c>
       <c r="F11" t="n">
-        <v>34.84</v>
+        <v>33.65</v>
       </c>
       <c r="G11" t="n">
-        <v>11.67</v>
+        <v>11.28</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1175</v>
+        <v>1135</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>439</v>
+        <v>421.5</v>
       </c>
       <c r="F12" t="n">
-        <v>21.79</v>
+        <v>21.33</v>
       </c>
       <c r="G12" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-2.12</v>
+        <v>-3.99</v>
       </c>
       <c r="M12" t="n">
-        <v>448.5</v>
+        <v>439</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>138</v>
+        <v>133.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.4</v>
+        <v>16.85</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-3.16</v>
+        <v>-3.26</v>
       </c>
       <c r="M13" t="n">
-        <v>142.5</v>
+        <v>138</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.65</v>
+        <v>37.9</v>
       </c>
       <c r="F14" t="n">
-        <v>8.529999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="G14" t="n">
         <v>1.16</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.39</v>
+        <v>-1.94</v>
       </c>
       <c r="M14" t="n">
-        <v>38.8</v>
+        <v>38.65</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2405</v>
+        <v>2280</v>
       </c>
       <c r="F15" t="n">
-        <v>46.71</v>
+        <v>45.48</v>
       </c>
       <c r="G15" t="n">
-        <v>21.13</v>
+        <v>20.58</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-2.63</v>
+        <v>-5.2</v>
       </c>
       <c r="M15" t="n">
-        <v>2470</v>
+        <v>2405</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>905</v>
+        <v>864</v>
       </c>
       <c r="F16" t="n">
-        <v>26.55</v>
+        <v>26.12</v>
       </c>
       <c r="G16" t="n">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.63</v>
+        <v>-4.53</v>
       </c>
       <c r="M16" t="n">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="F17" t="n">
-        <v>10.61</v>
+        <v>10.71</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.9</v>
+        <v>-1.79</v>
       </c>
       <c r="M17" t="n">
-        <v>88.5</v>
+        <v>89.3</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>72.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F18" t="n">
-        <v>7.99</v>
+        <v>7.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.76</v>
+        <v>-1.52</v>
       </c>
       <c r="M18" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>61.6</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
-        <v>11.64</v>
+        <v>11.45</v>
       </c>
       <c r="G19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.6</v>
+        <v>-2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>62.6</v>
+        <v>61.6</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F20" t="n">
-        <v>18.78</v>
+        <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>6.94</v>
+        <v>7.02</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="M20" t="n">
-        <v>373.5</v>
+        <v>378</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>4960</v>
+        <v>4905</v>
       </c>
       <c r="F21" t="n">
-        <v>16.89</v>
+        <v>16.63</v>
       </c>
       <c r="G21" t="n">
-        <v>6.68</v>
+        <v>6.58</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.59</v>
+        <v>-1.11</v>
       </c>
       <c r="M21" t="n">
-        <v>5040</v>
+        <v>4960</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.49</v>
+        <v>14.39</v>
       </c>
       <c r="G22" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="M22" t="n">
-        <v>144.5</v>
+        <v>143.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="F23" t="n">
-        <v>18.16</v>
+        <v>18.53</v>
       </c>
       <c r="G23" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>0.99</v>
       </c>
       <c r="M23" t="n">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>157.5</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>17.14</v>
+        <v>17.08</v>
       </c>
       <c r="G2" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.32</v>
+        <v>-0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>158</v>
+        <v>157.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="F3" t="n">
-        <v>21.6</v>
+        <v>23.72</v>
       </c>
       <c r="G3" t="n">
-        <v>5.13</v>
+        <v>5.63</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9.82</v>
+        <v>-1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>509</v>
+        <v>559</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.41</v>
+        <v>-0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>328.5</v>
+        <v>322</v>
       </c>
       <c r="F5" t="n">
-        <v>34.98</v>
+        <v>32.05</v>
       </c>
       <c r="G5" t="n">
-        <v>9.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-8.369999999999999</v>
+        <v>-1.98</v>
       </c>
       <c r="M5" t="n">
-        <v>358.5</v>
+        <v>328.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>19.37</v>
+        <v>19.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.76</v>
+        <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>148</v>
+        <v>145.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.51</v>
+        <v>20.19</v>
       </c>
       <c r="G7" t="n">
-        <v>5.33</v>
+        <v>5.51</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>-1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>236.5</v>
+        <v>235.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.87</v>
+        <v>16.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11111,7 +11111,7 @@
         <v>-0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>237.5</v>
+        <v>236.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1050</v>
+        <v>1085</v>
       </c>
       <c r="F9" t="n">
-        <v>55.26</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>28.77</v>
+        <v>28.63</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>3.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
       <c r="F10" t="n">
-        <v>26.54</v>
+        <v>24.6</v>
       </c>
       <c r="G10" t="n">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-7.31</v>
+        <v>-1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>69.8</v>
+        <v>64.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1240</v>
+        <v>1175</v>
       </c>
       <c r="F2" t="n">
-        <v>87.73</v>
+        <v>88.45</v>
       </c>
       <c r="G2" t="n">
-        <v>24.63</v>
+        <v>24.83</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8100000000000001</v>
+        <v>-5.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.55</v>
+        <v>39.35</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09</v>
+        <v>11.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.76</v>
+        <v>-0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>39.25</v>
+        <v>39.55</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>151.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.82</v>
+        <v>17.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.78</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>145.5</v>
+        <v>151</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6640</v>
+        <v>6340</v>
       </c>
       <c r="F5" t="n">
-        <v>188.5</v>
+        <v>176.78</v>
       </c>
       <c r="G5" t="n">
-        <v>44.03</v>
+        <v>41.29</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-6.21</v>
+        <v>-4.52</v>
       </c>
       <c r="M5" t="n">
-        <v>7080</v>
+        <v>6640</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>22.01</v>
+        <v>22.21</v>
       </c>
       <c r="G6" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>108.5</v>
+        <v>109.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>120.5</v>
+        <v>109.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.71</v>
+        <v>35.13</v>
       </c>
       <c r="G7" t="n">
-        <v>5.07</v>
+        <v>4.99</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.63</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>122.5</v>
+        <v>120.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>251.5</v>
+        <v>241</v>
       </c>
       <c r="F8" t="n">
-        <v>36.64</v>
+        <v>38.4</v>
       </c>
       <c r="G8" t="n">
-        <v>7.1</v>
+        <v>7.44</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.79</v>
+        <v>-4.17</v>
       </c>
       <c r="M8" t="n">
-        <v>240</v>
+        <v>251.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>96.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>24.11</v>
+        <v>24.39</v>
       </c>
       <c r="G9" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.16</v>
+        <v>-1.04</v>
       </c>
       <c r="M9" t="n">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>162.5</v>
+        <v>159</v>
       </c>
       <c r="F10" t="n">
-        <v>20.07</v>
+        <v>19.53</v>
       </c>
       <c r="G10" t="n">
-        <v>5.52</v>
+        <v>5.37</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.69</v>
+        <v>-2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>167</v>
+        <v>162.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1320</v>
+        <v>1290</v>
       </c>
       <c r="F11" t="n">
-        <v>28.02</v>
+        <v>28.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5.03</v>
+        <v>5.19</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.12</v>
+        <v>-2.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1280</v>
+        <v>1320</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>176.5</v>
+        <v>174</v>
       </c>
       <c r="F12" t="n">
-        <v>24.07</v>
+        <v>24.34</v>
       </c>
       <c r="G12" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>-1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>174.5</v>
+        <v>176.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>222</v>
+        <v>212.5</v>
       </c>
       <c r="F13" t="n">
-        <v>31.4</v>
+        <v>32.65</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>5.72</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.98</v>
+        <v>-4.28</v>
       </c>
       <c r="M13" t="n">
-        <v>213.5</v>
+        <v>222</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,7 +12427,7 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>133.5</v>
+        <v>133</v>
       </c>
       <c r="F14" t="n">
         <v>26.54</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="M14" t="n">
         <v>133.5</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>239.5</v>
+        <v>242</v>
       </c>
       <c r="F15" t="n">
-        <v>21.97</v>
+        <v>21.83</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.36</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.62</v>
+        <v>1.04</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4270</v>
+        <v>4020</v>
       </c>
       <c r="F16" t="n">
-        <v>130.57</v>
+        <v>128.46</v>
       </c>
       <c r="G16" t="n">
-        <v>39.88</v>
+        <v>39.24</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.61</v>
+        <v>-5.85</v>
       </c>
       <c r="M16" t="n">
-        <v>4340</v>
+        <v>4270</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1890</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="n">
-        <v>69.31999999999999</v>
+        <v>69.69</v>
       </c>
       <c r="G2" t="n">
-        <v>16.3</v>
+        <v>16.39</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.53</v>
+        <v>-1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="F3" t="n">
-        <v>22.89</v>
+        <v>21.27</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>11.15</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-7.08</v>
+        <v>-1.94</v>
       </c>
       <c r="M3" t="n">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3195</v>
+        <v>3070</v>
       </c>
       <c r="F4" t="n">
-        <v>88.66</v>
+        <v>88.38</v>
       </c>
       <c r="G4" t="n">
-        <v>22.2</v>
+        <v>22.13</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.31</v>
+        <v>-3.91</v>
       </c>
       <c r="M4" t="n">
-        <v>3205</v>
+        <v>3195</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5125</v>
+        <v>4970</v>
       </c>
       <c r="F5" t="n">
-        <v>114.86</v>
+        <v>111.17</v>
       </c>
       <c r="G5" t="n">
-        <v>39.57</v>
+        <v>38.3</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.21</v>
+        <v>-3.02</v>
       </c>
       <c r="M5" t="n">
-        <v>5295</v>
+        <v>5125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>727</v>
+        <v>692</v>
       </c>
       <c r="F6" t="n">
-        <v>49.55</v>
+        <v>49.97</v>
       </c>
       <c r="G6" t="n">
-        <v>27.65</v>
+        <v>27.88</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.83</v>
+        <v>-4.81</v>
       </c>
       <c r="M6" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>100.5</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>11.94</v>
+        <v>11.82</v>
       </c>
       <c r="G7" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.99</v>
+        <v>-1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>197</v>
+        <v>189.5</v>
       </c>
       <c r="F8" t="n">
-        <v>15.34</v>
+        <v>15.57</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>-3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,7 +13368,7 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>107.5</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
         <v>15.86</v>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="M9" t="n">
         <v>107.5</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="F10" t="n">
-        <v>18.67</v>
+        <v>18.45</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.14</v>
+        <v>-3.61</v>
       </c>
       <c r="M10" t="n">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="F11" t="n">
-        <v>33.01</v>
+        <v>32.79</v>
       </c>
       <c r="G11" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.68</v>
+        <v>-6.82</v>
       </c>
       <c r="M11" t="n">
-        <v>221.5</v>
+        <v>220</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4135</v>
+        <v>3725</v>
       </c>
       <c r="F12" t="n">
-        <v>61.7</v>
+        <v>60.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.95</v>
+        <v>7.81</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.78</v>
+        <v>-9.92</v>
       </c>
       <c r="M12" t="n">
-        <v>4210</v>
+        <v>4135</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="F2" t="n">
-        <v>88.45</v>
+        <v>83.81</v>
       </c>
       <c r="G2" t="n">
-        <v>24.83</v>
+        <v>23.53</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.24</v>
+        <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1240</v>
+        <v>1175</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.35</v>
+        <v>39.55</v>
       </c>
       <c r="F3" t="n">
-        <v>11.17</v>
+        <v>11.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.51</v>
+        <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>39.55</v>
+        <v>39.35</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46</v>
+        <v>17.51</v>
       </c>
       <c r="G4" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -741,7 +741,7 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>151</v>
+        <v>151.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="F5" t="n">
-        <v>176.78</v>
+        <v>168.8</v>
       </c>
       <c r="G5" t="n">
-        <v>41.29</v>
+        <v>39.43</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-4.52</v>
+        <v>-0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>6640</v>
+        <v>6340</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -880,10 +880,10 @@
         <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>22.21</v>
+        <v>22.11</v>
       </c>
       <c r="G6" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.13</v>
+        <v>31.92</v>
       </c>
       <c r="G7" t="n">
-        <v>4.99</v>
+        <v>4.54</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-9.130000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="M7" t="n">
-        <v>120.5</v>
+        <v>109.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F8" t="n">
-        <v>38.4</v>
+        <v>36.79</v>
       </c>
       <c r="G8" t="n">
-        <v>7.44</v>
+        <v>7.13</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-4.17</v>
+        <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>251.5</v>
+        <v>241</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="F9" t="n">
-        <v>24.39</v>
+        <v>24.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.04</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
-        <v>96.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.53</v>
+        <v>19.11</v>
       </c>
       <c r="G10" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.15</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>162.5</v>
+        <v>159</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1290</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="n">
-        <v>28.9</v>
+        <v>28.24</v>
       </c>
       <c r="G11" t="n">
-        <v>5.19</v>
+        <v>5.07</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.27</v>
+        <v>5.81</v>
       </c>
       <c r="M11" t="n">
-        <v>1320</v>
+        <v>1290</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174</v>
+        <v>184.5</v>
       </c>
       <c r="F12" t="n">
-        <v>24.34</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.42</v>
+        <v>6.03</v>
       </c>
       <c r="M12" t="n">
-        <v>176.5</v>
+        <v>174</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>212.5</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
-        <v>32.65</v>
+        <v>31.25</v>
       </c>
       <c r="G13" t="n">
-        <v>5.72</v>
+        <v>5.47</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-4.28</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>222</v>
+        <v>212.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1528,10 +1528,10 @@
         <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>26.54</v>
+        <v>26.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>133.5</v>
+        <v>133</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>242</v>
+        <v>244.5</v>
       </c>
       <c r="F15" t="n">
-        <v>21.83</v>
+        <v>22.06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="M15" t="n">
-        <v>239.5</v>
+        <v>242</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4020</v>
+        <v>4120</v>
       </c>
       <c r="F16" t="n">
-        <v>128.46</v>
+        <v>120.94</v>
       </c>
       <c r="G16" t="n">
-        <v>39.24</v>
+        <v>36.94</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-5.85</v>
+        <v>2.49</v>
       </c>
       <c r="M16" t="n">
-        <v>4270</v>
+        <v>4020</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1315</v>
+        <v>1430</v>
       </c>
       <c r="F17" t="n">
-        <v>51.87</v>
+        <v>49.6</v>
       </c>
       <c r="G17" t="n">
-        <v>15.19</v>
+        <v>14.53</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-4.36</v>
+        <v>8.75</v>
       </c>
       <c r="M17" t="n">
-        <v>1375</v>
+        <v>1315</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7995</v>
+        <v>8500</v>
       </c>
       <c r="F18" t="n">
-        <v>71.22</v>
+        <v>70.47</v>
       </c>
       <c r="G18" t="n">
-        <v>24.42</v>
+        <v>24.17</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.05</v>
+        <v>6.32</v>
       </c>
       <c r="M18" t="n">
-        <v>8080</v>
+        <v>7995</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="F19" t="n">
-        <v>69.03</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>12.66</v>
+        <v>12.2</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-3.57</v>
+        <v>9.93</v>
       </c>
       <c r="M19" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>77.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>58.62</v>
+        <v>56.09</v>
       </c>
       <c r="G20" t="n">
-        <v>6.96</v>
+        <v>6.66</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-4.33</v>
+        <v>2.84</v>
       </c>
       <c r="M20" t="n">
-        <v>80.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>7040</v>
+        <v>7255</v>
       </c>
       <c r="F21" t="n">
-        <v>151.13</v>
+        <v>144.26</v>
       </c>
       <c r="G21" t="n">
-        <v>40.91</v>
+        <v>39.05</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-4.54</v>
+        <v>3.05</v>
       </c>
       <c r="M21" t="n">
-        <v>7375</v>
+        <v>7040</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1820</v>
+        <v>1905</v>
       </c>
       <c r="F22" t="n">
-        <v>58.34</v>
+        <v>57.4</v>
       </c>
       <c r="G22" t="n">
-        <v>28.26</v>
+        <v>27.8</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-1.62</v>
+        <v>4.67</v>
       </c>
       <c r="M22" t="n">
-        <v>1850</v>
+        <v>1820</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="F23" t="n">
-        <v>39.65</v>
+        <v>37.11</v>
       </c>
       <c r="G23" t="n">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-6.41</v>
+        <v>6.23</v>
       </c>
       <c r="M23" t="n">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2317,13 +2317,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1395</v>
+        <v>1435</v>
       </c>
       <c r="F24" t="n">
-        <v>111.99</v>
+        <v>100.79</v>
       </c>
       <c r="G24" t="n">
-        <v>24.78</v>
+        <v>22.31</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-10</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>1550</v>
+        <v>1395</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>36.95</v>
+        <v>35.05</v>
       </c>
       <c r="F25" t="n">
-        <v>146.67</v>
+        <v>136.85</v>
       </c>
       <c r="G25" t="n">
-        <v>3.41</v>
+        <v>3.19</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-6.69</v>
+        <v>-5.14</v>
       </c>
       <c r="M25" t="n">
-        <v>39.6</v>
+        <v>36.95</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>1925</v>
+        <v>1755</v>
       </c>
       <c r="F26" t="n">
-        <v>261.5</v>
+        <v>252.96</v>
       </c>
       <c r="G26" t="n">
-        <v>43.43</v>
+        <v>42.01</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-3.27</v>
+        <v>-8.83</v>
       </c>
       <c r="M26" t="n">
-        <v>1990</v>
+        <v>1925</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2558,13 +2558,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>641</v>
+        <v>683</v>
       </c>
       <c r="F27" t="n">
-        <v>62.21</v>
+        <v>59.52</v>
       </c>
       <c r="G27" t="n">
-        <v>8.390000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-4.33</v>
+        <v>6.55</v>
       </c>
       <c r="M27" t="n">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="F28" t="n">
-        <v>78.37</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>13.49</v>
+        <v>12.95</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="F29" t="n">
-        <v>75.77</v>
+        <v>72.88</v>
       </c>
       <c r="G29" t="n">
-        <v>14.43</v>
+        <v>13.88</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-3.82</v>
+        <v>1.74</v>
       </c>
       <c r="M29" t="n">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2799,13 +2799,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>2700</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="n">
-        <v>81.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="G30" t="n">
-        <v>9.279999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-2.7</v>
+        <v>4.07</v>
       </c>
       <c r="M30" t="n">
-        <v>2775</v>
+        <v>2700</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2880,13 +2880,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F31" t="n">
-        <v>153.27</v>
+        <v>141.67</v>
       </c>
       <c r="G31" t="n">
-        <v>14.39</v>
+        <v>13.3</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-7.57</v>
+        <v>0.84</v>
       </c>
       <c r="M31" t="n">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2959,13 +2959,13 @@
         <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>247.5</v>
+        <v>267</v>
       </c>
       <c r="F32" t="n">
-        <v>38.2</v>
+        <v>36.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-4.44</v>
+        <v>7.88</v>
       </c>
       <c r="M32" t="n">
-        <v>259</v>
+        <v>247.5</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3036,13 +3036,13 @@
         <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="F33" t="n">
-        <v>37.87</v>
+        <v>40.11</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.91</v>
+        <v>7.37</v>
       </c>
       <c r="M33" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3115,13 +3115,13 @@
         <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F34" t="n">
-        <v>41.58</v>
+        <v>41.04</v>
       </c>
       <c r="G34" t="n">
-        <v>9.380000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-1.31</v>
+        <v>0.76</v>
       </c>
       <c r="M34" t="n">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
@@ -3192,13 +3192,13 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="F35" t="n">
-        <v>64.25</v>
+        <v>61.26</v>
       </c>
       <c r="G35" t="n">
-        <v>10.06</v>
+        <v>9.59</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-4.66</v>
+        <v>2.57</v>
       </c>
       <c r="M35" t="n">
-        <v>816</v>
+        <v>778</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>164.5</v>
+        <v>180.5</v>
       </c>
       <c r="F36" t="n">
-        <v>49.55</v>
+        <v>48.81</v>
       </c>
       <c r="G36" t="n">
-        <v>6.44</v>
+        <v>6.35</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1.5</v>
+        <v>9.73</v>
       </c>
       <c r="M36" t="n">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3352,13 +3352,13 @@
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>3660</v>
+        <v>3740</v>
       </c>
       <c r="F37" t="n">
-        <v>60.96</v>
+        <v>58.33</v>
       </c>
       <c r="G37" t="n">
-        <v>15.64</v>
+        <v>14.97</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-4.31</v>
+        <v>2.19</v>
       </c>
       <c r="M37" t="n">
-        <v>3825</v>
+        <v>3660</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>1855</v>
+        <v>1890</v>
       </c>
       <c r="F38" t="n">
-        <v>69.69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>16.39</v>
+        <v>16.09</v>
       </c>
       <c r="H38" t="n">
         <v>59.1</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-1.85</v>
+        <v>1.89</v>
       </c>
       <c r="M38" t="n">
-        <v>1890</v>
+        <v>1855</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3512,13 +3512,13 @@
         <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="F39" t="n">
-        <v>21.27</v>
+        <v>20.86</v>
       </c>
       <c r="G39" t="n">
-        <v>11.15</v>
+        <v>10.94</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-1.94</v>
+        <v>3.2</v>
       </c>
       <c r="M39" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3595,13 +3595,13 @@
         <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>3070</v>
+        <v>3280</v>
       </c>
       <c r="F40" t="n">
-        <v>88.38</v>
+        <v>84.92</v>
       </c>
       <c r="G40" t="n">
-        <v>22.13</v>
+        <v>21.27</v>
       </c>
       <c r="H40" t="n">
         <v>70.2</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-3.91</v>
+        <v>6.84</v>
       </c>
       <c r="M40" t="n">
-        <v>3195</v>
+        <v>3070</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>4970</v>
+        <v>5080</v>
       </c>
       <c r="F41" t="n">
-        <v>111.17</v>
+        <v>107.81</v>
       </c>
       <c r="G41" t="n">
-        <v>38.3</v>
+        <v>37.14</v>
       </c>
       <c r="H41" t="n">
         <v>75.3</v>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-3.02</v>
+        <v>2.21</v>
       </c>
       <c r="M41" t="n">
-        <v>5125</v>
+        <v>4970</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3753,13 +3753,13 @@
         <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="F42" t="n">
-        <v>49.97</v>
+        <v>47.56</v>
       </c>
       <c r="G42" t="n">
-        <v>27.88</v>
+        <v>26.53</v>
       </c>
       <c r="H42" t="n">
         <v>47.5</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-4.81</v>
+        <v>2.46</v>
       </c>
       <c r="M42" t="n">
-        <v>727</v>
+        <v>692</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3836,13 +3836,13 @@
         <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="F43" t="n">
-        <v>11.82</v>
+        <v>11.65</v>
       </c>
       <c r="G43" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H43" t="n">
         <v>11</v>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-1.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>100.5</v>
+        <v>99</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3915,13 +3915,13 @@
         <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>189.5</v>
+        <v>191</v>
       </c>
       <c r="F44" t="n">
-        <v>15.57</v>
+        <v>14.98</v>
       </c>
       <c r="G44" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="H44" t="n">
         <v>13.4</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-3.81</v>
+        <v>0.79</v>
       </c>
       <c r="M44" t="n">
-        <v>197</v>
+        <v>189.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -3998,13 +3998,13 @@
         <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="F45" t="n">
-        <v>15.86</v>
+        <v>15.71</v>
       </c>
       <c r="G45" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="H45" t="n">
         <v>16</v>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.93</v>
+        <v>0.47</v>
       </c>
       <c r="M45" t="n">
-        <v>107.5</v>
+        <v>106.5</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -4077,13 +4077,13 @@
         <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="F46" t="n">
-        <v>18.45</v>
+        <v>17.79</v>
       </c>
       <c r="G46" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="H46" t="n">
         <v>21.4</v>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-3.61</v>
+        <v>-5.62</v>
       </c>
       <c r="M46" t="n">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4160,13 +4160,13 @@
         <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>205</v>
+        <v>209.5</v>
       </c>
       <c r="F47" t="n">
-        <v>32.79</v>
+        <v>30.55</v>
       </c>
       <c r="G47" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="H47" t="n">
         <v>30.9</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-6.82</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4243,13 +4243,13 @@
         <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>3725</v>
+        <v>3735</v>
       </c>
       <c r="F48" t="n">
-        <v>60.6</v>
+        <v>54.59</v>
       </c>
       <c r="G48" t="n">
-        <v>7.81</v>
+        <v>7.04</v>
       </c>
       <c r="H48" t="n">
         <v>51.7</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-9.92</v>
+        <v>0.27</v>
       </c>
       <c r="M48" t="n">
-        <v>4135</v>
+        <v>3725</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4326,13 +4326,13 @@
         <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="F49" t="n">
-        <v>21.34</v>
+        <v>20.17</v>
       </c>
       <c r="G49" t="n">
-        <v>6.32</v>
+        <v>5.97</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-5.45</v>
+        <v>4.83</v>
       </c>
       <c r="M49" t="n">
-        <v>394.5</v>
+        <v>373</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4386,34 +4386,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E50" t="n">
-        <v>164</v>
+        <v>129.5</v>
       </c>
       <c r="F50" t="n">
-        <v>20.41</v>
+        <v>27.92</v>
       </c>
       <c r="G50" t="n">
-        <v>3.86</v>
+        <v>2.87</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>57.1</v>
+        <v>11</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-2.38</v>
+        <v>6.15</v>
       </c>
       <c r="M50" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4434,24 +4434,24 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>18.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="R50" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>48.7</v>
       </c>
       <c r="T50" t="n">
-        <v>22</v>
+        <v>28.4</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4477,20 +4477,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E51" t="n">
-        <v>122</v>
+        <v>166.5</v>
       </c>
       <c r="F51" t="n">
-        <v>28.95</v>
+        <v>33.4</v>
       </c>
       <c r="G51" t="n">
-        <v>2.97</v>
+        <v>1.8</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4499,36 +4499,40 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-3.56</v>
+        <v>2.78</v>
       </c>
       <c r="M51" t="n">
-        <v>126.5</v>
+        <v>162</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="R51" t="n">
-        <v>3.8</v>
+        <v>22.1</v>
       </c>
       <c r="S51" t="n">
-        <v>48.7</v>
+        <v>14.6</v>
       </c>
       <c r="T51" t="n">
-        <v>28.4</v>
+        <v>34.2</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4540,12 +4544,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4554,20 +4558,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E52" t="n">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="F52" t="n">
-        <v>33.61</v>
+        <v>24.92</v>
       </c>
       <c r="G52" t="n">
-        <v>1.82</v>
+        <v>6.07</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4576,40 +4580,36 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-0.61</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>163</v>
+        <v>222.5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R52" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S52" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T52" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4621,34 +4621,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E53" t="n">
-        <v>222.5</v>
+        <v>753</v>
       </c>
       <c r="F53" t="n">
-        <v>26.93</v>
+        <v>27.14</v>
       </c>
       <c r="G53" t="n">
-        <v>6.56</v>
+        <v>8.6</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4657,31 +4657,35 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-7.48</v>
+        <v>-0.13</v>
       </c>
       <c r="M53" t="n">
-        <v>240.5</v>
+        <v>754</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P53" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R53" t="n">
-        <v>20.4</v>
+        <v>3.8</v>
       </c>
       <c r="S53" t="n">
-        <v>812.4</v>
+        <v>21.9</v>
       </c>
       <c r="T53" t="n">
-        <v>34.6</v>
+        <v>32.2</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
@@ -4698,12 +4702,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4712,20 +4716,20 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
-        <v>754</v>
+        <v>132</v>
       </c>
       <c r="F54" t="n">
-        <v>27.21</v>
+        <v>28.88</v>
       </c>
       <c r="G54" t="n">
-        <v>8.619999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -4734,10 +4738,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-0.26</v>
+        <v>2.72</v>
       </c>
       <c r="M54" t="n">
-        <v>756</v>
+        <v>128.5</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4746,28 +4750,28 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R54" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S54" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T54" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -4779,12 +4783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4793,20 +4797,20 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E55" t="n">
-        <v>128.5</v>
+        <v>4040</v>
       </c>
       <c r="F55" t="n">
-        <v>30.34</v>
+        <v>26.62</v>
       </c>
       <c r="G55" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>186.3</v>
+        <v>9</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -4815,10 +4819,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-4.81</v>
+        <v>-5.28</v>
       </c>
       <c r="M55" t="n">
-        <v>135</v>
+        <v>4265</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4827,28 +4831,28 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="R55" t="n">
-        <v>-3.4</v>
+        <v>6.8</v>
       </c>
       <c r="S55" t="n">
-        <v>37</v>
+        <v>41.8</v>
       </c>
       <c r="T55" t="n">
-        <v>35.8</v>
+        <v>32.9</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4860,73 +4864,71 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E56" t="n">
-        <v>4265</v>
+        <v>585</v>
       </c>
       <c r="F56" t="n">
-        <v>27.12</v>
+        <v>34.33</v>
       </c>
       <c r="G56" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="H56" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I56" t="n">
-        <v>9</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-1.84</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>4345</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="R56" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="S56" t="n">
-        <v>41.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T56" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4934,19 +4936,19 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4955,25 +4957,25 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E57" t="n">
-        <v>539</v>
+        <v>842</v>
       </c>
       <c r="F57" t="n">
-        <v>35.1</v>
+        <v>51.93</v>
       </c>
       <c r="G57" t="n">
-        <v>6.95</v>
+        <v>8.06</v>
       </c>
       <c r="H57" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I57" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J57" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4981,78 +4983,78 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-2.18</v>
+        <v>9.92</v>
       </c>
       <c r="M57" t="n">
-        <v>551</v>
+        <v>766</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R57" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S57" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T57" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U57" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E58" t="n">
-        <v>766</v>
+        <v>67.7</v>
       </c>
       <c r="F58" t="n">
-        <v>53.83</v>
+        <v>16.5</v>
       </c>
       <c r="G58" t="n">
-        <v>8.35</v>
+        <v>2.82</v>
       </c>
       <c r="H58" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I58" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J58" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5060,30 +5062,30 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-3.53</v>
+        <v>0.59</v>
       </c>
       <c r="M58" t="n">
-        <v>794</v>
+        <v>67.3</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R58" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S58" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T58" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U58" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -5092,19 +5094,19 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5113,25 +5115,25 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>67.3</v>
+        <v>163.5</v>
       </c>
       <c r="F59" t="n">
-        <v>16.99</v>
+        <v>15.3</v>
       </c>
       <c r="G59" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="H59" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I59" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J59" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5139,34 +5141,34 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-2.89</v>
+        <v>0.62</v>
       </c>
       <c r="M59" t="n">
-        <v>69.3</v>
+        <v>162.5</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R59" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S59" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T59" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U59" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -5178,79 +5180,77 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E60" t="n">
-        <v>162.5</v>
+        <v>171</v>
       </c>
       <c r="F60" t="n">
-        <v>15.54</v>
+        <v>19.93</v>
       </c>
       <c r="G60" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="H60" t="n">
-        <v>15.5</v>
-      </c>
+        <v>3.76</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1.95</v>
-      </c>
+        <v>57.1</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1.52</v>
+        <v>4.27</v>
       </c>
       <c r="M60" t="n">
-        <v>165</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>10.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
       <c r="R60" t="n">
-        <v>30.2</v>
+        <v>11.1</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="T60" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.95</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
@@ -5274,13 +5274,13 @@
         <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>20.6</v>
+        <v>20.65</v>
       </c>
       <c r="F61" t="n">
-        <v>17.28</v>
+        <v>16.75</v>
       </c>
       <c r="G61" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-3.06</v>
+        <v>0.24</v>
       </c>
       <c r="M61" t="n">
-        <v>21.25</v>
+        <v>20.6</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>92.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="F62" t="n">
-        <v>19.57</v>
+        <v>19.08</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-2.52</v>
+        <v>6.57</v>
       </c>
       <c r="M62" t="n">
-        <v>95.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>44.5</v>
+        <v>45.6</v>
       </c>
       <c r="F63" t="n">
-        <v>14.66</v>
+        <v>14.31</v>
       </c>
       <c r="G63" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-2.41</v>
+        <v>2.47</v>
       </c>
       <c r="M63" t="n">
-        <v>45.6</v>
+        <v>44.5</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
       <c r="F64" t="n">
-        <v>18.26</v>
+        <v>18.03</v>
       </c>
       <c r="G64" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.24</v>
+        <v>-1.01</v>
       </c>
       <c r="M64" t="n">
-        <v>201</v>
+        <v>198.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="F65" t="n">
-        <v>18.06</v>
+        <v>17.61</v>
       </c>
       <c r="G65" t="n">
-        <v>17.06</v>
+        <v>16.64</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-2.47</v>
+        <v>-0.98</v>
       </c>
       <c r="M65" t="n">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
       <c r="F66" t="n">
-        <v>18.97</v>
+        <v>18.52</v>
       </c>
       <c r="G66" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-2.4</v>
+        <v>1.85</v>
       </c>
       <c r="M66" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F67" t="n">
-        <v>17.08</v>
+        <v>16.92</v>
       </c>
       <c r="G67" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.95</v>
+        <v>0.64</v>
       </c>
       <c r="M67" t="n">
-        <v>157.5</v>
+        <v>156</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="F68" t="n">
-        <v>23.72</v>
+        <v>23.33</v>
       </c>
       <c r="G68" t="n">
-        <v>5.63</v>
+        <v>5.54</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M68" t="n">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="F69" t="n">
-        <v>17.6</v>
+        <v>17.46</v>
       </c>
       <c r="G69" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.82</v>
+        <v>0.82</v>
       </c>
       <c r="M69" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>322</v>
+        <v>334.5</v>
       </c>
       <c r="F70" t="n">
-        <v>32.05</v>
+        <v>31.41</v>
       </c>
       <c r="G70" t="n">
-        <v>8.789999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.98</v>
+        <v>3.88</v>
       </c>
       <c r="M70" t="n">
-        <v>328.5</v>
+        <v>322</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>91.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="F71" t="n">
-        <v>19.22</v>
+        <v>19.2</v>
       </c>
       <c r="G71" t="n">
         <v>2.1</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.11</v>
+        <v>0.88</v>
       </c>
       <c r="M71" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>145.5</v>
+        <v>158</v>
       </c>
       <c r="F72" t="n">
-        <v>20.19</v>
+        <v>19.85</v>
       </c>
       <c r="G72" t="n">
-        <v>5.51</v>
+        <v>5.42</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.69</v>
+        <v>8.59</v>
       </c>
       <c r="M72" t="n">
-        <v>148</v>
+        <v>145.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>235.5</v>
+        <v>239</v>
       </c>
       <c r="F73" t="n">
-        <v>16.8</v>
+        <v>16.73</v>
       </c>
       <c r="G73" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-0.42</v>
+        <v>1.49</v>
       </c>
       <c r="M73" t="n">
-        <v>236.5</v>
+        <v>235.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F74" t="n">
-        <v>55</v>
+        <v>56.84</v>
       </c>
       <c r="G74" t="n">
-        <v>28.63</v>
+        <v>29.59</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.33</v>
+        <v>1.84</v>
       </c>
       <c r="M74" t="n">
-        <v>1050</v>
+        <v>1085</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>63.7</v>
+        <v>61.1</v>
       </c>
       <c r="F75" t="n">
-        <v>24.6</v>
+        <v>24.22</v>
       </c>
       <c r="G75" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.55</v>
+        <v>-4.08</v>
       </c>
       <c r="M75" t="n">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2120</v>
+        <v>2165</v>
       </c>
       <c r="F76" t="n">
-        <v>36.56</v>
+        <v>34.83</v>
       </c>
       <c r="G76" t="n">
-        <v>19.34</v>
+        <v>18.43</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-4.72</v>
+        <v>2.12</v>
       </c>
       <c r="M76" t="n">
-        <v>2225</v>
+        <v>2120</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>834</v>
+        <v>895</v>
       </c>
       <c r="F77" t="n">
-        <v>24.51</v>
+        <v>23.15</v>
       </c>
       <c r="G77" t="n">
-        <v>9.5</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-5.55</v>
+        <v>7.31</v>
       </c>
       <c r="M77" t="n">
-        <v>883</v>
+        <v>834</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2420</v>
+        <v>2440</v>
       </c>
       <c r="F78" t="n">
-        <v>32.8</v>
+        <v>32.54</v>
       </c>
       <c r="G78" t="n">
-        <v>10.74</v>
+        <v>10.65</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M78" t="n">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>101.5</v>
+        <v>103</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="G79" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.49</v>
+        <v>1.48</v>
       </c>
       <c r="M79" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>115.5</v>
+        <v>117</v>
       </c>
       <c r="F80" t="n">
-        <v>16.17</v>
+        <v>15.63</v>
       </c>
       <c r="G80" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-3.35</v>
+        <v>1.3</v>
       </c>
       <c r="M80" t="n">
-        <v>119.5</v>
+        <v>115.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6872,13 +6872,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>28.3</v>
+        <v>28.65</v>
       </c>
       <c r="F81" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="G81" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-2.08</v>
+        <v>1.24</v>
       </c>
       <c r="M81" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F82" t="n">
-        <v>12.23</v>
+        <v>12.18</v>
       </c>
       <c r="G82" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="M82" t="n">
-        <v>113.5</v>
+        <v>113</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="F83" t="n">
-        <v>13.14</v>
+        <v>13.03</v>
       </c>
       <c r="G83" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="M83" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>40.8</v>
+        <v>42.15</v>
       </c>
       <c r="F84" t="n">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
       <c r="G84" t="n">
         <v>1.63</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.12</v>
+        <v>3.31</v>
       </c>
       <c r="M84" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="F85" t="n">
-        <v>33.65</v>
+        <v>32.91</v>
       </c>
       <c r="G85" t="n">
-        <v>11.28</v>
+        <v>11.03</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-2.2</v>
+        <v>3.15</v>
       </c>
       <c r="M85" t="n">
-        <v>1135</v>
+        <v>1110</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>421.5</v>
+        <v>426</v>
       </c>
       <c r="F86" t="n">
-        <v>21.33</v>
+        <v>20.48</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-3.99</v>
+        <v>1.07</v>
       </c>
       <c r="M86" t="n">
-        <v>439</v>
+        <v>421.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>133.5</v>
+        <v>139</v>
       </c>
       <c r="F87" t="n">
-        <v>16.85</v>
+        <v>16.3</v>
       </c>
       <c r="G87" t="n">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-3.26</v>
+        <v>4.12</v>
       </c>
       <c r="M87" t="n">
-        <v>138</v>
+        <v>133.5</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="F88" t="n">
-        <v>8.49</v>
+        <v>8.33</v>
       </c>
       <c r="G88" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1.94</v>
+        <v>1.58</v>
       </c>
       <c r="M88" t="n">
-        <v>38.65</v>
+        <v>37.9</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2280</v>
+        <v>2340</v>
       </c>
       <c r="F89" t="n">
-        <v>45.48</v>
+        <v>43.12</v>
       </c>
       <c r="G89" t="n">
-        <v>20.58</v>
+        <v>19.51</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-5.2</v>
+        <v>2.63</v>
       </c>
       <c r="M89" t="n">
-        <v>2405</v>
+        <v>2280</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="F90" t="n">
-        <v>26.12</v>
+        <v>24.94</v>
       </c>
       <c r="G90" t="n">
-        <v>6.28</v>
+        <v>5.99</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-4.53</v>
+        <v>3.7</v>
       </c>
       <c r="M90" t="n">
-        <v>905</v>
+        <v>864</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>87.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>10.71</v>
+        <v>10.52</v>
       </c>
       <c r="G91" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-1.79</v>
+        <v>0.46</v>
       </c>
       <c r="M91" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>71.5</v>
+        <v>72.7</v>
       </c>
       <c r="F92" t="n">
-        <v>7.85</v>
+        <v>7.73</v>
       </c>
       <c r="G92" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1.52</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>72.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="F93" t="n">
-        <v>11.45</v>
+        <v>11.15</v>
       </c>
       <c r="G93" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-2.6</v>
+        <v>1.5</v>
       </c>
       <c r="M93" t="n">
-        <v>61.6</v>
+        <v>60</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F94" t="n">
-        <v>19</v>
+        <v>19.11</v>
       </c>
       <c r="G94" t="n">
-        <v>7.02</v>
+        <v>7.06</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="M94" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>4905</v>
+        <v>5095</v>
       </c>
       <c r="F95" t="n">
-        <v>16.63</v>
+        <v>16.44</v>
       </c>
       <c r="G95" t="n">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-1.11</v>
+        <v>3.87</v>
       </c>
       <c r="M95" t="n">
-        <v>4960</v>
+        <v>4905</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>142.5</v>
+        <v>145.5</v>
       </c>
       <c r="F96" t="n">
-        <v>14.39</v>
+        <v>14.29</v>
       </c>
       <c r="G96" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-0.7</v>
+        <v>2.11</v>
       </c>
       <c r="M96" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="F97" t="n">
-        <v>18.53</v>
+        <v>18.71</v>
       </c>
       <c r="G97" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="M97" t="n">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>67.3</v>
+        <v>67.8</v>
       </c>
       <c r="F98" t="n">
-        <v>5.79</v>
+        <v>5.6</v>
       </c>
       <c r="G98" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-3.3</v>
+        <v>0.74</v>
       </c>
       <c r="M98" t="n">
-        <v>69.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F99" t="n">
-        <v>8.09</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G99" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-0.49</v>
+        <v>1.24</v>
       </c>
       <c r="M99" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8412,10 +8412,10 @@
         <v>23.9</v>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="G100" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>173.5</v>
+        <v>181.5</v>
       </c>
       <c r="F101" t="n">
-        <v>8.92</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G101" t="n">
-        <v>3.71</v>
+        <v>3.52</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-5.19</v>
+        <v>4.61</v>
       </c>
       <c r="M101" t="n">
-        <v>183</v>
+        <v>173.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2120</v>
+        <v>2165</v>
       </c>
       <c r="F2" t="n">
-        <v>36.56</v>
+        <v>34.83</v>
       </c>
       <c r="G2" t="n">
-        <v>19.34</v>
+        <v>18.43</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-4.72</v>
+        <v>2.12</v>
       </c>
       <c r="M2" t="n">
-        <v>2225</v>
+        <v>2120</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>834</v>
+        <v>895</v>
       </c>
       <c r="F3" t="n">
-        <v>24.51</v>
+        <v>23.15</v>
       </c>
       <c r="G3" t="n">
-        <v>9.5</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-5.55</v>
+        <v>7.31</v>
       </c>
       <c r="M3" t="n">
-        <v>883</v>
+        <v>834</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2420</v>
+        <v>2440</v>
       </c>
       <c r="F4" t="n">
-        <v>32.8</v>
+        <v>32.54</v>
       </c>
       <c r="G4" t="n">
-        <v>10.74</v>
+        <v>10.65</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>101.5</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="G5" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.49</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>115.5</v>
+        <v>117</v>
       </c>
       <c r="F6" t="n">
-        <v>16.17</v>
+        <v>15.63</v>
       </c>
       <c r="G6" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3.35</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>119.5</v>
+        <v>115.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>28.3</v>
+        <v>28.65</v>
       </c>
       <c r="F7" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.08</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>12.23</v>
+        <v>12.18</v>
       </c>
       <c r="G8" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="M8" t="n">
-        <v>113.5</v>
+        <v>113</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="F9" t="n">
-        <v>13.14</v>
+        <v>13.03</v>
       </c>
       <c r="G9" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,10 +9334,10 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>40.8</v>
+        <v>42.15</v>
       </c>
       <c r="F10" t="n">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
       <c r="G10" t="n">
         <v>1.63</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.12</v>
+        <v>3.31</v>
       </c>
       <c r="M10" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="F11" t="n">
-        <v>33.65</v>
+        <v>32.91</v>
       </c>
       <c r="G11" t="n">
-        <v>11.28</v>
+        <v>11.03</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.2</v>
+        <v>3.15</v>
       </c>
       <c r="M11" t="n">
-        <v>1135</v>
+        <v>1110</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>421.5</v>
+        <v>426</v>
       </c>
       <c r="F12" t="n">
-        <v>21.33</v>
+        <v>20.48</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-3.99</v>
+        <v>1.07</v>
       </c>
       <c r="M12" t="n">
-        <v>439</v>
+        <v>421.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>133.5</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>16.85</v>
+        <v>16.3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-3.26</v>
+        <v>4.12</v>
       </c>
       <c r="M13" t="n">
-        <v>138</v>
+        <v>133.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="F14" t="n">
-        <v>8.49</v>
+        <v>8.33</v>
       </c>
       <c r="G14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-1.94</v>
+        <v>1.58</v>
       </c>
       <c r="M14" t="n">
-        <v>38.65</v>
+        <v>37.9</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2280</v>
+        <v>2340</v>
       </c>
       <c r="F15" t="n">
-        <v>45.48</v>
+        <v>43.12</v>
       </c>
       <c r="G15" t="n">
-        <v>20.58</v>
+        <v>19.51</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-5.2</v>
+        <v>2.63</v>
       </c>
       <c r="M15" t="n">
-        <v>2405</v>
+        <v>2280</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="F16" t="n">
-        <v>26.12</v>
+        <v>24.94</v>
       </c>
       <c r="G16" t="n">
-        <v>6.28</v>
+        <v>5.99</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-4.53</v>
+        <v>3.7</v>
       </c>
       <c r="M16" t="n">
-        <v>905</v>
+        <v>864</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>87.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>10.71</v>
+        <v>10.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-1.79</v>
+        <v>0.46</v>
       </c>
       <c r="M17" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>71.5</v>
+        <v>72.7</v>
       </c>
       <c r="F18" t="n">
-        <v>7.85</v>
+        <v>7.73</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.52</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>72.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="F19" t="n">
-        <v>11.45</v>
+        <v>11.15</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-2.6</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>61.6</v>
+        <v>60</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>19.11</v>
       </c>
       <c r="G20" t="n">
-        <v>7.02</v>
+        <v>7.06</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="M20" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>4905</v>
+        <v>5095</v>
       </c>
       <c r="F21" t="n">
-        <v>16.63</v>
+        <v>16.44</v>
       </c>
       <c r="G21" t="n">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.11</v>
+        <v>3.87</v>
       </c>
       <c r="M21" t="n">
-        <v>4960</v>
+        <v>4905</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>142.5</v>
+        <v>145.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.39</v>
+        <v>14.29</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.7</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>143.5</v>
+        <v>142.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="F23" t="n">
-        <v>18.53</v>
+        <v>18.71</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="M23" t="n">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F2" t="n">
-        <v>17.08</v>
+        <v>16.92</v>
       </c>
       <c r="G2" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.95</v>
+        <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>157.5</v>
+        <v>156</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="F3" t="n">
-        <v>23.72</v>
+        <v>23.33</v>
       </c>
       <c r="G3" t="n">
-        <v>5.63</v>
+        <v>5.54</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M3" t="n">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.6</v>
+        <v>17.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.82</v>
+        <v>0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>322</v>
+        <v>334.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32.05</v>
+        <v>31.41</v>
       </c>
       <c r="G5" t="n">
-        <v>8.789999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.98</v>
+        <v>3.88</v>
       </c>
       <c r="M5" t="n">
-        <v>328.5</v>
+        <v>322</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,10 +10923,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="F6" t="n">
-        <v>19.22</v>
+        <v>19.2</v>
       </c>
       <c r="G6" t="n">
         <v>2.1</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.11</v>
+        <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>145.5</v>
+        <v>158</v>
       </c>
       <c r="F7" t="n">
-        <v>20.19</v>
+        <v>19.85</v>
       </c>
       <c r="G7" t="n">
-        <v>5.51</v>
+        <v>5.42</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.69</v>
+        <v>8.59</v>
       </c>
       <c r="M7" t="n">
-        <v>148</v>
+        <v>145.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>235.5</v>
+        <v>239</v>
       </c>
       <c r="F8" t="n">
-        <v>16.8</v>
+        <v>16.73</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.42</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>236.5</v>
+        <v>235.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>56.84</v>
       </c>
       <c r="G9" t="n">
-        <v>28.63</v>
+        <v>29.59</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.33</v>
+        <v>1.84</v>
       </c>
       <c r="M9" t="n">
-        <v>1050</v>
+        <v>1085</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>63.7</v>
+        <v>61.1</v>
       </c>
       <c r="F10" t="n">
-        <v>24.6</v>
+        <v>24.22</v>
       </c>
       <c r="G10" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.55</v>
+        <v>-4.08</v>
       </c>
       <c r="M10" t="n">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="F2" t="n">
-        <v>88.45</v>
+        <v>83.81</v>
       </c>
       <c r="G2" t="n">
-        <v>24.83</v>
+        <v>23.53</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.24</v>
+        <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1240</v>
+        <v>1175</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.35</v>
+        <v>39.55</v>
       </c>
       <c r="F3" t="n">
-        <v>11.17</v>
+        <v>11.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.51</v>
+        <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>39.55</v>
+        <v>39.35</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46</v>
+        <v>17.51</v>
       </c>
       <c r="G4" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11643,7 +11643,7 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>151</v>
+        <v>151.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="F5" t="n">
-        <v>176.78</v>
+        <v>168.8</v>
       </c>
       <c r="G5" t="n">
-        <v>41.29</v>
+        <v>39.43</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-4.52</v>
+        <v>-0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>6640</v>
+        <v>6340</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11782,10 +11782,10 @@
         <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>22.21</v>
+        <v>22.11</v>
       </c>
       <c r="G6" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.13</v>
+        <v>31.92</v>
       </c>
       <c r="G7" t="n">
-        <v>4.99</v>
+        <v>4.54</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-9.130000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="M7" t="n">
-        <v>120.5</v>
+        <v>109.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F8" t="n">
-        <v>38.4</v>
+        <v>36.79</v>
       </c>
       <c r="G8" t="n">
-        <v>7.44</v>
+        <v>7.13</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-4.17</v>
+        <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>251.5</v>
+        <v>241</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="F9" t="n">
-        <v>24.39</v>
+        <v>24.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.04</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
-        <v>96.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.53</v>
+        <v>19.11</v>
       </c>
       <c r="G10" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.15</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>162.5</v>
+        <v>159</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1290</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="n">
-        <v>28.9</v>
+        <v>28.24</v>
       </c>
       <c r="G11" t="n">
-        <v>5.19</v>
+        <v>5.07</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.27</v>
+        <v>5.81</v>
       </c>
       <c r="M11" t="n">
-        <v>1320</v>
+        <v>1290</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174</v>
+        <v>184.5</v>
       </c>
       <c r="F12" t="n">
-        <v>24.34</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.42</v>
+        <v>6.03</v>
       </c>
       <c r="M12" t="n">
-        <v>176.5</v>
+        <v>174</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>212.5</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
-        <v>32.65</v>
+        <v>31.25</v>
       </c>
       <c r="G13" t="n">
-        <v>5.72</v>
+        <v>5.47</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-4.28</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>222</v>
+        <v>212.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12430,10 +12430,10 @@
         <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>26.54</v>
+        <v>26.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>133.5</v>
+        <v>133</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>242</v>
+        <v>244.5</v>
       </c>
       <c r="F15" t="n">
-        <v>21.83</v>
+        <v>22.06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="M15" t="n">
-        <v>239.5</v>
+        <v>242</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4020</v>
+        <v>4120</v>
       </c>
       <c r="F16" t="n">
-        <v>128.46</v>
+        <v>120.94</v>
       </c>
       <c r="G16" t="n">
-        <v>39.24</v>
+        <v>36.94</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-5.85</v>
+        <v>2.49</v>
       </c>
       <c r="M16" t="n">
-        <v>4270</v>
+        <v>4020</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1855</v>
+        <v>1890</v>
       </c>
       <c r="F2" t="n">
-        <v>69.69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>16.39</v>
+        <v>16.09</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.85</v>
+        <v>1.89</v>
       </c>
       <c r="M2" t="n">
-        <v>1890</v>
+        <v>1855</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="F3" t="n">
-        <v>21.27</v>
+        <v>20.86</v>
       </c>
       <c r="G3" t="n">
-        <v>11.15</v>
+        <v>10.94</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.94</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3070</v>
+        <v>3280</v>
       </c>
       <c r="F4" t="n">
-        <v>88.38</v>
+        <v>84.92</v>
       </c>
       <c r="G4" t="n">
-        <v>22.13</v>
+        <v>21.27</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-3.91</v>
+        <v>6.84</v>
       </c>
       <c r="M4" t="n">
-        <v>3195</v>
+        <v>3070</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4970</v>
+        <v>5080</v>
       </c>
       <c r="F5" t="n">
-        <v>111.17</v>
+        <v>107.81</v>
       </c>
       <c r="G5" t="n">
-        <v>38.3</v>
+        <v>37.14</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.02</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>5125</v>
+        <v>4970</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="F6" t="n">
-        <v>49.97</v>
+        <v>47.56</v>
       </c>
       <c r="G6" t="n">
-        <v>27.88</v>
+        <v>26.53</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-4.81</v>
+        <v>2.46</v>
       </c>
       <c r="M6" t="n">
-        <v>727</v>
+        <v>692</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="F7" t="n">
-        <v>11.82</v>
+        <v>11.65</v>
       </c>
       <c r="G7" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>100.5</v>
+        <v>99</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>189.5</v>
+        <v>191</v>
       </c>
       <c r="F8" t="n">
-        <v>15.57</v>
+        <v>14.98</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.81</v>
+        <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>197</v>
+        <v>189.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>15.86</v>
+        <v>15.71</v>
       </c>
       <c r="G9" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.93</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>107.5</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="F10" t="n">
-        <v>18.45</v>
+        <v>17.79</v>
       </c>
       <c r="G10" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.61</v>
+        <v>-5.62</v>
       </c>
       <c r="M10" t="n">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>205</v>
+        <v>209.5</v>
       </c>
       <c r="F11" t="n">
-        <v>32.79</v>
+        <v>30.55</v>
       </c>
       <c r="G11" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-6.82</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3725</v>
+        <v>3735</v>
       </c>
       <c r="F12" t="n">
-        <v>60.6</v>
+        <v>54.59</v>
       </c>
       <c r="G12" t="n">
-        <v>7.81</v>
+        <v>7.04</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-9.92</v>
+        <v>0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>4135</v>
+        <v>3725</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1185</v>
+        <v>1125</v>
       </c>
       <c r="F2" t="n">
-        <v>83.81</v>
+        <v>84.52</v>
       </c>
       <c r="G2" t="n">
-        <v>23.53</v>
+        <v>23.73</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.85</v>
+        <v>-5.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -639,10 +639,10 @@
         <v>39.55</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12</v>
+        <v>11.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.35</v>
+        <v>39.55</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F4" t="n">
-        <v>17.51</v>
+        <v>17.57</v>
       </c>
       <c r="G4" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>6.58</v>
       </c>
       <c r="M4" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6330</v>
+        <v>6220</v>
       </c>
       <c r="F5" t="n">
-        <v>168.8</v>
+        <v>168.53</v>
       </c>
       <c r="G5" t="n">
-        <v>39.43</v>
+        <v>39.37</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.16</v>
+        <v>-1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="F6" t="n">
         <v>22.11</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>109</v>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>110.5</v>
+        <v>106.5</v>
       </c>
       <c r="F7" t="n">
-        <v>31.92</v>
+        <v>32.22</v>
       </c>
       <c r="G7" t="n">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.91</v>
+        <v>-3.62</v>
       </c>
       <c r="M7" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>242</v>
+        <v>231.5</v>
       </c>
       <c r="F8" t="n">
-        <v>36.79</v>
+        <v>36.95</v>
       </c>
       <c r="G8" t="n">
-        <v>7.13</v>
+        <v>7.16</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.41</v>
+        <v>-4.34</v>
       </c>
       <c r="M8" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>96.3</v>
+        <v>101</v>
       </c>
       <c r="F9" t="n">
-        <v>24.14</v>
+        <v>24.44</v>
       </c>
       <c r="G9" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>4.88</v>
       </c>
       <c r="M9" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>157.5</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>19.11</v>
+        <v>18.93</v>
       </c>
       <c r="G10" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="M10" t="n">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1350</v>
       </c>
       <c r="F11" t="n">
-        <v>28.24</v>
+        <v>29.88</v>
       </c>
       <c r="G11" t="n">
-        <v>5.07</v>
+        <v>5.37</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.81</v>
+        <v>-1.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1290</v>
+        <v>1365</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>184.5</v>
+        <v>181.5</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>25.45</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.03</v>
+        <v>-1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>174</v>
+        <v>184.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>31.25</v>
+        <v>31.76</v>
       </c>
       <c r="G13" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>0.93</v>
       </c>
       <c r="M13" t="n">
-        <v>212.5</v>
+        <v>216</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,7 +1525,7 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
         <v>26.44</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M14" t="n">
         <v>133</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>244.5</v>
+        <v>245.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.06</v>
+        <v>22.29</v>
       </c>
       <c r="G15" t="n">
-        <v>5.41</v>
+        <v>5.47</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="M15" t="n">
-        <v>242</v>
+        <v>244.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4120</v>
+        <v>4185</v>
       </c>
       <c r="F16" t="n">
-        <v>120.94</v>
+        <v>123.95</v>
       </c>
       <c r="G16" t="n">
-        <v>36.94</v>
+        <v>37.86</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.49</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>4020</v>
+        <v>4120</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1430</v>
+        <v>1350</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>53.94</v>
       </c>
       <c r="G17" t="n">
-        <v>14.53</v>
+        <v>15.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.75</v>
+        <v>-5.59</v>
       </c>
       <c r="M17" t="n">
-        <v>1315</v>
+        <v>1430</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>8500</v>
+        <v>8655</v>
       </c>
       <c r="F18" t="n">
-        <v>70.47</v>
+        <v>74.92</v>
       </c>
       <c r="G18" t="n">
-        <v>24.17</v>
+        <v>25.69</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.32</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>7995</v>
+        <v>8500</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="F19" t="n">
-        <v>66.56999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2</v>
+        <v>13.42</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.93</v>
+        <v>-1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>79.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="F20" t="n">
-        <v>56.09</v>
+        <v>57.68</v>
       </c>
       <c r="G20" t="n">
-        <v>6.66</v>
+        <v>6.84</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.84</v>
+        <v>-2.39</v>
       </c>
       <c r="M20" t="n">
-        <v>77.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>7255</v>
+        <v>6735</v>
       </c>
       <c r="F21" t="n">
-        <v>144.26</v>
+        <v>148.67</v>
       </c>
       <c r="G21" t="n">
-        <v>39.05</v>
+        <v>40.24</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.05</v>
+        <v>-7.17</v>
       </c>
       <c r="M21" t="n">
-        <v>7040</v>
+        <v>7255</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1905</v>
+        <v>1990</v>
       </c>
       <c r="F22" t="n">
-        <v>57.4</v>
+        <v>60.08</v>
       </c>
       <c r="G22" t="n">
-        <v>27.8</v>
+        <v>29.1</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="M22" t="n">
-        <v>1820</v>
+        <v>1905</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="F23" t="n">
-        <v>37.11</v>
+        <v>39.42</v>
       </c>
       <c r="G23" t="n">
-        <v>5.5</v>
+        <v>5.84</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.23</v>
+        <v>-6.16</v>
       </c>
       <c r="M23" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2317,13 +2317,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1435</v>
+        <v>1295</v>
       </c>
       <c r="F24" t="n">
-        <v>100.79</v>
+        <v>103.68</v>
       </c>
       <c r="G24" t="n">
-        <v>22.31</v>
+        <v>22.95</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>-9.76</v>
       </c>
       <c r="M24" t="n">
-        <v>1395</v>
+        <v>1435</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>35.05</v>
+        <v>34.4</v>
       </c>
       <c r="F25" t="n">
-        <v>136.85</v>
+        <v>129.81</v>
       </c>
       <c r="G25" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-5.14</v>
+        <v>-1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>36.95</v>
+        <v>35.05</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>1755</v>
+        <v>1620</v>
       </c>
       <c r="F26" t="n">
-        <v>252.96</v>
+        <v>230.62</v>
       </c>
       <c r="G26" t="n">
-        <v>42.01</v>
+        <v>38.3</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-8.83</v>
+        <v>-7.69</v>
       </c>
       <c r="M26" t="n">
-        <v>1925</v>
+        <v>1755</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2558,13 +2558,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F27" t="n">
-        <v>59.52</v>
+        <v>63.42</v>
       </c>
       <c r="G27" t="n">
-        <v>8.02</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6.55</v>
+        <v>-0.15</v>
       </c>
       <c r="M27" t="n">
-        <v>641</v>
+        <v>683</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1320</v>
+        <v>1260</v>
       </c>
       <c r="F28" t="n">
-        <v>75.23999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>12.95</v>
+        <v>14.25</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>-4.55</v>
       </c>
       <c r="M28" t="n">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="F29" t="n">
-        <v>72.88</v>
+        <v>74.14</v>
       </c>
       <c r="G29" t="n">
-        <v>13.88</v>
+        <v>14.12</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.74</v>
+        <v>-4.39</v>
       </c>
       <c r="M29" t="n">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2799,13 +2799,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>2680</v>
       </c>
       <c r="F30" t="n">
-        <v>79.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>9.029999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.07</v>
+        <v>-4.63</v>
       </c>
       <c r="M30" t="n">
-        <v>2700</v>
+        <v>2810</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2883,10 +2883,10 @@
         <v>480</v>
       </c>
       <c r="F31" t="n">
-        <v>141.67</v>
+        <v>142.86</v>
       </c>
       <c r="G31" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2959,13 +2959,13 @@
         <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F32" t="n">
-        <v>36.5</v>
+        <v>39.38</v>
       </c>
       <c r="G32" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>7.88</v>
+        <v>-3.75</v>
       </c>
       <c r="M32" t="n">
-        <v>247.5</v>
+        <v>267</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3036,13 +3036,13 @@
         <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>481</v>
+        <v>439</v>
       </c>
       <c r="F33" t="n">
-        <v>40.11</v>
+        <v>43.06</v>
       </c>
       <c r="G33" t="n">
-        <v>7.2</v>
+        <v>7.73</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>7.37</v>
+        <v>-8.73</v>
       </c>
       <c r="M33" t="n">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3115,13 +3115,13 @@
         <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F34" t="n">
-        <v>41.04</v>
+        <v>41.35</v>
       </c>
       <c r="G34" t="n">
-        <v>9.26</v>
+        <v>9.33</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.76</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
@@ -3192,13 +3192,13 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>798</v>
+        <v>776</v>
       </c>
       <c r="F35" t="n">
-        <v>61.26</v>
+        <v>62.83</v>
       </c>
       <c r="G35" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.57</v>
+        <v>-2.76</v>
       </c>
       <c r="M35" t="n">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>180.5</v>
+        <v>172</v>
       </c>
       <c r="F36" t="n">
-        <v>48.81</v>
+        <v>53.56</v>
       </c>
       <c r="G36" t="n">
-        <v>6.35</v>
+        <v>6.96</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9.73</v>
+        <v>-4.71</v>
       </c>
       <c r="M36" t="n">
-        <v>164.5</v>
+        <v>180.5</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3352,13 +3352,13 @@
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>3740</v>
+        <v>3700</v>
       </c>
       <c r="F37" t="n">
-        <v>58.33</v>
+        <v>59.6</v>
       </c>
       <c r="G37" t="n">
-        <v>14.97</v>
+        <v>15.3</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.19</v>
+        <v>-1.07</v>
       </c>
       <c r="M37" t="n">
-        <v>3660</v>
+        <v>3740</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="F38" t="n">
-        <v>68.40000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="G38" t="n">
-        <v>16.09</v>
+        <v>16.39</v>
       </c>
       <c r="H38" t="n">
         <v>59.1</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.89</v>
+        <v>0.79</v>
       </c>
       <c r="M38" t="n">
-        <v>1855</v>
+        <v>1890</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3512,13 +3512,13 @@
         <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="F39" t="n">
-        <v>20.86</v>
+        <v>21.53</v>
       </c>
       <c r="G39" t="n">
-        <v>10.94</v>
+        <v>11.29</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>-7.98</v>
       </c>
       <c r="M39" t="n">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3595,13 +3595,13 @@
         <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>3280</v>
+        <v>3395</v>
       </c>
       <c r="F40" t="n">
-        <v>84.92</v>
+        <v>90.73</v>
       </c>
       <c r="G40" t="n">
-        <v>21.27</v>
+        <v>22.72</v>
       </c>
       <c r="H40" t="n">
         <v>70.2</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.84</v>
+        <v>3.51</v>
       </c>
       <c r="M40" t="n">
-        <v>3070</v>
+        <v>3280</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>5080</v>
+        <v>4990</v>
       </c>
       <c r="F41" t="n">
-        <v>107.81</v>
+        <v>110.2</v>
       </c>
       <c r="G41" t="n">
-        <v>37.14</v>
+        <v>37.97</v>
       </c>
       <c r="H41" t="n">
         <v>75.3</v>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.21</v>
+        <v>-1.77</v>
       </c>
       <c r="M41" t="n">
-        <v>4970</v>
+        <v>5080</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3753,13 +3753,13 @@
         <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="F42" t="n">
-        <v>47.56</v>
+        <v>48.73</v>
       </c>
       <c r="G42" t="n">
-        <v>26.53</v>
+        <v>27.19</v>
       </c>
       <c r="H42" t="n">
         <v>47.5</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.46</v>
+        <v>-2.54</v>
       </c>
       <c r="M42" t="n">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3836,13 +3836,13 @@
         <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>99.8</v>
+        <v>100.5</v>
       </c>
       <c r="F43" t="n">
-        <v>11.65</v>
+        <v>11.74</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H43" t="n">
         <v>11</v>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M43" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3915,13 +3915,13 @@
         <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F44" t="n">
-        <v>14.98</v>
+        <v>15.1</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="H44" t="n">
         <v>13.4</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.79</v>
+        <v>-1.05</v>
       </c>
       <c r="M44" t="n">
-        <v>189.5</v>
+        <v>191</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -3998,13 +3998,13 @@
         <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F45" t="n">
-        <v>15.71</v>
+        <v>15.78</v>
       </c>
       <c r="G45" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="H45" t="n">
         <v>16</v>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="M45" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -4077,13 +4077,13 @@
         <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F46" t="n">
-        <v>17.79</v>
+        <v>16.79</v>
       </c>
       <c r="G46" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="H46" t="n">
         <v>21.4</v>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-5.62</v>
+        <v>0.54</v>
       </c>
       <c r="M46" t="n">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4160,13 +4160,13 @@
         <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>209.5</v>
+        <v>204</v>
       </c>
       <c r="F47" t="n">
-        <v>30.55</v>
+        <v>31.22</v>
       </c>
       <c r="G47" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="H47" t="n">
         <v>30.9</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>-2.63</v>
       </c>
       <c r="M47" t="n">
-        <v>205</v>
+        <v>209.5</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4243,13 +4243,13 @@
         <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>3735</v>
+        <v>3770</v>
       </c>
       <c r="F48" t="n">
-        <v>54.59</v>
+        <v>54.74</v>
       </c>
       <c r="G48" t="n">
-        <v>7.04</v>
+        <v>7.06</v>
       </c>
       <c r="H48" t="n">
         <v>51.7</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>3725</v>
+        <v>3735</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4326,13 +4326,13 @@
         <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="F49" t="n">
-        <v>20.17</v>
+        <v>21.15</v>
       </c>
       <c r="G49" t="n">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.83</v>
+        <v>-1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4386,34 +4386,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E50" t="n">
-        <v>129.5</v>
+        <v>167</v>
       </c>
       <c r="F50" t="n">
-        <v>27.92</v>
+        <v>20.78</v>
       </c>
       <c r="G50" t="n">
-        <v>2.87</v>
+        <v>3.92</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>57.1</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>6.15</v>
+        <v>-2.34</v>
       </c>
       <c r="M50" t="n">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4434,24 +4434,24 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>10.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="S50" t="n">
-        <v>48.7</v>
+        <v>3.6</v>
       </c>
       <c r="T50" t="n">
-        <v>28.4</v>
+        <v>22</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4477,20 +4477,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E51" t="n">
-        <v>166.5</v>
+        <v>131.5</v>
       </c>
       <c r="F51" t="n">
-        <v>33.4</v>
+        <v>29.63</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8</v>
+        <v>3.04</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4499,40 +4499,36 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.78</v>
+        <v>1.54</v>
       </c>
       <c r="M51" t="n">
-        <v>162</v>
+        <v>129.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>5.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="R51" t="n">
-        <v>22.1</v>
+        <v>3.8</v>
       </c>
       <c r="S51" t="n">
-        <v>14.6</v>
+        <v>48.7</v>
       </c>
       <c r="T51" t="n">
-        <v>34.2</v>
+        <v>28.4</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4544,12 +4540,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4558,20 +4554,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>243</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>24.92</v>
+        <v>20.33</v>
       </c>
       <c r="G52" t="n">
-        <v>6.07</v>
+        <v>1.92</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>9.6</v>
+        <v>11.3</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4580,36 +4576,40 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>9.210000000000001</v>
+        <v>-3.03</v>
       </c>
       <c r="M52" t="n">
-        <v>222.5</v>
+        <v>99</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>30.7</v>
+        <v>9.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="R52" t="n">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>812.4</v>
+        <v>-2.7</v>
       </c>
       <c r="T52" t="n">
-        <v>34.6</v>
+        <v>20.3</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4621,34 +4621,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E53" t="n">
-        <v>753</v>
+        <v>167.5</v>
       </c>
       <c r="F53" t="n">
-        <v>27.14</v>
+        <v>34.33</v>
       </c>
       <c r="G53" t="n">
-        <v>8.6</v>
+        <v>1.85</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>12.4</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-0.13</v>
+        <v>0.6</v>
       </c>
       <c r="M53" t="n">
-        <v>754</v>
+        <v>166.5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4669,28 +4669,28 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>31.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="R53" t="n">
-        <v>3.8</v>
+        <v>22.1</v>
       </c>
       <c r="S53" t="n">
-        <v>21.9</v>
+        <v>14.6</v>
       </c>
       <c r="T53" t="n">
-        <v>32.2</v>
+        <v>34.2</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4702,34 +4702,34 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E54" t="n">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="F54" t="n">
-        <v>28.88</v>
+        <v>27.21</v>
       </c>
       <c r="G54" t="n">
-        <v>3.08</v>
+        <v>6.62</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>186.3</v>
+        <v>9.6</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -4738,40 +4738,36 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.72</v>
+        <v>-4.53</v>
       </c>
       <c r="M54" t="n">
-        <v>128.5</v>
+        <v>243</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>10.7</v>
+        <v>30.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="R54" t="n">
-        <v>-3.4</v>
+        <v>20.4</v>
       </c>
       <c r="S54" t="n">
-        <v>37</v>
+        <v>812.4</v>
       </c>
       <c r="T54" t="n">
-        <v>35.8</v>
+        <v>34.6</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -4783,12 +4779,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4797,20 +4793,20 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E55" t="n">
-        <v>4040</v>
+        <v>712</v>
       </c>
       <c r="F55" t="n">
-        <v>26.62</v>
+        <v>27.11</v>
       </c>
       <c r="G55" t="n">
-        <v>3.02</v>
+        <v>8.59</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -4819,10 +4815,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-5.28</v>
+        <v>-5.44</v>
       </c>
       <c r="M55" t="n">
-        <v>4265</v>
+        <v>753</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4831,23 +4827,23 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>11.4</v>
+        <v>31.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="R55" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="S55" t="n">
-        <v>41.8</v>
+        <v>21.9</v>
       </c>
       <c r="T55" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
@@ -4864,197 +4860,201 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>585</v>
+        <v>127</v>
       </c>
       <c r="F56" t="n">
-        <v>34.33</v>
+        <v>29.66</v>
       </c>
       <c r="G56" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>29.3</v>
-      </c>
+        <v>3.16</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.87</v>
-      </c>
+        <v>186.3</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>8.529999999999999</v>
+        <v>-3.79</v>
       </c>
       <c r="M56" t="n">
-        <v>539</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P56" t="n">
-        <v>19.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="R56" t="n">
-        <v>10.6</v>
+        <v>-3.4</v>
       </c>
       <c r="S56" t="n">
-        <v>64.90000000000001</v>
+        <v>37</v>
       </c>
       <c r="T56" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.87</v>
-      </c>
+        <v>35.8</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E57" t="n">
-        <v>842</v>
+        <v>4260</v>
       </c>
       <c r="F57" t="n">
-        <v>51.93</v>
+        <v>25.22</v>
       </c>
       <c r="G57" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="H57" t="n">
-        <v>46.1</v>
-      </c>
+        <v>2.86</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.97</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>9.92</v>
+        <v>5.45</v>
       </c>
       <c r="M57" t="n">
-        <v>766</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+        <v>4040</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P57" t="n">
-        <v>15.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="R57" t="n">
-        <v>24.8</v>
+        <v>6.8</v>
       </c>
       <c r="S57" t="n">
-        <v>1.5</v>
+        <v>41.8</v>
       </c>
       <c r="T57" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.97</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E58" t="n">
-        <v>67.7</v>
+        <v>590</v>
       </c>
       <c r="F58" t="n">
-        <v>16.5</v>
+        <v>37.26</v>
       </c>
       <c r="G58" t="n">
-        <v>2.82</v>
+        <v>7.38</v>
       </c>
       <c r="H58" t="n">
-        <v>17.3</v>
+        <v>29.3</v>
       </c>
       <c r="I58" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="J58" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5062,78 +5062,78 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="M58" t="n">
-        <v>67.3</v>
+        <v>585</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>11.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="R58" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="S58" t="n">
-        <v>768.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T58" t="n">
-        <v>19.4</v>
+        <v>34.7</v>
       </c>
       <c r="U58" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E59" t="n">
-        <v>163.5</v>
+        <v>830</v>
       </c>
       <c r="F59" t="n">
-        <v>15.3</v>
+        <v>57.08</v>
       </c>
       <c r="G59" t="n">
-        <v>1.66</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>15.5</v>
+        <v>46.1</v>
       </c>
       <c r="I59" t="n">
-        <v>8.6</v>
+        <v>30.6</v>
       </c>
       <c r="J59" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5141,108 +5141,110 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.62</v>
+        <v>-1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>162.5</v>
+        <v>842</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.03</v>
+        <v>1.83</v>
       </c>
       <c r="R59" t="n">
-        <v>30.2</v>
+        <v>24.8</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="T59" t="n">
-        <v>16.9</v>
+        <v>60.2</v>
       </c>
       <c r="U59" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E60" t="n">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="F60" t="n">
-        <v>19.93</v>
+        <v>16.59</v>
       </c>
       <c r="G60" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>2.84</v>
+      </c>
+      <c r="H60" t="n">
+        <v>17.3</v>
+      </c>
       <c r="I60" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.27</v>
+        <v>-1.03</v>
       </c>
       <c r="M60" t="n">
-        <v>164</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>67.7</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>18.6</v>
+        <v>11.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.74</v>
+        <v>1.15</v>
       </c>
       <c r="R60" t="n">
-        <v>11.1</v>
+        <v>4.4</v>
       </c>
       <c r="S60" t="n">
-        <v>3.6</v>
+        <v>768.2</v>
       </c>
       <c r="T60" t="n">
-        <v>22</v>
-      </c>
-      <c r="U60" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.64</v>
+      </c>
       <c r="V60" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -5250,19 +5252,19 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5271,79 +5273,77 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E61" t="n">
-        <v>20.65</v>
+        <v>164</v>
       </c>
       <c r="F61" t="n">
-        <v>16.75</v>
+        <v>15.4</v>
       </c>
       <c r="G61" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>1.67</v>
+      </c>
+      <c r="H61" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I61" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="M61" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>月營收轉負-5%</t>
-        </is>
-      </c>
+        <v>163.5</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.03</v>
+        <v>4.03</v>
       </c>
       <c r="R61" t="n">
-        <v>12.8</v>
+        <v>30.2</v>
       </c>
       <c r="S61" t="n">
-        <v>-5.3</v>
+        <v>10</v>
       </c>
       <c r="T61" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5355,17 +5355,17 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>99</v>
+        <v>20.65</v>
       </c>
       <c r="F62" t="n">
-        <v>19.08</v>
+        <v>16.79</v>
       </c>
       <c r="G62" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>92.90000000000001</v>
+        <v>20.65</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5386,28 +5386,28 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>月營收轉負-5%</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.99</v>
+        <v>1.03</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.7</v>
+        <v>-5.3</v>
       </c>
       <c r="T62" t="n">
-        <v>20.3</v>
+        <v>18.2</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5436,13 +5436,13 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>45.6</v>
+        <v>44.3</v>
       </c>
       <c r="F63" t="n">
-        <v>14.31</v>
+        <v>14.66</v>
       </c>
       <c r="G63" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.47</v>
+        <v>-2.85</v>
       </c>
       <c r="M63" t="n">
-        <v>44.5</v>
+        <v>45.6</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>196.5</v>
+        <v>190</v>
       </c>
       <c r="F64" t="n">
-        <v>18.03</v>
+        <v>17.85</v>
       </c>
       <c r="G64" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.01</v>
+        <v>-3.31</v>
       </c>
       <c r="M64" t="n">
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>704</v>
       </c>
       <c r="F65" t="n">
-        <v>17.61</v>
+        <v>17.44</v>
       </c>
       <c r="G65" t="n">
-        <v>16.64</v>
+        <v>16.48</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>49.6</v>
+        <v>49.05</v>
       </c>
       <c r="F66" t="n">
-        <v>18.52</v>
+        <v>18.86</v>
       </c>
       <c r="G66" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.85</v>
+        <v>-1.11</v>
       </c>
       <c r="M66" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5759,10 +5759,10 @@
         <v>157</v>
       </c>
       <c r="F67" t="n">
-        <v>16.92</v>
+        <v>17.03</v>
       </c>
       <c r="G67" t="n">
-        <v>4.98</v>
+        <v>5.01</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="F68" t="n">
-        <v>23.33</v>
+        <v>23.59</v>
       </c>
       <c r="G68" t="n">
-        <v>5.54</v>
+        <v>5.6</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.09</v>
+        <v>7.19</v>
       </c>
       <c r="M68" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="F69" t="n">
-        <v>17.46</v>
+        <v>17.6</v>
       </c>
       <c r="G69" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.82</v>
+        <v>-0.41</v>
       </c>
       <c r="M69" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>334.5</v>
+        <v>325.5</v>
       </c>
       <c r="F70" t="n">
-        <v>31.41</v>
+        <v>32.63</v>
       </c>
       <c r="G70" t="n">
-        <v>8.609999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.88</v>
+        <v>-2.69</v>
       </c>
       <c r="M70" t="n">
-        <v>322</v>
+        <v>334.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>19.2</v>
+        <v>19.37</v>
       </c>
       <c r="G71" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.88</v>
+        <v>0.43</v>
       </c>
       <c r="M71" t="n">
-        <v>91.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>158</v>
+        <v>156.5</v>
       </c>
       <c r="F72" t="n">
-        <v>19.85</v>
+        <v>21.56</v>
       </c>
       <c r="G72" t="n">
-        <v>5.42</v>
+        <v>5.88</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>8.59</v>
+        <v>-0.95</v>
       </c>
       <c r="M72" t="n">
-        <v>145.5</v>
+        <v>158</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>239</v>
+        <v>242.5</v>
       </c>
       <c r="F73" t="n">
-        <v>16.73</v>
+        <v>16.97</v>
       </c>
       <c r="G73" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="M73" t="n">
-        <v>235.5</v>
+        <v>239</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1105</v>
+        <v>1215</v>
       </c>
       <c r="F74" t="n">
-        <v>56.84</v>
+        <v>57.88</v>
       </c>
       <c r="G74" t="n">
-        <v>29.59</v>
+        <v>30.13</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.84</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M74" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="F75" t="n">
-        <v>24.22</v>
+        <v>23.23</v>
       </c>
       <c r="G75" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-4.08</v>
+        <v>-0.65</v>
       </c>
       <c r="M75" t="n">
-        <v>63.7</v>
+        <v>61.1</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2165</v>
+        <v>2225</v>
       </c>
       <c r="F76" t="n">
-        <v>34.83</v>
+        <v>35.57</v>
       </c>
       <c r="G76" t="n">
-        <v>18.43</v>
+        <v>18.82</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.12</v>
+        <v>2.77</v>
       </c>
       <c r="M76" t="n">
-        <v>2120</v>
+        <v>2165</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="F77" t="n">
-        <v>23.15</v>
+        <v>24.84</v>
       </c>
       <c r="G77" t="n">
-        <v>8.970000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>7.31</v>
+        <v>-3.02</v>
       </c>
       <c r="M77" t="n">
-        <v>834</v>
+        <v>895</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2440</v>
+        <v>2470</v>
       </c>
       <c r="F78" t="n">
-        <v>32.54</v>
+        <v>32.8</v>
       </c>
       <c r="G78" t="n">
-        <v>10.65</v>
+        <v>10.74</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="M78" t="n">
-        <v>2420</v>
+        <v>2440</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="F79" t="n">
-        <v>14.93</v>
+        <v>15.15</v>
       </c>
       <c r="G79" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M79" t="n">
-        <v>101.5</v>
+        <v>103</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>117</v>
+        <v>114.5</v>
       </c>
       <c r="F80" t="n">
-        <v>15.63</v>
+        <v>15.83</v>
       </c>
       <c r="G80" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.3</v>
+        <v>-2.14</v>
       </c>
       <c r="M80" t="n">
-        <v>115.5</v>
+        <v>117</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6872,13 +6872,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>28.65</v>
+        <v>28.45</v>
       </c>
       <c r="F81" t="n">
-        <v>5.67</v>
+        <v>5.74</v>
       </c>
       <c r="G81" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="M81" t="n">
-        <v>28.3</v>
+        <v>28.65</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="F82" t="n">
-        <v>12.18</v>
+        <v>12.07</v>
       </c>
       <c r="G82" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.88</v>
+        <v>0.45</v>
       </c>
       <c r="M82" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>177</v>
+        <v>178.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.03</v>
+        <v>13.14</v>
       </c>
       <c r="G83" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7056,7 +7056,7 @@
         <v>0.85</v>
       </c>
       <c r="M83" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>42.15</v>
+        <v>41.9</v>
       </c>
       <c r="F84" t="n">
-        <v>7.74</v>
+        <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.31</v>
+        <v>-0.59</v>
       </c>
       <c r="M84" t="n">
-        <v>40.8</v>
+        <v>42.15</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F85" t="n">
-        <v>32.91</v>
+        <v>33.95</v>
       </c>
       <c r="G85" t="n">
-        <v>11.03</v>
+        <v>11.37</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="M85" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F86" t="n">
-        <v>20.48</v>
+        <v>20.7</v>
       </c>
       <c r="G86" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.07</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M86" t="n">
-        <v>421.5</v>
+        <v>426</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F87" t="n">
-        <v>16.3</v>
+        <v>16.97</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.12</v>
+        <v>-2.88</v>
       </c>
       <c r="M87" t="n">
-        <v>133.5</v>
+        <v>139</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
       <c r="F88" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.58</v>
+        <v>-0.78</v>
       </c>
       <c r="M88" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="F89" t="n">
-        <v>43.12</v>
+        <v>44.25</v>
       </c>
       <c r="G89" t="n">
-        <v>19.51</v>
+        <v>20.02</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.63</v>
+        <v>-0.85</v>
       </c>
       <c r="M89" t="n">
-        <v>2280</v>
+        <v>2340</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="F90" t="n">
-        <v>24.94</v>
+        <v>25.86</v>
       </c>
       <c r="G90" t="n">
-        <v>5.99</v>
+        <v>6.21</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.7</v>
+        <v>0.67</v>
       </c>
       <c r="M90" t="n">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>88.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F91" t="n">
-        <v>10.52</v>
+        <v>10.56</v>
       </c>
       <c r="G91" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.46</v>
+        <v>1.36</v>
       </c>
       <c r="M91" t="n">
-        <v>87.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>7.73</v>
+        <v>7.86</v>
       </c>
       <c r="G92" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
       <c r="M92" t="n">
-        <v>71.5</v>
+        <v>72.7</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>60.9</v>
+        <v>59.7</v>
       </c>
       <c r="F93" t="n">
-        <v>11.15</v>
+        <v>11.32</v>
       </c>
       <c r="G93" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.5</v>
+        <v>-1.97</v>
       </c>
       <c r="M93" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="F94" t="n">
-        <v>19.11</v>
+        <v>19.16</v>
       </c>
       <c r="G94" t="n">
-        <v>7.06</v>
+        <v>7.08</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.26</v>
+        <v>-7.61</v>
       </c>
       <c r="M94" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5095</v>
+        <v>5115</v>
       </c>
       <c r="F95" t="n">
-        <v>16.44</v>
+        <v>17.08</v>
       </c>
       <c r="G95" t="n">
-        <v>6.5</v>
+        <v>6.76</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.87</v>
+        <v>0.39</v>
       </c>
       <c r="M95" t="n">
-        <v>4905</v>
+        <v>5095</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F96" t="n">
-        <v>14.29</v>
+        <v>14.59</v>
       </c>
       <c r="G96" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M96" t="n">
-        <v>142.5</v>
+        <v>145.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8171,10 +8171,10 @@
         <v>1515</v>
       </c>
       <c r="F97" t="n">
-        <v>18.71</v>
+        <v>18.59</v>
       </c>
       <c r="G97" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>67.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="G98" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.74</v>
+        <v>-2.06</v>
       </c>
       <c r="M98" t="n">
-        <v>67.3</v>
+        <v>67.8</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>408</v>
+        <v>400.5</v>
       </c>
       <c r="F99" t="n">
-        <v>8.050000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="G99" t="n">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.24</v>
+        <v>-1.84</v>
       </c>
       <c r="M99" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>181.5</v>
+        <v>187.5</v>
       </c>
       <c r="F101" t="n">
-        <v>8.460000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="G101" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.61</v>
+        <v>3.31</v>
       </c>
       <c r="M101" t="n">
-        <v>173.5</v>
+        <v>181.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2165</v>
+        <v>2225</v>
       </c>
       <c r="F2" t="n">
-        <v>34.83</v>
+        <v>35.57</v>
       </c>
       <c r="G2" t="n">
-        <v>18.43</v>
+        <v>18.82</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.12</v>
+        <v>2.77</v>
       </c>
       <c r="M2" t="n">
-        <v>2120</v>
+        <v>2165</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="F3" t="n">
-        <v>23.15</v>
+        <v>24.84</v>
       </c>
       <c r="G3" t="n">
-        <v>8.970000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.31</v>
+        <v>-3.02</v>
       </c>
       <c r="M3" t="n">
-        <v>834</v>
+        <v>895</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2440</v>
+        <v>2470</v>
       </c>
       <c r="F4" t="n">
-        <v>32.54</v>
+        <v>32.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.65</v>
+        <v>10.74</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
-        <v>2420</v>
+        <v>2440</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="F5" t="n">
-        <v>14.93</v>
+        <v>15.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>101.5</v>
+        <v>103</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>114.5</v>
       </c>
       <c r="F6" t="n">
-        <v>15.63</v>
+        <v>15.83</v>
       </c>
       <c r="G6" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>-2.14</v>
       </c>
       <c r="M6" t="n">
-        <v>115.5</v>
+        <v>117</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>28.65</v>
+        <v>28.45</v>
       </c>
       <c r="F7" t="n">
-        <v>5.67</v>
+        <v>5.74</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>28.3</v>
+        <v>28.65</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.18</v>
+        <v>12.07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.88</v>
+        <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>177</v>
+        <v>178.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03</v>
+        <v>13.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9281,7 +9281,7 @@
         <v>0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.15</v>
+        <v>41.9</v>
       </c>
       <c r="F10" t="n">
-        <v>7.74</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.31</v>
+        <v>-0.59</v>
       </c>
       <c r="M10" t="n">
-        <v>40.8</v>
+        <v>42.15</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="F11" t="n">
-        <v>32.91</v>
+        <v>33.95</v>
       </c>
       <c r="G11" t="n">
-        <v>11.03</v>
+        <v>11.37</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="M11" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F12" t="n">
-        <v>20.48</v>
+        <v>20.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.07</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>421.5</v>
+        <v>426</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F13" t="n">
-        <v>16.3</v>
+        <v>16.97</v>
       </c>
       <c r="G13" t="n">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.12</v>
+        <v>-2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>133.5</v>
+        <v>139</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
       <c r="F14" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>-0.78</v>
       </c>
       <c r="M14" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="F15" t="n">
-        <v>43.12</v>
+        <v>44.25</v>
       </c>
       <c r="G15" t="n">
-        <v>19.51</v>
+        <v>20.02</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>-0.85</v>
       </c>
       <c r="M15" t="n">
-        <v>2280</v>
+        <v>2340</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="F16" t="n">
-        <v>24.94</v>
+        <v>25.86</v>
       </c>
       <c r="G16" t="n">
-        <v>5.99</v>
+        <v>6.21</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.7</v>
+        <v>0.67</v>
       </c>
       <c r="M16" t="n">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F17" t="n">
-        <v>10.52</v>
+        <v>10.56</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.46</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
-        <v>87.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>7.73</v>
+        <v>7.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
       <c r="M18" t="n">
-        <v>71.5</v>
+        <v>72.7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>60.9</v>
+        <v>59.7</v>
       </c>
       <c r="F19" t="n">
-        <v>11.15</v>
+        <v>11.32</v>
       </c>
       <c r="G19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>-1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="F20" t="n">
-        <v>19.11</v>
+        <v>19.16</v>
       </c>
       <c r="G20" t="n">
-        <v>7.06</v>
+        <v>7.08</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.26</v>
+        <v>-7.61</v>
       </c>
       <c r="M20" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5095</v>
+        <v>5115</v>
       </c>
       <c r="F21" t="n">
-        <v>16.44</v>
+        <v>17.08</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>6.76</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.87</v>
+        <v>0.39</v>
       </c>
       <c r="M21" t="n">
-        <v>4905</v>
+        <v>5095</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.29</v>
+        <v>14.59</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>142.5</v>
+        <v>145.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10396,10 +10396,10 @@
         <v>1515</v>
       </c>
       <c r="F23" t="n">
-        <v>18.71</v>
+        <v>18.59</v>
       </c>
       <c r="G23" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>157</v>
       </c>
       <c r="F2" t="n">
-        <v>16.92</v>
+        <v>17.03</v>
       </c>
       <c r="G2" t="n">
-        <v>4.98</v>
+        <v>5.01</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="F3" t="n">
-        <v>23.33</v>
+        <v>23.59</v>
       </c>
       <c r="G3" t="n">
-        <v>5.54</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.09</v>
+        <v>7.19</v>
       </c>
       <c r="M3" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46</v>
+        <v>17.6</v>
       </c>
       <c r="G4" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.82</v>
+        <v>-0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>334.5</v>
+        <v>325.5</v>
       </c>
       <c r="F5" t="n">
-        <v>31.41</v>
+        <v>32.63</v>
       </c>
       <c r="G5" t="n">
-        <v>8.609999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.88</v>
+        <v>-2.69</v>
       </c>
       <c r="M5" t="n">
-        <v>322</v>
+        <v>334.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>19.2</v>
+        <v>19.37</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.88</v>
+        <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>91.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>158</v>
+        <v>156.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.85</v>
+        <v>21.56</v>
       </c>
       <c r="G7" t="n">
-        <v>5.42</v>
+        <v>5.88</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.59</v>
+        <v>-0.95</v>
       </c>
       <c r="M7" t="n">
-        <v>145.5</v>
+        <v>158</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>239</v>
+        <v>242.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.73</v>
+        <v>16.97</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>235.5</v>
+        <v>239</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1105</v>
+        <v>1215</v>
       </c>
       <c r="F9" t="n">
-        <v>56.84</v>
+        <v>57.88</v>
       </c>
       <c r="G9" t="n">
-        <v>29.59</v>
+        <v>30.13</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.84</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="F10" t="n">
-        <v>24.22</v>
+        <v>23.23</v>
       </c>
       <c r="G10" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-4.08</v>
+        <v>-0.65</v>
       </c>
       <c r="M10" t="n">
-        <v>63.7</v>
+        <v>61.1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1185</v>
+        <v>1125</v>
       </c>
       <c r="F2" t="n">
-        <v>83.81</v>
+        <v>84.52</v>
       </c>
       <c r="G2" t="n">
-        <v>23.53</v>
+        <v>23.73</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.85</v>
+        <v>-5.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11541,10 +11541,10 @@
         <v>39.55</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12</v>
+        <v>11.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.35</v>
+        <v>39.55</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F4" t="n">
-        <v>17.51</v>
+        <v>17.57</v>
       </c>
       <c r="G4" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>6.58</v>
       </c>
       <c r="M4" t="n">
-        <v>151.5</v>
+        <v>152</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6330</v>
+        <v>6220</v>
       </c>
       <c r="F5" t="n">
-        <v>168.8</v>
+        <v>168.53</v>
       </c>
       <c r="G5" t="n">
-        <v>39.43</v>
+        <v>39.37</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.16</v>
+        <v>-1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,7 +11779,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="F6" t="n">
         <v>22.11</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>109</v>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>110.5</v>
+        <v>106.5</v>
       </c>
       <c r="F7" t="n">
-        <v>31.92</v>
+        <v>32.22</v>
       </c>
       <c r="G7" t="n">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.91</v>
+        <v>-3.62</v>
       </c>
       <c r="M7" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>242</v>
+        <v>231.5</v>
       </c>
       <c r="F8" t="n">
-        <v>36.79</v>
+        <v>36.95</v>
       </c>
       <c r="G8" t="n">
-        <v>7.13</v>
+        <v>7.16</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.41</v>
+        <v>-4.34</v>
       </c>
       <c r="M8" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>96.3</v>
+        <v>101</v>
       </c>
       <c r="F9" t="n">
-        <v>24.14</v>
+        <v>24.44</v>
       </c>
       <c r="G9" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>4.88</v>
       </c>
       <c r="M9" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>157.5</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>19.11</v>
+        <v>18.93</v>
       </c>
       <c r="G10" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="M10" t="n">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1350</v>
       </c>
       <c r="F11" t="n">
-        <v>28.24</v>
+        <v>29.88</v>
       </c>
       <c r="G11" t="n">
-        <v>5.07</v>
+        <v>5.37</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.81</v>
+        <v>-1.1</v>
       </c>
       <c r="M11" t="n">
-        <v>1290</v>
+        <v>1365</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>184.5</v>
+        <v>181.5</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>25.45</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.03</v>
+        <v>-1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>174</v>
+        <v>184.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>31.25</v>
+        <v>31.76</v>
       </c>
       <c r="G13" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>0.93</v>
       </c>
       <c r="M13" t="n">
-        <v>212.5</v>
+        <v>216</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,7 +12427,7 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
         <v>26.44</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M14" t="n">
         <v>133</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>244.5</v>
+        <v>245.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.06</v>
+        <v>22.29</v>
       </c>
       <c r="G15" t="n">
-        <v>5.41</v>
+        <v>5.47</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="M15" t="n">
-        <v>242</v>
+        <v>244.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4120</v>
+        <v>4185</v>
       </c>
       <c r="F16" t="n">
-        <v>120.94</v>
+        <v>123.95</v>
       </c>
       <c r="G16" t="n">
-        <v>36.94</v>
+        <v>37.86</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.49</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>4020</v>
+        <v>4120</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="F2" t="n">
-        <v>68.40000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="G2" t="n">
-        <v>16.09</v>
+        <v>16.39</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>0.79</v>
       </c>
       <c r="M2" t="n">
-        <v>1855</v>
+        <v>1890</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="F3" t="n">
-        <v>20.86</v>
+        <v>21.53</v>
       </c>
       <c r="G3" t="n">
-        <v>10.94</v>
+        <v>11.29</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>-7.98</v>
       </c>
       <c r="M3" t="n">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3280</v>
+        <v>3395</v>
       </c>
       <c r="F4" t="n">
-        <v>84.92</v>
+        <v>90.73</v>
       </c>
       <c r="G4" t="n">
-        <v>21.27</v>
+        <v>22.72</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.84</v>
+        <v>3.51</v>
       </c>
       <c r="M4" t="n">
-        <v>3070</v>
+        <v>3280</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5080</v>
+        <v>4990</v>
       </c>
       <c r="F5" t="n">
-        <v>107.81</v>
+        <v>110.2</v>
       </c>
       <c r="G5" t="n">
-        <v>37.14</v>
+        <v>37.97</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>-1.77</v>
       </c>
       <c r="M5" t="n">
-        <v>4970</v>
+        <v>5080</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="F6" t="n">
-        <v>47.56</v>
+        <v>48.73</v>
       </c>
       <c r="G6" t="n">
-        <v>26.53</v>
+        <v>27.19</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.46</v>
+        <v>-2.54</v>
       </c>
       <c r="M6" t="n">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>99.8</v>
+        <v>100.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.65</v>
+        <v>11.74</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F8" t="n">
-        <v>14.98</v>
+        <v>15.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.79</v>
+        <v>-1.05</v>
       </c>
       <c r="M8" t="n">
-        <v>189.5</v>
+        <v>191</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>15.71</v>
+        <v>15.78</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F10" t="n">
-        <v>17.79</v>
+        <v>16.79</v>
       </c>
       <c r="G10" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-5.62</v>
+        <v>0.54</v>
       </c>
       <c r="M10" t="n">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>209.5</v>
+        <v>204</v>
       </c>
       <c r="F11" t="n">
-        <v>30.55</v>
+        <v>31.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>-2.63</v>
       </c>
       <c r="M11" t="n">
-        <v>205</v>
+        <v>209.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3735</v>
+        <v>3770</v>
       </c>
       <c r="F12" t="n">
-        <v>54.59</v>
+        <v>54.74</v>
       </c>
       <c r="G12" t="n">
-        <v>7.04</v>
+        <v>7.06</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>3725</v>
+        <v>3735</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1125</v>
+        <v>1015</v>
       </c>
       <c r="F2" t="n">
-        <v>84.52</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>23.73</v>
+        <v>22.53</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.06</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1185</v>
+        <v>1125</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,7 +636,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.55</v>
+        <v>39.1</v>
       </c>
       <c r="F3" t="n">
         <v>11.17</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="M3" t="n">
         <v>39.55</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>162</v>
+        <v>168.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.57</v>
+        <v>18.73</v>
       </c>
       <c r="G4" t="n">
-        <v>3.87</v>
+        <v>4.13</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.58</v>
+        <v>4.01</v>
       </c>
       <c r="M4" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6220</v>
+        <v>5600</v>
       </c>
       <c r="F5" t="n">
-        <v>168.53</v>
+        <v>165.6</v>
       </c>
       <c r="G5" t="n">
-        <v>39.37</v>
+        <v>38.68</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.74</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>6330</v>
+        <v>6220</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>22.11</v>
+        <v>22.41</v>
       </c>
       <c r="G6" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>106.5</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>32.22</v>
+        <v>31.05</v>
       </c>
       <c r="G7" t="n">
-        <v>4.58</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.62</v>
+        <v>-3.76</v>
       </c>
       <c r="M7" t="n">
-        <v>110.5</v>
+        <v>106.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>231.5</v>
+        <v>216.5</v>
       </c>
       <c r="F8" t="n">
-        <v>36.95</v>
+        <v>35.34</v>
       </c>
       <c r="G8" t="n">
-        <v>7.16</v>
+        <v>6.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-4.34</v>
+        <v>-6.48</v>
       </c>
       <c r="M8" t="n">
-        <v>242</v>
+        <v>231.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>24.44</v>
+        <v>25.63</v>
       </c>
       <c r="G9" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.88</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>96.3</v>
+        <v>101</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F10" t="n">
-        <v>18.93</v>
+        <v>18.99</v>
       </c>
       <c r="G10" t="n">
-        <v>5.2</v>
+        <v>5.22</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.32</v>
+        <v>-3.8</v>
       </c>
       <c r="M10" t="n">
-        <v>157.5</v>
+        <v>158</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1350</v>
+        <v>1265</v>
       </c>
       <c r="F11" t="n">
-        <v>29.88</v>
+        <v>29.55</v>
       </c>
       <c r="G11" t="n">
-        <v>5.37</v>
+        <v>5.31</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.1</v>
+        <v>-6.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1365</v>
+        <v>1350</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>181.5</v>
+        <v>174.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25.45</v>
+        <v>25.03</v>
       </c>
       <c r="G12" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.63</v>
+        <v>-3.86</v>
       </c>
       <c r="M12" t="n">
-        <v>184.5</v>
+        <v>181.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>196.5</v>
       </c>
       <c r="F13" t="n">
-        <v>31.76</v>
+        <v>32.06</v>
       </c>
       <c r="G13" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.93</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>26.44</v>
+        <v>27.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>245.5</v>
+        <v>243</v>
       </c>
       <c r="F15" t="n">
-        <v>22.29</v>
+        <v>22.38</v>
       </c>
       <c r="G15" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.41</v>
+        <v>-1.02</v>
       </c>
       <c r="M15" t="n">
-        <v>244.5</v>
+        <v>245.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4185</v>
+        <v>3835</v>
       </c>
       <c r="F16" t="n">
-        <v>123.95</v>
+        <v>125.9</v>
       </c>
       <c r="G16" t="n">
-        <v>37.86</v>
+        <v>38.45</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4120</v>
+        <v>4185</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="F17" t="n">
-        <v>53.94</v>
+        <v>50.92</v>
       </c>
       <c r="G17" t="n">
-        <v>15.8</v>
+        <v>14.92</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-5.59</v>
+        <v>-3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>1430</v>
+        <v>1350</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>8655</v>
+        <v>7890</v>
       </c>
       <c r="F18" t="n">
-        <v>74.92</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>25.69</v>
+        <v>26.16</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>-8.84</v>
       </c>
       <c r="M18" t="n">
-        <v>8500</v>
+        <v>8655</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>728</v>
+        <v>656</v>
       </c>
       <c r="F19" t="n">
-        <v>73.18000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>13.42</v>
+        <v>13.16</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.89</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>77.7</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
-        <v>57.68</v>
+        <v>56.3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.84</v>
+        <v>6.68</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.39</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>79.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6735</v>
+        <v>6055</v>
       </c>
       <c r="F21" t="n">
-        <v>148.67</v>
+        <v>138.01</v>
       </c>
       <c r="G21" t="n">
-        <v>40.24</v>
+        <v>37.36</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-7.17</v>
+        <v>-10.1</v>
       </c>
       <c r="M21" t="n">
-        <v>7255</v>
+        <v>6735</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1990</v>
+        <v>1850</v>
       </c>
       <c r="F22" t="n">
-        <v>60.08</v>
+        <v>62.76</v>
       </c>
       <c r="G22" t="n">
-        <v>29.1</v>
+        <v>30.4</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.46</v>
+        <v>-7.04</v>
       </c>
       <c r="M22" t="n">
-        <v>1905</v>
+        <v>1990</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="F23" t="n">
-        <v>39.42</v>
+        <v>36.99</v>
       </c>
       <c r="G23" t="n">
-        <v>5.84</v>
+        <v>5.48</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-6.16</v>
+        <v>-10</v>
       </c>
       <c r="M23" t="n">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2317,13 +2317,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1295</v>
+        <v>1170</v>
       </c>
       <c r="F24" t="n">
-        <v>103.68</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>22.95</v>
+        <v>20.71</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-9.76</v>
+        <v>-9.65</v>
       </c>
       <c r="M24" t="n">
-        <v>1435</v>
+        <v>1295</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>34.4</v>
+        <v>32.15</v>
       </c>
       <c r="F25" t="n">
-        <v>129.81</v>
+        <v>127.41</v>
       </c>
       <c r="G25" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-1.85</v>
+        <v>-6.54</v>
       </c>
       <c r="M25" t="n">
-        <v>35.05</v>
+        <v>34.4</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2479,13 +2479,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>1620</v>
+        <v>1480</v>
       </c>
       <c r="F26" t="n">
-        <v>230.62</v>
+        <v>212.88</v>
       </c>
       <c r="G26" t="n">
-        <v>38.3</v>
+        <v>35.36</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-7.69</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>1755</v>
+        <v>1620</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2558,13 +2558,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>682</v>
+        <v>614</v>
       </c>
       <c r="F27" t="n">
-        <v>63.42</v>
+        <v>63.32</v>
       </c>
       <c r="G27" t="n">
-        <v>8.550000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-0.15</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1260</v>
+        <v>1195</v>
       </c>
       <c r="F28" t="n">
-        <v>82.76000000000001</v>
+        <v>79</v>
       </c>
       <c r="G28" t="n">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-4.55</v>
+        <v>-5.16</v>
       </c>
       <c r="M28" t="n">
-        <v>1320</v>
+        <v>1260</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="F29" t="n">
-        <v>74.14</v>
+        <v>70.89</v>
       </c>
       <c r="G29" t="n">
-        <v>14.12</v>
+        <v>13.5</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-4.39</v>
+        <v>-9.18</v>
       </c>
       <c r="M29" t="n">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2799,13 +2799,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>2680</v>
+        <v>2585</v>
       </c>
       <c r="F30" t="n">
-        <v>82.43000000000001</v>
+        <v>78.62</v>
       </c>
       <c r="G30" t="n">
-        <v>9.4</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-4.63</v>
+        <v>-3.54</v>
       </c>
       <c r="M30" t="n">
-        <v>2810</v>
+        <v>2680</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="F31" t="n">
         <v>142.86</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M31" t="n">
         <v>480</v>
@@ -2959,13 +2959,13 @@
         <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>257</v>
+        <v>234.5</v>
       </c>
       <c r="F32" t="n">
-        <v>39.38</v>
+        <v>37.91</v>
       </c>
       <c r="G32" t="n">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-3.75</v>
+        <v>-8.75</v>
       </c>
       <c r="M32" t="n">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3036,13 +3036,13 @@
         <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>439</v>
+        <v>395.5</v>
       </c>
       <c r="F33" t="n">
-        <v>43.06</v>
+        <v>39.3</v>
       </c>
       <c r="G33" t="n">
-        <v>7.73</v>
+        <v>7.05</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-8.73</v>
+        <v>-9.91</v>
       </c>
       <c r="M33" t="n">
-        <v>481</v>
+        <v>439</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3115,13 +3115,13 @@
         <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="F34" t="n">
-        <v>41.35</v>
+        <v>41.12</v>
       </c>
       <c r="G34" t="n">
-        <v>9.33</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-3.21</v>
       </c>
       <c r="M34" t="n">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
@@ -3192,13 +3192,13 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>776</v>
+        <v>699</v>
       </c>
       <c r="F35" t="n">
-        <v>62.83</v>
+        <v>61.1</v>
       </c>
       <c r="G35" t="n">
-        <v>9.83</v>
+        <v>9.56</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-2.76</v>
+        <v>-9.92</v>
       </c>
       <c r="M35" t="n">
-        <v>798</v>
+        <v>776</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         <v>56</v>
       </c>
       <c r="E36" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="F36" t="n">
-        <v>53.56</v>
+        <v>51.04</v>
       </c>
       <c r="G36" t="n">
-        <v>6.96</v>
+        <v>6.64</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-4.71</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>180.5</v>
+        <v>172</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3352,13 +3352,13 @@
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>3700</v>
+        <v>3370</v>
       </c>
       <c r="F37" t="n">
-        <v>59.6</v>
+        <v>58.96</v>
       </c>
       <c r="G37" t="n">
-        <v>15.3</v>
+        <v>15.13</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1.07</v>
+        <v>-8.92</v>
       </c>
       <c r="M37" t="n">
-        <v>3740</v>
+        <v>3700</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>1905</v>
+        <v>1740</v>
       </c>
       <c r="F38" t="n">
-        <v>69.69</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>16.39</v>
+        <v>16.52</v>
       </c>
       <c r="H38" t="n">
         <v>59.1</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.79</v>
+        <v>-8.66</v>
       </c>
       <c r="M38" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3512,13 +3512,13 @@
         <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="F39" t="n">
-        <v>21.53</v>
+        <v>19.81</v>
       </c>
       <c r="G39" t="n">
-        <v>11.29</v>
+        <v>10.39</v>
       </c>
       <c r="H39" t="n">
         <v>19</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-7.98</v>
+        <v>-1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3595,13 +3595,13 @@
         <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>3395</v>
+        <v>3210</v>
       </c>
       <c r="F40" t="n">
-        <v>90.73</v>
+        <v>93.91</v>
       </c>
       <c r="G40" t="n">
-        <v>22.72</v>
+        <v>23.52</v>
       </c>
       <c r="H40" t="n">
         <v>70.2</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.51</v>
+        <v>-5.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3280</v>
+        <v>3395</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
         <v>90</v>
       </c>
       <c r="E41" t="n">
-        <v>4990</v>
+        <v>4495</v>
       </c>
       <c r="F41" t="n">
-        <v>110.2</v>
+        <v>108.24</v>
       </c>
       <c r="G41" t="n">
-        <v>37.97</v>
+        <v>37.29</v>
       </c>
       <c r="H41" t="n">
         <v>75.3</v>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-1.77</v>
+        <v>-9.92</v>
       </c>
       <c r="M41" t="n">
-        <v>5080</v>
+        <v>4990</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3753,13 +3753,13 @@
         <v>89</v>
       </c>
       <c r="E42" t="n">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="F42" t="n">
-        <v>48.73</v>
+        <v>47.49</v>
       </c>
       <c r="G42" t="n">
-        <v>27.19</v>
+        <v>26.5</v>
       </c>
       <c r="H42" t="n">
         <v>47.5</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-2.54</v>
+        <v>-5.21</v>
       </c>
       <c r="M42" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3836,13 +3836,13 @@
         <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>100.5</v>
+        <v>98.5</v>
       </c>
       <c r="F43" t="n">
-        <v>11.74</v>
+        <v>11.82</v>
       </c>
       <c r="G43" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H43" t="n">
         <v>11</v>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.7</v>
+        <v>-1.99</v>
       </c>
       <c r="M43" t="n">
-        <v>99.8</v>
+        <v>100.5</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3915,13 +3915,13 @@
         <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>189</v>
+        <v>181.5</v>
       </c>
       <c r="F44" t="n">
-        <v>15.1</v>
+        <v>14.94</v>
       </c>
       <c r="G44" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="H44" t="n">
         <v>13.4</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1.05</v>
+        <v>-3.97</v>
       </c>
       <c r="M44" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -3998,13 +3998,13 @@
         <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F45" t="n">
-        <v>15.78</v>
+        <v>15.93</v>
       </c>
       <c r="G45" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="H45" t="n">
         <v>16</v>
@@ -4024,7 +4024,7 @@
         <v>0.93</v>
       </c>
       <c r="M45" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -4077,13 +4077,13 @@
         <v>69</v>
       </c>
       <c r="E46" t="n">
-        <v>557</v>
+        <v>519</v>
       </c>
       <c r="F46" t="n">
-        <v>16.79</v>
+        <v>16.88</v>
       </c>
       <c r="G46" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="H46" t="n">
         <v>21.4</v>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.54</v>
+        <v>-6.82</v>
       </c>
       <c r="M46" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4160,13 +4160,13 @@
         <v>65</v>
       </c>
       <c r="E47" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F47" t="n">
-        <v>31.22</v>
+        <v>30.4</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="H47" t="n">
         <v>30.9</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-2.63</v>
+        <v>-4.9</v>
       </c>
       <c r="M47" t="n">
-        <v>209.5</v>
+        <v>204</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4243,13 +4243,13 @@
         <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>3770</v>
+        <v>3480</v>
       </c>
       <c r="F48" t="n">
-        <v>54.74</v>
+        <v>55.25</v>
       </c>
       <c r="G48" t="n">
-        <v>7.06</v>
+        <v>7.12</v>
       </c>
       <c r="H48" t="n">
         <v>51.7</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.9399999999999999</v>
+        <v>-7.69</v>
       </c>
       <c r="M48" t="n">
-        <v>3735</v>
+        <v>3770</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4326,13 +4326,13 @@
         <v>96</v>
       </c>
       <c r="E49" t="n">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="F49" t="n">
-        <v>21.15</v>
+        <v>20.77</v>
       </c>
       <c r="G49" t="n">
-        <v>6.26</v>
+        <v>6.15</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1.79</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4403,13 +4403,13 @@
         <v>94</v>
       </c>
       <c r="E50" t="n">
-        <v>167</v>
+        <v>158.5</v>
       </c>
       <c r="F50" t="n">
-        <v>20.78</v>
+        <v>20.29</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92</v>
+        <v>3.83</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-2.34</v>
+        <v>-5.09</v>
       </c>
       <c r="M50" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4480,13 +4480,13 @@
         <v>78</v>
       </c>
       <c r="E51" t="n">
-        <v>131.5</v>
+        <v>118.5</v>
       </c>
       <c r="F51" t="n">
-        <v>29.63</v>
+        <v>30.09</v>
       </c>
       <c r="G51" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.54</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>129.5</v>
+        <v>131.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4540,12 +4540,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4554,20 +4554,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E52" t="n">
-        <v>96</v>
+        <v>158.5</v>
       </c>
       <c r="F52" t="n">
-        <v>20.33</v>
+        <v>34.54</v>
       </c>
       <c r="G52" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-3.03</v>
+        <v>-5.37</v>
       </c>
       <c r="M52" t="n">
-        <v>99</v>
+        <v>167.5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4588,23 +4588,23 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S52" t="n">
-        <v>-2.7</v>
+        <v>14.6</v>
       </c>
       <c r="T52" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4635,20 +4635,20 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E53" t="n">
-        <v>167.5</v>
+        <v>217</v>
       </c>
       <c r="F53" t="n">
-        <v>34.33</v>
+        <v>25.98</v>
       </c>
       <c r="G53" t="n">
-        <v>1.85</v>
+        <v>6.32</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4657,40 +4657,36 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.6</v>
+        <v>-6.47</v>
       </c>
       <c r="M53" t="n">
-        <v>166.5</v>
+        <v>232</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R53" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S53" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T53" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4702,34 +4698,34 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E54" t="n">
-        <v>232</v>
+        <v>718</v>
       </c>
       <c r="F54" t="n">
-        <v>27.21</v>
+        <v>25.63</v>
       </c>
       <c r="G54" t="n">
-        <v>6.62</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -4738,31 +4734,35 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-4.53</v>
+        <v>0.84</v>
       </c>
       <c r="M54" t="n">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P54" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R54" t="n">
-        <v>20.4</v>
+        <v>3.8</v>
       </c>
       <c r="S54" t="n">
-        <v>812.4</v>
+        <v>21.9</v>
       </c>
       <c r="T54" t="n">
-        <v>34.6</v>
+        <v>32.2</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4793,20 +4793,20 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>712</v>
+        <v>118.5</v>
       </c>
       <c r="F55" t="n">
-        <v>27.11</v>
+        <v>28.54</v>
       </c>
       <c r="G55" t="n">
-        <v>8.59</v>
+        <v>3.04</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-5.44</v>
+        <v>-6.69</v>
       </c>
       <c r="M55" t="n">
-        <v>753</v>
+        <v>127</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4827,28 +4827,28 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R55" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S55" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T55" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4860,12 +4860,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4874,20 +4874,20 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E56" t="n">
-        <v>127</v>
+        <v>4010</v>
       </c>
       <c r="F56" t="n">
-        <v>29.66</v>
+        <v>26.59</v>
       </c>
       <c r="G56" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>186.3</v>
+        <v>9</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-3.79</v>
+        <v>-5.87</v>
       </c>
       <c r="M56" t="n">
-        <v>132</v>
+        <v>4260</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4908,28 +4908,28 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.4</v>
+        <v>6.8</v>
       </c>
       <c r="S56" t="n">
-        <v>37</v>
+        <v>41.8</v>
       </c>
       <c r="T56" t="n">
-        <v>35.8</v>
+        <v>32.9</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -4941,73 +4941,71 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E57" t="n">
-        <v>4260</v>
+        <v>542</v>
       </c>
       <c r="F57" t="n">
-        <v>25.22</v>
+        <v>37.58</v>
       </c>
       <c r="G57" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>7.44</v>
+      </c>
+      <c r="H57" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I57" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5.45</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>4040</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="R57" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="S57" t="n">
-        <v>41.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T57" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="U57" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -5015,19 +5013,19 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5036,25 +5034,25 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E58" t="n">
-        <v>590</v>
+        <v>747</v>
       </c>
       <c r="F58" t="n">
-        <v>37.26</v>
+        <v>56.27</v>
       </c>
       <c r="G58" t="n">
-        <v>7.38</v>
+        <v>8.73</v>
       </c>
       <c r="H58" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I58" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J58" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5062,78 +5060,78 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.85</v>
+        <v>-10</v>
       </c>
       <c r="M58" t="n">
-        <v>585</v>
+        <v>830</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R58" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S58" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T58" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E59" t="n">
-        <v>830</v>
+        <v>65.5</v>
       </c>
       <c r="F59" t="n">
-        <v>57.08</v>
+        <v>16.42</v>
       </c>
       <c r="G59" t="n">
-        <v>8.859999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="H59" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I59" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J59" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5141,30 +5139,30 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1.43</v>
+        <v>-2.24</v>
       </c>
       <c r="M59" t="n">
-        <v>842</v>
+        <v>67</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R59" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S59" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T59" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U59" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -5173,19 +5171,19 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5194,25 +5192,25 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>67</v>
+        <v>159.5</v>
       </c>
       <c r="F60" t="n">
-        <v>16.59</v>
+        <v>15.44</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84</v>
+        <v>1.68</v>
       </c>
       <c r="H60" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I60" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J60" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5220,34 +5218,34 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1.03</v>
+        <v>-2.74</v>
       </c>
       <c r="M60" t="n">
-        <v>67.7</v>
+        <v>164</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R60" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S60" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T60" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U60" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5259,12 +5257,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5273,77 +5271,79 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>164</v>
+        <v>19.8</v>
       </c>
       <c r="F61" t="n">
-        <v>15.4</v>
+        <v>16.79</v>
       </c>
       <c r="G61" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H61" t="n">
-        <v>15.5</v>
-      </c>
+        <v>1.72</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.95</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.31</v>
+        <v>-4.12</v>
       </c>
       <c r="M61" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+        <v>20.65</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>月營收轉負-5%</t>
+        </is>
+      </c>
       <c r="P61" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.03</v>
+        <v>1.03</v>
       </c>
       <c r="R61" t="n">
-        <v>30.2</v>
+        <v>12.8</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>-5.3</v>
       </c>
       <c r="T61" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.95</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5355,17 +5355,17 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>20.65</v>
+        <v>88.7</v>
       </c>
       <c r="F62" t="n">
-        <v>16.79</v>
+        <v>19.71</v>
       </c>
       <c r="G62" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>13.7</v>
+        <v>11.3</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5374,40 +5374,40 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="M62" t="n">
+        <v>96</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="M62" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>月營收轉負-5%</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R62" t="n">
-        <v>12.8</v>
-      </c>
       <c r="S62" t="n">
-        <v>-5.3</v>
+        <v>-2.7</v>
       </c>
       <c r="T62" t="n">
-        <v>18.2</v>
+        <v>20.3</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5436,13 +5436,13 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>44.3</v>
+        <v>42.3</v>
       </c>
       <c r="F63" t="n">
-        <v>14.66</v>
+        <v>14.24</v>
       </c>
       <c r="G63" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-2.85</v>
+        <v>-4.51</v>
       </c>
       <c r="M63" t="n">
-        <v>45.6</v>
+        <v>44.3</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F64" t="n">
-        <v>17.85</v>
+        <v>17.26</v>
       </c>
       <c r="G64" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-3.31</v>
+        <v>-6.32</v>
       </c>
       <c r="M64" t="n">
-        <v>196.5</v>
+        <v>190</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="F65" t="n">
         <v>17.44</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
       <c r="M65" t="n">
         <v>704</v>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>49.05</v>
+        <v>47.35</v>
       </c>
       <c r="F66" t="n">
-        <v>18.86</v>
+        <v>18.65</v>
       </c>
       <c r="G66" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1.11</v>
+        <v>-3.47</v>
       </c>
       <c r="M66" t="n">
-        <v>49.6</v>
+        <v>49.05</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F67" t="n">
         <v>17.03</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M67" t="n">
         <v>157</v>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="F68" t="n">
-        <v>23.59</v>
+        <v>25.29</v>
       </c>
       <c r="G68" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>7.19</v>
+        <v>-5.7</v>
       </c>
       <c r="M68" t="n">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         <v>122</v>
       </c>
       <c r="F69" t="n">
-        <v>17.6</v>
+        <v>17.53</v>
       </c>
       <c r="G69" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>325.5</v>
+        <v>304.5</v>
       </c>
       <c r="F70" t="n">
-        <v>32.63</v>
+        <v>31.76</v>
       </c>
       <c r="G70" t="n">
-        <v>8.949999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-2.69</v>
+        <v>-6.45</v>
       </c>
       <c r="M70" t="n">
-        <v>334.5</v>
+        <v>325.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>92.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>19.37</v>
+        <v>19.45</v>
       </c>
       <c r="G71" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.43</v>
+        <v>-1.62</v>
       </c>
       <c r="M71" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>156.5</v>
+        <v>145.5</v>
       </c>
       <c r="F72" t="n">
-        <v>21.56</v>
+        <v>21.35</v>
       </c>
       <c r="G72" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-0.95</v>
+        <v>-7.03</v>
       </c>
       <c r="M72" t="n">
-        <v>158</v>
+        <v>156.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>242.5</v>
+        <v>234</v>
       </c>
       <c r="F73" t="n">
-        <v>16.97</v>
+        <v>17.22</v>
       </c>
       <c r="G73" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.46</v>
+        <v>-3.51</v>
       </c>
       <c r="M73" t="n">
-        <v>239</v>
+        <v>242.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1215</v>
+        <v>1120</v>
       </c>
       <c r="F74" t="n">
-        <v>57.88</v>
+        <v>63.65</v>
       </c>
       <c r="G74" t="n">
-        <v>30.13</v>
+        <v>33.13</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>9.949999999999999</v>
+        <v>-7.82</v>
       </c>
       <c r="M74" t="n">
-        <v>1105</v>
+        <v>1215</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>60.7</v>
+        <v>58.5</v>
       </c>
       <c r="F75" t="n">
-        <v>23.23</v>
+        <v>23.08</v>
       </c>
       <c r="G75" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-0.65</v>
+        <v>-3.62</v>
       </c>
       <c r="M75" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="F76" t="n">
-        <v>35.57</v>
+        <v>36.56</v>
       </c>
       <c r="G76" t="n">
-        <v>18.82</v>
+        <v>19.34</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.77</v>
+        <v>-1.12</v>
       </c>
       <c r="M76" t="n">
-        <v>2165</v>
+        <v>2225</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>868</v>
+        <v>799</v>
       </c>
       <c r="F77" t="n">
-        <v>24.84</v>
+        <v>24.09</v>
       </c>
       <c r="G77" t="n">
-        <v>9.630000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-3.02</v>
+        <v>-7.95</v>
       </c>
       <c r="M77" t="n">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2470</v>
+        <v>2290</v>
       </c>
       <c r="F78" t="n">
-        <v>32.8</v>
+        <v>33.21</v>
       </c>
       <c r="G78" t="n">
-        <v>10.74</v>
+        <v>10.87</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.23</v>
+        <v>-7.29</v>
       </c>
       <c r="M78" t="n">
-        <v>2440</v>
+        <v>2470</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>104.5</v>
+        <v>102.5</v>
       </c>
       <c r="F79" t="n">
-        <v>15.15</v>
+        <v>15.37</v>
       </c>
       <c r="G79" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.46</v>
+        <v>-1.91</v>
       </c>
       <c r="M79" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>114.5</v>
+        <v>106</v>
       </c>
       <c r="F80" t="n">
-        <v>15.83</v>
+        <v>15.49</v>
       </c>
       <c r="G80" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-2.14</v>
+        <v>-7.42</v>
       </c>
       <c r="M80" t="n">
-        <v>117</v>
+        <v>114.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6872,13 +6872,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>28.45</v>
+        <v>28</v>
       </c>
       <c r="F81" t="n">
-        <v>5.74</v>
+        <v>5.7</v>
       </c>
       <c r="G81" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.7</v>
+        <v>-1.58</v>
       </c>
       <c r="M81" t="n">
-        <v>28.65</v>
+        <v>28.45</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>112.5</v>
+        <v>110.5</v>
       </c>
       <c r="F82" t="n">
-        <v>12.07</v>
+        <v>12.12</v>
       </c>
       <c r="G82" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.45</v>
+        <v>-1.78</v>
       </c>
       <c r="M82" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>178.5</v>
+        <v>175</v>
       </c>
       <c r="F83" t="n">
-        <v>13.14</v>
+        <v>13.25</v>
       </c>
       <c r="G83" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.85</v>
+        <v>-1.96</v>
       </c>
       <c r="M83" t="n">
-        <v>177</v>
+        <v>178.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="F84" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="G84" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.59</v>
+        <v>-1.67</v>
       </c>
       <c r="M84" t="n">
-        <v>42.15</v>
+        <v>41.9</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1175</v>
+        <v>1095</v>
       </c>
       <c r="F85" t="n">
-        <v>33.95</v>
+        <v>34.84</v>
       </c>
       <c r="G85" t="n">
-        <v>11.37</v>
+        <v>11.67</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.62</v>
+        <v>-6.81</v>
       </c>
       <c r="M85" t="n">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>422</v>
+        <v>397.5</v>
       </c>
       <c r="F86" t="n">
-        <v>20.7</v>
+        <v>20.51</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-5.81</v>
       </c>
       <c r="M86" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F87" t="n">
-        <v>16.97</v>
+        <v>16.48</v>
       </c>
       <c r="G87" t="n">
-        <v>3.51</v>
+        <v>3.41</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-2.88</v>
+        <v>-5.93</v>
       </c>
       <c r="M87" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>38.2</v>
+        <v>37.35</v>
       </c>
       <c r="F88" t="n">
-        <v>8.460000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G88" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-0.78</v>
+        <v>-2.23</v>
       </c>
       <c r="M88" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2320</v>
+        <v>2090</v>
       </c>
       <c r="F89" t="n">
-        <v>44.25</v>
+        <v>43.87</v>
       </c>
       <c r="G89" t="n">
-        <v>20.02</v>
+        <v>19.85</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.85</v>
+        <v>-9.91</v>
       </c>
       <c r="M89" t="n">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="F90" t="n">
-        <v>25.86</v>
+        <v>26.03</v>
       </c>
       <c r="G90" t="n">
-        <v>6.21</v>
+        <v>6.25</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="M90" t="n">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="F91" t="n">
-        <v>10.56</v>
+        <v>10.71</v>
       </c>
       <c r="G91" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.36</v>
+        <v>-3.14</v>
       </c>
       <c r="M91" t="n">
-        <v>88.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>72.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F92" t="n">
-        <v>7.86</v>
+        <v>7.79</v>
       </c>
       <c r="G92" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.83</v>
+        <v>-3.61</v>
       </c>
       <c r="M92" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>59.7</v>
+        <v>57</v>
       </c>
       <c r="F93" t="n">
-        <v>11.32</v>
+        <v>11.1</v>
       </c>
       <c r="G93" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.97</v>
+        <v>-4.52</v>
       </c>
       <c r="M93" t="n">
-        <v>60.9</v>
+        <v>59.7</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>352</v>
+        <v>325.5</v>
       </c>
       <c r="F94" t="n">
-        <v>19.16</v>
+        <v>17.7</v>
       </c>
       <c r="G94" t="n">
-        <v>7.08</v>
+        <v>6.54</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-7.61</v>
+        <v>-7.53</v>
       </c>
       <c r="M94" t="n">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5115</v>
+        <v>4620</v>
       </c>
       <c r="F95" t="n">
-        <v>17.08</v>
+        <v>17.15</v>
       </c>
       <c r="G95" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.39</v>
+        <v>-9.68</v>
       </c>
       <c r="M95" t="n">
-        <v>5095</v>
+        <v>5115</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>146.5</v>
+        <v>139</v>
       </c>
       <c r="F96" t="n">
-        <v>14.59</v>
+        <v>14.69</v>
       </c>
       <c r="G96" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.6899999999999999</v>
+        <v>-5.12</v>
       </c>
       <c r="M96" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,7 +8168,7 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1515</v>
+        <v>1435</v>
       </c>
       <c r="F97" t="n">
         <v>18.59</v>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-5.28</v>
       </c>
       <c r="M97" t="n">
         <v>1515</v>
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>66.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>5.64</v>
+        <v>5.52</v>
       </c>
       <c r="G98" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-2.06</v>
+        <v>2.26</v>
       </c>
       <c r="M98" t="n">
-        <v>67.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>400.5</v>
+        <v>366.5</v>
       </c>
       <c r="F99" t="n">
-        <v>8.15</v>
+        <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.84</v>
+        <v>-8.49</v>
       </c>
       <c r="M99" t="n">
-        <v>408</v>
+        <v>400.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="F100" t="n">
         <v>3.96</v>
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="M100" t="n">
         <v>23.9</v>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>187.5</v>
+        <v>190</v>
       </c>
       <c r="F101" t="n">
-        <v>8.85</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G101" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.31</v>
+        <v>1.33</v>
       </c>
       <c r="M101" t="n">
-        <v>181.5</v>
+        <v>187.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="F2" t="n">
-        <v>35.57</v>
+        <v>36.56</v>
       </c>
       <c r="G2" t="n">
-        <v>18.82</v>
+        <v>19.34</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.77</v>
+        <v>-1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>2165</v>
+        <v>2225</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>868</v>
+        <v>799</v>
       </c>
       <c r="F3" t="n">
-        <v>24.84</v>
+        <v>24.09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.630000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-3.02</v>
+        <v>-7.95</v>
       </c>
       <c r="M3" t="n">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2470</v>
+        <v>2290</v>
       </c>
       <c r="F4" t="n">
-        <v>32.8</v>
+        <v>33.21</v>
       </c>
       <c r="G4" t="n">
-        <v>10.74</v>
+        <v>10.87</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>-7.29</v>
       </c>
       <c r="M4" t="n">
-        <v>2440</v>
+        <v>2470</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>104.5</v>
+        <v>102.5</v>
       </c>
       <c r="F5" t="n">
-        <v>15.15</v>
+        <v>15.37</v>
       </c>
       <c r="G5" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>-1.91</v>
       </c>
       <c r="M5" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>114.5</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
-        <v>15.83</v>
+        <v>15.49</v>
       </c>
       <c r="G6" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-2.14</v>
+        <v>-7.42</v>
       </c>
       <c r="M6" t="n">
-        <v>117</v>
+        <v>114.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>28.45</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>5.74</v>
+        <v>5.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.7</v>
+        <v>-1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>28.65</v>
+        <v>28.45</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>112.5</v>
+        <v>110.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.07</v>
+        <v>12.12</v>
       </c>
       <c r="G8" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.45</v>
+        <v>-1.78</v>
       </c>
       <c r="M8" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>178.5</v>
+        <v>175</v>
       </c>
       <c r="F9" t="n">
-        <v>13.14</v>
+        <v>13.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.85</v>
+        <v>-1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>177</v>
+        <v>178.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.59</v>
+        <v>-1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>42.15</v>
+        <v>41.9</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1175</v>
+        <v>1095</v>
       </c>
       <c r="F11" t="n">
-        <v>33.95</v>
+        <v>34.84</v>
       </c>
       <c r="G11" t="n">
-        <v>11.37</v>
+        <v>11.67</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.62</v>
+        <v>-6.81</v>
       </c>
       <c r="M11" t="n">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>422</v>
+        <v>397.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.7</v>
+        <v>20.51</v>
       </c>
       <c r="G12" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-5.81</v>
       </c>
       <c r="M12" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>16.97</v>
+        <v>16.48</v>
       </c>
       <c r="G13" t="n">
-        <v>3.51</v>
+        <v>3.41</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-2.88</v>
+        <v>-5.93</v>
       </c>
       <c r="M13" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.2</v>
+        <v>37.35</v>
       </c>
       <c r="F14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.78</v>
+        <v>-2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2320</v>
+        <v>2090</v>
       </c>
       <c r="F15" t="n">
-        <v>44.25</v>
+        <v>43.87</v>
       </c>
       <c r="G15" t="n">
-        <v>20.02</v>
+        <v>19.85</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.85</v>
+        <v>-9.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="F16" t="n">
-        <v>25.86</v>
+        <v>26.03</v>
       </c>
       <c r="G16" t="n">
-        <v>6.21</v>
+        <v>6.25</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="F17" t="n">
-        <v>10.56</v>
+        <v>10.71</v>
       </c>
       <c r="G17" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>-3.14</v>
       </c>
       <c r="M17" t="n">
-        <v>88.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>72.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F18" t="n">
-        <v>7.86</v>
+        <v>7.79</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.83</v>
+        <v>-3.61</v>
       </c>
       <c r="M18" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>59.7</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>11.32</v>
+        <v>11.1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.97</v>
+        <v>-4.52</v>
       </c>
       <c r="M19" t="n">
-        <v>60.9</v>
+        <v>59.7</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>352</v>
+        <v>325.5</v>
       </c>
       <c r="F20" t="n">
-        <v>19.16</v>
+        <v>17.7</v>
       </c>
       <c r="G20" t="n">
-        <v>7.08</v>
+        <v>6.54</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-7.61</v>
+        <v>-7.53</v>
       </c>
       <c r="M20" t="n">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5115</v>
+        <v>4620</v>
       </c>
       <c r="F21" t="n">
-        <v>17.08</v>
+        <v>17.15</v>
       </c>
       <c r="G21" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.39</v>
+        <v>-9.68</v>
       </c>
       <c r="M21" t="n">
-        <v>5095</v>
+        <v>5115</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>146.5</v>
+        <v>139</v>
       </c>
       <c r="F22" t="n">
-        <v>14.59</v>
+        <v>14.69</v>
       </c>
       <c r="G22" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.6899999999999999</v>
+        <v>-5.12</v>
       </c>
       <c r="M22" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,7 +10393,7 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1515</v>
+        <v>1435</v>
       </c>
       <c r="F23" t="n">
         <v>18.59</v>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-5.28</v>
       </c>
       <c r="M23" t="n">
         <v>1515</v>
@@ -10607,7 +10607,7 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F2" t="n">
         <v>17.03</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M2" t="n">
         <v>157</v>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="F3" t="n">
-        <v>23.59</v>
+        <v>25.29</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.19</v>
+        <v>-5.7</v>
       </c>
       <c r="M3" t="n">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10768,10 +10768,10 @@
         <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>17.6</v>
+        <v>17.53</v>
       </c>
       <c r="G4" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>325.5</v>
+        <v>304.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32.63</v>
+        <v>31.76</v>
       </c>
       <c r="G5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.69</v>
+        <v>-6.45</v>
       </c>
       <c r="M5" t="n">
-        <v>334.5</v>
+        <v>325.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>92.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>19.37</v>
+        <v>19.45</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.43</v>
+        <v>-1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>156.5</v>
+        <v>145.5</v>
       </c>
       <c r="F7" t="n">
-        <v>21.56</v>
+        <v>21.35</v>
       </c>
       <c r="G7" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.95</v>
+        <v>-7.03</v>
       </c>
       <c r="M7" t="n">
-        <v>158</v>
+        <v>156.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>242.5</v>
+        <v>234</v>
       </c>
       <c r="F8" t="n">
-        <v>16.97</v>
+        <v>17.22</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>-3.51</v>
       </c>
       <c r="M8" t="n">
-        <v>239</v>
+        <v>242.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1215</v>
+        <v>1120</v>
       </c>
       <c r="F9" t="n">
-        <v>57.88</v>
+        <v>63.65</v>
       </c>
       <c r="G9" t="n">
-        <v>30.13</v>
+        <v>33.13</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9.949999999999999</v>
+        <v>-7.82</v>
       </c>
       <c r="M9" t="n">
-        <v>1105</v>
+        <v>1215</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>60.7</v>
+        <v>58.5</v>
       </c>
       <c r="F10" t="n">
-        <v>23.23</v>
+        <v>23.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.65</v>
+        <v>-3.62</v>
       </c>
       <c r="M10" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1125</v>
+        <v>1015</v>
       </c>
       <c r="F2" t="n">
-        <v>84.52</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>23.73</v>
+        <v>22.53</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.06</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1185</v>
+        <v>1125</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,7 +11538,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.55</v>
+        <v>39.1</v>
       </c>
       <c r="F3" t="n">
         <v>11.17</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="M3" t="n">
         <v>39.55</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>162</v>
+        <v>168.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.57</v>
+        <v>18.73</v>
       </c>
       <c r="G4" t="n">
-        <v>3.87</v>
+        <v>4.13</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.58</v>
+        <v>4.01</v>
       </c>
       <c r="M4" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6220</v>
+        <v>5600</v>
       </c>
       <c r="F5" t="n">
-        <v>168.53</v>
+        <v>165.6</v>
       </c>
       <c r="G5" t="n">
-        <v>39.37</v>
+        <v>38.68</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.74</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>6330</v>
+        <v>6220</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>22.11</v>
+        <v>22.41</v>
       </c>
       <c r="G6" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>106.5</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>32.22</v>
+        <v>31.05</v>
       </c>
       <c r="G7" t="n">
-        <v>4.58</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.62</v>
+        <v>-3.76</v>
       </c>
       <c r="M7" t="n">
-        <v>110.5</v>
+        <v>106.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>231.5</v>
+        <v>216.5</v>
       </c>
       <c r="F8" t="n">
-        <v>36.95</v>
+        <v>35.34</v>
       </c>
       <c r="G8" t="n">
-        <v>7.16</v>
+        <v>6.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-4.34</v>
+        <v>-6.48</v>
       </c>
       <c r="M8" t="n">
-        <v>242</v>
+        <v>231.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>24.44</v>
+        <v>25.63</v>
       </c>
       <c r="G9" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.88</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>96.3</v>
+        <v>101</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F10" t="n">
-        <v>18.93</v>
+        <v>18.99</v>
       </c>
       <c r="G10" t="n">
-        <v>5.2</v>
+        <v>5.22</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.32</v>
+        <v>-3.8</v>
       </c>
       <c r="M10" t="n">
-        <v>157.5</v>
+        <v>158</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1350</v>
+        <v>1265</v>
       </c>
       <c r="F11" t="n">
-        <v>29.88</v>
+        <v>29.55</v>
       </c>
       <c r="G11" t="n">
-        <v>5.37</v>
+        <v>5.31</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.1</v>
+        <v>-6.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1365</v>
+        <v>1350</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>181.5</v>
+        <v>174.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25.45</v>
+        <v>25.03</v>
       </c>
       <c r="G12" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.63</v>
+        <v>-3.86</v>
       </c>
       <c r="M12" t="n">
-        <v>184.5</v>
+        <v>181.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>196.5</v>
       </c>
       <c r="F13" t="n">
-        <v>31.76</v>
+        <v>32.06</v>
       </c>
       <c r="G13" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.93</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>26.44</v>
+        <v>27.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>245.5</v>
+        <v>243</v>
       </c>
       <c r="F15" t="n">
-        <v>22.29</v>
+        <v>22.38</v>
       </c>
       <c r="G15" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.41</v>
+        <v>-1.02</v>
       </c>
       <c r="M15" t="n">
-        <v>244.5</v>
+        <v>245.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4185</v>
+        <v>3835</v>
       </c>
       <c r="F16" t="n">
-        <v>123.95</v>
+        <v>125.9</v>
       </c>
       <c r="G16" t="n">
-        <v>37.86</v>
+        <v>38.45</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4120</v>
+        <v>4185</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1905</v>
+        <v>1740</v>
       </c>
       <c r="F2" t="n">
-        <v>69.69</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>16.39</v>
+        <v>16.52</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.79</v>
+        <v>-8.66</v>
       </c>
       <c r="M2" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="F3" t="n">
-        <v>21.53</v>
+        <v>19.81</v>
       </c>
       <c r="G3" t="n">
-        <v>11.29</v>
+        <v>10.39</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-7.98</v>
+        <v>-1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3395</v>
+        <v>3210</v>
       </c>
       <c r="F4" t="n">
-        <v>90.73</v>
+        <v>93.91</v>
       </c>
       <c r="G4" t="n">
-        <v>22.72</v>
+        <v>23.52</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.51</v>
+        <v>-5.45</v>
       </c>
       <c r="M4" t="n">
-        <v>3280</v>
+        <v>3395</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4990</v>
+        <v>4495</v>
       </c>
       <c r="F5" t="n">
-        <v>110.2</v>
+        <v>108.24</v>
       </c>
       <c r="G5" t="n">
-        <v>37.97</v>
+        <v>37.29</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.77</v>
+        <v>-9.92</v>
       </c>
       <c r="M5" t="n">
-        <v>5080</v>
+        <v>4990</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="F6" t="n">
-        <v>48.73</v>
+        <v>47.49</v>
       </c>
       <c r="G6" t="n">
-        <v>27.19</v>
+        <v>26.5</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-2.54</v>
+        <v>-5.21</v>
       </c>
       <c r="M6" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>100.5</v>
+        <v>98.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.74</v>
+        <v>11.82</v>
       </c>
       <c r="G7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>-1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8</v>
+        <v>100.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>189</v>
+        <v>181.5</v>
       </c>
       <c r="F8" t="n">
-        <v>15.1</v>
+        <v>14.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.05</v>
+        <v>-3.97</v>
       </c>
       <c r="M8" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F9" t="n">
-        <v>15.78</v>
+        <v>15.93</v>
       </c>
       <c r="G9" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13394,7 +13394,7 @@
         <v>0.93</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>557</v>
+        <v>519</v>
       </c>
       <c r="F10" t="n">
-        <v>16.79</v>
+        <v>16.88</v>
       </c>
       <c r="G10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.54</v>
+        <v>-6.82</v>
       </c>
       <c r="M10" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F11" t="n">
-        <v>31.22</v>
+        <v>30.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.63</v>
+        <v>-4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>209.5</v>
+        <v>204</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3770</v>
+        <v>3480</v>
       </c>
       <c r="F12" t="n">
-        <v>54.74</v>
+        <v>55.25</v>
       </c>
       <c r="G12" t="n">
-        <v>7.06</v>
+        <v>7.12</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.9399999999999999</v>
+        <v>-7.69</v>
       </c>
       <c r="M12" t="n">
-        <v>3735</v>
+        <v>3770</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1015</v>
+        <v>971</v>
       </c>
       <c r="F2" t="n">
-        <v>80.23999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22.53</v>
+        <v>20.32</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-4.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1125</v>
+        <v>1015</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -639,10 +639,10 @@
         <v>39.1</v>
       </c>
       <c r="F3" t="n">
-        <v>11.17</v>
+        <v>11.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.55</v>
+        <v>39.1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>168.5</v>
+        <v>159.5</v>
       </c>
       <c r="F4" t="n">
-        <v>18.73</v>
+        <v>19.48</v>
       </c>
       <c r="G4" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.01</v>
+        <v>-5.34</v>
       </c>
       <c r="M4" t="n">
-        <v>162</v>
+        <v>168.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5600</v>
+        <v>5455</v>
       </c>
       <c r="F5" t="n">
-        <v>165.6</v>
+        <v>149.09</v>
       </c>
       <c r="G5" t="n">
-        <v>38.68</v>
+        <v>34.83</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-9.970000000000001</v>
+        <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>6220</v>
+        <v>5600</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>22.41</v>
+        <v>22.52</v>
       </c>
       <c r="G6" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="M6" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>31.05</v>
+        <v>29.88</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.25</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.76</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>106.5</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>216.5</v>
+        <v>208</v>
       </c>
       <c r="F8" t="n">
-        <v>35.34</v>
+        <v>33.05</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85</v>
+        <v>6.41</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-6.48</v>
+        <v>-3.93</v>
       </c>
       <c r="M8" t="n">
-        <v>231.5</v>
+        <v>216.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.63</v>
+        <v>26.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F10" t="n">
-        <v>18.99</v>
+        <v>18.27</v>
       </c>
       <c r="G10" t="n">
-        <v>5.22</v>
+        <v>5.02</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.8</v>
+        <v>-1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1265</v>
+        <v>1335</v>
       </c>
       <c r="F11" t="n">
-        <v>29.55</v>
+        <v>27.69</v>
       </c>
       <c r="G11" t="n">
-        <v>5.31</v>
+        <v>4.98</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-6.3</v>
+        <v>5.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1350</v>
+        <v>1265</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174.5</v>
+        <v>167.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25.03</v>
+        <v>24.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-3.86</v>
+        <v>-4.01</v>
       </c>
       <c r="M12" t="n">
-        <v>181.5</v>
+        <v>174.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>196.5</v>
+        <v>193.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.06</v>
+        <v>28.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.61</v>
+        <v>5.06</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-9.859999999999999</v>
+        <v>-1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>218</v>
+        <v>196.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>27.04</v>
+        <v>27.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>0.72</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>243</v>
+        <v>243.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.38</v>
+        <v>22.15</v>
       </c>
       <c r="G15" t="n">
-        <v>5.49</v>
+        <v>5.44</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.02</v>
+        <v>0.21</v>
       </c>
       <c r="M15" t="n">
-        <v>245.5</v>
+        <v>243</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>3835</v>
+        <v>3745</v>
       </c>
       <c r="F16" t="n">
-        <v>125.9</v>
+        <v>115.37</v>
       </c>
       <c r="G16" t="n">
-        <v>38.45</v>
+        <v>35.24</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-8.359999999999999</v>
+        <v>-2.35</v>
       </c>
       <c r="M16" t="n">
-        <v>4185</v>
+        <v>3835</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="F17" t="n">
-        <v>50.92</v>
+        <v>49.04</v>
       </c>
       <c r="G17" t="n">
-        <v>14.92</v>
+        <v>14.36</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.7</v>
+        <v>-6.15</v>
       </c>
       <c r="M17" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7890</v>
+        <v>7750</v>
       </c>
       <c r="F18" t="n">
-        <v>76.29000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="G18" t="n">
-        <v>26.16</v>
+        <v>23.85</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-8.84</v>
+        <v>-1.77</v>
       </c>
       <c r="M18" t="n">
-        <v>8655</v>
+        <v>7890</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="F19" t="n">
-        <v>71.79000000000001</v>
+        <v>64.69</v>
       </c>
       <c r="G19" t="n">
-        <v>13.16</v>
+        <v>11.86</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-9.890000000000001</v>
+        <v>-1.37</v>
       </c>
       <c r="M19" t="n">
-        <v>728</v>
+        <v>656</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>56.3</v>
+        <v>51.45</v>
       </c>
       <c r="G20" t="n">
-        <v>6.68</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-8.619999999999999</v>
+        <v>-2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>77.7</v>
+        <v>71</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6055</v>
+        <v>6050</v>
       </c>
       <c r="F21" t="n">
-        <v>138.01</v>
+        <v>124.08</v>
       </c>
       <c r="G21" t="n">
-        <v>37.36</v>
+        <v>33.59</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-10.1</v>
+        <v>-0.08</v>
       </c>
       <c r="M21" t="n">
-        <v>6735</v>
+        <v>6055</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1850</v>
+        <v>1835</v>
       </c>
       <c r="F22" t="n">
-        <v>62.76</v>
+        <v>58.34</v>
       </c>
       <c r="G22" t="n">
-        <v>30.4</v>
+        <v>28.26</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-7.04</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>1990</v>
+        <v>1850</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2223,12 +2223,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2237,20 +2237,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>288</v>
+        <v>1125</v>
       </c>
       <c r="F23" t="n">
-        <v>36.99</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>5.48</v>
+        <v>18.71</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>24.9</v>
+        <v>99.8</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -2259,31 +2259,35 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-10</v>
+        <v>-3.85</v>
       </c>
       <c r="M23" t="n">
-        <v>320</v>
+        <v>1170</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>含金量-0.4差</t>
+        </is>
+      </c>
       <c r="P23" t="n">
-        <v>13.7</v>
+        <v>22.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
       <c r="R23" t="n">
-        <v>3.2</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>124.4</v>
       </c>
       <c r="T23" t="n">
-        <v>43.5</v>
+        <v>135.1</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
@@ -2300,12 +2304,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2314,20 +2318,20 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>1170</v>
+        <v>32.35</v>
       </c>
       <c r="F24" t="n">
-        <v>93.56999999999999</v>
+        <v>119.07</v>
       </c>
       <c r="G24" t="n">
-        <v>20.71</v>
+        <v>2.77</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>99.8</v>
+        <v>158.2</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -2336,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-9.65</v>
+        <v>0.62</v>
       </c>
       <c r="M24" t="n">
-        <v>1295</v>
+        <v>32.15</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2348,28 +2352,28 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>含金量-0.4差</t>
+          <t>ROE4低</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>22.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.38</v>
+        <v>0.77</v>
       </c>
       <c r="R24" t="n">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="S24" t="n">
-        <v>124.4</v>
+        <v>97.8</v>
       </c>
       <c r="T24" t="n">
-        <v>135.1</v>
+        <v>130</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2381,12 +2385,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2395,21 +2399,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>32.15</v>
+        <v>1435</v>
       </c>
       <c r="F25" t="n">
-        <v>127.41</v>
+        <v>194.48</v>
       </c>
       <c r="G25" t="n">
-        <v>2.97</v>
+        <v>32.3</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>158.2</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -2417,10 +2419,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-6.54</v>
+        <v>-3.04</v>
       </c>
       <c r="M25" t="n">
-        <v>34.4</v>
+        <v>1480</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2429,28 +2431,28 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ROE4低</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="R25" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>97.8</v>
+        <v>118.8</v>
       </c>
       <c r="T25" t="n">
-        <v>130</v>
+        <v>310.9</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2462,12 +2464,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2476,19 +2478,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E26" t="n">
-        <v>1480</v>
+        <v>597</v>
       </c>
       <c r="F26" t="n">
-        <v>212.88</v>
+        <v>57.01</v>
       </c>
       <c r="G26" t="n">
-        <v>35.36</v>
+        <v>7.68</v>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>12.6</v>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2496,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-8.640000000000001</v>
+        <v>-2.77</v>
       </c>
       <c r="M26" t="n">
-        <v>1620</v>
+        <v>614</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2508,23 +2512,23 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>16.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.13</v>
+        <v>3.26</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="S26" t="n">
-        <v>118.8</v>
+        <v>28.6</v>
       </c>
       <c r="T26" t="n">
-        <v>310.9</v>
+        <v>62.1</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
@@ -2541,12 +2545,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2555,21 +2559,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E27" t="n">
-        <v>614</v>
+        <v>1175</v>
       </c>
       <c r="F27" t="n">
-        <v>63.32</v>
+        <v>74.92</v>
       </c>
       <c r="G27" t="n">
-        <v>8.539999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -2577,10 +2579,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-9.970000000000001</v>
+        <v>-1.67</v>
       </c>
       <c r="M27" t="n">
-        <v>682</v>
+        <v>1195</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2589,28 +2591,28 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>12.8</v>
+        <v>17.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.26</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>3.2</v>
+        <v>120.6</v>
       </c>
       <c r="S27" t="n">
-        <v>28.6</v>
+        <v>108.5</v>
       </c>
       <c r="T27" t="n">
-        <v>62.1</v>
+        <v>65.2</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2622,12 +2624,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2639,16 +2641,18 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1195</v>
+        <v>340</v>
       </c>
       <c r="F28" t="n">
-        <v>79</v>
+        <v>64.38</v>
       </c>
       <c r="G28" t="n">
-        <v>13.6</v>
+        <v>12.26</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>27.5</v>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -2656,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-5.16</v>
+        <v>-4.49</v>
       </c>
       <c r="M28" t="n">
-        <v>1260</v>
+        <v>356</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2672,24 +2676,24 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>17.2</v>
+        <v>18.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="R28" t="n">
-        <v>120.6</v>
+        <v>50.3</v>
       </c>
       <c r="S28" t="n">
-        <v>108.5</v>
+        <v>21.1</v>
       </c>
       <c r="T28" t="n">
-        <v>65.2</v>
+        <v>99.8</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2701,12 +2705,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2718,17 +2722,17 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>356</v>
+        <v>2565</v>
       </c>
       <c r="F29" t="n">
-        <v>70.89</v>
+        <v>75.83</v>
       </c>
       <c r="G29" t="n">
-        <v>13.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>27.5</v>
+        <v>454.2</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -2737,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-9.18</v>
+        <v>-0.77</v>
       </c>
       <c r="M29" t="n">
-        <v>392</v>
+        <v>2585</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2749,23 +2753,23 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>18.9</v>
+        <v>14.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="R29" t="n">
-        <v>50.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>21.1</v>
+        <v>34.1</v>
       </c>
       <c r="T29" t="n">
-        <v>99.8</v>
+        <v>95.3</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
@@ -2782,35 +2786,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>2585</v>
+        <v>389</v>
       </c>
       <c r="F30" t="n">
-        <v>78.62</v>
+        <v>128.57</v>
       </c>
       <c r="G30" t="n">
-        <v>8.960000000000001</v>
+        <v>12.07</v>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>454.2</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -2818,10 +2820,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-3.54</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>2680</v>
+        <v>432</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2830,23 +2832,23 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>14.1</v>
+        <v>10.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="S30" t="n">
-        <v>34.1</v>
+        <v>49.9</v>
       </c>
       <c r="T30" t="n">
-        <v>95.3</v>
+        <v>165.8</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
@@ -2863,12 +2865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2877,16 +2879,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="F31" t="n">
-        <v>142.86</v>
+        <v>35.41</v>
       </c>
       <c r="G31" t="n">
-        <v>13.41</v>
+        <v>6.35</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2897,10 +2899,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-10</v>
+        <v>-3.67</v>
       </c>
       <c r="M31" t="n">
-        <v>480</v>
+        <v>395.5</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2909,23 +2911,23 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>10.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="S31" t="n">
-        <v>49.9</v>
+        <v>730.1</v>
       </c>
       <c r="T31" t="n">
-        <v>165.8</v>
+        <v>45.2</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -2942,12 +2944,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2956,20 +2958,20 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>234.5</v>
+        <v>516</v>
       </c>
       <c r="F32" t="n">
-        <v>37.91</v>
+        <v>39.8</v>
       </c>
       <c r="G32" t="n">
-        <v>3.55</v>
+        <v>8.98</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>-15.3</v>
+        <v>-2.9</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -2978,10 +2980,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-8.75</v>
+        <v>0.58</v>
       </c>
       <c r="M32" t="n">
-        <v>257</v>
+        <v>513</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -2990,19 +2992,19 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>9.4</v>
+        <v>22.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="R32" t="n">
-        <v>13.2</v>
+        <v>4.9</v>
       </c>
       <c r="S32" t="n">
-        <v>34.8</v>
+        <v>32.1</v>
       </c>
       <c r="T32" t="n">
-        <v>34.5</v>
+        <v>38.6</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
@@ -3012,19 +3014,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3033,19 +3035,21 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>395.5</v>
+        <v>630</v>
       </c>
       <c r="F33" t="n">
-        <v>39.3</v>
+        <v>55.04</v>
       </c>
       <c r="G33" t="n">
-        <v>7.05</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>-19.8</v>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -3053,10 +3057,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-9.91</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>439</v>
+        <v>699</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3065,23 +3069,23 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>17.9</v>
+        <v>15.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="R33" t="n">
-        <v>-6.1</v>
+        <v>5.7</v>
       </c>
       <c r="S33" t="n">
-        <v>730.1</v>
+        <v>47.5</v>
       </c>
       <c r="T33" t="n">
-        <v>45.2</v>
+        <v>53.2</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
@@ -3098,12 +3102,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3112,21 +3116,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E34" t="n">
-        <v>513</v>
+        <v>151</v>
       </c>
       <c r="F34" t="n">
-        <v>41.12</v>
+        <v>45.99</v>
       </c>
       <c r="G34" t="n">
-        <v>9.279999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>-2.9</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -3134,31 +3136,35 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-3.21</v>
+        <v>-2.58</v>
       </c>
       <c r="M34" t="n">
-        <v>530</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>22.4</v>
+        <v>11.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.77</v>
+        <v>1.62</v>
       </c>
       <c r="R34" t="n">
-        <v>4.9</v>
+        <v>-2.7</v>
       </c>
       <c r="S34" t="n">
-        <v>32.1</v>
+        <v>182</v>
       </c>
       <c r="T34" t="n">
-        <v>38.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3168,41 +3174,41 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>699</v>
+        <v>3340</v>
       </c>
       <c r="F35" t="n">
-        <v>61.1</v>
+        <v>53.71</v>
       </c>
       <c r="G35" t="n">
-        <v>9.56</v>
+        <v>13.78</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>-19.8</v>
+        <v>16.8</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -3211,10 +3217,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-9.92</v>
+        <v>-0.89</v>
       </c>
       <c r="M35" t="n">
-        <v>776</v>
+        <v>3370</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3223,23 +3229,23 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>15.5</v>
+        <v>25.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="R35" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="S35" t="n">
-        <v>47.5</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>53.2</v>
+        <v>61.7</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
@@ -3256,172 +3262,174 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>155</v>
+        <v>1705</v>
       </c>
       <c r="F36" t="n">
-        <v>51.04</v>
+        <v>64.16</v>
       </c>
       <c r="G36" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+        <v>15.09</v>
+      </c>
+      <c r="H36" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.32</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1740</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R36" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="M36" t="n">
-        <v>172</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="S36" t="n">
-        <v>182</v>
-      </c>
-      <c r="T36" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>3370</v>
+        <v>611</v>
       </c>
       <c r="F37" t="n">
-        <v>58.96</v>
+        <v>19.55</v>
       </c>
       <c r="G37" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>10.25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>19</v>
+      </c>
       <c r="I37" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.09</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-8.92</v>
+        <v>-0.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3700</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+          <t>⚠️高槓桿(負債80%)</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>25.3</v>
+        <v>52.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>4.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>19.2</v>
       </c>
       <c r="T37" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+        <v>20.9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.09</v>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3430,25 +3438,25 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>1740</v>
+        <v>3200</v>
       </c>
       <c r="F38" t="n">
-        <v>70.23999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="G38" t="n">
-        <v>16.52</v>
+        <v>22.24</v>
       </c>
       <c r="H38" t="n">
-        <v>59.1</v>
+        <v>70.2</v>
       </c>
       <c r="I38" t="n">
-        <v>34.1</v>
+        <v>49</v>
       </c>
       <c r="J38" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3456,30 +3464,30 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-8.66</v>
+        <v>-0.31</v>
       </c>
       <c r="M38" t="n">
-        <v>1905</v>
+        <v>3210</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>22.3</v>
+        <v>25</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.28</v>
+        <v>0.92</v>
       </c>
       <c r="R38" t="n">
-        <v>15.2</v>
+        <v>23.2</v>
       </c>
       <c r="S38" t="n">
-        <v>43.7</v>
+        <v>37.7</v>
       </c>
       <c r="T38" t="n">
-        <v>79.3</v>
+        <v>104.6</v>
       </c>
       <c r="U38" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3495,12 +3503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3509,25 +3517,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>615</v>
+        <v>4395</v>
       </c>
       <c r="F39" t="n">
-        <v>19.81</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>10.39</v>
+        <v>33.59</v>
       </c>
       <c r="H39" t="n">
-        <v>19</v>
+        <v>75.3</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>59.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3535,55 +3543,51 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-1.28</v>
+        <v>-2.22</v>
       </c>
       <c r="M39" t="n">
-        <v>623</v>
+        <v>4495</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>⚠️高槓桿(負債80%)</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>52.4</v>
+        <v>34.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.91</v>
+        <v>0.76</v>
       </c>
       <c r="R39" t="n">
-        <v>9.699999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="S39" t="n">
-        <v>19.2</v>
+        <v>114.6</v>
       </c>
       <c r="T39" t="n">
-        <v>20.9</v>
+        <v>120.3</v>
       </c>
       <c r="U39" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3592,25 +3596,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>3210</v>
+        <v>668</v>
       </c>
       <c r="F40" t="n">
-        <v>93.91</v>
+        <v>45.02</v>
       </c>
       <c r="G40" t="n">
-        <v>23.52</v>
+        <v>25.12</v>
       </c>
       <c r="H40" t="n">
-        <v>70.2</v>
+        <v>47.5</v>
       </c>
       <c r="I40" t="n">
-        <v>49</v>
+        <v>20.2</v>
       </c>
       <c r="J40" t="n">
-        <v>2.13</v>
+        <v>2.83</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3618,30 +3622,34 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-5.45</v>
+        <v>1.98</v>
       </c>
       <c r="M40" t="n">
-        <v>3395</v>
+        <v>655</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>月營收轉負-9%</t>
+        </is>
+      </c>
       <c r="P40" t="n">
-        <v>25</v>
+        <v>53.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="R40" t="n">
-        <v>23.2</v>
+        <v>28.3</v>
       </c>
       <c r="S40" t="n">
-        <v>37.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>104.6</v>
+        <v>57.1</v>
       </c>
       <c r="U40" t="n">
-        <v>2.13</v>
+        <v>2.83</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3657,12 +3665,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3671,25 +3679,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>4495</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>108.24</v>
+        <v>11.59</v>
       </c>
       <c r="G41" t="n">
-        <v>37.29</v>
+        <v>1.82</v>
       </c>
       <c r="H41" t="n">
-        <v>75.3</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>59.7</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3697,30 +3705,30 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-9.92</v>
+        <v>-0.1</v>
       </c>
       <c r="M41" t="n">
-        <v>4990</v>
+        <v>98.5</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>34.5</v>
+        <v>17.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.76</v>
+        <v>2.11</v>
       </c>
       <c r="R41" t="n">
-        <v>25.1</v>
+        <v>5.3</v>
       </c>
       <c r="S41" t="n">
-        <v>114.6</v>
+        <v>7.7</v>
       </c>
       <c r="T41" t="n">
-        <v>120.3</v>
+        <v>11.6</v>
       </c>
       <c r="U41" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3729,46 +3737,46 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>655</v>
+        <v>178</v>
       </c>
       <c r="F42" t="n">
-        <v>47.49</v>
+        <v>14.35</v>
       </c>
       <c r="G42" t="n">
-        <v>26.5</v>
+        <v>2.54</v>
       </c>
       <c r="H42" t="n">
-        <v>47.5</v>
+        <v>13.4</v>
       </c>
       <c r="I42" t="n">
-        <v>20.2</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3776,82 +3784,82 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-5.21</v>
+        <v>-1.93</v>
       </c>
       <c r="M42" t="n">
-        <v>691</v>
+        <v>181.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>月營收轉負-9%</t>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>53.6</v>
+        <v>17.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="R42" t="n">
-        <v>28.3</v>
+        <v>8.5</v>
       </c>
       <c r="S42" t="n">
-        <v>-9.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
-        <v>57.1</v>
+        <v>14.4</v>
       </c>
       <c r="U42" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>98.5</v>
+        <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>11.82</v>
+        <v>16.08</v>
       </c>
       <c r="G43" t="n">
-        <v>1.85</v>
+        <v>3.38</v>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="J43" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3859,51 +3867,51 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-1.99</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>100.5</v>
+        <v>109</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>17.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.11</v>
+        <v>1.3</v>
       </c>
       <c r="R43" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="S43" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="T43" t="n">
-        <v>11.6</v>
+        <v>17.2</v>
       </c>
       <c r="U43" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3912,25 +3920,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>181.5</v>
+        <v>500</v>
       </c>
       <c r="F44" t="n">
-        <v>14.94</v>
+        <v>15.73</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="H44" t="n">
-        <v>13.4</v>
+        <v>21.4</v>
       </c>
       <c r="I44" t="n">
-        <v>7.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3938,55 +3946,55 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-3.97</v>
+        <v>-3.66</v>
       </c>
       <c r="M44" t="n">
-        <v>189</v>
+        <v>519</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>17.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="R44" t="n">
-        <v>8.5</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>4.2</v>
+        <v>30.2</v>
       </c>
       <c r="T44" t="n">
-        <v>14.4</v>
+        <v>23.4</v>
       </c>
       <c r="U44" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3995,25 +4003,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="F45" t="n">
-        <v>15.93</v>
+        <v>28.91</v>
       </c>
       <c r="G45" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="H45" t="n">
-        <v>16</v>
+        <v>30.9</v>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4021,78 +4029,82 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.93</v>
+        <v>3.09</v>
       </c>
       <c r="M45" t="n">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>含金量0.5差</t>
+        </is>
+      </c>
       <c r="P45" t="n">
-        <v>20.6</v>
+        <v>9.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.3</v>
+        <v>0.49</v>
       </c>
       <c r="R45" t="n">
         <v>7.6</v>
       </c>
       <c r="S45" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="T45" t="n">
-        <v>17.2</v>
+        <v>36.5</v>
       </c>
       <c r="U45" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>519</v>
+        <v>3365</v>
       </c>
       <c r="F46" t="n">
-        <v>16.88</v>
+        <v>51</v>
       </c>
       <c r="G46" t="n">
-        <v>2.4</v>
+        <v>6.58</v>
       </c>
       <c r="H46" t="n">
-        <v>21.4</v>
+        <v>51.7</v>
       </c>
       <c r="I46" t="n">
-        <v>9.800000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4100,55 +4112,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-6.82</v>
+        <v>-3.3</v>
       </c>
       <c r="M46" t="n">
-        <v>557</v>
+        <v>3480</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>含金量0.3差、月營收轉負-34%</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.02</v>
+        <v>0.26</v>
       </c>
       <c r="R46" t="n">
-        <v>10.6</v>
+        <v>31.2</v>
       </c>
       <c r="S46" t="n">
-        <v>30.2</v>
+        <v>-33.5</v>
       </c>
       <c r="T46" t="n">
-        <v>23.4</v>
+        <v>63.8</v>
       </c>
       <c r="U46" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4157,61 +4169,55 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E47" t="n">
-        <v>194</v>
+        <v>265.5</v>
       </c>
       <c r="F47" t="n">
-        <v>30.4</v>
+        <v>33.29</v>
       </c>
       <c r="G47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>30.9</v>
-      </c>
+        <v>4.93</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>18</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.03</v>
-      </c>
+        <v>24.9</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-4.9</v>
+        <v>-7.81</v>
       </c>
       <c r="M47" t="n">
-        <v>204</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>含金量0.5差</t>
-        </is>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>9.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.49</v>
+        <v>1.04</v>
       </c>
       <c r="R47" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="S47" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="T47" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.03</v>
-      </c>
+        <v>43.5</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4219,124 +4225,118 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>3480</v>
+        <v>113.5</v>
       </c>
       <c r="F48" t="n">
-        <v>55.25</v>
+        <v>27.12</v>
       </c>
       <c r="G48" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="H48" t="n">
-        <v>51.7</v>
-      </c>
+        <v>2.78</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.73</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-7.69</v>
+        <v>-4.22</v>
       </c>
       <c r="M48" t="n">
-        <v>3770</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
-        </is>
-      </c>
+        <v>118.5</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.26</v>
+        <v>1.4</v>
       </c>
       <c r="R48" t="n">
-        <v>31.2</v>
+        <v>3.8</v>
       </c>
       <c r="S48" t="n">
-        <v>-33.5</v>
+        <v>48.7</v>
       </c>
       <c r="T48" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.73</v>
-      </c>
+        <v>28.4</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E49" t="n">
-        <v>349</v>
+        <v>157</v>
       </c>
       <c r="F49" t="n">
-        <v>20.77</v>
+        <v>32.68</v>
       </c>
       <c r="G49" t="n">
-        <v>6.15</v>
+        <v>1.77</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>49</v>
+        <v>12.4</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4345,36 +4345,40 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-9.109999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="M49" t="n">
-        <v>384</v>
+        <v>158.5</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P49" t="n">
-        <v>29.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="R49" t="n">
-        <v>24.2</v>
+        <v>22.1</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>14.6</v>
       </c>
       <c r="T49" t="n">
-        <v>24</v>
+        <v>34.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4386,34 +4390,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="E50" t="n">
-        <v>158.5</v>
+        <v>208</v>
       </c>
       <c r="F50" t="n">
-        <v>20.29</v>
+        <v>24.3</v>
       </c>
       <c r="G50" t="n">
-        <v>3.83</v>
+        <v>5.92</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>57.1</v>
+        <v>9.6</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4422,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-5.09</v>
+        <v>-4.15</v>
       </c>
       <c r="M50" t="n">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4434,24 +4438,24 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>18.6</v>
+        <v>30.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.74</v>
+        <v>1.44</v>
       </c>
       <c r="R50" t="n">
-        <v>11.1</v>
+        <v>20.4</v>
       </c>
       <c r="S50" t="n">
-        <v>3.6</v>
+        <v>812.4</v>
       </c>
       <c r="T50" t="n">
-        <v>22</v>
+        <v>34.6</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4463,34 +4467,34 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E51" t="n">
-        <v>118.5</v>
+        <v>235</v>
       </c>
       <c r="F51" t="n">
-        <v>30.09</v>
+        <v>34.59</v>
       </c>
       <c r="G51" t="n">
-        <v>3.09</v>
+        <v>3.24</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>-15.3</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4499,31 +4503,31 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-9.890000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="M51" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+        <v>234.5</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>EPS單期衰退</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>10.8</v>
+        <v>9.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="R51" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="S51" t="n">
-        <v>48.7</v>
+        <v>34.8</v>
       </c>
       <c r="T51" t="n">
-        <v>28.4</v>
+        <v>34.5</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4533,41 +4537,41 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>158.5</v>
+        <v>709</v>
       </c>
       <c r="F52" t="n">
-        <v>34.54</v>
+        <v>25.85</v>
       </c>
       <c r="G52" t="n">
-        <v>1.87</v>
+        <v>8.19</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>12.4</v>
+        <v>27</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4576,10 +4580,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-5.37</v>
+        <v>-1.25</v>
       </c>
       <c r="M52" t="n">
-        <v>167.5</v>
+        <v>718</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4588,28 +4592,28 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>ROE5低</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>5.4</v>
+        <v>31.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="R52" t="n">
-        <v>22.1</v>
+        <v>3.8</v>
       </c>
       <c r="S52" t="n">
-        <v>14.6</v>
+        <v>21.9</v>
       </c>
       <c r="T52" t="n">
-        <v>34.2</v>
+        <v>32.2</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4621,34 +4625,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="F53" t="n">
-        <v>25.98</v>
+        <v>26.63</v>
       </c>
       <c r="G53" t="n">
-        <v>6.32</v>
+        <v>2.84</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>9.6</v>
+        <v>186.3</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -4657,36 +4661,40 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-6.47</v>
+        <v>-2.95</v>
       </c>
       <c r="M53" t="n">
-        <v>232</v>
+        <v>118.5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P53" t="n">
-        <v>30.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="R53" t="n">
-        <v>20.4</v>
+        <v>-3.4</v>
       </c>
       <c r="S53" t="n">
-        <v>812.4</v>
+        <v>37</v>
       </c>
       <c r="T53" t="n">
-        <v>34.6</v>
+        <v>35.8</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4698,12 +4706,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4712,20 +4720,20 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>718</v>
+        <v>3875</v>
       </c>
       <c r="F54" t="n">
-        <v>25.63</v>
+        <v>25.03</v>
       </c>
       <c r="G54" t="n">
-        <v>8.119999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -4734,10 +4742,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.84</v>
+        <v>-3.37</v>
       </c>
       <c r="M54" t="n">
-        <v>712</v>
+        <v>4010</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4746,23 +4754,23 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>31.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="R54" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="S54" t="n">
-        <v>21.9</v>
+        <v>41.8</v>
       </c>
       <c r="T54" t="n">
-        <v>32.2</v>
+        <v>32.9</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
@@ -4779,201 +4787,197 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E55" t="n">
-        <v>118.5</v>
+        <v>518</v>
       </c>
       <c r="F55" t="n">
-        <v>28.54</v>
+        <v>34.52</v>
       </c>
       <c r="G55" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>6.84</v>
+      </c>
+      <c r="H55" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I55" t="n">
-        <v>186.3</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-6.69</v>
+        <v>-4.43</v>
       </c>
       <c r="M55" t="n">
-        <v>127</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>10.7</v>
+        <v>19.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R55" t="n">
-        <v>-3.4</v>
+        <v>10.6</v>
       </c>
       <c r="S55" t="n">
-        <v>37</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E56" t="n">
-        <v>4010</v>
+        <v>728</v>
       </c>
       <c r="F56" t="n">
-        <v>26.59</v>
+        <v>50.64</v>
       </c>
       <c r="G56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>7.86</v>
+      </c>
+      <c r="H56" t="n">
+        <v>46.1</v>
+      </c>
       <c r="I56" t="n">
-        <v>9</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.97</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="M56" t="n">
+        <v>747</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R56" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>-5.87</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4260</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R56" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="T56" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E57" t="n">
-        <v>542</v>
+        <v>64</v>
       </c>
       <c r="F57" t="n">
-        <v>37.58</v>
+        <v>16.05</v>
       </c>
       <c r="G57" t="n">
-        <v>7.44</v>
+        <v>2.74</v>
       </c>
       <c r="H57" t="n">
-        <v>29.3</v>
+        <v>17.3</v>
       </c>
       <c r="I57" t="n">
-        <v>18.6</v>
+        <v>11.8</v>
       </c>
       <c r="J57" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4981,78 +4985,78 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-8.140000000000001</v>
+        <v>-2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>590</v>
+        <v>65.5</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>19.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.94</v>
+        <v>1.15</v>
       </c>
       <c r="R57" t="n">
-        <v>10.6</v>
+        <v>4.4</v>
       </c>
       <c r="S57" t="n">
-        <v>64.90000000000001</v>
+        <v>768.2</v>
       </c>
       <c r="T57" t="n">
-        <v>34.7</v>
+        <v>19.4</v>
       </c>
       <c r="U57" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E58" t="n">
-        <v>747</v>
+        <v>162.5</v>
       </c>
       <c r="F58" t="n">
-        <v>56.27</v>
+        <v>15.02</v>
       </c>
       <c r="G58" t="n">
-        <v>8.73</v>
+        <v>1.63</v>
       </c>
       <c r="H58" t="n">
-        <v>46.1</v>
+        <v>15.5</v>
       </c>
       <c r="I58" t="n">
-        <v>30.6</v>
+        <v>8.6</v>
       </c>
       <c r="J58" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5060,197 +5064,193 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-10</v>
+        <v>1.88</v>
       </c>
       <c r="M58" t="n">
-        <v>830</v>
+        <v>159.5</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>15.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.83</v>
+        <v>4.03</v>
       </c>
       <c r="R58" t="n">
-        <v>24.8</v>
+        <v>30.2</v>
       </c>
       <c r="S58" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="n">
-        <v>60.2</v>
+        <v>16.9</v>
       </c>
       <c r="U58" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E59" t="n">
-        <v>65.5</v>
+        <v>344.5</v>
       </c>
       <c r="F59" t="n">
-        <v>16.42</v>
+        <v>18.88</v>
       </c>
       <c r="G59" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H59" t="n">
-        <v>17.3</v>
-      </c>
+        <v>5.59</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.64</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-2.24</v>
+        <v>-1.29</v>
       </c>
       <c r="M59" t="n">
-        <v>67</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
+        <v>349</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>11.3</v>
+        <v>29.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="R59" t="n">
-        <v>4.4</v>
+        <v>24.2</v>
       </c>
       <c r="S59" t="n">
-        <v>768.2</v>
+        <v>25</v>
       </c>
       <c r="T59" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.64</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E60" t="n">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="F60" t="n">
-        <v>15.44</v>
+        <v>19.26</v>
       </c>
       <c r="G60" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H60" t="n">
-        <v>15.5</v>
-      </c>
+        <v>3.64</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1.95</v>
-      </c>
+        <v>57.1</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-2.74</v>
+        <v>-0.63</v>
       </c>
       <c r="M60" t="n">
-        <v>164</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
+        <v>158.5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>10.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
       <c r="R60" t="n">
-        <v>30.2</v>
+        <v>11.1</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="T60" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.95</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
@@ -5274,13 +5274,13 @@
         <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="F61" t="n">
-        <v>16.79</v>
+        <v>16.1</v>
       </c>
       <c r="G61" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-4.12</v>
+        <v>0.51</v>
       </c>
       <c r="M61" t="n">
-        <v>20.65</v>
+        <v>19.8</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>88.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>19.71</v>
+        <v>18.21</v>
       </c>
       <c r="G62" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-7.6</v>
+        <v>-1.8</v>
       </c>
       <c r="M62" t="n">
-        <v>96</v>
+        <v>88.7</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>14.24</v>
+        <v>13.6</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-4.51</v>
+        <v>-0.71</v>
       </c>
       <c r="M63" t="n">
-        <v>44.3</v>
+        <v>42.3</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>178</v>
+        <v>182.5</v>
       </c>
       <c r="F64" t="n">
-        <v>17.26</v>
+        <v>16.17</v>
       </c>
       <c r="G64" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-6.32</v>
+        <v>2.53</v>
       </c>
       <c r="M64" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="F65" t="n">
-        <v>17.44</v>
+        <v>16.99</v>
       </c>
       <c r="G65" t="n">
-        <v>16.48</v>
+        <v>16.06</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-2.56</v>
+        <v>2.92</v>
       </c>
       <c r="M65" t="n">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>47.35</v>
+        <v>46.95</v>
       </c>
       <c r="F66" t="n">
-        <v>18.65</v>
+        <v>18</v>
       </c>
       <c r="G66" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-3.47</v>
+        <v>-0.84</v>
       </c>
       <c r="M66" t="n">
-        <v>49.05</v>
+        <v>47.35</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>161</v>
+        <v>145.5</v>
       </c>
       <c r="F67" t="n">
-        <v>17.03</v>
+        <v>17.46</v>
       </c>
       <c r="G67" t="n">
-        <v>5.01</v>
+        <v>5.14</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.55</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="F68" t="n">
-        <v>25.29</v>
+        <v>23.84</v>
       </c>
       <c r="G68" t="n">
-        <v>6.01</v>
+        <v>5.66</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-5.7</v>
+        <v>-3.2</v>
       </c>
       <c r="M68" t="n">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F69" t="n">
         <v>17.53</v>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="M69" t="n">
         <v>122</v>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>304.5</v>
+        <v>301</v>
       </c>
       <c r="F70" t="n">
-        <v>31.76</v>
+        <v>29.71</v>
       </c>
       <c r="G70" t="n">
-        <v>8.710000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-6.45</v>
+        <v>-1.15</v>
       </c>
       <c r="M70" t="n">
-        <v>325.5</v>
+        <v>304.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="F71" t="n">
-        <v>19.45</v>
+        <v>19.14</v>
       </c>
       <c r="G71" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1.62</v>
+        <v>-0.11</v>
       </c>
       <c r="M71" t="n">
-        <v>92.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>145.5</v>
+        <v>140</v>
       </c>
       <c r="F72" t="n">
-        <v>21.35</v>
+        <v>19.85</v>
       </c>
       <c r="G72" t="n">
-        <v>5.83</v>
+        <v>5.42</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-7.03</v>
+        <v>-3.78</v>
       </c>
       <c r="M72" t="n">
-        <v>156.5</v>
+        <v>145.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>234</v>
+        <v>234.5</v>
       </c>
       <c r="F73" t="n">
-        <v>17.22</v>
+        <v>16.62</v>
       </c>
       <c r="G73" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-3.51</v>
+        <v>0.21</v>
       </c>
       <c r="M73" t="n">
-        <v>242.5</v>
+        <v>234</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="F74" t="n">
-        <v>63.65</v>
+        <v>58.67</v>
       </c>
       <c r="G74" t="n">
-        <v>33.13</v>
+        <v>30.54</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-7.82</v>
+        <v>3.57</v>
       </c>
       <c r="M74" t="n">
-        <v>1215</v>
+        <v>1120</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>58.5</v>
+        <v>57.2</v>
       </c>
       <c r="F75" t="n">
-        <v>23.08</v>
+        <v>22.24</v>
       </c>
       <c r="G75" t="n">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-3.62</v>
+        <v>-2.22</v>
       </c>
       <c r="M75" t="n">
-        <v>60.7</v>
+        <v>58.5</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2200</v>
+        <v>2135</v>
       </c>
       <c r="F76" t="n">
-        <v>36.56</v>
+        <v>36.15</v>
       </c>
       <c r="G76" t="n">
-        <v>19.34</v>
+        <v>19.12</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1.12</v>
+        <v>-2.95</v>
       </c>
       <c r="M76" t="n">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="F77" t="n">
-        <v>24.09</v>
+        <v>22.18</v>
       </c>
       <c r="G77" t="n">
-        <v>9.34</v>
+        <v>8.6</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-7.95</v>
+        <v>-3</v>
       </c>
       <c r="M77" t="n">
-        <v>868</v>
+        <v>799</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="F78" t="n">
-        <v>33.21</v>
+        <v>30.79</v>
       </c>
       <c r="G78" t="n">
-        <v>10.87</v>
+        <v>10.08</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-7.29</v>
+        <v>1.31</v>
       </c>
       <c r="M78" t="n">
-        <v>2470</v>
+        <v>2290</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="F79" t="n">
-        <v>15.37</v>
+        <v>15.07</v>
       </c>
       <c r="G79" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1.91</v>
+        <v>0.98</v>
       </c>
       <c r="M79" t="n">
-        <v>104.5</v>
+        <v>102.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6796,10 +6796,10 @@
         <v>106</v>
       </c>
       <c r="F80" t="n">
-        <v>15.49</v>
+        <v>14.34</v>
       </c>
       <c r="G80" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-7.42</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>114.5</v>
+        <v>106</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6875,10 +6875,10 @@
         <v>28</v>
       </c>
       <c r="F81" t="n">
-        <v>5.7</v>
+        <v>5.61</v>
       </c>
       <c r="G81" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1.58</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>28.45</v>
+        <v>28</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>110.5</v>
+        <v>109.5</v>
       </c>
       <c r="F82" t="n">
-        <v>12.12</v>
+        <v>11.91</v>
       </c>
       <c r="G82" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1.78</v>
+        <v>-0.9</v>
       </c>
       <c r="M82" t="n">
-        <v>112.5</v>
+        <v>110.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>175</v>
+        <v>175.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.25</v>
+        <v>12.99</v>
       </c>
       <c r="G83" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.96</v>
+        <v>0.29</v>
       </c>
       <c r="M83" t="n">
-        <v>178.5</v>
+        <v>175</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7112,10 +7112,10 @@
         <v>41.2</v>
       </c>
       <c r="F84" t="n">
-        <v>7.95</v>
+        <v>7.82</v>
       </c>
       <c r="G84" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="F85" t="n">
-        <v>34.84</v>
+        <v>32.46</v>
       </c>
       <c r="G85" t="n">
-        <v>11.67</v>
+        <v>10.88</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-6.81</v>
+        <v>-1.37</v>
       </c>
       <c r="M85" t="n">
-        <v>1175</v>
+        <v>1095</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>397.5</v>
+        <v>388</v>
       </c>
       <c r="F86" t="n">
-        <v>20.51</v>
+        <v>19.31</v>
       </c>
       <c r="G86" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-5.81</v>
+        <v>-2.39</v>
       </c>
       <c r="M86" t="n">
-        <v>422</v>
+        <v>397.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="F87" t="n">
-        <v>16.48</v>
+        <v>15.51</v>
       </c>
       <c r="G87" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-5.93</v>
+        <v>-1.18</v>
       </c>
       <c r="M87" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>37.35</v>
+        <v>37.5</v>
       </c>
       <c r="F88" t="n">
-        <v>8.4</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-2.23</v>
+        <v>0.4</v>
       </c>
       <c r="M88" t="n">
-        <v>38.2</v>
+        <v>37.35</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7507,10 +7507,10 @@
         <v>2090</v>
       </c>
       <c r="F89" t="n">
-        <v>43.87</v>
+        <v>39.52</v>
       </c>
       <c r="G89" t="n">
-        <v>19.85</v>
+        <v>17.88</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-9.91</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2320</v>
+        <v>2090</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>913</v>
+        <v>858</v>
       </c>
       <c r="F90" t="n">
-        <v>26.03</v>
+        <v>26.35</v>
       </c>
       <c r="G90" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.22</v>
+        <v>-6.02</v>
       </c>
       <c r="M90" t="n">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="F91" t="n">
-        <v>10.71</v>
+        <v>10.37</v>
       </c>
       <c r="G91" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-3.14</v>
+        <v>-0.58</v>
       </c>
       <c r="M91" t="n">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
       <c r="F92" t="n">
-        <v>7.79</v>
+        <v>7.51</v>
       </c>
       <c r="G92" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-3.61</v>
+        <v>0.43</v>
       </c>
       <c r="M92" t="n">
-        <v>72.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="F93" t="n">
-        <v>11.1</v>
+        <v>10.59</v>
       </c>
       <c r="G93" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-4.52</v>
+        <v>-0.53</v>
       </c>
       <c r="M93" t="n">
-        <v>59.7</v>
+        <v>57</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>325.5</v>
+        <v>316</v>
       </c>
       <c r="F94" t="n">
-        <v>17.7</v>
+        <v>16.37</v>
       </c>
       <c r="G94" t="n">
-        <v>6.54</v>
+        <v>6.05</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-7.53</v>
+        <v>-2.92</v>
       </c>
       <c r="M94" t="n">
-        <v>352</v>
+        <v>325.5</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>4620</v>
+        <v>4685</v>
       </c>
       <c r="F95" t="n">
-        <v>17.15</v>
+        <v>15.49</v>
       </c>
       <c r="G95" t="n">
-        <v>6.78</v>
+        <v>6.13</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-9.68</v>
+        <v>1.41</v>
       </c>
       <c r="M95" t="n">
-        <v>5115</v>
+        <v>4620</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>139</v>
+        <v>143.5</v>
       </c>
       <c r="F96" t="n">
-        <v>14.69</v>
+        <v>13.94</v>
       </c>
       <c r="G96" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-5.12</v>
+        <v>3.24</v>
       </c>
       <c r="M96" t="n">
-        <v>146.5</v>
+        <v>139</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1435</v>
+        <v>1470</v>
       </c>
       <c r="F97" t="n">
-        <v>18.59</v>
+        <v>17.61</v>
       </c>
       <c r="G97" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-5.28</v>
+        <v>2.44</v>
       </c>
       <c r="M97" t="n">
-        <v>1515</v>
+        <v>1435</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>67.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>5.52</v>
+        <v>5.65</v>
       </c>
       <c r="G98" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="M98" t="n">
-        <v>66.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>366.5</v>
+        <v>348.5</v>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>7.32</v>
       </c>
       <c r="G99" t="n">
-        <v>4.61</v>
+        <v>4.22</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-8.49</v>
+        <v>-4.91</v>
       </c>
       <c r="M99" t="n">
-        <v>400.5</v>
+        <v>366.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.5</v>
+        <v>23.55</v>
       </c>
       <c r="F100" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="G100" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-1.67</v>
+        <v>0.21</v>
       </c>
       <c r="M100" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F101" t="n">
-        <v>9.140000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="G101" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.33</v>
+        <v>-3.16</v>
       </c>
       <c r="M101" t="n">
-        <v>187.5</v>
+        <v>190</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2200</v>
+        <v>2135</v>
       </c>
       <c r="F2" t="n">
-        <v>36.56</v>
+        <v>36.15</v>
       </c>
       <c r="G2" t="n">
-        <v>19.34</v>
+        <v>19.12</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.12</v>
+        <v>-2.95</v>
       </c>
       <c r="M2" t="n">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="F3" t="n">
-        <v>24.09</v>
+        <v>22.18</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34</v>
+        <v>8.6</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-7.95</v>
+        <v>-3</v>
       </c>
       <c r="M3" t="n">
-        <v>868</v>
+        <v>799</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="F4" t="n">
-        <v>33.21</v>
+        <v>30.79</v>
       </c>
       <c r="G4" t="n">
-        <v>10.87</v>
+        <v>10.08</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-7.29</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>2470</v>
+        <v>2290</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="F5" t="n">
-        <v>15.37</v>
+        <v>15.07</v>
       </c>
       <c r="G5" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.91</v>
+        <v>0.98</v>
       </c>
       <c r="M5" t="n">
-        <v>104.5</v>
+        <v>102.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         <v>106</v>
       </c>
       <c r="F6" t="n">
-        <v>15.49</v>
+        <v>14.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-7.42</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>114.5</v>
+        <v>106</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9100,10 +9100,10 @@
         <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7</v>
+        <v>5.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.58</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>28.45</v>
+        <v>28</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>110.5</v>
+        <v>109.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.12</v>
+        <v>11.91</v>
       </c>
       <c r="G8" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.78</v>
+        <v>-0.9</v>
       </c>
       <c r="M8" t="n">
-        <v>112.5</v>
+        <v>110.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>175</v>
+        <v>175.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.25</v>
+        <v>12.99</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.96</v>
+        <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>178.5</v>
+        <v>175</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>7.95</v>
+        <v>7.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="F11" t="n">
-        <v>34.84</v>
+        <v>32.46</v>
       </c>
       <c r="G11" t="n">
-        <v>11.67</v>
+        <v>10.88</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-6.81</v>
+        <v>-1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>1175</v>
+        <v>1095</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>397.5</v>
+        <v>388</v>
       </c>
       <c r="F12" t="n">
-        <v>20.51</v>
+        <v>19.31</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-5.81</v>
+        <v>-2.39</v>
       </c>
       <c r="M12" t="n">
-        <v>422</v>
+        <v>397.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="F13" t="n">
-        <v>16.48</v>
+        <v>15.51</v>
       </c>
       <c r="G13" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-5.93</v>
+        <v>-1.18</v>
       </c>
       <c r="M13" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>37.35</v>
+        <v>37.5</v>
       </c>
       <c r="F14" t="n">
-        <v>8.4</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-2.23</v>
+        <v>0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>38.2</v>
+        <v>37.35</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9732,10 +9732,10 @@
         <v>2090</v>
       </c>
       <c r="F15" t="n">
-        <v>43.87</v>
+        <v>39.52</v>
       </c>
       <c r="G15" t="n">
-        <v>19.85</v>
+        <v>17.88</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-9.91</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2320</v>
+        <v>2090</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>913</v>
+        <v>858</v>
       </c>
       <c r="F16" t="n">
-        <v>26.03</v>
+        <v>26.35</v>
       </c>
       <c r="G16" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>-6.02</v>
       </c>
       <c r="M16" t="n">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="F17" t="n">
-        <v>10.71</v>
+        <v>10.37</v>
       </c>
       <c r="G17" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.14</v>
+        <v>-0.58</v>
       </c>
       <c r="M17" t="n">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
       <c r="F18" t="n">
-        <v>7.79</v>
+        <v>7.51</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-3.61</v>
+        <v>0.43</v>
       </c>
       <c r="M18" t="n">
-        <v>72.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="F19" t="n">
-        <v>11.1</v>
+        <v>10.59</v>
       </c>
       <c r="G19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-4.52</v>
+        <v>-0.53</v>
       </c>
       <c r="M19" t="n">
-        <v>59.7</v>
+        <v>57</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>325.5</v>
+        <v>316</v>
       </c>
       <c r="F20" t="n">
-        <v>17.7</v>
+        <v>16.37</v>
       </c>
       <c r="G20" t="n">
-        <v>6.54</v>
+        <v>6.05</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-7.53</v>
+        <v>-2.92</v>
       </c>
       <c r="M20" t="n">
-        <v>352</v>
+        <v>325.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>4620</v>
+        <v>4685</v>
       </c>
       <c r="F21" t="n">
-        <v>17.15</v>
+        <v>15.49</v>
       </c>
       <c r="G21" t="n">
-        <v>6.78</v>
+        <v>6.13</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-9.68</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>5115</v>
+        <v>4620</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>139</v>
+        <v>143.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.69</v>
+        <v>13.94</v>
       </c>
       <c r="G22" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-5.12</v>
+        <v>3.24</v>
       </c>
       <c r="M22" t="n">
-        <v>146.5</v>
+        <v>139</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1435</v>
+        <v>1470</v>
       </c>
       <c r="F23" t="n">
-        <v>18.59</v>
+        <v>17.61</v>
       </c>
       <c r="G23" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-5.28</v>
+        <v>2.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1515</v>
+        <v>1435</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>161</v>
+        <v>145.5</v>
       </c>
       <c r="F2" t="n">
-        <v>17.03</v>
+        <v>17.46</v>
       </c>
       <c r="G2" t="n">
-        <v>5.01</v>
+        <v>5.14</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.55</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="F3" t="n">
-        <v>25.29</v>
+        <v>23.84</v>
       </c>
       <c r="G3" t="n">
-        <v>6.01</v>
+        <v>5.66</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-5.7</v>
+        <v>-3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,7 +10765,7 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
         <v>17.53</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="M4" t="n">
         <v>122</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>304.5</v>
+        <v>301</v>
       </c>
       <c r="F5" t="n">
-        <v>31.76</v>
+        <v>29.71</v>
       </c>
       <c r="G5" t="n">
-        <v>8.710000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-6.45</v>
+        <v>-1.15</v>
       </c>
       <c r="M5" t="n">
-        <v>325.5</v>
+        <v>304.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>19.45</v>
+        <v>19.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.62</v>
+        <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>92.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>145.5</v>
+        <v>140</v>
       </c>
       <c r="F7" t="n">
-        <v>21.35</v>
+        <v>19.85</v>
       </c>
       <c r="G7" t="n">
-        <v>5.83</v>
+        <v>5.42</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-7.03</v>
+        <v>-3.78</v>
       </c>
       <c r="M7" t="n">
-        <v>156.5</v>
+        <v>145.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>234</v>
+        <v>234.5</v>
       </c>
       <c r="F8" t="n">
-        <v>17.22</v>
+        <v>16.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.51</v>
+        <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>242.5</v>
+        <v>234</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="F9" t="n">
-        <v>63.65</v>
+        <v>58.67</v>
       </c>
       <c r="G9" t="n">
-        <v>33.13</v>
+        <v>30.54</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-7.82</v>
+        <v>3.57</v>
       </c>
       <c r="M9" t="n">
-        <v>1215</v>
+        <v>1120</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>58.5</v>
+        <v>57.2</v>
       </c>
       <c r="F10" t="n">
-        <v>23.08</v>
+        <v>22.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.62</v>
+        <v>-2.22</v>
       </c>
       <c r="M10" t="n">
-        <v>60.7</v>
+        <v>58.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1015</v>
+        <v>971</v>
       </c>
       <c r="F2" t="n">
-        <v>80.23999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22.53</v>
+        <v>20.32</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-4.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1125</v>
+        <v>1015</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11541,10 +11541,10 @@
         <v>39.1</v>
       </c>
       <c r="F3" t="n">
-        <v>11.17</v>
+        <v>11.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>39.55</v>
+        <v>39.1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>168.5</v>
+        <v>159.5</v>
       </c>
       <c r="F4" t="n">
-        <v>18.73</v>
+        <v>19.48</v>
       </c>
       <c r="G4" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.01</v>
+        <v>-5.34</v>
       </c>
       <c r="M4" t="n">
-        <v>162</v>
+        <v>168.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5600</v>
+        <v>5455</v>
       </c>
       <c r="F5" t="n">
-        <v>165.6</v>
+        <v>149.09</v>
       </c>
       <c r="G5" t="n">
-        <v>38.68</v>
+        <v>34.83</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-9.970000000000001</v>
+        <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>6220</v>
+        <v>5600</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>22.41</v>
+        <v>22.52</v>
       </c>
       <c r="G6" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="M6" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>31.05</v>
+        <v>29.88</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.25</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.76</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>106.5</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>216.5</v>
+        <v>208</v>
       </c>
       <c r="F8" t="n">
-        <v>35.34</v>
+        <v>33.05</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85</v>
+        <v>6.41</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-6.48</v>
+        <v>-3.93</v>
       </c>
       <c r="M8" t="n">
-        <v>231.5</v>
+        <v>216.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.63</v>
+        <v>26.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F10" t="n">
-        <v>18.99</v>
+        <v>18.27</v>
       </c>
       <c r="G10" t="n">
-        <v>5.22</v>
+        <v>5.02</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.8</v>
+        <v>-1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1265</v>
+        <v>1335</v>
       </c>
       <c r="F11" t="n">
-        <v>29.55</v>
+        <v>27.69</v>
       </c>
       <c r="G11" t="n">
-        <v>5.31</v>
+        <v>4.98</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-6.3</v>
+        <v>5.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1350</v>
+        <v>1265</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174.5</v>
+        <v>167.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25.03</v>
+        <v>24.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-3.86</v>
+        <v>-4.01</v>
       </c>
       <c r="M12" t="n">
-        <v>181.5</v>
+        <v>174.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>196.5</v>
+        <v>193.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.06</v>
+        <v>28.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.61</v>
+        <v>5.06</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-9.859999999999999</v>
+        <v>-1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>218</v>
+        <v>196.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>27.04</v>
+        <v>27.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>0.72</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>243</v>
+        <v>243.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.38</v>
+        <v>22.15</v>
       </c>
       <c r="G15" t="n">
-        <v>5.49</v>
+        <v>5.44</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.02</v>
+        <v>0.21</v>
       </c>
       <c r="M15" t="n">
-        <v>245.5</v>
+        <v>243</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>3835</v>
+        <v>3745</v>
       </c>
       <c r="F16" t="n">
-        <v>125.9</v>
+        <v>115.37</v>
       </c>
       <c r="G16" t="n">
-        <v>38.45</v>
+        <v>35.24</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-8.359999999999999</v>
+        <v>-2.35</v>
       </c>
       <c r="M16" t="n">
-        <v>4185</v>
+        <v>3835</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1740</v>
+        <v>1705</v>
       </c>
       <c r="F2" t="n">
-        <v>70.23999999999999</v>
+        <v>64.16</v>
       </c>
       <c r="G2" t="n">
-        <v>16.52</v>
+        <v>15.09</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-8.66</v>
+        <v>-2.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1905</v>
+        <v>1740</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F3" t="n">
-        <v>19.81</v>
+        <v>19.55</v>
       </c>
       <c r="G3" t="n">
-        <v>10.39</v>
+        <v>10.25</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.28</v>
+        <v>-0.65</v>
       </c>
       <c r="M3" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3210</v>
+        <v>3200</v>
       </c>
       <c r="F4" t="n">
-        <v>93.91</v>
+        <v>88.8</v>
       </c>
       <c r="G4" t="n">
-        <v>23.52</v>
+        <v>22.24</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-5.45</v>
+        <v>-0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3395</v>
+        <v>3210</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4495</v>
+        <v>4395</v>
       </c>
       <c r="F5" t="n">
-        <v>108.24</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>37.29</v>
+        <v>33.59</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-9.92</v>
+        <v>-2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>4990</v>
+        <v>4495</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="F6" t="n">
-        <v>47.49</v>
+        <v>45.02</v>
       </c>
       <c r="G6" t="n">
-        <v>26.5</v>
+        <v>25.12</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-5.21</v>
+        <v>1.98</v>
       </c>
       <c r="M6" t="n">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>11.82</v>
+        <v>11.59</v>
       </c>
       <c r="G7" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.99</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>100.5</v>
+        <v>98.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>181.5</v>
+        <v>178</v>
       </c>
       <c r="F8" t="n">
-        <v>14.94</v>
+        <v>14.35</v>
       </c>
       <c r="G8" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.97</v>
+        <v>-1.93</v>
       </c>
       <c r="M8" t="n">
-        <v>189</v>
+        <v>181.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13371,10 +13371,10 @@
         <v>109</v>
       </c>
       <c r="F9" t="n">
-        <v>15.93</v>
+        <v>16.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>16.88</v>
+        <v>15.73</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-6.82</v>
+        <v>-3.66</v>
       </c>
       <c r="M10" t="n">
-        <v>557</v>
+        <v>519</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F11" t="n">
-        <v>30.4</v>
+        <v>28.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-4.9</v>
+        <v>3.09</v>
       </c>
       <c r="M11" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3480</v>
+        <v>3365</v>
       </c>
       <c r="F12" t="n">
-        <v>55.25</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>7.12</v>
+        <v>6.58</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-7.69</v>
+        <v>-3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3770</v>
+        <v>3480</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="F2" t="n">
-        <v>72.40000000000001</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>20.32</v>
+        <v>19.44</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-4.33</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1015</v>
+        <v>971</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,7 +636,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="F3" t="n">
         <v>11.05</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="M3" t="n">
         <v>39.1</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>159.5</v>
+        <v>163</v>
       </c>
       <c r="F4" t="n">
-        <v>19.48</v>
+        <v>18.44</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.07</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-5.34</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>168.5</v>
+        <v>159.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5455</v>
+        <v>5875</v>
       </c>
       <c r="F5" t="n">
-        <v>149.09</v>
+        <v>145.23</v>
       </c>
       <c r="G5" t="n">
-        <v>34.83</v>
+        <v>33.92</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.59</v>
+        <v>7.7</v>
       </c>
       <c r="M5" t="n">
-        <v>5600</v>
+        <v>5455</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -880,10 +880,10 @@
         <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>22.52</v>
+        <v>22.72</v>
       </c>
       <c r="G6" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>107.5</v>
       </c>
       <c r="F7" t="n">
-        <v>29.88</v>
+        <v>30.32</v>
       </c>
       <c r="G7" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>3.37</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>104</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F8" t="n">
-        <v>33.05</v>
+        <v>31.76</v>
       </c>
       <c r="G8" t="n">
-        <v>6.41</v>
+        <v>6.15</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.93</v>
+        <v>3.37</v>
       </c>
       <c r="M8" t="n">
-        <v>216.5</v>
+        <v>208</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>26.14</v>
+        <v>26.52</v>
       </c>
       <c r="G9" t="n">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>-2.39</v>
       </c>
       <c r="M9" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>18.27</v>
+        <v>18.03</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.32</v>
+        <v>2.67</v>
       </c>
       <c r="M10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="F11" t="n">
-        <v>27.69</v>
+        <v>29.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.98</v>
+        <v>5.25</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.53</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>1265</v>
+        <v>1335</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>167.5</v>
+        <v>169.5</v>
       </c>
       <c r="F12" t="n">
-        <v>24.07</v>
+        <v>20.89</v>
       </c>
       <c r="G12" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-4.01</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>174.5</v>
+        <v>167.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>193.5</v>
+        <v>207</v>
       </c>
       <c r="F13" t="n">
-        <v>28.9</v>
+        <v>28.46</v>
       </c>
       <c r="G13" t="n">
-        <v>5.06</v>
+        <v>4.98</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.53</v>
+        <v>6.98</v>
       </c>
       <c r="M13" t="n">
-        <v>196.5</v>
+        <v>193.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1528,10 +1528,10 @@
         <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>27.44</v>
+        <v>27.63</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15</v>
+        <v>22.2</v>
       </c>
       <c r="G15" t="n">
-        <v>5.44</v>
+        <v>5.45</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.21</v>
+        <v>-0.21</v>
       </c>
       <c r="M15" t="n">
-        <v>243</v>
+        <v>243.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>3745</v>
+        <v>4115</v>
       </c>
       <c r="F16" t="n">
-        <v>115.37</v>
+        <v>112.67</v>
       </c>
       <c r="G16" t="n">
-        <v>35.24</v>
+        <v>34.41</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2.35</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>3835</v>
+        <v>3745</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1220</v>
+        <v>1260</v>
       </c>
       <c r="F17" t="n">
-        <v>49.04</v>
+        <v>46.02</v>
       </c>
       <c r="G17" t="n">
-        <v>14.36</v>
+        <v>13.48</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-6.15</v>
+        <v>3.28</v>
       </c>
       <c r="M17" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7750</v>
+        <v>7975</v>
       </c>
       <c r="F18" t="n">
-        <v>69.55</v>
+        <v>68.31</v>
       </c>
       <c r="G18" t="n">
-        <v>23.85</v>
+        <v>23.42</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.77</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>7890</v>
+        <v>7750</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>647</v>
+        <v>676</v>
       </c>
       <c r="F19" t="n">
-        <v>64.69</v>
+        <v>63.81</v>
       </c>
       <c r="G19" t="n">
-        <v>11.86</v>
+        <v>11.7</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.37</v>
+        <v>4.48</v>
       </c>
       <c r="M19" t="n">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>69.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>51.45</v>
+        <v>50.29</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>5.97</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.25</v>
+        <v>3.17</v>
       </c>
       <c r="M20" t="n">
-        <v>71</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6050</v>
+        <v>6655</v>
       </c>
       <c r="F21" t="n">
-        <v>124.08</v>
+        <v>123.98</v>
       </c>
       <c r="G21" t="n">
-        <v>33.59</v>
+        <v>33.56</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.08</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>6055</v>
+        <v>6050</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>1835</v>
+        <v>2015</v>
       </c>
       <c r="F22" t="n">
-        <v>58.34</v>
+        <v>57.87</v>
       </c>
       <c r="G22" t="n">
-        <v>28.26</v>
+        <v>28.03</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.8100000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="M22" t="n">
-        <v>1850</v>
+        <v>1835</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>1125</v>
+        <v>1235</v>
       </c>
       <c r="F23" t="n">
-        <v>84.54000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>18.71</v>
+        <v>17.99</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-3.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>1170</v>
+        <v>1125</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>32.35</v>
+        <v>31.9</v>
       </c>
       <c r="F24" t="n">
-        <v>119.07</v>
+        <v>119.81</v>
       </c>
       <c r="G24" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.62</v>
+        <v>-1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>32.15</v>
+        <v>32.35</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>1435</v>
+        <v>1515</v>
       </c>
       <c r="F25" t="n">
-        <v>194.48</v>
+        <v>188.57</v>
       </c>
       <c r="G25" t="n">
-        <v>32.3</v>
+        <v>31.32</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-3.04</v>
+        <v>5.57</v>
       </c>
       <c r="M25" t="n">
-        <v>1480</v>
+        <v>1435</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2481,13 +2481,13 @@
         <v>68</v>
       </c>
       <c r="E26" t="n">
-        <v>597</v>
+        <v>633</v>
       </c>
       <c r="F26" t="n">
-        <v>57.01</v>
+        <v>55.43</v>
       </c>
       <c r="G26" t="n">
-        <v>7.68</v>
+        <v>7.47</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-2.77</v>
+        <v>6.03</v>
       </c>
       <c r="M26" t="n">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
         <v>1175</v>
       </c>
       <c r="F27" t="n">
-        <v>74.92</v>
+        <v>73.67</v>
       </c>
       <c r="G27" t="n">
-        <v>12.9</v>
+        <v>12.68</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2641,13 +2641,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="F28" t="n">
-        <v>64.38</v>
+        <v>61.48</v>
       </c>
       <c r="G28" t="n">
-        <v>12.26</v>
+        <v>11.71</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-4.49</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>2565</v>
+        <v>2645</v>
       </c>
       <c r="F29" t="n">
-        <v>75.83</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-0.77</v>
+        <v>3.12</v>
       </c>
       <c r="M29" t="n">
-        <v>2585</v>
+        <v>2565</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>389</v>
+        <v>427.5</v>
       </c>
       <c r="F30" t="n">
-        <v>128.57</v>
+        <v>115.77</v>
       </c>
       <c r="G30" t="n">
-        <v>12.07</v>
+        <v>10.87</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="M30" t="n">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2879,19 +2879,21 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>381</v>
+        <v>567</v>
       </c>
       <c r="F31" t="n">
-        <v>35.41</v>
+        <v>40.03</v>
       </c>
       <c r="G31" t="n">
-        <v>6.35</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
@@ -2899,35 +2901,31 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-3.67</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>395.5</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.5</v>
+        <v>0.77</v>
       </c>
       <c r="R31" t="n">
-        <v>-6.1</v>
+        <v>4.9</v>
       </c>
       <c r="S31" t="n">
-        <v>730.1</v>
+        <v>32.1</v>
       </c>
       <c r="T31" t="n">
-        <v>45.2</v>
+        <v>38.6</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -2937,19 +2935,19 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2958,20 +2956,20 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>516</v>
+        <v>670</v>
       </c>
       <c r="F32" t="n">
-        <v>39.8</v>
+        <v>49.61</v>
       </c>
       <c r="G32" t="n">
-        <v>8.98</v>
+        <v>7.76</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>-2.9</v>
+        <v>-19.8</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -2980,31 +2978,35 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.58</v>
+        <v>6.35</v>
       </c>
       <c r="M32" t="n">
-        <v>513</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
+        <v>630</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>22.4</v>
+        <v>15.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.77</v>
+        <v>1.24</v>
       </c>
       <c r="R32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="S32" t="n">
-        <v>32.1</v>
+        <v>47.5</v>
       </c>
       <c r="T32" t="n">
-        <v>38.6</v>
+        <v>53.2</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
@@ -3014,19 +3016,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3035,21 +3037,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E33" t="n">
-        <v>630</v>
+        <v>155.5</v>
       </c>
       <c r="F33" t="n">
-        <v>55.04</v>
+        <v>44.81</v>
       </c>
       <c r="G33" t="n">
-        <v>8.609999999999999</v>
+        <v>5.83</v>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>-19.8</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-9.869999999999999</v>
+        <v>2.98</v>
       </c>
       <c r="M33" t="n">
-        <v>699</v>
+        <v>151</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3069,23 +3069,23 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>-2.7</v>
       </c>
       <c r="S33" t="n">
-        <v>47.5</v>
+        <v>182</v>
       </c>
       <c r="T33" t="n">
-        <v>53.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
@@ -3102,33 +3102,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>151</v>
+        <v>3670</v>
       </c>
       <c r="F34" t="n">
-        <v>45.99</v>
+        <v>53.23</v>
       </c>
       <c r="G34" t="n">
-        <v>5.98</v>
+        <v>13.66</v>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>16.8</v>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -3136,10 +3138,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-2.58</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>155</v>
+        <v>3340</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3148,23 +3150,23 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>11.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.7</v>
+        <v>4.8</v>
       </c>
       <c r="S34" t="n">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>65.90000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3181,93 +3183,91 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>3340</v>
+        <v>1835</v>
       </c>
       <c r="F35" t="n">
-        <v>53.71</v>
+        <v>62.87</v>
       </c>
       <c r="G35" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>14.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>59.1</v>
+      </c>
       <c r="I35" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>34.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.32</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1705</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R35" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3370</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3276,25 +3276,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>1705</v>
+        <v>633</v>
       </c>
       <c r="F36" t="n">
-        <v>64.16</v>
+        <v>19.43</v>
       </c>
       <c r="G36" t="n">
-        <v>15.09</v>
+        <v>10.19</v>
       </c>
       <c r="H36" t="n">
-        <v>59.1</v>
+        <v>19</v>
       </c>
       <c r="I36" t="n">
-        <v>34.1</v>
+        <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3302,51 +3302,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-2.01</v>
+        <v>3.6</v>
       </c>
       <c r="M36" t="n">
-        <v>1740</v>
+        <v>611</v>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債80%)</t>
+        </is>
+      </c>
       <c r="P36" t="n">
-        <v>22.3</v>
+        <v>52.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="R36" t="n">
-        <v>15.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S36" t="n">
-        <v>43.7</v>
+        <v>19.2</v>
       </c>
       <c r="T36" t="n">
-        <v>79.3</v>
+        <v>20.9</v>
       </c>
       <c r="U36" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3355,81 +3359,77 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>611</v>
+        <v>3520</v>
       </c>
       <c r="F37" t="n">
-        <v>19.55</v>
+        <v>88.52</v>
       </c>
       <c r="G37" t="n">
-        <v>10.25</v>
+        <v>22.17</v>
       </c>
       <c r="H37" t="n">
-        <v>19</v>
+        <v>70.2</v>
       </c>
       <c r="I37" t="n">
+        <v>49</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
         <v>10</v>
       </c>
-      <c r="J37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="M37" t="n">
-        <v>615</v>
+        <v>3200</v>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>⚠️高槓桿(負債80%)</t>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>52.4</v>
+        <v>25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.91</v>
+        <v>0.92</v>
       </c>
       <c r="R37" t="n">
-        <v>9.699999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="S37" t="n">
-        <v>19.2</v>
+        <v>37.7</v>
       </c>
       <c r="T37" t="n">
-        <v>20.9</v>
+        <v>104.6</v>
       </c>
       <c r="U37" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3441,22 +3441,22 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>3200</v>
+        <v>4830</v>
       </c>
       <c r="F38" t="n">
-        <v>88.8</v>
+        <v>95.34</v>
       </c>
       <c r="G38" t="n">
-        <v>22.24</v>
+        <v>32.85</v>
       </c>
       <c r="H38" t="n">
-        <v>70.2</v>
+        <v>75.3</v>
       </c>
       <c r="I38" t="n">
-        <v>49</v>
+        <v>59.7</v>
       </c>
       <c r="J38" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3464,34 +3464,34 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.31</v>
+        <v>9.9</v>
       </c>
       <c r="M38" t="n">
-        <v>3210</v>
+        <v>4395</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="R38" t="n">
-        <v>23.2</v>
+        <v>25.1</v>
       </c>
       <c r="S38" t="n">
-        <v>37.7</v>
+        <v>114.6</v>
       </c>
       <c r="T38" t="n">
-        <v>104.6</v>
+        <v>120.3</v>
       </c>
       <c r="U38" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3517,25 +3517,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>4395</v>
+        <v>692</v>
       </c>
       <c r="F39" t="n">
-        <v>97.51000000000001</v>
+        <v>45.91</v>
       </c>
       <c r="G39" t="n">
-        <v>33.59</v>
+        <v>25.61</v>
       </c>
       <c r="H39" t="n">
-        <v>75.3</v>
+        <v>47.5</v>
       </c>
       <c r="I39" t="n">
-        <v>59.7</v>
+        <v>20.2</v>
       </c>
       <c r="J39" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3543,34 +3543,38 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-2.22</v>
+        <v>3.59</v>
       </c>
       <c r="M39" t="n">
-        <v>4495</v>
+        <v>668</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>月營收轉負-9%</t>
+        </is>
+      </c>
       <c r="P39" t="n">
-        <v>34.5</v>
+        <v>53.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.76</v>
+        <v>1.12</v>
       </c>
       <c r="R39" t="n">
-        <v>25.1</v>
+        <v>28.3</v>
       </c>
       <c r="S39" t="n">
-        <v>114.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>120.3</v>
+        <v>57.1</v>
       </c>
       <c r="U39" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -3582,12 +3586,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3596,25 +3600,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>668</v>
+        <v>99.5</v>
       </c>
       <c r="F40" t="n">
-        <v>45.02</v>
+        <v>11.58</v>
       </c>
       <c r="G40" t="n">
-        <v>25.12</v>
+        <v>1.81</v>
       </c>
       <c r="H40" t="n">
-        <v>47.5</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>20.2</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3622,79 +3626,75 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.98</v>
+        <v>1.12</v>
       </c>
       <c r="M40" t="n">
-        <v>655</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>53.6</v>
+        <v>17.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.12</v>
+        <v>2.11</v>
       </c>
       <c r="R40" t="n">
-        <v>28.3</v>
+        <v>5.3</v>
       </c>
       <c r="S40" t="n">
-        <v>-9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="T40" t="n">
-        <v>57.1</v>
+        <v>11.6</v>
       </c>
       <c r="U40" t="n">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>98.40000000000001</v>
+        <v>184.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11.59</v>
+        <v>14.07</v>
       </c>
       <c r="G41" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="J41" t="n">
         <v>2.02</v>
@@ -3705,34 +3705,38 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.1</v>
+        <v>3.65</v>
       </c>
       <c r="M41" t="n">
-        <v>98.5</v>
+        <v>178</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+        </is>
+      </c>
       <c r="P41" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R41" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="S41" t="n">
-        <v>7.7</v>
+        <v>4.2</v>
       </c>
       <c r="T41" t="n">
-        <v>11.6</v>
+        <v>14.4</v>
       </c>
       <c r="U41" t="n">
         <v>2.02</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -3744,12 +3748,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3758,25 +3762,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>178</v>
+        <v>108.5</v>
       </c>
       <c r="F42" t="n">
-        <v>14.35</v>
+        <v>16.08</v>
       </c>
       <c r="G42" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="H42" t="n">
-        <v>13.4</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J42" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3784,55 +3788,51 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-1.93</v>
+        <v>-0.46</v>
       </c>
       <c r="M42" t="n">
-        <v>181.5</v>
+        <v>109</v>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
-        </is>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>17.6</v>
+        <v>20.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="R42" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="T42" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="U42" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3841,25 +3841,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>109</v>
+        <v>531</v>
       </c>
       <c r="F43" t="n">
-        <v>16.08</v>
+        <v>15.15</v>
       </c>
       <c r="G43" t="n">
-        <v>3.38</v>
+        <v>2.16</v>
       </c>
       <c r="H43" t="n">
-        <v>16</v>
+        <v>21.4</v>
       </c>
       <c r="I43" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3867,34 +3867,38 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M43" t="n">
-        <v>109</v>
+        <v>500</v>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P43" t="n">
-        <v>20.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="R43" t="n">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="S43" t="n">
-        <v>1.4</v>
+        <v>30.2</v>
       </c>
       <c r="T43" t="n">
-        <v>17.2</v>
+        <v>23.4</v>
       </c>
       <c r="U43" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -3906,12 +3910,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3920,25 +3924,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>500</v>
+        <v>207.5</v>
       </c>
       <c r="F44" t="n">
-        <v>15.73</v>
+        <v>29.81</v>
       </c>
       <c r="G44" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="H44" t="n">
-        <v>21.4</v>
+        <v>30.9</v>
       </c>
       <c r="I44" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3946,34 +3950,34 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-3.66</v>
+        <v>3.75</v>
       </c>
       <c r="M44" t="n">
-        <v>519</v>
+        <v>200</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>含金量0.5差</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>14.3</v>
+        <v>9.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.02</v>
+        <v>0.49</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="S44" t="n">
-        <v>30.2</v>
+        <v>8.4</v>
       </c>
       <c r="T44" t="n">
-        <v>23.4</v>
+        <v>36.5</v>
       </c>
       <c r="U44" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3982,46 +3986,46 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>200</v>
+        <v>3490</v>
       </c>
       <c r="F45" t="n">
-        <v>28.91</v>
+        <v>49.32</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66</v>
+        <v>6.36</v>
       </c>
       <c r="H45" t="n">
-        <v>30.9</v>
+        <v>51.7</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>23.4</v>
       </c>
       <c r="J45" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4029,138 +4033,132 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.09</v>
+        <v>3.71</v>
       </c>
       <c r="M45" t="n">
-        <v>194</v>
+        <v>3365</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>含金量0.5差</t>
+          <t>含金量0.3差、月營收轉負-34%</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>9.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="R45" t="n">
-        <v>7.6</v>
+        <v>31.2</v>
       </c>
       <c r="S45" t="n">
-        <v>8.4</v>
+        <v>-33.5</v>
       </c>
       <c r="T45" t="n">
-        <v>36.5</v>
+        <v>63.8</v>
       </c>
       <c r="U45" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>3365</v>
+        <v>273</v>
       </c>
       <c r="F46" t="n">
-        <v>51</v>
+        <v>30.69</v>
       </c>
       <c r="G46" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="H46" t="n">
-        <v>51.7</v>
-      </c>
+        <v>4.55</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.73</v>
-      </c>
+        <v>24.9</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-3.3</v>
+        <v>2.82</v>
       </c>
       <c r="M46" t="n">
-        <v>3480</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
-        </is>
-      </c>
+        <v>265.5</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.26</v>
+        <v>1.04</v>
       </c>
       <c r="R46" t="n">
-        <v>31.2</v>
+        <v>3.2</v>
       </c>
       <c r="S46" t="n">
-        <v>-33.5</v>
+        <v>30</v>
       </c>
       <c r="T46" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.73</v>
-      </c>
+        <v>43.5</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4169,20 +4167,20 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>265.5</v>
+        <v>117</v>
       </c>
       <c r="F47" t="n">
-        <v>33.29</v>
+        <v>25.97</v>
       </c>
       <c r="G47" t="n">
-        <v>4.93</v>
+        <v>2.67</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>24.9</v>
+        <v>11</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4191,10 +4189,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-7.81</v>
+        <v>3.08</v>
       </c>
       <c r="M47" t="n">
-        <v>288</v>
+        <v>113.5</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4203,19 +4201,19 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>13.7</v>
+        <v>10.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="R47" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="S47" t="n">
-        <v>30</v>
+        <v>48.7</v>
       </c>
       <c r="T47" t="n">
-        <v>43.5</v>
+        <v>28.4</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -4232,12 +4230,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4246,20 +4244,20 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48" t="n">
-        <v>113.5</v>
+        <v>160</v>
       </c>
       <c r="F48" t="n">
-        <v>27.12</v>
+        <v>32.37</v>
       </c>
       <c r="G48" t="n">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4268,36 +4266,40 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-4.22</v>
+        <v>1.91</v>
       </c>
       <c r="M48" t="n">
-        <v>118.5</v>
+        <v>157</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P48" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="R48" t="n">
-        <v>3.8</v>
+        <v>22.1</v>
       </c>
       <c r="S48" t="n">
-        <v>48.7</v>
+        <v>14.6</v>
       </c>
       <c r="T48" t="n">
-        <v>28.4</v>
+        <v>34.2</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -4309,12 +4311,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4323,20 +4325,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E49" t="n">
-        <v>157</v>
+        <v>228.5</v>
       </c>
       <c r="F49" t="n">
-        <v>32.68</v>
+        <v>23.29</v>
       </c>
       <c r="G49" t="n">
-        <v>1.77</v>
+        <v>5.67</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4345,40 +4347,36 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-0.95</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>158.5</v>
+        <v>208</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R49" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S49" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T49" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4390,34 +4388,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E50" t="n">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="F50" t="n">
-        <v>24.3</v>
+        <v>34.66</v>
       </c>
       <c r="G50" t="n">
-        <v>5.92</v>
+        <v>3.25</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>9.6</v>
+        <v>-15.3</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4426,31 +4424,31 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-4.15</v>
+        <v>4.26</v>
       </c>
       <c r="M50" t="n">
-        <v>217</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>EPS單期衰退</t>
+        </is>
+      </c>
       <c r="P50" t="n">
-        <v>30.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="R50" t="n">
-        <v>20.4</v>
+        <v>13.2</v>
       </c>
       <c r="S50" t="n">
-        <v>812.4</v>
+        <v>34.8</v>
       </c>
       <c r="T50" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4460,19 +4458,19 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4481,21 +4479,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E51" t="n">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="F51" t="n">
-        <v>34.59</v>
+        <v>34.11</v>
       </c>
       <c r="G51" t="n">
-        <v>3.24</v>
+        <v>6.12</v>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="n">
-        <v>-15.3</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -4503,31 +4499,35 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.21</v>
+        <v>6.3</v>
       </c>
       <c r="M51" t="n">
-        <v>234.5</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
+        <v>381</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>9.4</v>
+        <v>17.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>13.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S51" t="n">
-        <v>34.8</v>
+        <v>730.1</v>
       </c>
       <c r="T51" t="n">
-        <v>34.5</v>
+        <v>45.2</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4561,13 @@
         <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>709</v>
+        <v>753</v>
       </c>
       <c r="F52" t="n">
-        <v>25.85</v>
+        <v>25.52</v>
       </c>
       <c r="G52" t="n">
-        <v>8.19</v>
+        <v>8.09</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.25</v>
+        <v>6.21</v>
       </c>
       <c r="M52" t="n">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4642,13 +4642,13 @@
         <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>115</v>
+        <v>119.5</v>
       </c>
       <c r="F53" t="n">
-        <v>26.63</v>
+        <v>25.84</v>
       </c>
       <c r="G53" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.95</v>
+        <v>3.91</v>
       </c>
       <c r="M53" t="n">
-        <v>118.5</v>
+        <v>115</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4723,13 +4723,13 @@
         <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>3875</v>
+        <v>3985</v>
       </c>
       <c r="F54" t="n">
-        <v>25.03</v>
+        <v>24.19</v>
       </c>
       <c r="G54" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-3.37</v>
+        <v>2.84</v>
       </c>
       <c r="M54" t="n">
-        <v>4010</v>
+        <v>3875</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4804,13 +4804,13 @@
         <v>97</v>
       </c>
       <c r="E55" t="n">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="F55" t="n">
-        <v>34.52</v>
+        <v>32.99</v>
       </c>
       <c r="G55" t="n">
-        <v>6.84</v>
+        <v>6.53</v>
       </c>
       <c r="H55" t="n">
         <v>29.3</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-4.43</v>
+        <v>4.25</v>
       </c>
       <c r="M55" t="n">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4883,13 +4883,13 @@
         <v>91</v>
       </c>
       <c r="E56" t="n">
-        <v>728</v>
+        <v>750</v>
       </c>
       <c r="F56" t="n">
-        <v>50.64</v>
+        <v>49.36</v>
       </c>
       <c r="G56" t="n">
-        <v>7.86</v>
+        <v>7.66</v>
       </c>
       <c r="H56" t="n">
         <v>46.1</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-2.54</v>
+        <v>3.02</v>
       </c>
       <c r="M56" t="n">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4962,13 +4962,13 @@
         <v>79</v>
       </c>
       <c r="E57" t="n">
-        <v>64</v>
+        <v>65.2</v>
       </c>
       <c r="F57" t="n">
-        <v>16.05</v>
+        <v>15.69</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H57" t="n">
         <v>17.3</v>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-2.29</v>
+        <v>1.88</v>
       </c>
       <c r="M57" t="n">
-        <v>65.5</v>
+        <v>64</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -5041,13 +5041,13 @@
         <v>77</v>
       </c>
       <c r="E58" t="n">
-        <v>162.5</v>
+        <v>165</v>
       </c>
       <c r="F58" t="n">
-        <v>15.02</v>
+        <v>15.3</v>
       </c>
       <c r="G58" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H58" t="n">
         <v>15.5</v>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="M58" t="n">
-        <v>159.5</v>
+        <v>162.5</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -5120,13 +5120,13 @@
         <v>96</v>
       </c>
       <c r="E59" t="n">
-        <v>344.5</v>
+        <v>354</v>
       </c>
       <c r="F59" t="n">
-        <v>18.88</v>
+        <v>18.63</v>
       </c>
       <c r="G59" t="n">
-        <v>5.59</v>
+        <v>5.51</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1.29</v>
+        <v>2.76</v>
       </c>
       <c r="M59" t="n">
-        <v>349</v>
+        <v>344.5</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5197,13 +5197,13 @@
         <v>94</v>
       </c>
       <c r="E60" t="n">
-        <v>157.5</v>
+        <v>162.5</v>
       </c>
       <c r="F60" t="n">
-        <v>19.26</v>
+        <v>19.14</v>
       </c>
       <c r="G60" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-0.63</v>
+        <v>3.17</v>
       </c>
       <c r="M60" t="n">
-        <v>158.5</v>
+        <v>157.5</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5274,13 +5274,13 @@
         <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="F61" t="n">
-        <v>16.1</v>
+        <v>16.18</v>
       </c>
       <c r="G61" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.51</v>
+        <v>1.51</v>
       </c>
       <c r="M61" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>87.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="F62" t="n">
-        <v>18.21</v>
+        <v>17.89</v>
       </c>
       <c r="G62" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1.8</v>
+        <v>2.18</v>
       </c>
       <c r="M62" t="n">
-        <v>88.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>42</v>
+        <v>43.85</v>
       </c>
       <c r="F63" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="G63" t="n">
         <v>1.19</v>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-0.71</v>
+        <v>4.4</v>
       </c>
       <c r="M63" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>182.5</v>
+        <v>193</v>
       </c>
       <c r="F64" t="n">
-        <v>16.17</v>
+        <v>16.58</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.53</v>
+        <v>5.75</v>
       </c>
       <c r="M64" t="n">
-        <v>178</v>
+        <v>182.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="F65" t="n">
-        <v>16.99</v>
+        <v>17.49</v>
       </c>
       <c r="G65" t="n">
-        <v>16.06</v>
+        <v>16.53</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.92</v>
+        <v>1.7</v>
       </c>
       <c r="M65" t="n">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>46.95</v>
+        <v>47.6</v>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>17.85</v>
       </c>
       <c r="G66" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.84</v>
+        <v>1.38</v>
       </c>
       <c r="M66" t="n">
-        <v>47.35</v>
+        <v>46.95</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5759,10 +5759,10 @@
         <v>145.5</v>
       </c>
       <c r="F67" t="n">
-        <v>17.46</v>
+        <v>15.78</v>
       </c>
       <c r="G67" t="n">
-        <v>5.14</v>
+        <v>4.64</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-9.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>161</v>
+        <v>145.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F68" t="n">
-        <v>23.84</v>
+        <v>23.08</v>
       </c>
       <c r="G68" t="n">
-        <v>5.66</v>
+        <v>5.48</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-3.2</v>
+        <v>0.55</v>
       </c>
       <c r="M68" t="n">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F69" t="n">
-        <v>17.53</v>
+        <v>17.67</v>
       </c>
       <c r="G69" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.82</v>
+        <v>1.63</v>
       </c>
       <c r="M69" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>301</v>
+        <v>307.5</v>
       </c>
       <c r="F70" t="n">
-        <v>29.71</v>
+        <v>29.37</v>
       </c>
       <c r="G70" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.15</v>
+        <v>2.16</v>
       </c>
       <c r="M70" t="n">
-        <v>304.5</v>
+        <v>301</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6075,7 +6075,7 @@
         <v>91</v>
       </c>
       <c r="F71" t="n">
-        <v>19.14</v>
+        <v>19.12</v>
       </c>
       <c r="G71" t="n">
         <v>2.09</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F72" t="n">
-        <v>19.85</v>
+        <v>19.1</v>
       </c>
       <c r="G72" t="n">
-        <v>5.42</v>
+        <v>5.21</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-3.78</v>
+        <v>2.86</v>
       </c>
       <c r="M72" t="n">
-        <v>145.5</v>
+        <v>140</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,10 +6234,10 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>234.5</v>
+        <v>246</v>
       </c>
       <c r="F73" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="G73" t="n">
         <v>1.84</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.21</v>
+        <v>4.9</v>
       </c>
       <c r="M73" t="n">
-        <v>234</v>
+        <v>234.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="F74" t="n">
-        <v>58.67</v>
+        <v>60.76</v>
       </c>
       <c r="G74" t="n">
-        <v>30.54</v>
+        <v>31.63</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="M74" t="n">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>57.2</v>
+        <v>60.1</v>
       </c>
       <c r="F75" t="n">
-        <v>22.24</v>
+        <v>21.75</v>
       </c>
       <c r="G75" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-2.22</v>
+        <v>5.07</v>
       </c>
       <c r="M75" t="n">
-        <v>58.5</v>
+        <v>57.2</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2135</v>
+        <v>2320</v>
       </c>
       <c r="F76" t="n">
-        <v>36.15</v>
+        <v>35.08</v>
       </c>
       <c r="G76" t="n">
-        <v>19.12</v>
+        <v>18.56</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-2.95</v>
+        <v>8.67</v>
       </c>
       <c r="M76" t="n">
-        <v>2200</v>
+        <v>2135</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="F77" t="n">
-        <v>22.18</v>
+        <v>21.51</v>
       </c>
       <c r="G77" t="n">
-        <v>8.6</v>
+        <v>8.34</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-3</v>
+        <v>5.16</v>
       </c>
       <c r="M77" t="n">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2320</v>
+        <v>2410</v>
       </c>
       <c r="F78" t="n">
-        <v>30.79</v>
+        <v>31.19</v>
       </c>
       <c r="G78" t="n">
-        <v>10.08</v>
+        <v>10.21</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.31</v>
+        <v>3.88</v>
       </c>
       <c r="M78" t="n">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>103.5</v>
+        <v>107</v>
       </c>
       <c r="F79" t="n">
-        <v>15.07</v>
+        <v>15.22</v>
       </c>
       <c r="G79" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.98</v>
+        <v>3.38</v>
       </c>
       <c r="M79" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>106</v>
+        <v>109.5</v>
       </c>
       <c r="F80" t="n">
         <v>14.34</v>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M80" t="n">
         <v>106</v>
@@ -6872,7 +6872,7 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="F81" t="n">
         <v>5.61</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="M81" t="n">
         <v>28</v>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="F82" t="n">
-        <v>11.91</v>
+        <v>11.8</v>
       </c>
       <c r="G82" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
       <c r="M82" t="n">
-        <v>110.5</v>
+        <v>109.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>175.5</v>
+        <v>179</v>
       </c>
       <c r="F83" t="n">
-        <v>12.99</v>
+        <v>13.03</v>
       </c>
       <c r="G83" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.29</v>
+        <v>1.99</v>
       </c>
       <c r="M83" t="n">
-        <v>175</v>
+        <v>175.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,7 +7109,7 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="F84" t="n">
         <v>7.82</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M84" t="n">
         <v>41.2</v>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1080</v>
+        <v>1165</v>
       </c>
       <c r="F85" t="n">
-        <v>32.46</v>
+        <v>32.02</v>
       </c>
       <c r="G85" t="n">
-        <v>10.88</v>
+        <v>10.73</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-1.37</v>
+        <v>7.87</v>
       </c>
       <c r="M85" t="n">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>388</v>
+        <v>404.5</v>
       </c>
       <c r="F86" t="n">
-        <v>19.31</v>
+        <v>18.85</v>
       </c>
       <c r="G86" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-2.39</v>
+        <v>4.25</v>
       </c>
       <c r="M86" t="n">
-        <v>397.5</v>
+        <v>388</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>125.5</v>
+        <v>128.5</v>
       </c>
       <c r="F87" t="n">
-        <v>15.51</v>
+        <v>15.32</v>
       </c>
       <c r="G87" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-1.18</v>
+        <v>2.39</v>
       </c>
       <c r="M87" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,10 +7425,10 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>37.5</v>
+        <v>38.15</v>
       </c>
       <c r="F88" t="n">
-        <v>8.210000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="G88" t="n">
         <v>1.12</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.4</v>
+        <v>1.73</v>
       </c>
       <c r="M88" t="n">
-        <v>37.35</v>
+        <v>37.5</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,7 +7504,7 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2090</v>
+        <v>2220</v>
       </c>
       <c r="F89" t="n">
         <v>39.52</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="M89" t="n">
         <v>2090</v>
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>858</v>
+        <v>926</v>
       </c>
       <c r="F90" t="n">
-        <v>26.35</v>
+        <v>24.76</v>
       </c>
       <c r="G90" t="n">
-        <v>6.33</v>
+        <v>5.95</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-6.02</v>
+        <v>7.93</v>
       </c>
       <c r="M90" t="n">
-        <v>913</v>
+        <v>858</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>86</v>
+        <v>88.5</v>
       </c>
       <c r="F91" t="n">
-        <v>10.37</v>
+        <v>10.31</v>
       </c>
       <c r="G91" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-0.58</v>
+        <v>2.91</v>
       </c>
       <c r="M91" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,10 +7753,10 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>69.8</v>
+        <v>72.2</v>
       </c>
       <c r="F92" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="G92" t="n">
         <v>1.75</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.43</v>
+        <v>3.44</v>
       </c>
       <c r="M92" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>56.7</v>
+        <v>58</v>
       </c>
       <c r="F93" t="n">
-        <v>10.59</v>
+        <v>10.54</v>
       </c>
       <c r="G93" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.53</v>
+        <v>2.29</v>
       </c>
       <c r="M93" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F94" t="n">
-        <v>16.37</v>
+        <v>15.89</v>
       </c>
       <c r="G94" t="n">
-        <v>6.05</v>
+        <v>5.87</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-2.92</v>
+        <v>2.53</v>
       </c>
       <c r="M94" t="n">
-        <v>325.5</v>
+        <v>316</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>4685</v>
+        <v>5000</v>
       </c>
       <c r="F95" t="n">
-        <v>15.49</v>
+        <v>15.7</v>
       </c>
       <c r="G95" t="n">
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.41</v>
+        <v>6.72</v>
       </c>
       <c r="M95" t="n">
-        <v>4620</v>
+        <v>4685</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>143.5</v>
+        <v>149.5</v>
       </c>
       <c r="F96" t="n">
-        <v>13.94</v>
+        <v>14.39</v>
       </c>
       <c r="G96" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.24</v>
+        <v>4.18</v>
       </c>
       <c r="M96" t="n">
-        <v>139</v>
+        <v>143.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="F97" t="n">
-        <v>17.61</v>
+        <v>18.04</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.44</v>
+        <v>-4.08</v>
       </c>
       <c r="M97" t="n">
-        <v>1435</v>
+        <v>1470</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="G98" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.77</v>
+        <v>3.62</v>
       </c>
       <c r="M98" t="n">
-        <v>67.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>348.5</v>
+        <v>368.5</v>
       </c>
       <c r="F99" t="n">
-        <v>7.32</v>
+        <v>6.96</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22</v>
+        <v>4.01</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-4.91</v>
+        <v>5.74</v>
       </c>
       <c r="M99" t="n">
-        <v>366.5</v>
+        <v>348.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,10 +8409,10 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.55</v>
+        <v>23.6</v>
       </c>
       <c r="F100" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="G100" t="n">
         <v>1.42</v>
@@ -8431,7 +8431,7 @@
         <v>0.21</v>
       </c>
       <c r="M100" t="n">
-        <v>23.5</v>
+        <v>23.55</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>184</v>
+        <v>191.5</v>
       </c>
       <c r="F101" t="n">
-        <v>9.26</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G101" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-3.16</v>
+        <v>4.08</v>
       </c>
       <c r="M101" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2135</v>
+        <v>2320</v>
       </c>
       <c r="F2" t="n">
-        <v>36.15</v>
+        <v>35.08</v>
       </c>
       <c r="G2" t="n">
-        <v>19.12</v>
+        <v>18.56</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.95</v>
+        <v>8.67</v>
       </c>
       <c r="M2" t="n">
-        <v>2200</v>
+        <v>2135</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="F3" t="n">
-        <v>22.18</v>
+        <v>21.51</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>8.34</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-3</v>
+        <v>5.16</v>
       </c>
       <c r="M3" t="n">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2320</v>
+        <v>2410</v>
       </c>
       <c r="F4" t="n">
-        <v>30.79</v>
+        <v>31.19</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08</v>
+        <v>10.21</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>3.88</v>
       </c>
       <c r="M4" t="n">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>103.5</v>
+        <v>107</v>
       </c>
       <c r="F5" t="n">
-        <v>15.07</v>
+        <v>15.22</v>
       </c>
       <c r="G5" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.98</v>
+        <v>3.38</v>
       </c>
       <c r="M5" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,7 +9018,7 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>106</v>
+        <v>109.5</v>
       </c>
       <c r="F6" t="n">
         <v>14.34</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
         <v>106</v>
@@ -9097,7 +9097,7 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="F7" t="n">
         <v>5.61</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="M7" t="n">
         <v>28</v>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.91</v>
+        <v>11.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
       <c r="M8" t="n">
-        <v>110.5</v>
+        <v>109.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>175.5</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>12.99</v>
+        <v>13.03</v>
       </c>
       <c r="G9" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>1.99</v>
       </c>
       <c r="M9" t="n">
-        <v>175</v>
+        <v>175.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,7 +9334,7 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="F10" t="n">
         <v>7.82</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M10" t="n">
         <v>41.2</v>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1080</v>
+        <v>1165</v>
       </c>
       <c r="F11" t="n">
-        <v>32.46</v>
+        <v>32.02</v>
       </c>
       <c r="G11" t="n">
-        <v>10.88</v>
+        <v>10.73</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.37</v>
+        <v>7.87</v>
       </c>
       <c r="M11" t="n">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>388</v>
+        <v>404.5</v>
       </c>
       <c r="F12" t="n">
-        <v>19.31</v>
+        <v>18.85</v>
       </c>
       <c r="G12" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-2.39</v>
+        <v>4.25</v>
       </c>
       <c r="M12" t="n">
-        <v>397.5</v>
+        <v>388</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>125.5</v>
+        <v>128.5</v>
       </c>
       <c r="F13" t="n">
-        <v>15.51</v>
+        <v>15.32</v>
       </c>
       <c r="G13" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.18</v>
+        <v>2.39</v>
       </c>
       <c r="M13" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>37.5</v>
+        <v>38.15</v>
       </c>
       <c r="F14" t="n">
-        <v>8.210000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="G14" t="n">
         <v>1.12</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.4</v>
+        <v>1.73</v>
       </c>
       <c r="M14" t="n">
-        <v>37.35</v>
+        <v>37.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,7 +9729,7 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2090</v>
+        <v>2220</v>
       </c>
       <c r="F15" t="n">
         <v>39.52</v>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="M15" t="n">
         <v>2090</v>
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>858</v>
+        <v>926</v>
       </c>
       <c r="F16" t="n">
-        <v>26.35</v>
+        <v>24.76</v>
       </c>
       <c r="G16" t="n">
-        <v>6.33</v>
+        <v>5.95</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-6.02</v>
+        <v>7.93</v>
       </c>
       <c r="M16" t="n">
-        <v>913</v>
+        <v>858</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>86</v>
+        <v>88.5</v>
       </c>
       <c r="F17" t="n">
-        <v>10.37</v>
+        <v>10.31</v>
       </c>
       <c r="G17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.58</v>
+        <v>2.91</v>
       </c>
       <c r="M17" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,10 +9978,10 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>69.8</v>
+        <v>72.2</v>
       </c>
       <c r="F18" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="G18" t="n">
         <v>1.75</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.43</v>
+        <v>3.44</v>
       </c>
       <c r="M18" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>56.7</v>
+        <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>10.59</v>
+        <v>10.54</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.53</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F20" t="n">
-        <v>16.37</v>
+        <v>15.89</v>
       </c>
       <c r="G20" t="n">
-        <v>6.05</v>
+        <v>5.87</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.92</v>
+        <v>2.53</v>
       </c>
       <c r="M20" t="n">
-        <v>325.5</v>
+        <v>316</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>4685</v>
+        <v>5000</v>
       </c>
       <c r="F21" t="n">
-        <v>15.49</v>
+        <v>15.7</v>
       </c>
       <c r="G21" t="n">
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>6.72</v>
       </c>
       <c r="M21" t="n">
-        <v>4620</v>
+        <v>4685</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>143.5</v>
+        <v>149.5</v>
       </c>
       <c r="F22" t="n">
-        <v>13.94</v>
+        <v>14.39</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.24</v>
+        <v>4.18</v>
       </c>
       <c r="M22" t="n">
-        <v>139</v>
+        <v>143.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="F23" t="n">
-        <v>17.61</v>
+        <v>18.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.44</v>
+        <v>-4.08</v>
       </c>
       <c r="M23" t="n">
-        <v>1435</v>
+        <v>1470</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10610,10 +10610,10 @@
         <v>145.5</v>
       </c>
       <c r="F2" t="n">
-        <v>17.46</v>
+        <v>15.78</v>
       </c>
       <c r="G2" t="n">
-        <v>5.14</v>
+        <v>4.64</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-9.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>161</v>
+        <v>145.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F3" t="n">
-        <v>23.84</v>
+        <v>23.08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.66</v>
+        <v>5.48</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-3.2</v>
+        <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>17.53</v>
+        <v>17.67</v>
       </c>
       <c r="G4" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.82</v>
+        <v>1.63</v>
       </c>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>301</v>
+        <v>307.5</v>
       </c>
       <c r="F5" t="n">
-        <v>29.71</v>
+        <v>29.37</v>
       </c>
       <c r="G5" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.15</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>304.5</v>
+        <v>301</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10926,7 +10926,7 @@
         <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>19.14</v>
+        <v>19.12</v>
       </c>
       <c r="G6" t="n">
         <v>2.09</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F7" t="n">
-        <v>19.85</v>
+        <v>19.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.42</v>
+        <v>5.21</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-3.78</v>
+        <v>2.86</v>
       </c>
       <c r="M7" t="n">
-        <v>145.5</v>
+        <v>140</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,10 +11085,10 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>234.5</v>
+        <v>246</v>
       </c>
       <c r="F8" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="G8" t="n">
         <v>1.84</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.21</v>
+        <v>4.9</v>
       </c>
       <c r="M8" t="n">
-        <v>234</v>
+        <v>234.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="F9" t="n">
-        <v>58.67</v>
+        <v>60.76</v>
       </c>
       <c r="G9" t="n">
-        <v>30.54</v>
+        <v>31.63</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="M9" t="n">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>57.2</v>
+        <v>60.1</v>
       </c>
       <c r="F10" t="n">
-        <v>22.24</v>
+        <v>21.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.22</v>
+        <v>5.07</v>
       </c>
       <c r="M10" t="n">
-        <v>58.5</v>
+        <v>57.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="F2" t="n">
-        <v>72.40000000000001</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>20.32</v>
+        <v>19.44</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-4.33</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1015</v>
+        <v>971</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,7 +11538,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="F3" t="n">
         <v>11.05</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="M3" t="n">
         <v>39.1</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>159.5</v>
+        <v>163</v>
       </c>
       <c r="F4" t="n">
-        <v>19.48</v>
+        <v>18.44</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.07</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-5.34</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>168.5</v>
+        <v>159.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5455</v>
+        <v>5875</v>
       </c>
       <c r="F5" t="n">
-        <v>149.09</v>
+        <v>145.23</v>
       </c>
       <c r="G5" t="n">
-        <v>34.83</v>
+        <v>33.92</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.59</v>
+        <v>7.7</v>
       </c>
       <c r="M5" t="n">
-        <v>5600</v>
+        <v>5455</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11782,10 +11782,10 @@
         <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>22.52</v>
+        <v>22.72</v>
       </c>
       <c r="G6" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>107.5</v>
       </c>
       <c r="F7" t="n">
-        <v>29.88</v>
+        <v>30.32</v>
       </c>
       <c r="G7" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>3.37</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>104</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F8" t="n">
-        <v>33.05</v>
+        <v>31.76</v>
       </c>
       <c r="G8" t="n">
-        <v>6.41</v>
+        <v>6.15</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-3.93</v>
+        <v>3.37</v>
       </c>
       <c r="M8" t="n">
-        <v>216.5</v>
+        <v>208</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>26.14</v>
+        <v>26.52</v>
       </c>
       <c r="G9" t="n">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>-2.39</v>
       </c>
       <c r="M9" t="n">
-        <v>103</v>
+        <v>104.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>18.27</v>
+        <v>18.03</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.32</v>
+        <v>2.67</v>
       </c>
       <c r="M10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="F11" t="n">
-        <v>27.69</v>
+        <v>29.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.98</v>
+        <v>5.25</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.53</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>1265</v>
+        <v>1335</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>167.5</v>
+        <v>169.5</v>
       </c>
       <c r="F12" t="n">
-        <v>24.07</v>
+        <v>20.89</v>
       </c>
       <c r="G12" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-4.01</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>174.5</v>
+        <v>167.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>193.5</v>
+        <v>207</v>
       </c>
       <c r="F13" t="n">
-        <v>28.9</v>
+        <v>28.46</v>
       </c>
       <c r="G13" t="n">
-        <v>5.06</v>
+        <v>4.98</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.53</v>
+        <v>6.98</v>
       </c>
       <c r="M13" t="n">
-        <v>196.5</v>
+        <v>193.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12430,10 +12430,10 @@
         <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>27.44</v>
+        <v>27.63</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15</v>
+        <v>22.2</v>
       </c>
       <c r="G15" t="n">
-        <v>5.44</v>
+        <v>5.45</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.21</v>
+        <v>-0.21</v>
       </c>
       <c r="M15" t="n">
-        <v>243</v>
+        <v>243.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>3745</v>
+        <v>4115</v>
       </c>
       <c r="F16" t="n">
-        <v>115.37</v>
+        <v>112.67</v>
       </c>
       <c r="G16" t="n">
-        <v>35.24</v>
+        <v>34.41</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2.35</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>3835</v>
+        <v>3745</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1705</v>
+        <v>1835</v>
       </c>
       <c r="F2" t="n">
-        <v>64.16</v>
+        <v>62.87</v>
       </c>
       <c r="G2" t="n">
-        <v>15.09</v>
+        <v>14.78</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.01</v>
+        <v>7.62</v>
       </c>
       <c r="M2" t="n">
-        <v>1740</v>
+        <v>1705</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="F3" t="n">
-        <v>19.55</v>
+        <v>19.43</v>
       </c>
       <c r="G3" t="n">
-        <v>10.25</v>
+        <v>10.19</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.65</v>
+        <v>3.6</v>
       </c>
       <c r="M3" t="n">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3200</v>
+        <v>3520</v>
       </c>
       <c r="F4" t="n">
-        <v>88.8</v>
+        <v>88.52</v>
       </c>
       <c r="G4" t="n">
-        <v>22.24</v>
+        <v>22.17</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.31</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>3210</v>
+        <v>3200</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4395</v>
+        <v>4830</v>
       </c>
       <c r="F5" t="n">
-        <v>97.51000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="G5" t="n">
-        <v>33.59</v>
+        <v>32.85</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.22</v>
+        <v>9.9</v>
       </c>
       <c r="M5" t="n">
-        <v>4495</v>
+        <v>4395</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="F6" t="n">
-        <v>45.02</v>
+        <v>45.91</v>
       </c>
       <c r="G6" t="n">
-        <v>25.12</v>
+        <v>25.61</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.98</v>
+        <v>3.59</v>
       </c>
       <c r="M6" t="n">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>98.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.59</v>
+        <v>11.58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.1</v>
+        <v>1.12</v>
       </c>
       <c r="M7" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>178</v>
+        <v>184.5</v>
       </c>
       <c r="F8" t="n">
-        <v>14.35</v>
+        <v>14.07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.93</v>
+        <v>3.65</v>
       </c>
       <c r="M8" t="n">
-        <v>181.5</v>
+        <v>178</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,7 +13368,7 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>109</v>
+        <v>108.5</v>
       </c>
       <c r="F9" t="n">
         <v>16.08</v>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="M9" t="n">
         <v>109</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F10" t="n">
-        <v>15.73</v>
+        <v>15.15</v>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.66</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>200</v>
+        <v>207.5</v>
       </c>
       <c r="F11" t="n">
-        <v>28.91</v>
+        <v>29.81</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.09</v>
+        <v>3.75</v>
       </c>
       <c r="M11" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3365</v>
+        <v>3490</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>49.32</v>
       </c>
       <c r="G12" t="n">
-        <v>6.58</v>
+        <v>6.36</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-3.3</v>
+        <v>3.71</v>
       </c>
       <c r="M12" t="n">
-        <v>3480</v>
+        <v>3365</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>983</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="n">
-        <v>69.26000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="G2" t="n">
-        <v>19.44</v>
+        <v>19.68</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.2</v>
+        <v>39.25</v>
       </c>
       <c r="F3" t="n">
-        <v>11.05</v>
+        <v>11.07</v>
       </c>
       <c r="G3" t="n">
         <v>1.83</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>153.5</v>
       </c>
       <c r="F4" t="n">
-        <v>18.44</v>
+        <v>18.84</v>
       </c>
       <c r="G4" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>-5.83</v>
       </c>
       <c r="M4" t="n">
-        <v>159.5</v>
+        <v>163</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5875</v>
+        <v>6000</v>
       </c>
       <c r="F5" t="n">
-        <v>145.23</v>
+        <v>156.42</v>
       </c>
       <c r="G5" t="n">
-        <v>33.92</v>
+        <v>36.54</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.7</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>5455</v>
+        <v>5875</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="F6" t="n">
         <v>22.72</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
         <v>112</v>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="F7" t="n">
-        <v>30.32</v>
+        <v>31.34</v>
       </c>
       <c r="G7" t="n">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.37</v>
+        <v>0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>104</v>
+        <v>107.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="F8" t="n">
-        <v>31.76</v>
+        <v>32.82</v>
       </c>
       <c r="G8" t="n">
-        <v>6.15</v>
+        <v>6.36</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.37</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>26.52</v>
+        <v>25.89</v>
       </c>
       <c r="G9" t="n">
-        <v>3.93</v>
+        <v>3.84</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-2.39</v>
+        <v>0.98</v>
       </c>
       <c r="M9" t="n">
-        <v>104.5</v>
+        <v>102</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>18.03</v>
+        <v>18.51</v>
       </c>
       <c r="G10" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.67</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="F11" t="n">
-        <v>29.23</v>
+        <v>29.77</v>
       </c>
       <c r="G11" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>5.15</v>
       </c>
       <c r="M11" t="n">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
-        <v>20.89</v>
+        <v>21.13</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.19</v>
+        <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>167.5</v>
+        <v>169.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>28.46</v>
+        <v>30.44</v>
       </c>
       <c r="G13" t="n">
-        <v>4.98</v>
+        <v>5.33</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.98</v>
+        <v>5.31</v>
       </c>
       <c r="M13" t="n">
-        <v>193.5</v>
+        <v>207</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,7 +1525,7 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>139</v>
+        <v>138.5</v>
       </c>
       <c r="F14" t="n">
         <v>27.63</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="M14" t="n">
         <v>139</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>243</v>
+        <v>239.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.2</v>
+        <v>22.15</v>
       </c>
       <c r="G15" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.21</v>
+        <v>-1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4115</v>
+        <v>4370</v>
       </c>
       <c r="F16" t="n">
-        <v>112.67</v>
+        <v>123.8</v>
       </c>
       <c r="G16" t="n">
-        <v>34.41</v>
+        <v>37.81</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.880000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3745</v>
+        <v>4115</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1260</v>
+        <v>1385</v>
       </c>
       <c r="F17" t="n">
-        <v>46.02</v>
+        <v>47.53</v>
       </c>
       <c r="G17" t="n">
-        <v>13.48</v>
+        <v>13.92</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.28</v>
+        <v>9.92</v>
       </c>
       <c r="M17" t="n">
-        <v>1220</v>
+        <v>1260</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>7975</v>
+        <v>8125</v>
       </c>
       <c r="F18" t="n">
-        <v>68.31</v>
+        <v>70.3</v>
       </c>
       <c r="G18" t="n">
-        <v>23.42</v>
+        <v>24.1</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>7750</v>
+        <v>7975</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="F19" t="n">
-        <v>63.81</v>
+        <v>66.67</v>
       </c>
       <c r="G19" t="n">
-        <v>11.7</v>
+        <v>12.22</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.48</v>
+        <v>4.59</v>
       </c>
       <c r="M19" t="n">
-        <v>647</v>
+        <v>676</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>71.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="F20" t="n">
-        <v>50.29</v>
+        <v>51.88</v>
       </c>
       <c r="G20" t="n">
-        <v>5.97</v>
+        <v>6.16</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.17</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>69.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6655</v>
+        <v>6500</v>
       </c>
       <c r="F21" t="n">
-        <v>123.98</v>
+        <v>136.37</v>
       </c>
       <c r="G21" t="n">
-        <v>33.56</v>
+        <v>36.91</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>-2.33</v>
       </c>
       <c r="M21" t="n">
-        <v>6050</v>
+        <v>6655</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2015</v>
+        <v>2125</v>
       </c>
       <c r="F22" t="n">
-        <v>57.87</v>
+        <v>63.54</v>
       </c>
       <c r="G22" t="n">
-        <v>28.03</v>
+        <v>30.78</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9.81</v>
+        <v>5.46</v>
       </c>
       <c r="M22" t="n">
-        <v>1835</v>
+        <v>2015</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>1235</v>
+        <v>1355</v>
       </c>
       <c r="F23" t="n">
-        <v>81.29000000000001</v>
+        <v>89.23</v>
       </c>
       <c r="G23" t="n">
-        <v>17.99</v>
+        <v>19.75</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>9.779999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>1125</v>
+        <v>1235</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>31.9</v>
+        <v>33.75</v>
       </c>
       <c r="F24" t="n">
-        <v>119.81</v>
+        <v>118.15</v>
       </c>
       <c r="G24" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1.39</v>
+        <v>5.8</v>
       </c>
       <c r="M24" t="n">
-        <v>32.35</v>
+        <v>31.9</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>1515</v>
+        <v>1665</v>
       </c>
       <c r="F25" t="n">
-        <v>188.57</v>
+        <v>199.08</v>
       </c>
       <c r="G25" t="n">
-        <v>31.32</v>
+        <v>33.06</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.57</v>
+        <v>9.9</v>
       </c>
       <c r="M25" t="n">
-        <v>1435</v>
+        <v>1515</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2481,13 +2481,13 @@
         <v>68</v>
       </c>
       <c r="E26" t="n">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="F26" t="n">
-        <v>55.43</v>
+        <v>58.77</v>
       </c>
       <c r="G26" t="n">
-        <v>7.47</v>
+        <v>7.92</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.03</v>
+        <v>3.63</v>
       </c>
       <c r="M26" t="n">
-        <v>597</v>
+        <v>633</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>66</v>
       </c>
       <c r="E27" t="n">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="F27" t="n">
         <v>73.67</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="M27" t="n">
         <v>1175</v>
@@ -2641,13 +2641,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="F28" t="n">
-        <v>61.48</v>
+        <v>64.56</v>
       </c>
       <c r="G28" t="n">
-        <v>11.71</v>
+        <v>12.3</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>6.16</v>
       </c>
       <c r="M28" t="n">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>2645</v>
+        <v>2710</v>
       </c>
       <c r="F29" t="n">
-        <v>75.23999999999999</v>
+        <v>77.59</v>
       </c>
       <c r="G29" t="n">
-        <v>8.58</v>
+        <v>8.84</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.12</v>
+        <v>2.46</v>
       </c>
       <c r="M29" t="n">
-        <v>2565</v>
+        <v>2645</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>427.5</v>
+        <v>458.5</v>
       </c>
       <c r="F30" t="n">
-        <v>115.77</v>
+        <v>127.23</v>
       </c>
       <c r="G30" t="n">
-        <v>10.87</v>
+        <v>11.94</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.9</v>
+        <v>7.25</v>
       </c>
       <c r="M30" t="n">
-        <v>389</v>
+        <v>427.5</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2879,20 +2879,20 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>567</v>
+        <v>253</v>
       </c>
       <c r="F31" t="n">
-        <v>40.03</v>
+        <v>36.14</v>
       </c>
       <c r="G31" t="n">
-        <v>9.029999999999999</v>
+        <v>3.39</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>-2.9</v>
+        <v>-15.3</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>9.880000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="M31" t="n">
-        <v>516</v>
+        <v>245</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
@@ -2913,19 +2913,19 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>22.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="R31" t="n">
-        <v>4.9</v>
+        <v>13.2</v>
       </c>
       <c r="S31" t="n">
-        <v>32.1</v>
+        <v>34.8</v>
       </c>
       <c r="T31" t="n">
-        <v>38.6</v>
+        <v>34.5</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
@@ -2935,19 +2935,19 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-3%)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2956,21 +2956,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E32" t="n">
-        <v>670</v>
+        <v>445.5</v>
       </c>
       <c r="F32" t="n">
-        <v>49.61</v>
+        <v>36.26</v>
       </c>
       <c r="G32" t="n">
-        <v>7.76</v>
+        <v>6.51</v>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>-19.8</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -2978,10 +2976,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.35</v>
+        <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>630</v>
+        <v>405</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2990,23 +2988,23 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
-        <v>5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="S32" t="n">
-        <v>47.5</v>
+        <v>730.1</v>
       </c>
       <c r="T32" t="n">
-        <v>53.2</v>
+        <v>45.2</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
@@ -3023,12 +3021,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3037,19 +3035,21 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E33" t="n">
-        <v>155.5</v>
+        <v>596</v>
       </c>
       <c r="F33" t="n">
-        <v>44.81</v>
+        <v>43.99</v>
       </c>
       <c r="G33" t="n">
-        <v>5.83</v>
+        <v>9.92</v>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -3057,35 +3057,31 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.98</v>
+        <v>5.11</v>
       </c>
       <c r="M33" t="n">
-        <v>151</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-3%</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>11.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.62</v>
+        <v>0.77</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S33" t="n">
-        <v>182</v>
+        <v>32.1</v>
       </c>
       <c r="T33" t="n">
-        <v>65.90000000000001</v>
+        <v>38.6</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
@@ -3095,41 +3091,41 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>3670</v>
+        <v>703</v>
       </c>
       <c r="F34" t="n">
-        <v>53.23</v>
+        <v>52.76</v>
       </c>
       <c r="G34" t="n">
-        <v>13.66</v>
+        <v>8.26</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>16.8</v>
+        <v>-19.8</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -3138,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>9.880000000000001</v>
+        <v>4.93</v>
       </c>
       <c r="M34" t="n">
-        <v>3340</v>
+        <v>670</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3150,23 +3146,23 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>25.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="R34" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>47.5</v>
       </c>
       <c r="T34" t="n">
-        <v>61.7</v>
+        <v>53.2</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3183,71 +3179,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E35" t="n">
-        <v>1835</v>
+        <v>171</v>
       </c>
       <c r="F35" t="n">
-        <v>62.87</v>
+        <v>46.14</v>
       </c>
       <c r="G35" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="H35" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.32</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>7.62</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>1705</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+        <v>155.5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>EPS資料不足、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P35" t="n">
-        <v>22.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>15.2</v>
+        <v>-2.7</v>
       </c>
       <c r="S35" t="n">
-        <v>43.7</v>
+        <v>182</v>
       </c>
       <c r="T35" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.32</v>
-      </c>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3255,102 +3251,100 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>633</v>
+        <v>3850</v>
       </c>
       <c r="F36" t="n">
-        <v>19.43</v>
+        <v>58.49</v>
       </c>
       <c r="G36" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="H36" t="n">
-        <v>19</v>
-      </c>
+        <v>15.01</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.09</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="M36" t="n">
-        <v>611</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>3670</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>⚠️高槓桿(負債80%)</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>52.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>9.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="S36" t="n">
-        <v>19.2</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.09</v>
-      </c>
+        <v>61.7</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3359,25 +3353,25 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E37" t="n">
-        <v>3520</v>
+        <v>1880</v>
       </c>
       <c r="F37" t="n">
-        <v>88.52</v>
+        <v>67.66</v>
       </c>
       <c r="G37" t="n">
-        <v>22.17</v>
+        <v>15.91</v>
       </c>
       <c r="H37" t="n">
-        <v>70.2</v>
+        <v>59.1</v>
       </c>
       <c r="I37" t="n">
-        <v>49</v>
+        <v>34.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3385,30 +3379,30 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>10</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3200</v>
+        <v>1835</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>25</v>
+        <v>22.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.92</v>
+        <v>1.28</v>
       </c>
       <c r="R37" t="n">
-        <v>23.2</v>
+        <v>15.2</v>
       </c>
       <c r="S37" t="n">
-        <v>37.7</v>
+        <v>43.7</v>
       </c>
       <c r="T37" t="n">
-        <v>104.6</v>
+        <v>79.3</v>
       </c>
       <c r="U37" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3424,12 +3418,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3438,25 +3432,25 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38" t="n">
-        <v>4830</v>
+        <v>631</v>
       </c>
       <c r="F38" t="n">
-        <v>95.34</v>
+        <v>20.13</v>
       </c>
       <c r="G38" t="n">
-        <v>32.85</v>
+        <v>10.55</v>
       </c>
       <c r="H38" t="n">
-        <v>75.3</v>
+        <v>19</v>
       </c>
       <c r="I38" t="n">
-        <v>59.7</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3464,51 +3458,55 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>9.9</v>
+        <v>-0.32</v>
       </c>
       <c r="M38" t="n">
-        <v>4395</v>
+        <v>633</v>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債80%)</t>
+        </is>
+      </c>
       <c r="P38" t="n">
-        <v>34.5</v>
+        <v>52.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.76</v>
+        <v>1.91</v>
       </c>
       <c r="R38" t="n">
-        <v>25.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S38" t="n">
-        <v>114.6</v>
+        <v>19.2</v>
       </c>
       <c r="T38" t="n">
-        <v>120.3</v>
+        <v>20.9</v>
       </c>
       <c r="U38" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3517,25 +3515,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>692</v>
+        <v>3500</v>
       </c>
       <c r="F39" t="n">
-        <v>45.91</v>
+        <v>97.37</v>
       </c>
       <c r="G39" t="n">
-        <v>25.61</v>
+        <v>24.38</v>
       </c>
       <c r="H39" t="n">
-        <v>47.5</v>
+        <v>70.2</v>
       </c>
       <c r="I39" t="n">
-        <v>20.2</v>
+        <v>49</v>
       </c>
       <c r="J39" t="n">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3543,34 +3541,30 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.59</v>
+        <v>-0.57</v>
       </c>
       <c r="M39" t="n">
-        <v>668</v>
+        <v>3520</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>53.6</v>
+        <v>25</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.12</v>
+        <v>0.92</v>
       </c>
       <c r="R39" t="n">
-        <v>28.3</v>
+        <v>23.2</v>
       </c>
       <c r="S39" t="n">
-        <v>-9.300000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="T39" t="n">
-        <v>57.1</v>
+        <v>104.6</v>
       </c>
       <c r="U39" t="n">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3586,12 +3580,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3600,25 +3594,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>99.5</v>
+        <v>5125</v>
       </c>
       <c r="F40" t="n">
-        <v>11.58</v>
+        <v>104.77</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81</v>
+        <v>36.1</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>75.3</v>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>59.7</v>
       </c>
       <c r="J40" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3626,30 +3620,30 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.12</v>
+        <v>6.11</v>
       </c>
       <c r="M40" t="n">
-        <v>98.40000000000001</v>
+        <v>4830</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>17.8</v>
+        <v>34.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.11</v>
+        <v>0.76</v>
       </c>
       <c r="R40" t="n">
-        <v>5.3</v>
+        <v>25.1</v>
       </c>
       <c r="S40" t="n">
-        <v>7.7</v>
+        <v>114.6</v>
       </c>
       <c r="T40" t="n">
-        <v>11.6</v>
+        <v>120.3</v>
       </c>
       <c r="U40" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3658,46 +3652,46 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E41" t="n">
-        <v>184.5</v>
+        <v>705</v>
       </c>
       <c r="F41" t="n">
-        <v>14.07</v>
+        <v>47.56</v>
       </c>
       <c r="G41" t="n">
-        <v>2.49</v>
+        <v>26.53</v>
       </c>
       <c r="H41" t="n">
-        <v>13.4</v>
+        <v>47.5</v>
       </c>
       <c r="I41" t="n">
-        <v>7.1</v>
+        <v>20.2</v>
       </c>
       <c r="J41" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3705,82 +3699,82 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.65</v>
+        <v>1.88</v>
       </c>
       <c r="M41" t="n">
-        <v>178</v>
+        <v>692</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+          <t>月營收轉負-9%</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>17.6</v>
+        <v>53.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.7</v>
+        <v>1.12</v>
       </c>
       <c r="R41" t="n">
-        <v>8.5</v>
+        <v>28.3</v>
       </c>
       <c r="S41" t="n">
-        <v>4.2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T41" t="n">
-        <v>14.4</v>
+        <v>57.1</v>
       </c>
       <c r="U41" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E42" t="n">
-        <v>108.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>16.08</v>
+        <v>11.71</v>
       </c>
       <c r="G42" t="n">
-        <v>3.38</v>
+        <v>1.83</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I42" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="J42" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3788,51 +3782,51 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.46</v>
+        <v>0.1</v>
       </c>
       <c r="M42" t="n">
-        <v>109</v>
+        <v>99.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>20.6</v>
+        <v>17.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.3</v>
+        <v>2.11</v>
       </c>
       <c r="R42" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="S42" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="T42" t="n">
-        <v>17.2</v>
+        <v>11.6</v>
       </c>
       <c r="U42" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3841,25 +3835,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E43" t="n">
-        <v>531</v>
+        <v>187.5</v>
       </c>
       <c r="F43" t="n">
-        <v>15.15</v>
+        <v>14.58</v>
       </c>
       <c r="G43" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="H43" t="n">
-        <v>21.4</v>
+        <v>13.4</v>
       </c>
       <c r="I43" t="n">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J43" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3867,55 +3861,55 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="M43" t="n">
-        <v>500</v>
+        <v>184.5</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="Q43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T43" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U43" t="n">
         <v>2.02</v>
       </c>
-      <c r="R43" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S43" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T43" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3924,25 +3918,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E44" t="n">
-        <v>207.5</v>
+        <v>107.5</v>
       </c>
       <c r="F44" t="n">
-        <v>29.81</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
-        <v>2.74</v>
+        <v>3.36</v>
       </c>
       <c r="H44" t="n">
-        <v>30.9</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="J44" t="n">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3950,82 +3944,78 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.75</v>
+        <v>-0.92</v>
       </c>
       <c r="M44" t="n">
-        <v>200</v>
+        <v>108.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>含金量0.5差</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>9.4</v>
+        <v>20.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.49</v>
+        <v>1.3</v>
       </c>
       <c r="R44" t="n">
         <v>7.6</v>
       </c>
       <c r="S44" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="T44" t="n">
-        <v>36.5</v>
+        <v>17.2</v>
       </c>
       <c r="U44" t="n">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E45" t="n">
-        <v>3490</v>
+        <v>529</v>
       </c>
       <c r="F45" t="n">
-        <v>49.32</v>
+        <v>16.09</v>
       </c>
       <c r="G45" t="n">
-        <v>6.36</v>
+        <v>2.29</v>
       </c>
       <c r="H45" t="n">
-        <v>51.7</v>
+        <v>21.4</v>
       </c>
       <c r="I45" t="n">
-        <v>23.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4033,55 +4023,55 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.71</v>
+        <v>-0.38</v>
       </c>
       <c r="M45" t="n">
-        <v>3365</v>
+        <v>531</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.26</v>
+        <v>2.02</v>
       </c>
       <c r="R45" t="n">
-        <v>31.2</v>
+        <v>10.6</v>
       </c>
       <c r="S45" t="n">
-        <v>-33.5</v>
+        <v>30.2</v>
       </c>
       <c r="T45" t="n">
-        <v>63.8</v>
+        <v>23.4</v>
       </c>
       <c r="U45" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4090,55 +4080,61 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E46" t="n">
-        <v>273</v>
+        <v>211.5</v>
       </c>
       <c r="F46" t="n">
-        <v>30.69</v>
+        <v>30.92</v>
       </c>
       <c r="G46" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>2.85</v>
+      </c>
+      <c r="H46" t="n">
+        <v>30.9</v>
+      </c>
       <c r="I46" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.03</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.82</v>
+        <v>1.93</v>
       </c>
       <c r="M46" t="n">
-        <v>265.5</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
+        <v>207.5</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>含金量0.5差</t>
+        </is>
+      </c>
       <c r="P46" t="n">
-        <v>13.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.04</v>
+        <v>0.49</v>
       </c>
       <c r="R46" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="S46" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="T46" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U46" t="inlineStr"/>
+        <v>36.5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.03</v>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4146,96 +4142,102 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E47" t="n">
-        <v>117</v>
+        <v>3590</v>
       </c>
       <c r="F47" t="n">
-        <v>25.97</v>
+        <v>51.15</v>
       </c>
       <c r="G47" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>6.59</v>
+      </c>
+      <c r="H47" t="n">
+        <v>51.7</v>
+      </c>
       <c r="I47" t="n">
-        <v>11</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.73</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3490</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>含金量0.3差、月營收轉負-34%</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R47" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="M47" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S47" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="T47" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4244,20 +4246,20 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E48" t="n">
-        <v>160</v>
+        <v>282.5</v>
       </c>
       <c r="F48" t="n">
-        <v>32.37</v>
+        <v>31.56</v>
       </c>
       <c r="G48" t="n">
-        <v>1.75</v>
+        <v>4.68</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>12.4</v>
+        <v>24.9</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4266,40 +4268,36 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.91</v>
+        <v>3.48</v>
       </c>
       <c r="M48" t="n">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>5.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="R48" t="n">
-        <v>22.1</v>
+        <v>3.2</v>
       </c>
       <c r="S48" t="n">
-        <v>14.6</v>
+        <v>30</v>
       </c>
       <c r="T48" t="n">
-        <v>34.2</v>
+        <v>43.5</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -4311,12 +4309,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4325,20 +4323,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E49" t="n">
-        <v>228.5</v>
+        <v>121</v>
       </c>
       <c r="F49" t="n">
-        <v>23.29</v>
+        <v>26.77</v>
       </c>
       <c r="G49" t="n">
-        <v>5.67</v>
+        <v>2.75</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4347,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>9.859999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="M49" t="n">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4359,19 +4357,19 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>30.7</v>
+        <v>10.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R49" t="n">
-        <v>20.4</v>
+        <v>3.8</v>
       </c>
       <c r="S49" t="n">
-        <v>812.4</v>
+        <v>48.7</v>
       </c>
       <c r="T49" t="n">
-        <v>34.6</v>
+        <v>28.4</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -4388,34 +4386,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E50" t="n">
-        <v>245</v>
+        <v>159.5</v>
       </c>
       <c r="F50" t="n">
-        <v>34.66</v>
+        <v>32.99</v>
       </c>
       <c r="G50" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>-15.3</v>
+        <v>12.4</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4424,74 +4422,80 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.26</v>
+        <v>-0.31</v>
       </c>
       <c r="M50" t="n">
-        <v>235</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.72</v>
+        <v>2.22</v>
       </c>
       <c r="R50" t="n">
-        <v>13.2</v>
+        <v>22.1</v>
       </c>
       <c r="S50" t="n">
-        <v>34.8</v>
+        <v>14.6</v>
       </c>
       <c r="T50" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E51" t="n">
-        <v>405</v>
+        <v>230</v>
       </c>
       <c r="F51" t="n">
-        <v>34.11</v>
+        <v>25.59</v>
       </c>
       <c r="G51" t="n">
-        <v>6.12</v>
+        <v>6.23</v>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>9.6</v>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -4499,35 +4503,31 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>6.3</v>
+        <v>0.66</v>
       </c>
       <c r="M51" t="n">
-        <v>381</v>
+        <v>228.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>17.9</v>
+        <v>30.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R51" t="n">
-        <v>-6.1</v>
+        <v>20.4</v>
       </c>
       <c r="S51" t="n">
-        <v>730.1</v>
+        <v>812.4</v>
       </c>
       <c r="T51" t="n">
-        <v>45.2</v>
+        <v>34.6</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4561,13 +4561,13 @@
         <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="F52" t="n">
-        <v>25.52</v>
+        <v>27.11</v>
       </c>
       <c r="G52" t="n">
-        <v>8.09</v>
+        <v>8.59</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6.21</v>
+        <v>-1.33</v>
       </c>
       <c r="M52" t="n">
-        <v>709</v>
+        <v>753</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4642,13 +4642,13 @@
         <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>119.5</v>
+        <v>122.5</v>
       </c>
       <c r="F53" t="n">
-        <v>25.84</v>
+        <v>26.85</v>
       </c>
       <c r="G53" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.91</v>
+        <v>2.51</v>
       </c>
       <c r="M53" t="n">
-        <v>115</v>
+        <v>119.5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4723,13 +4723,13 @@
         <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>3985</v>
+        <v>4000</v>
       </c>
       <c r="F54" t="n">
-        <v>24.19</v>
+        <v>24.87</v>
       </c>
       <c r="G54" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.84</v>
+        <v>0.38</v>
       </c>
       <c r="M54" t="n">
-        <v>3875</v>
+        <v>3985</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4804,13 +4804,13 @@
         <v>97</v>
       </c>
       <c r="E55" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="F55" t="n">
-        <v>32.99</v>
+        <v>34.39</v>
       </c>
       <c r="G55" t="n">
-        <v>6.53</v>
+        <v>6.81</v>
       </c>
       <c r="H55" t="n">
         <v>29.3</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4.25</v>
+        <v>1.48</v>
       </c>
       <c r="M55" t="n">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4883,13 +4883,13 @@
         <v>91</v>
       </c>
       <c r="E56" t="n">
-        <v>750</v>
+        <v>767</v>
       </c>
       <c r="F56" t="n">
-        <v>49.36</v>
+        <v>50.85</v>
       </c>
       <c r="G56" t="n">
-        <v>7.66</v>
+        <v>7.89</v>
       </c>
       <c r="H56" t="n">
         <v>46.1</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.02</v>
+        <v>2.27</v>
       </c>
       <c r="M56" t="n">
-        <v>728</v>
+        <v>750</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4962,13 +4962,13 @@
         <v>79</v>
       </c>
       <c r="E57" t="n">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
       <c r="F57" t="n">
-        <v>15.69</v>
+        <v>15.98</v>
       </c>
       <c r="G57" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="H57" t="n">
         <v>17.3</v>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.88</v>
+        <v>-0.77</v>
       </c>
       <c r="M57" t="n">
-        <v>64</v>
+        <v>65.2</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -5041,13 +5041,13 @@
         <v>77</v>
       </c>
       <c r="E58" t="n">
-        <v>165</v>
+        <v>165.5</v>
       </c>
       <c r="F58" t="n">
-        <v>15.3</v>
+        <v>15.54</v>
       </c>
       <c r="G58" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="H58" t="n">
         <v>15.5</v>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.54</v>
+        <v>0.3</v>
       </c>
       <c r="M58" t="n">
-        <v>162.5</v>
+        <v>165</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -5120,13 +5120,13 @@
         <v>96</v>
       </c>
       <c r="E59" t="n">
-        <v>354</v>
+        <v>354.5</v>
       </c>
       <c r="F59" t="n">
-        <v>18.63</v>
+        <v>19.15</v>
       </c>
       <c r="G59" t="n">
-        <v>5.51</v>
+        <v>5.67</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.76</v>
+        <v>0.14</v>
       </c>
       <c r="M59" t="n">
-        <v>344.5</v>
+        <v>354</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5200,10 +5200,10 @@
         <v>162.5</v>
       </c>
       <c r="F60" t="n">
-        <v>19.14</v>
+        <v>19.74</v>
       </c>
       <c r="G60" t="n">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>157.5</v>
+        <v>162.5</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5274,13 +5274,13 @@
         <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>20.2</v>
+        <v>20.05</v>
       </c>
       <c r="F61" t="n">
-        <v>16.18</v>
+        <v>16.42</v>
       </c>
       <c r="G61" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.51</v>
+        <v>-0.74</v>
       </c>
       <c r="M61" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>89</v>
+        <v>90.7</v>
       </c>
       <c r="F62" t="n">
-        <v>17.89</v>
+        <v>18.28</v>
       </c>
       <c r="G62" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="M62" t="n">
-        <v>87.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>43.85</v>
+        <v>44.05</v>
       </c>
       <c r="F63" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="G63" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.4</v>
+        <v>0.46</v>
       </c>
       <c r="M63" t="n">
-        <v>42</v>
+        <v>43.85</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>193</v>
+        <v>201.5</v>
       </c>
       <c r="F64" t="n">
-        <v>16.58</v>
+        <v>17.53</v>
       </c>
       <c r="G64" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="M64" t="n">
-        <v>182.5</v>
+        <v>193</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>718</v>
       </c>
       <c r="F65" t="n">
-        <v>17.49</v>
+        <v>17.79</v>
       </c>
       <c r="G65" t="n">
-        <v>16.53</v>
+        <v>16.81</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="F66" t="n">
-        <v>17.85</v>
+        <v>18.1</v>
       </c>
       <c r="G66" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.38</v>
+        <v>3.57</v>
       </c>
       <c r="M66" t="n">
-        <v>46.95</v>
+        <v>47.6</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F67" t="n">
         <v>15.78</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M67" t="n">
         <v>145.5</v>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="F68" t="n">
-        <v>23.08</v>
+        <v>23.21</v>
       </c>
       <c r="G68" t="n">
-        <v>5.48</v>
+        <v>5.51</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.55</v>
+        <v>3.29</v>
       </c>
       <c r="M68" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F69" t="n">
-        <v>17.67</v>
+        <v>17.96</v>
       </c>
       <c r="G69" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.63</v>
+        <v>-3.2</v>
       </c>
       <c r="M69" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>307.5</v>
+        <v>315</v>
       </c>
       <c r="F70" t="n">
-        <v>29.37</v>
+        <v>30</v>
       </c>
       <c r="G70" t="n">
-        <v>8.050000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="M70" t="n">
-        <v>301</v>
+        <v>307.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,7 +6072,7 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>91</v>
+        <v>91.7</v>
       </c>
       <c r="F71" t="n">
         <v>19.12</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="M71" t="n">
         <v>91</v>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F72" t="n">
-        <v>19.1</v>
+        <v>19.65</v>
       </c>
       <c r="G72" t="n">
-        <v>5.21</v>
+        <v>5.36</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.86</v>
+        <v>-2.78</v>
       </c>
       <c r="M72" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>246</v>
+        <v>251.5</v>
       </c>
       <c r="F73" t="n">
-        <v>16.65</v>
+        <v>17.47</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.9</v>
+        <v>2.24</v>
       </c>
       <c r="M73" t="n">
-        <v>234.5</v>
+        <v>246</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="F74" t="n">
-        <v>60.76</v>
+        <v>62.86</v>
       </c>
       <c r="G74" t="n">
-        <v>31.63</v>
+        <v>32.72</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.45</v>
+        <v>-2.5</v>
       </c>
       <c r="M74" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>60.1</v>
+        <v>61.7</v>
       </c>
       <c r="F75" t="n">
-        <v>21.75</v>
+        <v>22.85</v>
       </c>
       <c r="G75" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5.07</v>
+        <v>2.66</v>
       </c>
       <c r="M75" t="n">
-        <v>57.2</v>
+        <v>60.1</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2320</v>
+        <v>2265</v>
       </c>
       <c r="F76" t="n">
-        <v>35.08</v>
+        <v>38.12</v>
       </c>
       <c r="G76" t="n">
-        <v>18.56</v>
+        <v>20.16</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>8.67</v>
+        <v>-2.37</v>
       </c>
       <c r="M76" t="n">
-        <v>2135</v>
+        <v>2320</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="F77" t="n">
-        <v>21.51</v>
+        <v>22.62</v>
       </c>
       <c r="G77" t="n">
-        <v>8.34</v>
+        <v>8.77</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>5.16</v>
+        <v>3.56</v>
       </c>
       <c r="M77" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="F78" t="n">
-        <v>31.19</v>
+        <v>32.4</v>
       </c>
       <c r="G78" t="n">
-        <v>10.21</v>
+        <v>10.61</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.88</v>
+        <v>-0.41</v>
       </c>
       <c r="M78" t="n">
-        <v>2320</v>
+        <v>2410</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6714,13 +6714,13 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F79" t="n">
-        <v>15.22</v>
+        <v>15.74</v>
       </c>
       <c r="G79" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.38</v>
+        <v>-2.8</v>
       </c>
       <c r="M79" t="n">
-        <v>103.5</v>
+        <v>107</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="F80" t="n">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="G80" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="M80" t="n">
-        <v>106</v>
+        <v>109.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6875,10 +6875,10 @@
         <v>28.1</v>
       </c>
       <c r="F81" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="G81" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H81" t="n">
         <v>5.9</v>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>110.5</v>
+        <v>109</v>
       </c>
       <c r="F82" t="n">
-        <v>11.8</v>
+        <v>11.91</v>
       </c>
       <c r="G82" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.91</v>
+        <v>-1.36</v>
       </c>
       <c r="M82" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>179</v>
+        <v>176.5</v>
       </c>
       <c r="F83" t="n">
-        <v>13.03</v>
+        <v>13.29</v>
       </c>
       <c r="G83" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.99</v>
+        <v>-1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>175.5</v>
+        <v>179</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="F84" t="n">
-        <v>7.82</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.67</v>
+        <v>-0.47</v>
       </c>
       <c r="M84" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1165</v>
+        <v>1150</v>
       </c>
       <c r="F85" t="n">
-        <v>32.02</v>
+        <v>34.54</v>
       </c>
       <c r="G85" t="n">
-        <v>10.73</v>
+        <v>11.57</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>7.87</v>
+        <v>-1.29</v>
       </c>
       <c r="M85" t="n">
-        <v>1080</v>
+        <v>1165</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>404.5</v>
+        <v>417.5</v>
       </c>
       <c r="F86" t="n">
-        <v>18.85</v>
+        <v>19.66</v>
       </c>
       <c r="G86" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.25</v>
+        <v>3.21</v>
       </c>
       <c r="M86" t="n">
-        <v>388</v>
+        <v>404.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>128.5</v>
+        <v>132</v>
       </c>
       <c r="F87" t="n">
-        <v>15.32</v>
+        <v>15.69</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.39</v>
+        <v>2.72</v>
       </c>
       <c r="M87" t="n">
-        <v>125.5</v>
+        <v>128.5</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>38.15</v>
+        <v>39.1</v>
       </c>
       <c r="F88" t="n">
-        <v>8.24</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.73</v>
+        <v>2.49</v>
       </c>
       <c r="M88" t="n">
-        <v>37.5</v>
+        <v>38.15</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2220</v>
+        <v>2285</v>
       </c>
       <c r="F89" t="n">
-        <v>39.52</v>
+        <v>41.98</v>
       </c>
       <c r="G89" t="n">
-        <v>17.88</v>
+        <v>19</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>6.22</v>
+        <v>2.93</v>
       </c>
       <c r="M89" t="n">
-        <v>2090</v>
+        <v>2220</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="F90" t="n">
-        <v>24.76</v>
+        <v>26.72</v>
       </c>
       <c r="G90" t="n">
-        <v>5.95</v>
+        <v>6.42</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>7.93</v>
+        <v>-1.94</v>
       </c>
       <c r="M90" t="n">
-        <v>858</v>
+        <v>926</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="F91" t="n">
-        <v>10.31</v>
+        <v>10.61</v>
       </c>
       <c r="G91" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.91</v>
+        <v>-0.23</v>
       </c>
       <c r="M91" t="n">
-        <v>86</v>
+        <v>88.5</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="F92" t="n">
-        <v>7.55</v>
+        <v>7.81</v>
       </c>
       <c r="G92" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M92" t="n">
-        <v>69.8</v>
+        <v>72.2</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="F93" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="G93" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.29</v>
+        <v>0.52</v>
       </c>
       <c r="M93" t="n">
-        <v>56.7</v>
+        <v>58</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F94" t="n">
-        <v>15.89</v>
+        <v>16.29</v>
       </c>
       <c r="G94" t="n">
-        <v>5.87</v>
+        <v>6.02</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.53</v>
+        <v>1.54</v>
       </c>
       <c r="M94" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="F95" t="n">
-        <v>15.7</v>
+        <v>16.76</v>
       </c>
       <c r="G95" t="n">
-        <v>6.21</v>
+        <v>6.63</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>6.72</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>4685</v>
+        <v>5000</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>149.5</v>
+        <v>164</v>
       </c>
       <c r="F96" t="n">
-        <v>14.39</v>
+        <v>14.99</v>
       </c>
       <c r="G96" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.18</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M96" t="n">
-        <v>143.5</v>
+        <v>149.5</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="F97" t="n">
-        <v>18.04</v>
+        <v>17.3</v>
       </c>
       <c r="G97" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-4.08</v>
+        <v>0.35</v>
       </c>
       <c r="M97" t="n">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>71.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="G98" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.62</v>
+        <v>3.21</v>
       </c>
       <c r="M98" t="n">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>368.5</v>
+        <v>379.5</v>
       </c>
       <c r="F99" t="n">
-        <v>6.96</v>
+        <v>7.36</v>
       </c>
       <c r="G99" t="n">
-        <v>4.01</v>
+        <v>4.24</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5.74</v>
+        <v>2.99</v>
       </c>
       <c r="M99" t="n">
-        <v>348.5</v>
+        <v>368.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="F100" t="n">
         <v>3.91</v>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.21</v>
+        <v>0.85</v>
       </c>
       <c r="M100" t="n">
-        <v>23.55</v>
+        <v>23.6</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>191.5</v>
+        <v>196.5</v>
       </c>
       <c r="F101" t="n">
-        <v>8.970000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="G101" t="n">
-        <v>3.73</v>
+        <v>3.89</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.08</v>
+        <v>2.61</v>
       </c>
       <c r="M101" t="n">
-        <v>184</v>
+        <v>191.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2320</v>
+        <v>2265</v>
       </c>
       <c r="F2" t="n">
-        <v>35.08</v>
+        <v>38.12</v>
       </c>
       <c r="G2" t="n">
-        <v>18.56</v>
+        <v>20.16</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.67</v>
+        <v>-2.37</v>
       </c>
       <c r="M2" t="n">
-        <v>2135</v>
+        <v>2320</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="F3" t="n">
-        <v>21.51</v>
+        <v>22.62</v>
       </c>
       <c r="G3" t="n">
-        <v>8.34</v>
+        <v>8.77</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.16</v>
+        <v>3.56</v>
       </c>
       <c r="M3" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="F4" t="n">
-        <v>31.19</v>
+        <v>32.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.21</v>
+        <v>10.61</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.88</v>
+        <v>-0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>2320</v>
+        <v>2410</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>15.22</v>
+        <v>15.74</v>
       </c>
       <c r="G5" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.38</v>
+        <v>-2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>103.5</v>
+        <v>107</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="G6" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>106</v>
+        <v>109.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9100,10 +9100,10 @@
         <v>28.1</v>
       </c>
       <c r="F7" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="G7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>110.5</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>11.8</v>
+        <v>11.91</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.91</v>
+        <v>-1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>176.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03</v>
+        <v>13.29</v>
       </c>
       <c r="G9" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>-1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>175.5</v>
+        <v>179</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="F10" t="n">
-        <v>7.82</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.67</v>
+        <v>-0.47</v>
       </c>
       <c r="M10" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1165</v>
+        <v>1150</v>
       </c>
       <c r="F11" t="n">
-        <v>32.02</v>
+        <v>34.54</v>
       </c>
       <c r="G11" t="n">
-        <v>10.73</v>
+        <v>11.57</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.87</v>
+        <v>-1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1080</v>
+        <v>1165</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>404.5</v>
+        <v>417.5</v>
       </c>
       <c r="F12" t="n">
-        <v>18.85</v>
+        <v>19.66</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.25</v>
+        <v>3.21</v>
       </c>
       <c r="M12" t="n">
-        <v>388</v>
+        <v>404.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>128.5</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>15.32</v>
+        <v>15.69</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.39</v>
+        <v>2.72</v>
       </c>
       <c r="M13" t="n">
-        <v>125.5</v>
+        <v>128.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.15</v>
+        <v>39.1</v>
       </c>
       <c r="F14" t="n">
-        <v>8.24</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.73</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>37.5</v>
+        <v>38.15</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2220</v>
+        <v>2285</v>
       </c>
       <c r="F15" t="n">
-        <v>39.52</v>
+        <v>41.98</v>
       </c>
       <c r="G15" t="n">
-        <v>17.88</v>
+        <v>19</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.22</v>
+        <v>2.93</v>
       </c>
       <c r="M15" t="n">
-        <v>2090</v>
+        <v>2220</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="F16" t="n">
-        <v>24.76</v>
+        <v>26.72</v>
       </c>
       <c r="G16" t="n">
-        <v>5.95</v>
+        <v>6.42</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.93</v>
+        <v>-1.94</v>
       </c>
       <c r="M16" t="n">
-        <v>858</v>
+        <v>926</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="F17" t="n">
-        <v>10.31</v>
+        <v>10.61</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.91</v>
+        <v>-0.23</v>
       </c>
       <c r="M17" t="n">
-        <v>86</v>
+        <v>88.5</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="F18" t="n">
-        <v>7.55</v>
+        <v>7.81</v>
       </c>
       <c r="G18" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>69.8</v>
+        <v>72.2</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="F19" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="G19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>0.52</v>
       </c>
       <c r="M19" t="n">
-        <v>56.7</v>
+        <v>58</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F20" t="n">
-        <v>15.89</v>
+        <v>16.29</v>
       </c>
       <c r="G20" t="n">
-        <v>5.87</v>
+        <v>6.02</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.53</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="F21" t="n">
-        <v>15.7</v>
+        <v>16.76</v>
       </c>
       <c r="G21" t="n">
-        <v>6.21</v>
+        <v>6.63</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.72</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>4685</v>
+        <v>5000</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>149.5</v>
+        <v>164</v>
       </c>
       <c r="F22" t="n">
-        <v>14.39</v>
+        <v>14.99</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.18</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>143.5</v>
+        <v>149.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="F23" t="n">
-        <v>18.04</v>
+        <v>17.3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-4.08</v>
+        <v>0.35</v>
       </c>
       <c r="M23" t="n">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,7 +10607,7 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F2" t="n">
         <v>15.78</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>145.5</v>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="F3" t="n">
-        <v>23.08</v>
+        <v>23.21</v>
       </c>
       <c r="G3" t="n">
-        <v>5.48</v>
+        <v>5.51</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.55</v>
+        <v>3.29</v>
       </c>
       <c r="M3" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>17.67</v>
+        <v>17.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.63</v>
+        <v>-3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>307.5</v>
+        <v>315</v>
       </c>
       <c r="F5" t="n">
-        <v>29.37</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>8.050000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="M5" t="n">
-        <v>301</v>
+        <v>307.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,7 +10923,7 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>91.7</v>
       </c>
       <c r="F6" t="n">
         <v>19.12</v>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="M6" t="n">
         <v>91</v>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F7" t="n">
-        <v>19.1</v>
+        <v>19.65</v>
       </c>
       <c r="G7" t="n">
-        <v>5.21</v>
+        <v>5.36</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.86</v>
+        <v>-2.78</v>
       </c>
       <c r="M7" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>246</v>
+        <v>251.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.65</v>
+        <v>17.47</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.9</v>
+        <v>2.24</v>
       </c>
       <c r="M8" t="n">
-        <v>234.5</v>
+        <v>246</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="F9" t="n">
-        <v>60.76</v>
+        <v>62.86</v>
       </c>
       <c r="G9" t="n">
-        <v>31.63</v>
+        <v>32.72</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.45</v>
+        <v>-2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>60.1</v>
+        <v>61.7</v>
       </c>
       <c r="F10" t="n">
-        <v>21.75</v>
+        <v>22.85</v>
       </c>
       <c r="G10" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.07</v>
+        <v>2.66</v>
       </c>
       <c r="M10" t="n">
-        <v>57.2</v>
+        <v>60.1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>983</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="n">
-        <v>69.26000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="G2" t="n">
-        <v>19.44</v>
+        <v>19.68</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,10 +11538,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.2</v>
+        <v>39.25</v>
       </c>
       <c r="F3" t="n">
-        <v>11.05</v>
+        <v>11.07</v>
       </c>
       <c r="G3" t="n">
         <v>1.83</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>153.5</v>
       </c>
       <c r="F4" t="n">
-        <v>18.44</v>
+        <v>18.84</v>
       </c>
       <c r="G4" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>-5.83</v>
       </c>
       <c r="M4" t="n">
-        <v>159.5</v>
+        <v>163</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5875</v>
+        <v>6000</v>
       </c>
       <c r="F5" t="n">
-        <v>145.23</v>
+        <v>156.42</v>
       </c>
       <c r="G5" t="n">
-        <v>33.92</v>
+        <v>36.54</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.7</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>5455</v>
+        <v>5875</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,7 +11779,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="F6" t="n">
         <v>22.72</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
         <v>112</v>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="F7" t="n">
-        <v>30.32</v>
+        <v>31.34</v>
       </c>
       <c r="G7" t="n">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.37</v>
+        <v>0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>104</v>
+        <v>107.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="F8" t="n">
-        <v>31.76</v>
+        <v>32.82</v>
       </c>
       <c r="G8" t="n">
-        <v>6.15</v>
+        <v>6.36</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.37</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>26.52</v>
+        <v>25.89</v>
       </c>
       <c r="G9" t="n">
-        <v>3.93</v>
+        <v>3.84</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-2.39</v>
+        <v>0.98</v>
       </c>
       <c r="M9" t="n">
-        <v>104.5</v>
+        <v>102</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>18.03</v>
+        <v>18.51</v>
       </c>
       <c r="G10" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.67</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="F11" t="n">
-        <v>29.23</v>
+        <v>29.77</v>
       </c>
       <c r="G11" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>5.15</v>
       </c>
       <c r="M11" t="n">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
-        <v>20.89</v>
+        <v>21.13</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.19</v>
+        <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>167.5</v>
+        <v>169.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>28.46</v>
+        <v>30.44</v>
       </c>
       <c r="G13" t="n">
-        <v>4.98</v>
+        <v>5.33</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.98</v>
+        <v>5.31</v>
       </c>
       <c r="M13" t="n">
-        <v>193.5</v>
+        <v>207</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,7 +12427,7 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>139</v>
+        <v>138.5</v>
       </c>
       <c r="F14" t="n">
         <v>27.63</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="M14" t="n">
         <v>139</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>243</v>
+        <v>239.5</v>
       </c>
       <c r="F15" t="n">
-        <v>22.2</v>
+        <v>22.15</v>
       </c>
       <c r="G15" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.21</v>
+        <v>-1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4115</v>
+        <v>4370</v>
       </c>
       <c r="F16" t="n">
-        <v>112.67</v>
+        <v>123.8</v>
       </c>
       <c r="G16" t="n">
-        <v>34.41</v>
+        <v>37.81</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.880000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3745</v>
+        <v>4115</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1835</v>
+        <v>1880</v>
       </c>
       <c r="F2" t="n">
-        <v>62.87</v>
+        <v>67.66</v>
       </c>
       <c r="G2" t="n">
-        <v>14.78</v>
+        <v>15.91</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.62</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1705</v>
+        <v>1835</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F3" t="n">
-        <v>19.43</v>
+        <v>20.13</v>
       </c>
       <c r="G3" t="n">
-        <v>10.19</v>
+        <v>10.55</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.6</v>
+        <v>-0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3520</v>
+        <v>3500</v>
       </c>
       <c r="F4" t="n">
-        <v>88.52</v>
+        <v>97.37</v>
       </c>
       <c r="G4" t="n">
-        <v>22.17</v>
+        <v>24.38</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>-0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>3200</v>
+        <v>3520</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4830</v>
+        <v>5125</v>
       </c>
       <c r="F5" t="n">
-        <v>95.34</v>
+        <v>104.77</v>
       </c>
       <c r="G5" t="n">
-        <v>32.85</v>
+        <v>36.1</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.9</v>
+        <v>6.11</v>
       </c>
       <c r="M5" t="n">
-        <v>4395</v>
+        <v>4830</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="F6" t="n">
-        <v>45.91</v>
+        <v>47.56</v>
       </c>
       <c r="G6" t="n">
-        <v>25.61</v>
+        <v>26.53</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.59</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.58</v>
+        <v>11.71</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.12</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>98.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>184.5</v>
+        <v>187.5</v>
       </c>
       <c r="F8" t="n">
-        <v>14.07</v>
+        <v>14.58</v>
       </c>
       <c r="G8" t="n">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>178</v>
+        <v>184.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>108.5</v>
+        <v>107.5</v>
       </c>
       <c r="F9" t="n">
-        <v>16.08</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.46</v>
+        <v>-0.92</v>
       </c>
       <c r="M9" t="n">
-        <v>109</v>
+        <v>108.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F10" t="n">
-        <v>15.15</v>
+        <v>16.09</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>-0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>207.5</v>
+        <v>211.5</v>
       </c>
       <c r="F11" t="n">
-        <v>29.81</v>
+        <v>30.92</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>200</v>
+        <v>207.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3490</v>
+        <v>3590</v>
       </c>
       <c r="F12" t="n">
-        <v>49.32</v>
+        <v>51.15</v>
       </c>
       <c r="G12" t="n">
-        <v>6.36</v>
+        <v>6.59</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.71</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>3365</v>
+        <v>3490</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="F2" t="n">
-        <v>70.11</v>
+        <v>77.03</v>
       </c>
       <c r="G2" t="n">
-        <v>19.68</v>
+        <v>21.63</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.869999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>983</v>
+        <v>1080</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.25</v>
+        <v>39.3</v>
       </c>
       <c r="F3" t="n">
-        <v>11.07</v>
+        <v>11.09</v>
       </c>
       <c r="G3" t="n">
         <v>1.83</v>
@@ -662,7 +662,7 @@
         <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>39.2</v>
+        <v>39.25</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>18.84</v>
+        <v>17.75</v>
       </c>
       <c r="G4" t="n">
-        <v>4.15</v>
+        <v>3.91</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-5.83</v>
+        <v>-0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>163</v>
+        <v>153.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6000</v>
+        <v>6250</v>
       </c>
       <c r="F5" t="n">
-        <v>156.42</v>
+        <v>159.74</v>
       </c>
       <c r="G5" t="n">
-        <v>36.54</v>
+        <v>37.31</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>4.17</v>
       </c>
       <c r="M5" t="n">
-        <v>5875</v>
+        <v>6000</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>112.5</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>22.72</v>
+        <v>22.82</v>
       </c>
       <c r="G6" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>108.5</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
-        <v>31.34</v>
+        <v>31.63</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.93</v>
+        <v>-0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F8" t="n">
-        <v>32.82</v>
+        <v>29.77</v>
       </c>
       <c r="G8" t="n">
-        <v>6.36</v>
+        <v>5.77</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-9.300000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.89</v>
+        <v>26.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.98</v>
+        <v>-0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>18.51</v>
+        <v>18.75</v>
       </c>
       <c r="G10" t="n">
-        <v>5.09</v>
+        <v>5.15</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>-1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1430</v>
+        <v>1405</v>
       </c>
       <c r="F11" t="n">
-        <v>29.77</v>
+        <v>31.3</v>
       </c>
       <c r="G11" t="n">
-        <v>5.35</v>
+        <v>5.62</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.15</v>
+        <v>-1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>169</v>
+        <v>167.5</v>
       </c>
       <c r="F12" t="n">
-        <v>21.13</v>
+        <v>21.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.29</v>
+        <v>-0.89</v>
       </c>
       <c r="M12" t="n">
-        <v>169.5</v>
+        <v>169</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1445,10 +1445,10 @@
         <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>30.44</v>
+        <v>32.06</v>
       </c>
       <c r="G13" t="n">
-        <v>5.33</v>
+        <v>5.61</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>138.5</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>27.63</v>
+        <v>27.53</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1551,7 +1551,7 @@
         <v>-0.36</v>
       </c>
       <c r="M14" t="n">
-        <v>139</v>
+        <v>138.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>239.5</v>
+        <v>237</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15</v>
+        <v>21.83</v>
       </c>
       <c r="G15" t="n">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.44</v>
+        <v>-1.04</v>
       </c>
       <c r="M15" t="n">
-        <v>243</v>
+        <v>239.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4370</v>
+        <v>4380</v>
       </c>
       <c r="F16" t="n">
-        <v>123.8</v>
+        <v>131.47</v>
       </c>
       <c r="G16" t="n">
-        <v>37.81</v>
+        <v>40.15</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.2</v>
+        <v>0.23</v>
       </c>
       <c r="M16" t="n">
-        <v>4115</v>
+        <v>4370</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="n">
-        <v>47.53</v>
+        <v>52.24</v>
       </c>
       <c r="G17" t="n">
-        <v>13.92</v>
+        <v>15.3</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.92</v>
+        <v>0.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1260</v>
+        <v>1385</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>8125</v>
+        <v>8200</v>
       </c>
       <c r="F18" t="n">
-        <v>70.3</v>
+        <v>71.62</v>
       </c>
       <c r="G18" t="n">
-        <v>24.1</v>
+        <v>24.56</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>0.92</v>
       </c>
       <c r="M18" t="n">
-        <v>7975</v>
+        <v>8125</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="F19" t="n">
-        <v>66.67</v>
+        <v>69.72</v>
       </c>
       <c r="G19" t="n">
-        <v>12.22</v>
+        <v>12.78</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.59</v>
+        <v>-0.71</v>
       </c>
       <c r="M19" t="n">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>73.5</v>
+        <v>72.2</v>
       </c>
       <c r="F20" t="n">
-        <v>51.88</v>
+        <v>53.26</v>
       </c>
       <c r="G20" t="n">
-        <v>6.16</v>
+        <v>6.32</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.65</v>
+        <v>-1.77</v>
       </c>
       <c r="M20" t="n">
-        <v>71.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6500</v>
+        <v>6610</v>
       </c>
       <c r="F21" t="n">
-        <v>136.37</v>
+        <v>133.2</v>
       </c>
       <c r="G21" t="n">
-        <v>36.91</v>
+        <v>36.06</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.33</v>
+        <v>1.69</v>
       </c>
       <c r="M21" t="n">
-        <v>6655</v>
+        <v>6500</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2125</v>
+        <v>2155</v>
       </c>
       <c r="F22" t="n">
-        <v>63.54</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>30.78</v>
+        <v>32.46</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.46</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>2015</v>
+        <v>2125</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>1355</v>
+        <v>1335</v>
       </c>
       <c r="F23" t="n">
-        <v>89.23</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>19.75</v>
+        <v>21.67</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>9.720000000000001</v>
+        <v>-1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>1235</v>
+        <v>1355</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>33.75</v>
+        <v>34.35</v>
       </c>
       <c r="F24" t="n">
-        <v>118.15</v>
+        <v>125</v>
       </c>
       <c r="G24" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.8</v>
+        <v>1.78</v>
       </c>
       <c r="M24" t="n">
-        <v>31.9</v>
+        <v>33.75</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>1665</v>
+        <v>1830</v>
       </c>
       <c r="F25" t="n">
-        <v>199.08</v>
+        <v>218.79</v>
       </c>
       <c r="G25" t="n">
-        <v>33.06</v>
+        <v>36.34</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="M25" t="n">
-        <v>1515</v>
+        <v>1665</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2481,13 +2481,13 @@
         <v>68</v>
       </c>
       <c r="E26" t="n">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="F26" t="n">
-        <v>58.77</v>
+        <v>60.91</v>
       </c>
       <c r="G26" t="n">
-        <v>7.92</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.63</v>
+        <v>-1.07</v>
       </c>
       <c r="M26" t="n">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>66</v>
       </c>
       <c r="E27" t="n">
-        <v>1180</v>
+        <v>1150</v>
       </c>
       <c r="F27" t="n">
-        <v>73.67</v>
+        <v>73.98</v>
       </c>
       <c r="G27" t="n">
-        <v>12.68</v>
+        <v>12.74</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.43</v>
+        <v>-2.54</v>
       </c>
       <c r="M27" t="n">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2641,13 +2641,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>379</v>
+        <v>407.5</v>
       </c>
       <c r="F28" t="n">
-        <v>64.56</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>12.3</v>
+        <v>13.06</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>6.16</v>
+        <v>7.52</v>
       </c>
       <c r="M28" t="n">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>2710</v>
+        <v>2760</v>
       </c>
       <c r="F29" t="n">
-        <v>77.59</v>
+        <v>79.5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.84</v>
+        <v>9.06</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>2645</v>
+        <v>2710</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>458.5</v>
+        <v>474</v>
       </c>
       <c r="F30" t="n">
-        <v>127.23</v>
+        <v>136.46</v>
       </c>
       <c r="G30" t="n">
-        <v>11.94</v>
+        <v>12.81</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7.25</v>
+        <v>3.38</v>
       </c>
       <c r="M30" t="n">
-        <v>427.5</v>
+        <v>458.5</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2882,13 +2882,13 @@
         <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>253</v>
+        <v>258.5</v>
       </c>
       <c r="F31" t="n">
-        <v>36.14</v>
+        <v>37.32</v>
       </c>
       <c r="G31" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.27</v>
+        <v>2.17</v>
       </c>
       <c r="M31" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
@@ -2959,13 +2959,13 @@
         <v>62</v>
       </c>
       <c r="E32" t="n">
-        <v>445.5</v>
+        <v>426</v>
       </c>
       <c r="F32" t="n">
-        <v>36.26</v>
+        <v>39.88</v>
       </c>
       <c r="G32" t="n">
-        <v>6.51</v>
+        <v>7.16</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10</v>
+        <v>-4.38</v>
       </c>
       <c r="M32" t="n">
-        <v>405</v>
+        <v>445.5</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3038,13 +3038,13 @@
         <v>61</v>
       </c>
       <c r="E33" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F33" t="n">
-        <v>43.99</v>
+        <v>46.24</v>
       </c>
       <c r="G33" t="n">
-        <v>9.92</v>
+        <v>10.43</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.11</v>
+        <v>0.67</v>
       </c>
       <c r="M33" t="n">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
@@ -3115,13 +3115,13 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="F34" t="n">
-        <v>52.76</v>
+        <v>55.35</v>
       </c>
       <c r="G34" t="n">
-        <v>8.26</v>
+        <v>8.66</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.93</v>
+        <v>-1</v>
       </c>
       <c r="M34" t="n">
-        <v>670</v>
+        <v>703</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         <v>56</v>
       </c>
       <c r="E35" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F35" t="n">
-        <v>46.14</v>
+        <v>50.74</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>9.970000000000001</v>
+        <v>-5.85</v>
       </c>
       <c r="M35" t="n">
-        <v>155.5</v>
+        <v>171</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>3850</v>
+        <v>3875</v>
       </c>
       <c r="F36" t="n">
-        <v>58.49</v>
+        <v>61.35</v>
       </c>
       <c r="G36" t="n">
-        <v>15.01</v>
+        <v>15.75</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.9</v>
+        <v>0.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3670</v>
+        <v>3850</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         <v>1880</v>
       </c>
       <c r="F37" t="n">
-        <v>67.66</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>15.91</v>
+        <v>16.3</v>
       </c>
       <c r="H37" t="n">
         <v>59.1</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1835</v>
+        <v>1880</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3435,13 +3435,13 @@
         <v>92</v>
       </c>
       <c r="E38" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="F38" t="n">
-        <v>20.13</v>
+        <v>20.06</v>
       </c>
       <c r="G38" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="H38" t="n">
         <v>19</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.32</v>
+        <v>0.63</v>
       </c>
       <c r="M38" t="n">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
@@ -3518,13 +3518,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>3500</v>
+        <v>3710</v>
       </c>
       <c r="F39" t="n">
-        <v>97.37</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>24.38</v>
+        <v>24.24</v>
       </c>
       <c r="H39" t="n">
         <v>70.2</v>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.57</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>3520</v>
+        <v>3500</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3597,13 +3597,13 @@
         <v>90</v>
       </c>
       <c r="E40" t="n">
-        <v>5125</v>
+        <v>5095</v>
       </c>
       <c r="F40" t="n">
-        <v>104.77</v>
+        <v>111.17</v>
       </c>
       <c r="G40" t="n">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
       <c r="H40" t="n">
         <v>75.3</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.11</v>
+        <v>-0.59</v>
       </c>
       <c r="M40" t="n">
-        <v>4830</v>
+        <v>5125</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         <v>705</v>
       </c>
       <c r="F41" t="n">
-        <v>47.56</v>
+        <v>48.45</v>
       </c>
       <c r="G41" t="n">
-        <v>26.53</v>
+        <v>27.03</v>
       </c>
       <c r="H41" t="n">
         <v>47.5</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3759,13 +3759,13 @@
         <v>80</v>
       </c>
       <c r="E42" t="n">
-        <v>99.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="F42" t="n">
-        <v>11.71</v>
+        <v>11.72</v>
       </c>
       <c r="G42" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H42" t="n">
         <v>11</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="M42" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         <v>78</v>
       </c>
       <c r="E43" t="n">
-        <v>187.5</v>
+        <v>187</v>
       </c>
       <c r="F43" t="n">
-        <v>14.58</v>
+        <v>14.82</v>
       </c>
       <c r="G43" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="H43" t="n">
         <v>13.4</v>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.63</v>
+        <v>-0.27</v>
       </c>
       <c r="M43" t="n">
-        <v>184.5</v>
+        <v>187.5</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3921,13 +3921,13 @@
         <v>70</v>
       </c>
       <c r="E44" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>15.86</v>
       </c>
       <c r="G44" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="H44" t="n">
         <v>16</v>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M44" t="n">
-        <v>108.5</v>
+        <v>107.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -4000,13 +4000,13 @@
         <v>69</v>
       </c>
       <c r="E45" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F45" t="n">
-        <v>16.09</v>
+        <v>16.03</v>
       </c>
       <c r="G45" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="H45" t="n">
         <v>21.4</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.38</v>
+        <v>0.57</v>
       </c>
       <c r="M45" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4086,10 +4086,10 @@
         <v>211.5</v>
       </c>
       <c r="F46" t="n">
-        <v>30.92</v>
+        <v>31.52</v>
       </c>
       <c r="G46" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="H46" t="n">
         <v>30.9</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>207.5</v>
+        <v>211.5</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4166,13 +4166,13 @@
         <v>64</v>
       </c>
       <c r="E47" t="n">
-        <v>3590</v>
+        <v>3510</v>
       </c>
       <c r="F47" t="n">
-        <v>51.15</v>
+        <v>52.62</v>
       </c>
       <c r="G47" t="n">
-        <v>6.59</v>
+        <v>6.78</v>
       </c>
       <c r="H47" t="n">
         <v>51.7</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.87</v>
+        <v>-2.23</v>
       </c>
       <c r="M47" t="n">
-        <v>3490</v>
+        <v>3590</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4249,13 +4249,13 @@
         <v>79</v>
       </c>
       <c r="E48" t="n">
-        <v>282.5</v>
+        <v>276</v>
       </c>
       <c r="F48" t="n">
-        <v>31.56</v>
+        <v>32.66</v>
       </c>
       <c r="G48" t="n">
-        <v>4.68</v>
+        <v>4.84</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.48</v>
+        <v>-2.3</v>
       </c>
       <c r="M48" t="n">
-        <v>273</v>
+        <v>282.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4326,13 +4326,13 @@
         <v>78</v>
       </c>
       <c r="E49" t="n">
-        <v>121</v>
+        <v>120.5</v>
       </c>
       <c r="F49" t="n">
-        <v>26.77</v>
+        <v>27.69</v>
       </c>
       <c r="G49" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.42</v>
+        <v>-0.41</v>
       </c>
       <c r="M49" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>77</v>
       </c>
       <c r="E50" t="n">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="F50" t="n">
-        <v>32.99</v>
+        <v>32.89</v>
       </c>
       <c r="G50" t="n">
         <v>1.78</v>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.31</v>
+        <v>-1.25</v>
       </c>
       <c r="M50" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4484,13 +4484,13 @@
         <v>76</v>
       </c>
       <c r="E51" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F51" t="n">
-        <v>25.59</v>
+        <v>25.76</v>
       </c>
       <c r="G51" t="n">
-        <v>6.23</v>
+        <v>6.27</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.66</v>
+        <v>3.04</v>
       </c>
       <c r="M51" t="n">
-        <v>228.5</v>
+        <v>230</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4561,13 +4561,13 @@
         <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F52" t="n">
-        <v>27.11</v>
+        <v>26.75</v>
       </c>
       <c r="G52" t="n">
-        <v>8.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.33</v>
+        <v>0.27</v>
       </c>
       <c r="M52" t="n">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4642,13 +4642,13 @@
         <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F53" t="n">
-        <v>26.85</v>
+        <v>27.53</v>
       </c>
       <c r="G53" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.51</v>
+        <v>0.41</v>
       </c>
       <c r="M53" t="n">
-        <v>119.5</v>
+        <v>122.5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4723,13 +4723,13 @@
         <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>4000</v>
+        <v>4140</v>
       </c>
       <c r="F54" t="n">
-        <v>24.87</v>
+        <v>24.97</v>
       </c>
       <c r="G54" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.38</v>
+        <v>3.5</v>
       </c>
       <c r="M54" t="n">
-        <v>3985</v>
+        <v>4000</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4804,13 +4804,13 @@
         <v>97</v>
       </c>
       <c r="E55" t="n">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F55" t="n">
-        <v>34.39</v>
+        <v>34.9</v>
       </c>
       <c r="G55" t="n">
-        <v>6.81</v>
+        <v>6.91</v>
       </c>
       <c r="H55" t="n">
         <v>29.3</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.48</v>
+        <v>-0.91</v>
       </c>
       <c r="M55" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4883,13 +4883,13 @@
         <v>91</v>
       </c>
       <c r="E56" t="n">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="F56" t="n">
-        <v>50.85</v>
+        <v>52</v>
       </c>
       <c r="G56" t="n">
-        <v>7.89</v>
+        <v>8.07</v>
       </c>
       <c r="H56" t="n">
         <v>46.1</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.27</v>
+        <v>-1.04</v>
       </c>
       <c r="M56" t="n">
-        <v>750</v>
+        <v>767</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4962,13 +4962,13 @@
         <v>79</v>
       </c>
       <c r="E57" t="n">
-        <v>64.7</v>
+        <v>64.3</v>
       </c>
       <c r="F57" t="n">
-        <v>15.98</v>
+        <v>15.86</v>
       </c>
       <c r="G57" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="H57" t="n">
         <v>17.3</v>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-0.77</v>
+        <v>-0.62</v>
       </c>
       <c r="M57" t="n">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         <v>77</v>
       </c>
       <c r="E58" t="n">
-        <v>165.5</v>
+        <v>165</v>
       </c>
       <c r="F58" t="n">
-        <v>15.54</v>
+        <v>15.58</v>
       </c>
       <c r="G58" t="n">
         <v>1.69</v>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="M58" t="n">
-        <v>165</v>
+        <v>165.5</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         <v>96</v>
       </c>
       <c r="E59" t="n">
-        <v>354.5</v>
+        <v>349</v>
       </c>
       <c r="F59" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
       <c r="G59" t="n">
         <v>5.67</v>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.14</v>
+        <v>-1.55</v>
       </c>
       <c r="M59" t="n">
-        <v>354</v>
+        <v>354.5</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>94</v>
       </c>
       <c r="E60" t="n">
-        <v>162.5</v>
+        <v>160</v>
       </c>
       <c r="F60" t="n">
         <v>19.74</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="M60" t="n">
         <v>162.5</v>
@@ -5274,13 +5274,13 @@
         <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>20.05</v>
+        <v>19.8</v>
       </c>
       <c r="F61" t="n">
-        <v>16.42</v>
+        <v>16.3</v>
       </c>
       <c r="G61" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-0.74</v>
+        <v>-1.25</v>
       </c>
       <c r="M61" t="n">
-        <v>20.2</v>
+        <v>20.05</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>90.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>18.28</v>
+        <v>18.62</v>
       </c>
       <c r="G62" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.91</v>
+        <v>-1.21</v>
       </c>
       <c r="M62" t="n">
-        <v>89</v>
+        <v>90.7</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
         <v>75</v>
       </c>
       <c r="E63" t="n">
-        <v>44.05</v>
+        <v>43.7</v>
       </c>
       <c r="F63" t="n">
-        <v>14.1</v>
+        <v>14.16</v>
       </c>
       <c r="G63" t="n">
         <v>1.24</v>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.46</v>
+        <v>-0.79</v>
       </c>
       <c r="M63" t="n">
-        <v>43.85</v>
+        <v>44.05</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>201.5</v>
+        <v>202</v>
       </c>
       <c r="F64" t="n">
-        <v>17.53</v>
+        <v>18.3</v>
       </c>
       <c r="G64" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.4</v>
+        <v>0.25</v>
       </c>
       <c r="M64" t="n">
-        <v>193</v>
+        <v>201.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="F65" t="n">
         <v>17.79</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="M65" t="n">
         <v>718</v>
@@ -5675,13 +5675,13 @@
         <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>49.3</v>
+        <v>49.05</v>
       </c>
       <c r="F66" t="n">
-        <v>18.1</v>
+        <v>18.75</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.57</v>
+        <v>-0.51</v>
       </c>
       <c r="M66" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>97</v>
       </c>
       <c r="E67" t="n">
-        <v>146.5</v>
+        <v>145.5</v>
       </c>
       <c r="F67" t="n">
-        <v>15.78</v>
+        <v>15.89</v>
       </c>
       <c r="G67" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
       <c r="H67" t="n">
         <v>14.7</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="M67" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="F68" t="n">
-        <v>23.21</v>
+        <v>23.97</v>
       </c>
       <c r="G68" t="n">
-        <v>5.51</v>
+        <v>5.69</v>
       </c>
       <c r="H68" t="n">
         <v>17.9</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.29</v>
+        <v>-1.06</v>
       </c>
       <c r="M68" t="n">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5914,13 +5914,13 @@
         <v>91</v>
       </c>
       <c r="E69" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>17.96</v>
+        <v>17.39</v>
       </c>
       <c r="G69" t="n">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-3.2</v>
+        <v>-0.83</v>
       </c>
       <c r="M69" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         <v>90</v>
       </c>
       <c r="E70" t="n">
-        <v>315</v>
+        <v>315.5</v>
       </c>
       <c r="F70" t="n">
-        <v>30</v>
+        <v>30.73</v>
       </c>
       <c r="G70" t="n">
-        <v>8.220000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="H70" t="n">
         <v>27.5</v>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.44</v>
+        <v>0.16</v>
       </c>
       <c r="M70" t="n">
-        <v>307.5</v>
+        <v>315</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6072,13 +6072,13 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>91.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>19.12</v>
+        <v>19.26</v>
       </c>
       <c r="G71" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H71" t="n">
         <v>16.7</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.77</v>
+        <v>-4.14</v>
       </c>
       <c r="M71" t="n">
-        <v>91</v>
+        <v>91.7</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F72" t="n">
-        <v>19.65</v>
+        <v>19.1</v>
       </c>
       <c r="G72" t="n">
-        <v>5.36</v>
+        <v>5.21</v>
       </c>
       <c r="H72" t="n">
         <v>16.4</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-2.78</v>
+        <v>2.14</v>
       </c>
       <c r="M72" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6234,13 +6234,13 @@
         <v>77</v>
       </c>
       <c r="E73" t="n">
-        <v>251.5</v>
+        <v>257.5</v>
       </c>
       <c r="F73" t="n">
-        <v>17.47</v>
+        <v>17.86</v>
       </c>
       <c r="G73" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H73" t="n">
         <v>15.3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="M73" t="n">
-        <v>246</v>
+        <v>251.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -6313,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="E74" t="n">
-        <v>1170</v>
+        <v>1190</v>
       </c>
       <c r="F74" t="n">
-        <v>62.86</v>
+        <v>61.29</v>
       </c>
       <c r="G74" t="n">
-        <v>32.72</v>
+        <v>31.91</v>
       </c>
       <c r="H74" t="n">
         <v>38.8</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-2.5</v>
+        <v>1.71</v>
       </c>
       <c r="M74" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6394,13 +6394,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="n">
-        <v>61.7</v>
+        <v>63</v>
       </c>
       <c r="F75" t="n">
-        <v>22.85</v>
+        <v>23.46</v>
       </c>
       <c r="G75" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="H75" t="n">
         <v>21.3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.66</v>
+        <v>2.11</v>
       </c>
       <c r="M75" t="n">
-        <v>60.1</v>
+        <v>61.7</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
@@ -6477,13 +6477,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2265</v>
+        <v>2440</v>
       </c>
       <c r="F76" t="n">
-        <v>38.12</v>
+        <v>37.22</v>
       </c>
       <c r="G76" t="n">
-        <v>20.16</v>
+        <v>19.69</v>
       </c>
       <c r="H76" t="n">
         <v>24.6</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-2.37</v>
+        <v>7.73</v>
       </c>
       <c r="M76" t="n">
-        <v>2320</v>
+        <v>2265</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6556,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="F77" t="n">
-        <v>22.62</v>
+        <v>23.42</v>
       </c>
       <c r="G77" t="n">
-        <v>8.77</v>
+        <v>9.08</v>
       </c>
       <c r="H77" t="n">
         <v>14.2</v>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="M77" t="n">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         <v>100</v>
       </c>
       <c r="E78" t="n">
-        <v>2400</v>
+        <v>2405</v>
       </c>
       <c r="F78" t="n">
-        <v>32.4</v>
+        <v>32.27</v>
       </c>
       <c r="G78" t="n">
-        <v>10.61</v>
+        <v>10.56</v>
       </c>
       <c r="H78" t="n">
         <v>23.6</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.41</v>
+        <v>0.21</v>
       </c>
       <c r="M78" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         <v>104</v>
       </c>
       <c r="F79" t="n">
-        <v>15.74</v>
+        <v>15.29</v>
       </c>
       <c r="G79" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="H79" t="n">
         <v>12.4</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6793,13 +6793,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F80" t="n">
-        <v>14.82</v>
+        <v>15.02</v>
       </c>
       <c r="G80" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H80" t="n">
         <v>12.3</v>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.37</v>
+        <v>-0.9</v>
       </c>
       <c r="M80" t="n">
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6872,7 +6872,7 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>28.1</v>
+        <v>27.95</v>
       </c>
       <c r="F81" t="n">
         <v>5.63</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="M81" t="n">
         <v>28.1</v>
@@ -6951,13 +6951,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>109</v>
+        <v>109.5</v>
       </c>
       <c r="F82" t="n">
-        <v>11.91</v>
+        <v>11.75</v>
       </c>
       <c r="G82" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="H82" t="n">
         <v>10.7</v>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1.36</v>
+        <v>0.46</v>
       </c>
       <c r="M82" t="n">
-        <v>110.5</v>
+        <v>109</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
         <v>94</v>
       </c>
       <c r="E83" t="n">
-        <v>176.5</v>
+        <v>176</v>
       </c>
       <c r="F83" t="n">
-        <v>13.29</v>
+        <v>13.1</v>
       </c>
       <c r="G83" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="H83" t="n">
         <v>11.4</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.4</v>
+        <v>-0.28</v>
       </c>
       <c r="M83" t="n">
-        <v>179</v>
+        <v>176.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7109,13 +7109,13 @@
         <v>92</v>
       </c>
       <c r="E84" t="n">
-        <v>42.1</v>
+        <v>40.85</v>
       </c>
       <c r="F84" t="n">
-        <v>8.029999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G84" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H84" t="n">
         <v>7.6</v>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.47</v>
+        <v>-2.97</v>
       </c>
       <c r="M84" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7188,13 +7188,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="F85" t="n">
-        <v>34.54</v>
+        <v>34.09</v>
       </c>
       <c r="G85" t="n">
-        <v>11.57</v>
+        <v>11.42</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-1.29</v>
+        <v>2.61</v>
       </c>
       <c r="M85" t="n">
-        <v>1165</v>
+        <v>1150</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7267,13 +7267,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>417.5</v>
+        <v>406</v>
       </c>
       <c r="F86" t="n">
-        <v>19.66</v>
+        <v>20.29</v>
       </c>
       <c r="G86" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="H86" t="n">
         <v>21.2</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.21</v>
+        <v>-2.75</v>
       </c>
       <c r="M86" t="n">
-        <v>404.5</v>
+        <v>417.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7346,13 +7346,13 @@
         <v>90</v>
       </c>
       <c r="E87" t="n">
-        <v>132</v>
+        <v>133.5</v>
       </c>
       <c r="F87" t="n">
-        <v>15.69</v>
+        <v>16.12</v>
       </c>
       <c r="G87" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="H87" t="n">
         <v>14.1</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.72</v>
+        <v>1.14</v>
       </c>
       <c r="M87" t="n">
-        <v>128.5</v>
+        <v>132</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7425,13 +7425,13 @@
         <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>39.1</v>
+        <v>38.5</v>
       </c>
       <c r="F88" t="n">
-        <v>8.380000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="G88" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="H88" t="n">
         <v>6.2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.49</v>
+        <v>-1.53</v>
       </c>
       <c r="M88" t="n">
-        <v>38.15</v>
+        <v>39.1</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -7504,13 +7504,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>2285</v>
+        <v>2325</v>
       </c>
       <c r="F89" t="n">
-        <v>41.98</v>
+        <v>43.21</v>
       </c>
       <c r="G89" t="n">
-        <v>19</v>
+        <v>19.55</v>
       </c>
       <c r="H89" t="n">
         <v>30.7</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.93</v>
+        <v>1.75</v>
       </c>
       <c r="M89" t="n">
-        <v>2220</v>
+        <v>2285</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7587,13 +7587,13 @@
         <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="F90" t="n">
-        <v>26.72</v>
+        <v>26.2</v>
       </c>
       <c r="G90" t="n">
-        <v>6.42</v>
+        <v>6.3</v>
       </c>
       <c r="H90" t="n">
         <v>21.8</v>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-1.94</v>
+        <v>1.65</v>
       </c>
       <c r="M90" t="n">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7670,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="E91" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="F91" t="n">
-        <v>10.61</v>
+        <v>10.59</v>
       </c>
       <c r="G91" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="H91" t="n">
         <v>8.6</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-0.23</v>
+        <v>0.23</v>
       </c>
       <c r="M91" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7753,13 +7753,13 @@
         <v>78</v>
       </c>
       <c r="E92" t="n">
-        <v>72.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>7.81</v>
+        <v>7.86</v>
       </c>
       <c r="G92" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H92" t="n">
         <v>6.8</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="M92" t="n">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7836,13 +7836,13 @@
         <v>77</v>
       </c>
       <c r="E93" t="n">
-        <v>58.3</v>
+        <v>56.1</v>
       </c>
       <c r="F93" t="n">
-        <v>10.78</v>
+        <v>10.84</v>
       </c>
       <c r="G93" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H93" t="n">
         <v>10.4</v>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.52</v>
+        <v>-3.77</v>
       </c>
       <c r="M93" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7919,13 +7919,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F94" t="n">
-        <v>16.29</v>
+        <v>16.54</v>
       </c>
       <c r="G94" t="n">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="H94" t="n">
         <v>13.2</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="M94" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8002,13 +8002,13 @@
         <v>65</v>
       </c>
       <c r="E95" t="n">
-        <v>5500</v>
+        <v>5470</v>
       </c>
       <c r="F95" t="n">
-        <v>16.76</v>
+        <v>18.44</v>
       </c>
       <c r="G95" t="n">
-        <v>6.63</v>
+        <v>7.29</v>
       </c>
       <c r="H95" t="n">
         <v>9.6</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>10</v>
+        <v>-0.55</v>
       </c>
       <c r="M95" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8085,13 +8085,13 @@
         <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>164</v>
+        <v>173.5</v>
       </c>
       <c r="F96" t="n">
-        <v>14.99</v>
+        <v>16.45</v>
       </c>
       <c r="G96" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>9.699999999999999</v>
+        <v>5.79</v>
       </c>
       <c r="M96" t="n">
-        <v>149.5</v>
+        <v>164</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8168,13 +8168,13 @@
         <v>60</v>
       </c>
       <c r="E97" t="n">
-        <v>1415</v>
+        <v>1405</v>
       </c>
       <c r="F97" t="n">
-        <v>17.3</v>
+        <v>17.36</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="H97" t="n">
         <v>11.9</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="M97" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="E98" t="n">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>5.96</v>
+        <v>6.15</v>
       </c>
       <c r="G98" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.21</v>
+        <v>0.27</v>
       </c>
       <c r="M98" t="n">
-        <v>71.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>379.5</v>
+        <v>378.5</v>
       </c>
       <c r="F99" t="n">
-        <v>7.36</v>
+        <v>7.58</v>
       </c>
       <c r="G99" t="n">
-        <v>4.24</v>
+        <v>4.37</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.99</v>
+        <v>-0.26</v>
       </c>
       <c r="M99" t="n">
-        <v>368.5</v>
+        <v>379.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>77</v>
       </c>
       <c r="E100" t="n">
-        <v>23.8</v>
+        <v>23.65</v>
       </c>
       <c r="F100" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="G100" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.85</v>
+        <v>-0.63</v>
       </c>
       <c r="M100" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>196.5</v>
+        <v>210</v>
       </c>
       <c r="F101" t="n">
-        <v>9.33</v>
+        <v>9.58</v>
       </c>
       <c r="G101" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.61</v>
+        <v>6.87</v>
       </c>
       <c r="M101" t="n">
-        <v>191.5</v>
+        <v>196.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2265</v>
+        <v>2440</v>
       </c>
       <c r="F2" t="n">
-        <v>38.12</v>
+        <v>37.22</v>
       </c>
       <c r="G2" t="n">
-        <v>20.16</v>
+        <v>19.69</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.37</v>
+        <v>7.73</v>
       </c>
       <c r="M2" t="n">
-        <v>2320</v>
+        <v>2265</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="F3" t="n">
-        <v>22.62</v>
+        <v>23.42</v>
       </c>
       <c r="G3" t="n">
-        <v>8.77</v>
+        <v>9.08</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2400</v>
+        <v>2405</v>
       </c>
       <c r="F4" t="n">
-        <v>32.4</v>
+        <v>32.27</v>
       </c>
       <c r="G4" t="n">
-        <v>10.61</v>
+        <v>10.56</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.41</v>
+        <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8942,10 +8942,10 @@
         <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>15.74</v>
+        <v>15.29</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>14.82</v>
+        <v>15.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>-0.9</v>
       </c>
       <c r="M6" t="n">
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,7 +9097,7 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>28.1</v>
+        <v>27.95</v>
       </c>
       <c r="F7" t="n">
         <v>5.63</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="M7" t="n">
         <v>28.1</v>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>109.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.91</v>
+        <v>11.75</v>
       </c>
       <c r="G8" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.36</v>
+        <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>110.5</v>
+        <v>109</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>176.5</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>13.29</v>
+        <v>13.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.4</v>
+        <v>-0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>179</v>
+        <v>176.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.1</v>
+        <v>40.85</v>
       </c>
       <c r="F10" t="n">
-        <v>8.029999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.47</v>
+        <v>-2.97</v>
       </c>
       <c r="M10" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="F11" t="n">
-        <v>34.54</v>
+        <v>34.09</v>
       </c>
       <c r="G11" t="n">
-        <v>11.57</v>
+        <v>11.42</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.29</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1165</v>
+        <v>1150</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>417.5</v>
+        <v>406</v>
       </c>
       <c r="F12" t="n">
-        <v>19.66</v>
+        <v>20.29</v>
       </c>
       <c r="G12" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.21</v>
+        <v>-2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>404.5</v>
+        <v>417.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>133.5</v>
       </c>
       <c r="F13" t="n">
-        <v>15.69</v>
+        <v>16.12</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.72</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>128.5</v>
+        <v>132</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>39.1</v>
+        <v>38.5</v>
       </c>
       <c r="F14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="G14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>-1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>38.15</v>
+        <v>39.1</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2285</v>
+        <v>2325</v>
       </c>
       <c r="F15" t="n">
-        <v>41.98</v>
+        <v>43.21</v>
       </c>
       <c r="G15" t="n">
-        <v>19</v>
+        <v>19.55</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.93</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>2220</v>
+        <v>2285</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="F16" t="n">
-        <v>26.72</v>
+        <v>26.2</v>
       </c>
       <c r="G16" t="n">
-        <v>6.42</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.94</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="F17" t="n">
-        <v>10.61</v>
+        <v>10.59</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.23</v>
+        <v>0.23</v>
       </c>
       <c r="M17" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>72.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>7.81</v>
+        <v>7.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="M18" t="n">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>58.3</v>
+        <v>56.1</v>
       </c>
       <c r="F19" t="n">
-        <v>10.78</v>
+        <v>10.84</v>
       </c>
       <c r="G19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.52</v>
+        <v>-3.77</v>
       </c>
       <c r="M19" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F20" t="n">
-        <v>16.29</v>
+        <v>16.54</v>
       </c>
       <c r="G20" t="n">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>5500</v>
+        <v>5470</v>
       </c>
       <c r="F21" t="n">
-        <v>16.76</v>
+        <v>18.44</v>
       </c>
       <c r="G21" t="n">
-        <v>6.63</v>
+        <v>7.29</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>-0.55</v>
       </c>
       <c r="M21" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>164</v>
+        <v>173.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.99</v>
+        <v>16.45</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9.699999999999999</v>
+        <v>5.79</v>
       </c>
       <c r="M22" t="n">
-        <v>149.5</v>
+        <v>164</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1415</v>
+        <v>1405</v>
       </c>
       <c r="F23" t="n">
-        <v>17.3</v>
+        <v>17.36</v>
       </c>
       <c r="G23" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="M23" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>146.5</v>
+        <v>145.5</v>
       </c>
       <c r="F2" t="n">
-        <v>15.78</v>
+        <v>15.89</v>
       </c>
       <c r="G2" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="F3" t="n">
-        <v>23.21</v>
+        <v>23.97</v>
       </c>
       <c r="G3" t="n">
-        <v>5.51</v>
+        <v>5.69</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.29</v>
+        <v>-1.06</v>
       </c>
       <c r="M3" t="n">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
-        <v>17.96</v>
+        <v>17.39</v>
       </c>
       <c r="G4" t="n">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-3.2</v>
+        <v>-0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>315</v>
+        <v>315.5</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>30.73</v>
       </c>
       <c r="G5" t="n">
-        <v>8.220000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.44</v>
+        <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>307.5</v>
+        <v>315</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>91.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>19.12</v>
+        <v>19.26</v>
       </c>
       <c r="G6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.77</v>
+        <v>-4.14</v>
       </c>
       <c r="M6" t="n">
-        <v>91</v>
+        <v>91.7</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F7" t="n">
-        <v>19.65</v>
+        <v>19.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.36</v>
+        <v>5.21</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.78</v>
+        <v>2.14</v>
       </c>
       <c r="M7" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>251.5</v>
+        <v>257.5</v>
       </c>
       <c r="F8" t="n">
-        <v>17.47</v>
+        <v>17.86</v>
       </c>
       <c r="G8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="M8" t="n">
-        <v>246</v>
+        <v>251.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1170</v>
+        <v>1190</v>
       </c>
       <c r="F9" t="n">
-        <v>62.86</v>
+        <v>61.29</v>
       </c>
       <c r="G9" t="n">
-        <v>32.72</v>
+        <v>31.91</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-2.5</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.7</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>22.85</v>
+        <v>23.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.66</v>
+        <v>2.11</v>
       </c>
       <c r="M10" t="n">
-        <v>60.1</v>
+        <v>61.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="F2" t="n">
-        <v>70.11</v>
+        <v>77.03</v>
       </c>
       <c r="G2" t="n">
-        <v>19.68</v>
+        <v>21.63</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.869999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>983</v>
+        <v>1080</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,10 +11538,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.25</v>
+        <v>39.3</v>
       </c>
       <c r="F3" t="n">
-        <v>11.07</v>
+        <v>11.09</v>
       </c>
       <c r="G3" t="n">
         <v>1.83</v>
@@ -11564,7 +11564,7 @@
         <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>39.2</v>
+        <v>39.25</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>18.84</v>
+        <v>17.75</v>
       </c>
       <c r="G4" t="n">
-        <v>4.15</v>
+        <v>3.91</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-5.83</v>
+        <v>-0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>163</v>
+        <v>153.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6000</v>
+        <v>6250</v>
       </c>
       <c r="F5" t="n">
-        <v>156.42</v>
+        <v>159.74</v>
       </c>
       <c r="G5" t="n">
-        <v>36.54</v>
+        <v>37.31</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>4.17</v>
       </c>
       <c r="M5" t="n">
-        <v>5875</v>
+        <v>6000</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>112.5</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>22.72</v>
+        <v>22.82</v>
       </c>
       <c r="G6" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>108.5</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
-        <v>31.34</v>
+        <v>31.63</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.93</v>
+        <v>-0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F8" t="n">
-        <v>32.82</v>
+        <v>29.77</v>
       </c>
       <c r="G8" t="n">
-        <v>6.36</v>
+        <v>5.77</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-9.300000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.89</v>
+        <v>26.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.98</v>
+        <v>-0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>18.51</v>
+        <v>18.75</v>
       </c>
       <c r="G10" t="n">
-        <v>5.09</v>
+        <v>5.15</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>-1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1430</v>
+        <v>1405</v>
       </c>
       <c r="F11" t="n">
-        <v>29.77</v>
+        <v>31.3</v>
       </c>
       <c r="G11" t="n">
-        <v>5.35</v>
+        <v>5.62</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.15</v>
+        <v>-1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>169</v>
+        <v>167.5</v>
       </c>
       <c r="F12" t="n">
-        <v>21.13</v>
+        <v>21.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.29</v>
+        <v>-0.89</v>
       </c>
       <c r="M12" t="n">
-        <v>169.5</v>
+        <v>169</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12347,10 +12347,10 @@
         <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>30.44</v>
+        <v>32.06</v>
       </c>
       <c r="G13" t="n">
-        <v>5.33</v>
+        <v>5.61</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>138.5</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>27.63</v>
+        <v>27.53</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12453,7 +12453,7 @@
         <v>-0.36</v>
       </c>
       <c r="M14" t="n">
-        <v>139</v>
+        <v>138.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>239.5</v>
+        <v>237</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15</v>
+        <v>21.83</v>
       </c>
       <c r="G15" t="n">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.44</v>
+        <v>-1.04</v>
       </c>
       <c r="M15" t="n">
-        <v>243</v>
+        <v>239.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4370</v>
+        <v>4380</v>
       </c>
       <c r="F16" t="n">
-        <v>123.8</v>
+        <v>131.47</v>
       </c>
       <c r="G16" t="n">
-        <v>37.81</v>
+        <v>40.15</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.2</v>
+        <v>0.23</v>
       </c>
       <c r="M16" t="n">
-        <v>4115</v>
+        <v>4370</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12806,10 +12806,10 @@
         <v>1880</v>
       </c>
       <c r="F2" t="n">
-        <v>67.66</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>15.91</v>
+        <v>16.3</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1835</v>
+        <v>1880</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="F3" t="n">
-        <v>20.13</v>
+        <v>20.06</v>
       </c>
       <c r="G3" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.32</v>
+        <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3500</v>
+        <v>3710</v>
       </c>
       <c r="F4" t="n">
-        <v>97.37</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>24.38</v>
+        <v>24.24</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.57</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>3520</v>
+        <v>3500</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5125</v>
+        <v>5095</v>
       </c>
       <c r="F5" t="n">
-        <v>104.77</v>
+        <v>111.17</v>
       </c>
       <c r="G5" t="n">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.11</v>
+        <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>4830</v>
+        <v>5125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13126,10 +13126,10 @@
         <v>705</v>
       </c>
       <c r="F6" t="n">
-        <v>47.56</v>
+        <v>48.45</v>
       </c>
       <c r="G6" t="n">
-        <v>26.53</v>
+        <v>27.03</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>99.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.71</v>
+        <v>11.72</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>187.5</v>
+        <v>187</v>
       </c>
       <c r="F8" t="n">
-        <v>14.58</v>
+        <v>14.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>-0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>184.5</v>
+        <v>187.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>15.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M9" t="n">
-        <v>108.5</v>
+        <v>107.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F10" t="n">
-        <v>16.09</v>
+        <v>16.03</v>
       </c>
       <c r="G10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.38</v>
+        <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13533,10 +13533,10 @@
         <v>211.5</v>
       </c>
       <c r="F11" t="n">
-        <v>30.92</v>
+        <v>31.52</v>
       </c>
       <c r="G11" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>207.5</v>
+        <v>211.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3590</v>
+        <v>3510</v>
       </c>
       <c r="F12" t="n">
-        <v>51.15</v>
+        <v>52.62</v>
       </c>
       <c r="G12" t="n">
-        <v>6.59</v>
+        <v>6.78</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>-2.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3490</v>
+        <v>3590</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1075</v>
+        <v>1005</v>
       </c>
       <c r="F2" t="n">
-        <v>77.03</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>21.63</v>
+        <v>21.53</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.46</v>
+        <v>-6.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>39.3</v>
+        <v>39.15</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09</v>
+        <v>11.1</v>
       </c>
       <c r="G3" t="n">
         <v>1.83</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.13</v>
+        <v>-0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>39.25</v>
+        <v>39.3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.75</v>
+        <v>17.57</v>
       </c>
       <c r="G4" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.98</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>152</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6250</v>
+        <v>5705</v>
       </c>
       <c r="F5" t="n">
-        <v>159.74</v>
+        <v>166.4</v>
       </c>
       <c r="G5" t="n">
-        <v>37.31</v>
+        <v>38.87</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.17</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>6000</v>
+        <v>6250</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="F6" t="n">
-        <v>22.82</v>
+        <v>22.72</v>
       </c>
       <c r="G6" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.44</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>112.5</v>
+        <v>112</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>31.63</v>
+        <v>31.49</v>
       </c>
       <c r="G7" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.46</v>
+        <v>-2.78</v>
       </c>
       <c r="M7" t="n">
-        <v>108.5</v>
+        <v>108</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>198</v>
+        <v>196.5</v>
       </c>
       <c r="F8" t="n">
-        <v>29.77</v>
+        <v>30.23</v>
       </c>
       <c r="G8" t="n">
-        <v>5.77</v>
+        <v>5.86</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>-0.76</v>
       </c>
       <c r="M8" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>102.5</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>26.14</v>
+        <v>26.02</v>
       </c>
       <c r="G9" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.49</v>
+        <v>2.93</v>
       </c>
       <c r="M9" t="n">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>154</v>
+        <v>151.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.75</v>
+        <v>18.51</v>
       </c>
       <c r="G10" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.28</v>
+        <v>-1.62</v>
       </c>
       <c r="M10" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1405</v>
+        <v>1425</v>
       </c>
       <c r="F11" t="n">
-        <v>31.3</v>
+        <v>30.76</v>
       </c>
       <c r="G11" t="n">
-        <v>5.62</v>
+        <v>5.53</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.75</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1430</v>
+        <v>1405</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>167.5</v>
+        <v>163</v>
       </c>
       <c r="F12" t="n">
-        <v>21.07</v>
+        <v>20.89</v>
       </c>
       <c r="G12" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.89</v>
+        <v>-2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>169</v>
+        <v>167.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,7 +1442,7 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>214.5</v>
       </c>
       <c r="F13" t="n">
         <v>32.06</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="M13" t="n">
         <v>218</v>
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>27.53</v>
+        <v>27.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.36</v>
+        <v>0.72</v>
       </c>
       <c r="M14" t="n">
-        <v>138.5</v>
+        <v>138</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F15" t="n">
-        <v>21.83</v>
+        <v>21.6</v>
       </c>
       <c r="G15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.04</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
-        <v>239.5</v>
+        <v>237</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>4380</v>
+        <v>4070</v>
       </c>
       <c r="F16" t="n">
-        <v>131.47</v>
+        <v>131.77</v>
       </c>
       <c r="G16" t="n">
-        <v>40.15</v>
+        <v>40.25</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.23</v>
+        <v>-7.08</v>
       </c>
       <c r="M16" t="n">
-        <v>4370</v>
+        <v>4380</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1325</v>
       </c>
       <c r="F17" t="n">
-        <v>52.24</v>
+        <v>52.43</v>
       </c>
       <c r="G17" t="n">
-        <v>15.3</v>
+        <v>15.36</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.36</v>
+        <v>-4.68</v>
       </c>
       <c r="M17" t="n">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>8200</v>
+        <v>7735</v>
       </c>
       <c r="F18" t="n">
-        <v>71.62</v>
+        <v>72.28</v>
       </c>
       <c r="G18" t="n">
-        <v>24.56</v>
+        <v>24.78</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.92</v>
+        <v>-5.67</v>
       </c>
       <c r="M18" t="n">
-        <v>8125</v>
+        <v>8200</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="F19" t="n">
-        <v>69.72</v>
+        <v>69.23</v>
       </c>
       <c r="G19" t="n">
-        <v>12.78</v>
+        <v>12.69</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.71</v>
+        <v>-4.27</v>
       </c>
       <c r="M19" t="n">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>72.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>53.26</v>
+        <v>52.32</v>
       </c>
       <c r="G20" t="n">
-        <v>6.32</v>
+        <v>6.21</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1.77</v>
+        <v>-5.68</v>
       </c>
       <c r="M20" t="n">
-        <v>73.5</v>
+        <v>72.2</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6610</v>
+        <v>6295</v>
       </c>
       <c r="F21" t="n">
-        <v>133.2</v>
+        <v>135.45</v>
       </c>
       <c r="G21" t="n">
-        <v>36.06</v>
+        <v>36.67</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.69</v>
+        <v>-4.77</v>
       </c>
       <c r="M21" t="n">
-        <v>6500</v>
+        <v>6610</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2155</v>
+        <v>2080</v>
       </c>
       <c r="F22" t="n">
-        <v>67.01000000000001</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>32.46</v>
+        <v>32.92</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>-3.48</v>
       </c>
       <c r="M22" t="n">
-        <v>2125</v>
+        <v>2155</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>1335</v>
+        <v>1250</v>
       </c>
       <c r="F23" t="n">
-        <v>97.90000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>21.67</v>
+        <v>21.35</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.48</v>
+        <v>-6.37</v>
       </c>
       <c r="M23" t="n">
-        <v>1355</v>
+        <v>1335</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>34.35</v>
+        <v>32.3</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>127.22</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.78</v>
+        <v>-5.97</v>
       </c>
       <c r="M24" t="n">
-        <v>33.75</v>
+        <v>34.35</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>1830</v>
+        <v>1760</v>
       </c>
       <c r="F25" t="n">
-        <v>218.79</v>
+        <v>240.47</v>
       </c>
       <c r="G25" t="n">
-        <v>36.34</v>
+        <v>39.94</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.91</v>
+        <v>-3.83</v>
       </c>
       <c r="M25" t="n">
-        <v>1665</v>
+        <v>1830</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2481,13 +2481,13 @@
         <v>68</v>
       </c>
       <c r="E26" t="n">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="F26" t="n">
-        <v>60.91</v>
+        <v>60.26</v>
       </c>
       <c r="G26" t="n">
-        <v>8.210000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-1.07</v>
+        <v>-5.55</v>
       </c>
       <c r="M26" t="n">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>66</v>
       </c>
       <c r="E27" t="n">
-        <v>1150</v>
+        <v>1135</v>
       </c>
       <c r="F27" t="n">
-        <v>73.98</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>12.74</v>
+        <v>12.41</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-2.54</v>
+        <v>-1.3</v>
       </c>
       <c r="M27" t="n">
-        <v>1180</v>
+        <v>1150</v>
       </c>
       <c r="N27" t="inlineStr">
     